--- a/output/passport_filled.xlsx
+++ b/output/passport_filled.xlsx
@@ -124,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -170,6 +170,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1094,8 +1098,10 @@
     </row>
     <row r="7">
       <c r="A7" s="8" t="n"/>
-      <c r="B7" s="8" t="n">
-        <v>1</v>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C7" s="8" t="n"/>
       <c r="D7" s="8" t="n"/>
@@ -1104,46 +1110,64 @@
           <t>Earth work in excavation in foundation trenches or drains not exceeding 1.5 m in width or 10 Sq.m on plan including dressing of sides and ramming of bottoms, lift upto 1.5 m including getting out the excavated soil and disposal of surplus excavated soil as directed within a lead of 50 m in all types of soil except rocks.</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="8" t="n"/>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Soil</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Soil</t>
+        </is>
+      </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
           <t>Earthwork</t>
         </is>
       </c>
-      <c r="K7" s="8" t="n"/>
+      <c r="K7" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L7" s="8" t="n"/>
       <c r="M7" s="8" t="n"/>
-      <c r="N7" s="8" t="n"/>
+      <c r="N7" s="17" t="n">
+        <v>32</v>
+      </c>
       <c r="O7" s="8" t="inlineStr">
         <is>
-          <t>Cu.m</t>
-        </is>
-      </c>
-      <c r="P7" s="8" t="n"/>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P7" s="17" t="n">
+        <v>32</v>
+      </c>
       <c r="Q7" s="8" t="n"/>
       <c r="R7" s="8" t="n"/>
       <c r="S7" s="8" t="n"/>
       <c r="T7" s="8" t="n"/>
       <c r="U7" s="8" t="n"/>
       <c r="V7" s="8" t="n"/>
-      <c r="W7" s="8" t="n">
-        <v>32</v>
-      </c>
+      <c r="W7" s="8" t="n"/>
       <c r="X7" s="8" t="n"/>
       <c r="Y7" s="8" t="n"/>
       <c r="Z7" s="8" t="n"/>
       <c r="AA7" s="8" t="n"/>
-      <c r="AB7" s="8" t="n"/>
-      <c r="AC7" s="8" t="n">
-        <v>2.8</v>
-      </c>
+      <c r="AB7" s="8" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="AC7" s="8" t="n"/>
       <c r="AD7" s="8" t="n"/>
       <c r="AE7" s="8" t="n"/>
       <c r="AF7" s="8" t="n"/>
@@ -1168,8 +1192,10 @@
     </row>
     <row r="8">
       <c r="A8" s="8" t="n"/>
-      <c r="B8" s="8" t="n">
-        <v>2</v>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C8" s="8" t="n"/>
       <c r="D8" s="8" t="n"/>
@@ -1178,46 +1204,64 @@
           <t>Filling available excavated earth (excluding rock) in trenches, plinth, sides of foundations etc. in layers not exceeding 20 cm in depth consolidating each deposited layer by ramming &amp; watering, lead upto 50 m and lift upto 1.5 m.</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="8" t="n"/>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Earth</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Earth</t>
+        </is>
+      </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
           <t>Earthwork</t>
         </is>
       </c>
-      <c r="K8" s="8" t="n"/>
+      <c r="K8" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L8" s="8" t="n"/>
       <c r="M8" s="8" t="n"/>
-      <c r="N8" s="8" t="n"/>
+      <c r="N8" s="17" t="n">
+        <v>12</v>
+      </c>
       <c r="O8" s="8" t="inlineStr">
         <is>
-          <t>Cu.m</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="n"/>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P8" s="17" t="n">
+        <v>12</v>
+      </c>
       <c r="Q8" s="8" t="n"/>
       <c r="R8" s="8" t="n"/>
       <c r="S8" s="8" t="n"/>
       <c r="T8" s="8" t="n"/>
       <c r="U8" s="8" t="n"/>
       <c r="V8" s="8" t="n"/>
-      <c r="W8" s="8" t="n">
-        <v>12</v>
-      </c>
+      <c r="W8" s="8" t="n"/>
       <c r="X8" s="8" t="n"/>
       <c r="Y8" s="8" t="n"/>
       <c r="Z8" s="8" t="n"/>
       <c r="AA8" s="8" t="n"/>
-      <c r="AB8" s="8" t="n"/>
-      <c r="AC8" s="8" t="n">
-        <v>2.26</v>
-      </c>
+      <c r="AB8" s="8" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="AC8" s="8" t="n"/>
       <c r="AD8" s="8" t="n"/>
       <c r="AE8" s="8" t="n"/>
       <c r="AF8" s="8" t="n"/>
@@ -1242,8 +1286,10 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="n"/>
-      <c r="B9" s="8" t="n">
-        <v>3</v>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C9" s="8" t="n"/>
       <c r="D9" s="8" t="n"/>
@@ -1252,46 +1298,64 @@
           <t>Filling the plinth with fine sand under floors including watering, ramming consolidating and dressing complete.</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr"/>
-      <c r="I9" s="8" t="n"/>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Sand</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>Fine sand</t>
+        </is>
+      </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
           <t>Earthwork</t>
         </is>
       </c>
-      <c r="K9" s="8" t="n"/>
+      <c r="K9" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L9" s="8" t="n"/>
       <c r="M9" s="8" t="n"/>
-      <c r="N9" s="8" t="n"/>
+      <c r="N9" s="17" t="n">
+        <v>11</v>
+      </c>
       <c r="O9" s="8" t="inlineStr">
         <is>
-          <t>Cu.m</t>
-        </is>
-      </c>
-      <c r="P9" s="8" t="n"/>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P9" s="17" t="n">
+        <v>11</v>
+      </c>
       <c r="Q9" s="8" t="n"/>
       <c r="R9" s="8" t="n"/>
       <c r="S9" s="8" t="n"/>
       <c r="T9" s="8" t="n"/>
       <c r="U9" s="8" t="n"/>
       <c r="V9" s="8" t="n"/>
-      <c r="W9" s="8" t="n">
-        <v>11</v>
-      </c>
+      <c r="W9" s="8" t="n"/>
       <c r="X9" s="8" t="n"/>
       <c r="Y9" s="8" t="n"/>
       <c r="Z9" s="8" t="n"/>
       <c r="AA9" s="8" t="n"/>
-      <c r="AB9" s="8" t="n"/>
-      <c r="AC9" s="8" t="n">
-        <v>2.28</v>
-      </c>
+      <c r="AB9" s="8" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="AC9" s="8" t="n"/>
       <c r="AD9" s="8" t="n"/>
       <c r="AE9" s="8" t="n"/>
       <c r="AF9" s="8" t="n"/>
@@ -1316,8 +1380,10 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="n"/>
-      <c r="B10" s="8" t="n">
-        <v>4</v>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C10" s="8" t="n"/>
       <c r="D10" s="8" t="n"/>
@@ -1326,23 +1392,39 @@
           <t>Surface dressing of the ground including removing vegetation, and inequalities not exceeding 15 cm deep and disposal of rubbish, lead upto 50 m and lift upto 1.5 m in soft/loose soil.</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr"/>
-      <c r="I10" s="8" t="n"/>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Soil</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Soil</t>
+        </is>
+      </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
           <t>Earthwork</t>
         </is>
       </c>
-      <c r="K10" s="8" t="n"/>
+      <c r="K10" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L10" s="8" t="n"/>
       <c r="M10" s="8" t="n"/>
-      <c r="N10" s="8" t="n"/>
+      <c r="N10" s="17" t="n">
+        <v>1.4</v>
+      </c>
       <c r="O10" s="8" t="inlineStr">
         <is>
           <t>100 Sq.m</t>
@@ -1355,19 +1437,17 @@
       <c r="T10" s="8" t="n"/>
       <c r="U10" s="8" t="n"/>
       <c r="V10" s="8" t="n"/>
-      <c r="W10" s="8" t="n">
-        <v>1.4</v>
-      </c>
+      <c r="W10" s="8" t="n"/>
       <c r="X10" s="8" t="n"/>
       <c r="Y10" s="8" t="n"/>
       <c r="Z10" s="8" t="n"/>
       <c r="AA10" s="8" t="n"/>
-      <c r="AB10" s="8" t="n"/>
-      <c r="AC10" s="8" t="inlineStr">
+      <c r="AB10" s="8" t="inlineStr">
         <is>
           <t>2.29.1</t>
         </is>
       </c>
+      <c r="AC10" s="8" t="n"/>
       <c r="AD10" s="8" t="n"/>
       <c r="AE10" s="8" t="n"/>
       <c r="AF10" s="8" t="n"/>
@@ -1392,8 +1472,10 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="n"/>
-      <c r="B11" s="8" t="n">
-        <v>5</v>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="C11" s="8" t="n"/>
       <c r="D11" s="8" t="n"/>
@@ -1402,48 +1484,60 @@
           <t>Providing and injecting chemical emulsion for PRECONSTRUCTIONAL anti termite treatment and creating a chemical barrier under and alround the column pits, wall trenches, basement excavation, top surface of plinth filling junction of wall and floor, along the external perimetre of building, expansion joints, surroundings of pipes &amp; conduits etc. complete (plinth area of the building at ground floor only shall be measured) with Aldrin Emulsifiable Concentrate (0.5%)</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr"/>
+      <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr"/>
-      <c r="I11" s="8" t="n"/>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Aldrin Emulsifiable Concentrate</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Chemical emulsion, Aldrin</t>
+        </is>
+      </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K11" s="8" t="n"/>
+      <c r="K11" s="17" t="n">
+        <v>0.9</v>
+      </c>
       <c r="L11" s="8" t="n"/>
       <c r="M11" s="8" t="n"/>
-      <c r="N11" s="8" t="n"/>
+      <c r="N11" s="17" t="n">
+        <v>90.59999999999999</v>
+      </c>
       <c r="O11" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P11" s="8" t="n"/>
-      <c r="Q11" s="8" t="n"/>
+      <c r="Q11" s="17" t="n">
+        <v>90.59999999999999</v>
+      </c>
       <c r="R11" s="8" t="n"/>
       <c r="S11" s="8" t="n"/>
       <c r="T11" s="8" t="n"/>
       <c r="U11" s="8" t="n"/>
       <c r="V11" s="8" t="n"/>
-      <c r="W11" s="8" t="n">
-        <v>90.59999999999999</v>
-      </c>
+      <c r="W11" s="8" t="n"/>
       <c r="X11" s="8" t="n"/>
       <c r="Y11" s="8" t="n"/>
       <c r="Z11" s="8" t="n"/>
       <c r="AA11" s="8" t="n"/>
-      <c r="AB11" s="8" t="n"/>
-      <c r="AC11" s="8" t="inlineStr">
+      <c r="AB11" s="8" t="inlineStr">
         <is>
           <t>2.35.2</t>
         </is>
       </c>
+      <c r="AC11" s="8" t="n"/>
       <c r="AD11" s="8" t="n"/>
       <c r="AE11" s="8" t="n"/>
       <c r="AF11" s="8" t="n"/>
@@ -1468,8 +1562,10 @@
     </row>
     <row r="12">
       <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="n">
-        <v>6</v>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="8" t="n"/>
@@ -1478,48 +1574,64 @@
           <t>Providing and laying cement concrete in footings and bases for columns, excluding the cost of centring and shuttering with 1:5:10 (1 cement : 5 coarse sand : 10 graded stone aggregate 40 mm nominal size).</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr"/>
+      <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="8" t="n"/>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Cement concrete</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
+        </is>
+      </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K12" s="8" t="n"/>
+      <c r="K12" s="17" t="n">
+        <v>0.98</v>
+      </c>
       <c r="L12" s="8" t="n"/>
-      <c r="M12" s="8" t="n"/>
-      <c r="N12" s="8" t="n"/>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>1:5:10</t>
+        </is>
+      </c>
+      <c r="N12" s="17" t="n">
+        <v>8</v>
+      </c>
       <c r="O12" s="8" t="inlineStr">
         <is>
-          <t>Cu.m</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="n"/>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P12" s="17" t="n">
+        <v>8</v>
+      </c>
       <c r="Q12" s="8" t="n"/>
       <c r="R12" s="8" t="n"/>
       <c r="S12" s="8" t="n"/>
       <c r="T12" s="8" t="n"/>
       <c r="U12" s="8" t="n"/>
       <c r="V12" s="8" t="n"/>
-      <c r="W12" s="8" t="n">
-        <v>8</v>
-      </c>
+      <c r="W12" s="8" t="n"/>
       <c r="X12" s="8" t="n"/>
       <c r="Y12" s="8" t="n"/>
       <c r="Z12" s="8" t="n"/>
       <c r="AA12" s="8" t="n"/>
-      <c r="AB12" s="8" t="n"/>
-      <c r="AC12" s="8" t="inlineStr">
+      <c r="AB12" s="8" t="inlineStr">
         <is>
           <t>4.5.10</t>
         </is>
       </c>
+      <c r="AC12" s="8" t="n"/>
       <c r="AD12" s="8" t="n"/>
       <c r="AE12" s="8" t="n"/>
       <c r="AF12" s="8" t="n"/>
@@ -1544,8 +1656,10 @@
     </row>
     <row r="13">
       <c r="A13" s="8" t="n"/>
-      <c r="B13" s="8" t="n">
-        <v>7</v>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="C13" s="8" t="n"/>
       <c r="D13" s="8" t="n"/>
@@ -1554,48 +1668,64 @@
           <t>Providing and laying cement concrete in retaining walls, return walls, walls (any thickness) including attached pilasters, buttresses, plinth, string courses, fillets etc. upto floor two level, excluding the cost of centring and shuttering with 1:5:10 (1 cement : 5 fine sand : 10 graded stone aggregate 40 mm nominal size)</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr"/>
+      <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr"/>
-      <c r="I13" s="8" t="n"/>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Cement concrete</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>Cement, Fine sand, Graded stone aggregate</t>
+        </is>
+      </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K13" s="8" t="n"/>
+      <c r="K13" s="17" t="n">
+        <v>0.98</v>
+      </c>
       <c r="L13" s="8" t="n"/>
-      <c r="M13" s="8" t="n"/>
-      <c r="N13" s="8" t="n"/>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>1:5:10</t>
+        </is>
+      </c>
+      <c r="N13" s="17" t="n">
+        <v>7.3</v>
+      </c>
       <c r="O13" s="8" t="inlineStr">
         <is>
-          <t>Cu.m</t>
-        </is>
-      </c>
-      <c r="P13" s="8" t="n"/>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P13" s="17" t="n">
+        <v>7.3</v>
+      </c>
       <c r="Q13" s="8" t="n"/>
       <c r="R13" s="8" t="n"/>
       <c r="S13" s="8" t="n"/>
       <c r="T13" s="8" t="n"/>
       <c r="U13" s="8" t="n"/>
       <c r="V13" s="8" t="n"/>
-      <c r="W13" s="8" t="n">
-        <v>7.3</v>
-      </c>
+      <c r="W13" s="8" t="n"/>
       <c r="X13" s="8" t="n"/>
       <c r="Y13" s="8" t="n"/>
       <c r="Z13" s="8" t="n"/>
       <c r="AA13" s="8" t="n"/>
-      <c r="AB13" s="8" t="n"/>
-      <c r="AC13" s="8" t="inlineStr">
+      <c r="AB13" s="8" t="inlineStr">
         <is>
           <t>4.6.11</t>
         </is>
       </c>
+      <c r="AC13" s="8" t="n"/>
       <c r="AD13" s="8" t="n"/>
       <c r="AE13" s="8" t="n"/>
       <c r="AF13" s="8" t="n"/>
@@ -1620,8 +1750,10 @@
     </row>
     <row r="14">
       <c r="A14" s="8" t="n"/>
-      <c r="B14" s="8" t="n">
-        <v>8</v>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="C14" s="8" t="n"/>
       <c r="D14" s="8" t="n"/>
@@ -1630,48 +1762,64 @@
           <t>Providing and laying upto floor two level cement concrete in string or lacing courses, parapets, copings, bed blocks anchor blocks, plain window sills and the like excluding centring and shuttering, etc. with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr"/>
+      <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr"/>
-      <c r="I14" s="8" t="n"/>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Cement concrete</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
+        </is>
+      </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K14" s="8" t="n"/>
+      <c r="K14" s="17" t="n">
+        <v>0.98</v>
+      </c>
       <c r="L14" s="8" t="n"/>
-      <c r="M14" s="8" t="n"/>
-      <c r="N14" s="8" t="n"/>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>1:2:4</t>
+        </is>
+      </c>
+      <c r="N14" s="17" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O14" s="8" t="inlineStr">
         <is>
-          <t>Cu.m</t>
-        </is>
-      </c>
-      <c r="P14" s="8" t="n"/>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P14" s="17" t="n">
+        <v>0.1</v>
+      </c>
       <c r="Q14" s="8" t="n"/>
       <c r="R14" s="8" t="n"/>
       <c r="S14" s="8" t="n"/>
       <c r="T14" s="8" t="n"/>
       <c r="U14" s="8" t="n"/>
       <c r="V14" s="8" t="n"/>
-      <c r="W14" s="8" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="W14" s="8" t="n"/>
       <c r="X14" s="8" t="n"/>
       <c r="Y14" s="8" t="n"/>
       <c r="Z14" s="8" t="n"/>
       <c r="AA14" s="8" t="n"/>
-      <c r="AB14" s="8" t="n"/>
-      <c r="AC14" s="8" t="inlineStr">
+      <c r="AB14" s="8" t="inlineStr">
         <is>
           <t>4.11.1</t>
         </is>
       </c>
+      <c r="AC14" s="8" t="n"/>
       <c r="AD14" s="8" t="n"/>
       <c r="AE14" s="8" t="n"/>
       <c r="AF14" s="8" t="n"/>
@@ -1696,8 +1844,10 @@
     </row>
     <row r="15">
       <c r="A15" s="8" t="n"/>
-      <c r="B15" s="8" t="n">
-        <v>9</v>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="C15" s="8" t="n"/>
       <c r="D15" s="8" t="n"/>
@@ -1706,46 +1856,64 @@
           <t>Providing and laying damp-proof course 40 mm thick with cement concrete 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 12.5 mm nominal size)</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr"/>
+      <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr"/>
-      <c r="I15" s="8" t="n"/>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>Cement concrete</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
+        </is>
+      </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K15" s="8" t="n"/>
+      <c r="K15" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L15" s="8" t="n"/>
-      <c r="M15" s="8" t="n"/>
-      <c r="N15" s="8" t="n"/>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t>1:2:4</t>
+        </is>
+      </c>
+      <c r="N15" s="17" t="n">
+        <v>14.4</v>
+      </c>
       <c r="O15" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P15" s="8" t="n"/>
-      <c r="Q15" s="8" t="n"/>
+      <c r="Q15" s="17" t="n">
+        <v>14.4</v>
+      </c>
       <c r="R15" s="8" t="n"/>
       <c r="S15" s="8" t="n"/>
       <c r="T15" s="8" t="n"/>
       <c r="U15" s="8" t="n"/>
       <c r="V15" s="8" t="n"/>
-      <c r="W15" s="8" t="n">
-        <v>14.4</v>
-      </c>
+      <c r="W15" s="8" t="n"/>
       <c r="X15" s="8" t="n"/>
       <c r="Y15" s="8" t="n"/>
       <c r="Z15" s="8" t="n"/>
       <c r="AA15" s="8" t="n"/>
-      <c r="AB15" s="8" t="n"/>
-      <c r="AC15" s="8" t="n">
-        <v>4.24</v>
-      </c>
+      <c r="AB15" s="8" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="AC15" s="8" t="n"/>
       <c r="AD15" s="8" t="n"/>
       <c r="AE15" s="8" t="n"/>
       <c r="AF15" s="8" t="n"/>
@@ -1760,7 +1928,9 @@
       <c r="AO15" s="8" t="n"/>
       <c r="AP15" s="8" t="n"/>
       <c r="AQ15" s="8" t="n"/>
-      <c r="AR15" s="8" t="n"/>
+      <c r="AR15" s="17" t="n">
+        <v>40</v>
+      </c>
       <c r="AS15" s="8" t="n"/>
       <c r="AT15" s="8" t="n"/>
       <c r="AU15" s="8" t="n"/>
@@ -1770,8 +1940,10 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="n"/>
-      <c r="B16" s="8" t="n">
-        <v>10</v>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="C16" s="8" t="n"/>
       <c r="D16" s="8" t="n"/>
@@ -1780,46 +1952,60 @@
           <t>Applying a coat of residual petroleum bitumen of penetration 80/100 of approved quality using 1.7 Kg. per square metre on damp proof course after cleaning the surface with brushes and finally with a piece of cloth lightly soaked in kerosene oil.</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr"/>
+      <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr"/>
-      <c r="I16" s="8" t="n"/>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>Petroleum bitumen</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>Petroleum bitumen, Kerosene oil</t>
+        </is>
+      </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish</t>
-        </is>
-      </c>
-      <c r="K16" s="8" t="n"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="K16" s="17" t="n">
+        <v>0.9</v>
+      </c>
       <c r="L16" s="8" t="n"/>
       <c r="M16" s="8" t="n"/>
-      <c r="N16" s="8" t="n"/>
+      <c r="N16" s="17" t="n">
+        <v>14.4</v>
+      </c>
       <c r="O16" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P16" s="8" t="n"/>
-      <c r="Q16" s="8" t="n"/>
+      <c r="Q16" s="17" t="n">
+        <v>14.4</v>
+      </c>
       <c r="R16" s="8" t="n"/>
       <c r="S16" s="8" t="n"/>
       <c r="T16" s="8" t="n"/>
       <c r="U16" s="8" t="n"/>
       <c r="V16" s="8" t="n"/>
-      <c r="W16" s="8" t="n">
-        <v>14.4</v>
-      </c>
+      <c r="W16" s="8" t="n"/>
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="8" t="n"/>
       <c r="Z16" s="8" t="n"/>
       <c r="AA16" s="8" t="n"/>
-      <c r="AB16" s="8" t="n"/>
-      <c r="AC16" s="8" t="n">
-        <v>4.27</v>
-      </c>
+      <c r="AB16" s="8" t="inlineStr">
+        <is>
+          <t>4.27</t>
+        </is>
+      </c>
+      <c r="AC16" s="8" t="n"/>
       <c r="AD16" s="8" t="n"/>
       <c r="AE16" s="8" t="n"/>
       <c r="AF16" s="8" t="n"/>
@@ -1844,8 +2030,10 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="n"/>
-      <c r="B17" s="8" t="n">
-        <v>11</v>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="C17" s="8" t="n"/>
       <c r="D17" s="8" t="n"/>
@@ -1854,46 +2042,64 @@
           <t>Reinforced cement concrete work in suspended floors, roofs, landings and balconies upto floor two level excluding cost of centring, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size)</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr"/>
+      <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr"/>
-      <c r="I17" s="8" t="n"/>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>Reinforced cement concrete</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
+        </is>
+      </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K17" s="8" t="n"/>
+      <c r="K17" s="17" t="n">
+        <v>0.98</v>
+      </c>
       <c r="L17" s="8" t="n"/>
-      <c r="M17" s="8" t="n"/>
-      <c r="N17" s="8" t="n"/>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>1:2:4</t>
+        </is>
+      </c>
+      <c r="N17" s="17" t="n">
+        <v>11.3</v>
+      </c>
       <c r="O17" s="8" t="inlineStr">
         <is>
-          <t>Cu.m</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="n"/>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P17" s="17" t="n">
+        <v>11.3</v>
+      </c>
       <c r="Q17" s="8" t="n"/>
       <c r="R17" s="8" t="n"/>
       <c r="S17" s="8" t="n"/>
       <c r="T17" s="8" t="n"/>
       <c r="U17" s="8" t="n"/>
       <c r="V17" s="8" t="n"/>
-      <c r="W17" s="8" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="W17" s="8" t="n"/>
       <c r="X17" s="8" t="n"/>
       <c r="Y17" s="8" t="n"/>
       <c r="Z17" s="8" t="n"/>
       <c r="AA17" s="8" t="n"/>
-      <c r="AB17" s="8" t="n"/>
-      <c r="AC17" s="8" t="n">
-        <v>5.3</v>
-      </c>
+      <c r="AB17" s="8" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="AC17" s="8" t="n"/>
       <c r="AD17" s="8" t="n"/>
       <c r="AE17" s="8" t="n"/>
       <c r="AF17" s="8" t="n"/>
@@ -1918,8 +2124,10 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="n"/>
-      <c r="B18" s="8" t="n">
-        <v>12</v>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="C18" s="8" t="n"/>
       <c r="D18" s="8" t="n"/>
@@ -1928,46 +2136,64 @@
           <t>Reinforced cement concrete work in shelves upto floor two level excluding the cost of centering and shuttering and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr"/>
+      <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr"/>
-      <c r="I18" s="8" t="n"/>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>Reinforced cement concrete</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
+        </is>
+      </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K18" s="8" t="n"/>
+      <c r="K18" s="17" t="n">
+        <v>0.98</v>
+      </c>
       <c r="L18" s="8" t="n"/>
-      <c r="M18" s="8" t="n"/>
-      <c r="N18" s="8" t="n"/>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>1:2:4</t>
+        </is>
+      </c>
+      <c r="N18" s="17" t="n">
+        <v>1</v>
+      </c>
       <c r="O18" s="8" t="inlineStr">
         <is>
-          <t>Cu.m</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="n"/>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P18" s="17" t="n">
+        <v>1</v>
+      </c>
       <c r="Q18" s="8" t="n"/>
       <c r="R18" s="8" t="n"/>
       <c r="S18" s="8" t="n"/>
       <c r="T18" s="8" t="n"/>
       <c r="U18" s="8" t="n"/>
       <c r="V18" s="8" t="n"/>
-      <c r="W18" s="8" t="n">
-        <v>1</v>
-      </c>
+      <c r="W18" s="8" t="n"/>
       <c r="X18" s="8" t="n"/>
       <c r="Y18" s="8" t="n"/>
       <c r="Z18" s="8" t="n"/>
       <c r="AA18" s="8" t="n"/>
-      <c r="AB18" s="8" t="n"/>
-      <c r="AC18" s="8" t="n">
-        <v>5.4</v>
-      </c>
+      <c r="AB18" s="8" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="AC18" s="8" t="n"/>
       <c r="AD18" s="8" t="n"/>
       <c r="AE18" s="8" t="n"/>
       <c r="AF18" s="8" t="n"/>
@@ -1992,8 +2218,10 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="n"/>
-      <c r="B19" s="8" t="n">
-        <v>13</v>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="n"/>
@@ -2002,46 +2230,64 @@
           <t>Reinforced cement concrete work in chajjas facias and gutters upto floor two level including throating of plastered drip and moulding excluding cost of centring, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr"/>
+      <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr"/>
-      <c r="I19" s="8" t="n"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Reinforced cement concrete</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
+        </is>
+      </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K19" s="8" t="n"/>
+      <c r="K19" s="17" t="n">
+        <v>0.98</v>
+      </c>
       <c r="L19" s="8" t="n"/>
-      <c r="M19" s="8" t="n"/>
-      <c r="N19" s="8" t="n"/>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t>1:2:4</t>
+        </is>
+      </c>
+      <c r="N19" s="17" t="n">
+        <v>0.6</v>
+      </c>
       <c r="O19" s="8" t="inlineStr">
         <is>
-          <t>Cu.m</t>
-        </is>
-      </c>
-      <c r="P19" s="8" t="n"/>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P19" s="17" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Q19" s="8" t="n"/>
       <c r="R19" s="8" t="n"/>
       <c r="S19" s="8" t="n"/>
       <c r="T19" s="8" t="n"/>
       <c r="U19" s="8" t="n"/>
       <c r="V19" s="8" t="n"/>
-      <c r="W19" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="W19" s="8" t="n"/>
       <c r="X19" s="8" t="n"/>
       <c r="Y19" s="8" t="n"/>
       <c r="Z19" s="8" t="n"/>
       <c r="AA19" s="8" t="n"/>
-      <c r="AB19" s="8" t="n"/>
-      <c r="AC19" s="8" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="AB19" s="8" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AC19" s="8" t="n"/>
       <c r="AD19" s="8" t="n"/>
       <c r="AE19" s="8" t="n"/>
       <c r="AF19" s="8" t="n"/>
@@ -2066,8 +2312,10 @@
     </row>
     <row r="20">
       <c r="A20" s="8" t="n"/>
-      <c r="B20" s="8" t="n">
-        <v>14</v>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="n"/>
@@ -2076,48 +2324,64 @@
           <t>Reinforced cement concrete work in lintels, beams, plinth beams and bresummers upto floor two level excluding the cost of centring, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr"/>
+      <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr"/>
-      <c r="I20" s="8" t="n"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>Reinforced cement concrete</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
+        </is>
+      </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K20" s="8" t="n"/>
+      <c r="K20" s="17" t="n">
+        <v>0.98</v>
+      </c>
       <c r="L20" s="8" t="n"/>
-      <c r="M20" s="8" t="n"/>
-      <c r="N20" s="8" t="n"/>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>1:2:4</t>
+        </is>
+      </c>
+      <c r="N20" s="17" t="n">
+        <v>1.7</v>
+      </c>
       <c r="O20" s="8" t="inlineStr">
         <is>
-          <t>Cu.m</t>
-        </is>
-      </c>
-      <c r="P20" s="8" t="n"/>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P20" s="17" t="n">
+        <v>1.7</v>
+      </c>
       <c r="Q20" s="8" t="n"/>
       <c r="R20" s="8" t="n"/>
       <c r="S20" s="8" t="n"/>
       <c r="T20" s="8" t="n"/>
       <c r="U20" s="8" t="n"/>
       <c r="V20" s="8" t="n"/>
-      <c r="W20" s="8" t="n">
-        <v>1.7</v>
-      </c>
+      <c r="W20" s="8" t="n"/>
       <c r="X20" s="8" t="n"/>
       <c r="Y20" s="8" t="n"/>
       <c r="Z20" s="8" t="n"/>
       <c r="AA20" s="8" t="n"/>
-      <c r="AB20" s="8" t="n"/>
-      <c r="AC20" s="8" t="inlineStr">
+      <c r="AB20" s="8" t="inlineStr">
         <is>
           <t>5.6.3</t>
         </is>
       </c>
+      <c r="AC20" s="8" t="n"/>
       <c r="AD20" s="8" t="n"/>
       <c r="AE20" s="8" t="n"/>
       <c r="AF20" s="8" t="n"/>
@@ -2142,8 +2406,10 @@
     </row>
     <row r="21">
       <c r="A21" s="8" t="n"/>
-      <c r="B21" s="8" t="n">
-        <v>15</v>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="n"/>
@@ -2152,48 +2418,64 @@
           <t>Reinforced cement concrete work in columns, pillars, piers, abutments, posts and struts upto floor two level excluding the cost of centring, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr"/>
+      <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr"/>
-      <c r="I21" s="8" t="n"/>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Reinforced cement concrete</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
+        </is>
+      </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K21" s="8" t="n"/>
+      <c r="K21" s="17" t="n">
+        <v>0.98</v>
+      </c>
       <c r="L21" s="8" t="n"/>
-      <c r="M21" s="8" t="n"/>
-      <c r="N21" s="8" t="n"/>
+      <c r="M21" s="8" t="inlineStr">
+        <is>
+          <t>1:2:4</t>
+        </is>
+      </c>
+      <c r="N21" s="17" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O21" s="8" t="inlineStr">
         <is>
-          <t>Cu.m</t>
-        </is>
-      </c>
-      <c r="P21" s="8" t="n"/>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P21" s="17" t="n">
+        <v>0.1</v>
+      </c>
       <c r="Q21" s="8" t="n"/>
       <c r="R21" s="8" t="n"/>
       <c r="S21" s="8" t="n"/>
       <c r="T21" s="8" t="n"/>
       <c r="U21" s="8" t="n"/>
       <c r="V21" s="8" t="n"/>
-      <c r="W21" s="8" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="W21" s="8" t="n"/>
       <c r="X21" s="8" t="n"/>
       <c r="Y21" s="8" t="n"/>
       <c r="Z21" s="8" t="n"/>
       <c r="AA21" s="8" t="n"/>
-      <c r="AB21" s="8" t="n"/>
-      <c r="AC21" s="8" t="inlineStr">
+      <c r="AB21" s="8" t="inlineStr">
         <is>
           <t>5.7.3</t>
         </is>
       </c>
+      <c r="AC21" s="8" t="n"/>
       <c r="AD21" s="8" t="n"/>
       <c r="AE21" s="8" t="n"/>
       <c r="AF21" s="8" t="n"/>
@@ -2220,56 +2502,70 @@
       <c r="A22" s="8" t="n"/>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>16a</t>
+          <t>16i</t>
         </is>
       </c>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : i) Suspended floors, roofs, landings balconies and chajjas.</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr"/>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Suspended floors,roofs,landings balconies and chajjas.</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr"/>
-      <c r="I22" s="8" t="n"/>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>Formwork</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>Formwork</t>
+        </is>
+      </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>Concrete</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="n"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="K22" s="17" t="n">
+        <v>0.9</v>
+      </c>
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
-      <c r="N22" s="8" t="n"/>
+      <c r="N22" s="17" t="n">
+        <v>108</v>
+      </c>
       <c r="O22" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P22" s="8" t="n"/>
-      <c r="Q22" s="8" t="n"/>
+      <c r="Q22" s="17" t="n">
+        <v>108</v>
+      </c>
       <c r="R22" s="8" t="n"/>
       <c r="S22" s="8" t="n"/>
       <c r="T22" s="8" t="n"/>
       <c r="U22" s="8" t="n"/>
       <c r="V22" s="8" t="n"/>
-      <c r="W22" s="8" t="n">
-        <v>108</v>
-      </c>
+      <c r="W22" s="8" t="n"/>
       <c r="X22" s="8" t="n"/>
       <c r="Y22" s="8" t="n"/>
       <c r="Z22" s="8" t="n"/>
       <c r="AA22" s="8" t="n"/>
-      <c r="AB22" s="8" t="n"/>
-      <c r="AC22" s="8" t="n">
-        <v>5.14</v>
-      </c>
+      <c r="AB22" s="8" t="inlineStr">
+        <is>
+          <t>5.14</t>
+        </is>
+      </c>
+      <c r="AC22" s="8" t="n"/>
       <c r="AD22" s="8" t="n"/>
       <c r="AE22" s="8" t="n"/>
       <c r="AF22" s="8" t="n"/>
@@ -2296,56 +2592,70 @@
       <c r="A23" s="8" t="n"/>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>16b</t>
+          <t>16ii</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : ii) Shelves</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr"/>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Shelves</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr"/>
-      <c r="I23" s="8" t="n"/>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Formwork</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>Formwork</t>
+        </is>
+      </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>Concrete</t>
-        </is>
-      </c>
-      <c r="K23" s="8" t="n"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="K23" s="17" t="n">
+        <v>0.9</v>
+      </c>
       <c r="L23" s="8" t="n"/>
       <c r="M23" s="8" t="n"/>
-      <c r="N23" s="8" t="n"/>
+      <c r="N23" s="17" t="n">
+        <v>17</v>
+      </c>
       <c r="O23" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P23" s="8" t="n"/>
-      <c r="Q23" s="8" t="n"/>
+      <c r="Q23" s="17" t="n">
+        <v>17</v>
+      </c>
       <c r="R23" s="8" t="n"/>
       <c r="S23" s="8" t="n"/>
       <c r="T23" s="8" t="n"/>
       <c r="U23" s="8" t="n"/>
       <c r="V23" s="8" t="n"/>
-      <c r="W23" s="8" t="n">
-        <v>17</v>
-      </c>
+      <c r="W23" s="8" t="n"/>
       <c r="X23" s="8" t="n"/>
       <c r="Y23" s="8" t="n"/>
       <c r="Z23" s="8" t="n"/>
       <c r="AA23" s="8" t="n"/>
-      <c r="AB23" s="8" t="n"/>
-      <c r="AC23" s="8" t="n">
-        <v>5.14</v>
-      </c>
+      <c r="AB23" s="8" t="inlineStr">
+        <is>
+          <t>5.14</t>
+        </is>
+      </c>
+      <c r="AC23" s="8" t="n"/>
       <c r="AD23" s="8" t="n"/>
       <c r="AE23" s="8" t="n"/>
       <c r="AF23" s="8" t="n"/>
@@ -2372,56 +2682,70 @@
       <c r="A24" s="8" t="n"/>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>16c</t>
+          <t>16iii</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : iii) Lintels, beams, plinth beams, girders bressumers and cantilever.</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr"/>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Lintels, beams, plinth beams, girders bressumers and cantilever.</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr"/>
-      <c r="I24" s="8" t="n"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Formwork</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>Formwork</t>
+        </is>
+      </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>Concrete</t>
-        </is>
-      </c>
-      <c r="K24" s="8" t="n"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="K24" s="17" t="n">
+        <v>0.9</v>
+      </c>
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
-      <c r="N24" s="8" t="n"/>
+      <c r="N24" s="17" t="n">
+        <v>19</v>
+      </c>
       <c r="O24" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P24" s="8" t="n"/>
-      <c r="Q24" s="8" t="n"/>
+      <c r="Q24" s="17" t="n">
+        <v>19</v>
+      </c>
       <c r="R24" s="8" t="n"/>
       <c r="S24" s="8" t="n"/>
       <c r="T24" s="8" t="n"/>
       <c r="U24" s="8" t="n"/>
       <c r="V24" s="8" t="n"/>
-      <c r="W24" s="8" t="n">
-        <v>19</v>
-      </c>
+      <c r="W24" s="8" t="n"/>
       <c r="X24" s="8" t="n"/>
       <c r="Y24" s="8" t="n"/>
       <c r="Z24" s="8" t="n"/>
       <c r="AA24" s="8" t="n"/>
-      <c r="AB24" s="8" t="n"/>
-      <c r="AC24" s="8" t="n">
-        <v>5.14</v>
-      </c>
+      <c r="AB24" s="8" t="inlineStr">
+        <is>
+          <t>5.14</t>
+        </is>
+      </c>
+      <c r="AC24" s="8" t="n"/>
       <c r="AD24" s="8" t="n"/>
       <c r="AE24" s="8" t="n"/>
       <c r="AF24" s="8" t="n"/>
@@ -2448,56 +2772,70 @@
       <c r="A25" s="8" t="n"/>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>16d</t>
+          <t>16iv</t>
         </is>
       </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : iv) Columns, pillars, posts and struts.</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr"/>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Columns, pillars, posts and struts.</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr"/>
-      <c r="I25" s="8" t="n"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>Formwork</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>Formwork</t>
+        </is>
+      </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>Concrete</t>
-        </is>
-      </c>
-      <c r="K25" s="8" t="n"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="n">
+        <v>0.9</v>
+      </c>
       <c r="L25" s="8" t="n"/>
       <c r="M25" s="8" t="n"/>
-      <c r="N25" s="8" t="n"/>
+      <c r="N25" s="17" t="n">
+        <v>2</v>
+      </c>
       <c r="O25" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P25" s="8" t="n"/>
-      <c r="Q25" s="8" t="n"/>
+      <c r="Q25" s="17" t="n">
+        <v>2</v>
+      </c>
       <c r="R25" s="8" t="n"/>
       <c r="S25" s="8" t="n"/>
       <c r="T25" s="8" t="n"/>
       <c r="U25" s="8" t="n"/>
       <c r="V25" s="8" t="n"/>
-      <c r="W25" s="8" t="n">
-        <v>2</v>
-      </c>
+      <c r="W25" s="8" t="n"/>
       <c r="X25" s="8" t="n"/>
       <c r="Y25" s="8" t="n"/>
       <c r="Z25" s="8" t="n"/>
       <c r="AA25" s="8" t="n"/>
-      <c r="AB25" s="8" t="n"/>
-      <c r="AC25" s="8" t="n">
-        <v>5.14</v>
-      </c>
+      <c r="AB25" s="8" t="inlineStr">
+        <is>
+          <t>5.14</t>
+        </is>
+      </c>
+      <c r="AC25" s="8" t="n"/>
       <c r="AD25" s="8" t="n"/>
       <c r="AE25" s="8" t="n"/>
       <c r="AF25" s="8" t="n"/>
@@ -2524,56 +2862,70 @@
       <c r="A26" s="8" t="n"/>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>16e</t>
+          <t>16v</t>
         </is>
       </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : v) Vertical and horizontal fins individually or forming box louvers hand and facias.</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr"/>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Vertical and horizontal fins individually or forming box louvers hand and facias.</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr"/>
-      <c r="I26" s="8" t="n"/>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>Formwork</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>Formwork</t>
+        </is>
+      </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>Concrete</t>
-        </is>
-      </c>
-      <c r="K26" s="8" t="n"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="K26" s="17" t="n">
+        <v>0.9</v>
+      </c>
       <c r="L26" s="8" t="n"/>
       <c r="M26" s="8" t="n"/>
-      <c r="N26" s="8" t="n"/>
+      <c r="N26" s="17" t="n">
+        <v>9</v>
+      </c>
       <c r="O26" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P26" s="8" t="n"/>
-      <c r="Q26" s="8" t="n"/>
+      <c r="Q26" s="17" t="n">
+        <v>9</v>
+      </c>
       <c r="R26" s="8" t="n"/>
       <c r="S26" s="8" t="n"/>
       <c r="T26" s="8" t="n"/>
       <c r="U26" s="8" t="n"/>
       <c r="V26" s="8" t="n"/>
-      <c r="W26" s="8" t="n">
-        <v>9</v>
-      </c>
+      <c r="W26" s="8" t="n"/>
       <c r="X26" s="8" t="n"/>
       <c r="Y26" s="8" t="n"/>
       <c r="Z26" s="8" t="n"/>
       <c r="AA26" s="8" t="n"/>
-      <c r="AB26" s="8" t="n"/>
-      <c r="AC26" s="8" t="n">
-        <v>5.14</v>
-      </c>
+      <c r="AB26" s="8" t="inlineStr">
+        <is>
+          <t>5.14</t>
+        </is>
+      </c>
+      <c r="AC26" s="8" t="n"/>
       <c r="AD26" s="8" t="n"/>
       <c r="AE26" s="8" t="n"/>
       <c r="AF26" s="8" t="n"/>
@@ -2600,56 +2952,70 @@
       <c r="A27" s="8" t="n"/>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>17a</t>
+          <t>17i</t>
         </is>
       </c>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Reinforcement for RCC work including bending binding and placing in position complete. i) Mild steel and medium tensile steel bars.</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr"/>
+          <t>Reinforcement for RCC work including bending binding and placing in position complete. Mild steel and medium tensile steel bars.</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr"/>
-      <c r="I27" s="8" t="n"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Mild steel</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>Steel</t>
+        </is>
+      </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
           <t>Steel</t>
         </is>
       </c>
-      <c r="K27" s="8" t="n"/>
+      <c r="K27" s="17" t="n">
+        <v>0.98</v>
+      </c>
       <c r="L27" s="8" t="n"/>
       <c r="M27" s="8" t="n"/>
-      <c r="N27" s="8" t="n"/>
+      <c r="N27" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="O27" s="8" t="inlineStr">
         <is>
-          <t>Kg.</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="P27" s="8" t="n"/>
       <c r="Q27" s="8" t="n"/>
       <c r="R27" s="8" t="n"/>
-      <c r="S27" s="8" t="n"/>
+      <c r="S27" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="T27" s="8" t="n"/>
       <c r="U27" s="8" t="n"/>
       <c r="V27" s="8" t="n"/>
-      <c r="W27" s="8" t="n">
-        <v>100</v>
-      </c>
+      <c r="W27" s="8" t="n"/>
       <c r="X27" s="8" t="n"/>
       <c r="Y27" s="8" t="n"/>
       <c r="Z27" s="8" t="n"/>
       <c r="AA27" s="8" t="n"/>
-      <c r="AB27" s="8" t="n"/>
-      <c r="AC27" s="8" t="n">
-        <v>5.29</v>
-      </c>
+      <c r="AB27" s="8" t="inlineStr">
+        <is>
+          <t>5.29</t>
+        </is>
+      </c>
+      <c r="AC27" s="8" t="n"/>
       <c r="AD27" s="8" t="n"/>
       <c r="AE27" s="8" t="n"/>
       <c r="AF27" s="8" t="n"/>
@@ -2676,56 +3042,70 @@
       <c r="A28" s="8" t="n"/>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>17b</t>
+          <t>17ii</t>
         </is>
       </c>
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Reinforcement for RCC work including bending binding and placing in position complete. ii) Cold twisted bars</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr"/>
+          <t>Reinforcement for RCC work including bending binding and placing in position complete. Cold twisted bars</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr"/>
-      <c r="I28" s="8" t="n"/>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>Cold twisted steel</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>Steel</t>
+        </is>
+      </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
           <t>Steel</t>
         </is>
       </c>
-      <c r="K28" s="8" t="n"/>
+      <c r="K28" s="17" t="n">
+        <v>0.98</v>
+      </c>
       <c r="L28" s="8" t="n"/>
       <c r="M28" s="8" t="n"/>
-      <c r="N28" s="8" t="n"/>
+      <c r="N28" s="17" t="n">
+        <v>1375</v>
+      </c>
       <c r="O28" s="8" t="inlineStr">
         <is>
-          <t>Kg.</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="P28" s="8" t="n"/>
       <c r="Q28" s="8" t="n"/>
       <c r="R28" s="8" t="n"/>
-      <c r="S28" s="8" t="n"/>
+      <c r="S28" s="17" t="n">
+        <v>1375</v>
+      </c>
       <c r="T28" s="8" t="n"/>
       <c r="U28" s="8" t="n"/>
       <c r="V28" s="8" t="n"/>
-      <c r="W28" s="8" t="n">
-        <v>1375</v>
-      </c>
+      <c r="W28" s="8" t="n"/>
       <c r="X28" s="8" t="n"/>
       <c r="Y28" s="8" t="n"/>
       <c r="Z28" s="8" t="n"/>
       <c r="AA28" s="8" t="n"/>
-      <c r="AB28" s="8" t="n"/>
-      <c r="AC28" s="8" t="n">
-        <v>5.29</v>
-      </c>
+      <c r="AB28" s="8" t="inlineStr">
+        <is>
+          <t>5.29</t>
+        </is>
+      </c>
+      <c r="AC28" s="8" t="n"/>
       <c r="AD28" s="8" t="n"/>
       <c r="AE28" s="8" t="n"/>
       <c r="AF28" s="8" t="n"/>
@@ -2750,8 +3130,10 @@
     </row>
     <row r="29">
       <c r="A29" s="8" t="n"/>
-      <c r="B29" s="8" t="n">
-        <v>18</v>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="C29" s="8" t="n"/>
       <c r="D29" s="8" t="n"/>
@@ -2760,46 +3142,64 @@
           <t>Providing and laying upto floor two level RCC in string courses, bands, copings, bed plates, anchor blocks, plain window sills and the like excluding the cost of centering, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr"/>
+      <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr"/>
-      <c r="I29" s="8" t="n"/>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>Reinforced cement concrete</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
+        </is>
+      </c>
       <c r="J29" s="8" t="inlineStr">
         <is>
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K29" s="8" t="n"/>
+      <c r="K29" s="17" t="n">
+        <v>0.98</v>
+      </c>
       <c r="L29" s="8" t="n"/>
-      <c r="M29" s="8" t="n"/>
-      <c r="N29" s="8" t="n"/>
+      <c r="M29" s="8" t="inlineStr">
+        <is>
+          <t>1:2:4</t>
+        </is>
+      </c>
+      <c r="N29" s="17" t="n">
+        <v>0.8</v>
+      </c>
       <c r="O29" s="8" t="inlineStr">
         <is>
-          <t>Cu.m</t>
-        </is>
-      </c>
-      <c r="P29" s="8" t="n"/>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P29" s="17" t="n">
+        <v>0.8</v>
+      </c>
       <c r="Q29" s="8" t="n"/>
       <c r="R29" s="8" t="n"/>
       <c r="S29" s="8" t="n"/>
       <c r="T29" s="8" t="n"/>
       <c r="U29" s="8" t="n"/>
       <c r="V29" s="8" t="n"/>
-      <c r="W29" s="8" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="W29" s="8" t="n"/>
       <c r="X29" s="8" t="n"/>
       <c r="Y29" s="8" t="n"/>
       <c r="Z29" s="8" t="n"/>
       <c r="AA29" s="8" t="n"/>
-      <c r="AB29" s="8" t="n"/>
-      <c r="AC29" s="8" t="n">
-        <v>5.16</v>
-      </c>
+      <c r="AB29" s="8" t="inlineStr">
+        <is>
+          <t>5.16</t>
+        </is>
+      </c>
+      <c r="AC29" s="8" t="n"/>
       <c r="AD29" s="8" t="n"/>
       <c r="AE29" s="8" t="n"/>
       <c r="AF29" s="8" t="n"/>
@@ -2824,58 +3224,76 @@
     </row>
     <row r="30">
       <c r="A30" s="8" t="n"/>
-      <c r="B30" s="8" t="n">
-        <v>19</v>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="C30" s="8" t="n"/>
       <c r="D30" s="8" t="n"/>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Brick work with bricks of class designation ______ in foundation and plinth in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr"/>
+          <t>Brick work with bricks of class designation___ in foundation and plinth in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr"/>
-      <c r="I30" s="8" t="n"/>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>Burnt brick</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>Brick, Cement, Coarse sand</t>
+        </is>
+      </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
           <t>Masonry</t>
         </is>
       </c>
-      <c r="K30" s="8" t="n"/>
+      <c r="K30" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L30" s="8" t="n"/>
-      <c r="M30" s="8" t="n"/>
-      <c r="N30" s="8" t="n"/>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>1:6</t>
+        </is>
+      </c>
+      <c r="N30" s="17" t="n">
+        <v>17</v>
+      </c>
       <c r="O30" s="8" t="inlineStr">
         <is>
-          <t>Cu.m</t>
-        </is>
-      </c>
-      <c r="P30" s="8" t="n"/>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P30" s="17" t="n">
+        <v>17</v>
+      </c>
       <c r="Q30" s="8" t="n"/>
       <c r="R30" s="8" t="n"/>
       <c r="S30" s="8" t="n"/>
       <c r="T30" s="8" t="n"/>
       <c r="U30" s="8" t="n"/>
       <c r="V30" s="8" t="n"/>
-      <c r="W30" s="8" t="n">
-        <v>17</v>
-      </c>
+      <c r="W30" s="8" t="n"/>
       <c r="X30" s="8" t="n"/>
       <c r="Y30" s="8" t="n"/>
       <c r="Z30" s="8" t="n"/>
       <c r="AA30" s="8" t="n"/>
-      <c r="AB30" s="8" t="n"/>
-      <c r="AC30" s="8" t="inlineStr">
-        <is>
-          <t>6.1.14/6.5.1/6.5.2</t>
-        </is>
-      </c>
+      <c r="AB30" s="8" t="inlineStr">
+        <is>
+          <t>6.1.14/6.5.1 6.5.2</t>
+        </is>
+      </c>
+      <c r="AC30" s="8" t="n"/>
       <c r="AD30" s="8" t="n"/>
       <c r="AE30" s="8" t="n"/>
       <c r="AF30" s="8" t="n"/>
@@ -2900,58 +3318,76 @@
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
-      <c r="B31" s="8" t="n">
-        <v>20</v>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="n"/>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Brick work with bricks of class designation ______ in super structure above plinth upto floor two level in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr"/>
+          <t>Brick work with bricks of class designation___ in super structure above plinth upto floor two level in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr"/>
-      <c r="I31" s="8" t="n"/>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>Burnt brick</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>Brick, Cement, Coarse sand</t>
+        </is>
+      </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
           <t>Masonry</t>
         </is>
       </c>
-      <c r="K31" s="8" t="n"/>
+      <c r="K31" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L31" s="8" t="n"/>
-      <c r="M31" s="8" t="n"/>
-      <c r="N31" s="8" t="n"/>
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t>1:6</t>
+        </is>
+      </c>
+      <c r="N31" s="17" t="n">
+        <v>40.3</v>
+      </c>
       <c r="O31" s="8" t="inlineStr">
         <is>
-          <t>Cu.m</t>
-        </is>
-      </c>
-      <c r="P31" s="8" t="n"/>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P31" s="17" t="n">
+        <v>40.3</v>
+      </c>
       <c r="Q31" s="8" t="n"/>
       <c r="R31" s="8" t="n"/>
       <c r="S31" s="8" t="n"/>
       <c r="T31" s="8" t="n"/>
       <c r="U31" s="8" t="n"/>
       <c r="V31" s="8" t="n"/>
-      <c r="W31" s="8" t="n">
-        <v>40.3</v>
-      </c>
+      <c r="W31" s="8" t="n"/>
       <c r="X31" s="8" t="n"/>
       <c r="Y31" s="8" t="n"/>
       <c r="Z31" s="8" t="n"/>
       <c r="AA31" s="8" t="n"/>
-      <c r="AB31" s="8" t="n"/>
-      <c r="AC31" s="8" t="inlineStr">
-        <is>
-          <t>6.1.14/6.3/6.5.1/6.5.2</t>
-        </is>
-      </c>
+      <c r="AB31" s="8" t="inlineStr">
+        <is>
+          <t>6.1.14/6.3 6.5.1/6.5.2</t>
+        </is>
+      </c>
+      <c r="AC31" s="8" t="n"/>
       <c r="AD31" s="8" t="n"/>
       <c r="AE31" s="8" t="n"/>
       <c r="AF31" s="8" t="n"/>
@@ -2976,58 +3412,76 @@
     </row>
     <row r="32">
       <c r="A32" s="8" t="n"/>
-      <c r="B32" s="8" t="n">
-        <v>21</v>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Brick work 7 cm thick with bricks of class designation ______ in super structure upto floor two level in cement mortar 1:3 (1 cement : 3 coarse sand).</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr"/>
+          <t>Brick work 7 cm thick with bricks of class designation ------ in super structure upto floor two level in cement mortar 1:3 (1 cement : 3 coarse sand).</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr"/>
-      <c r="I32" s="8" t="n"/>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>Burnt brick</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>Brick, Cement, Coarse sand</t>
+        </is>
+      </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
           <t>Masonry</t>
         </is>
       </c>
-      <c r="K32" s="8" t="n"/>
+      <c r="K32" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L32" s="8" t="n"/>
-      <c r="M32" s="8" t="n"/>
-      <c r="N32" s="8" t="n"/>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="N32" s="17" t="n">
+        <v>0.9</v>
+      </c>
       <c r="O32" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P32" s="8" t="n"/>
-      <c r="Q32" s="8" t="n"/>
+      <c r="Q32" s="17" t="n">
+        <v>0.9</v>
+      </c>
       <c r="R32" s="8" t="n"/>
       <c r="S32" s="8" t="n"/>
       <c r="T32" s="8" t="n"/>
       <c r="U32" s="8" t="n"/>
       <c r="V32" s="8" t="n"/>
-      <c r="W32" s="8" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="W32" s="8" t="n"/>
       <c r="X32" s="8" t="n"/>
       <c r="Y32" s="8" t="n"/>
       <c r="Z32" s="8" t="n"/>
       <c r="AA32" s="8" t="n"/>
-      <c r="AB32" s="8" t="n"/>
-      <c r="AC32" s="8" t="inlineStr">
-        <is>
-          <t>6.13/6.21/6.5.1/6.5.2</t>
-        </is>
-      </c>
+      <c r="AB32" s="8" t="inlineStr">
+        <is>
+          <t>6.13/6.21/ 6.5.1/6.5.2</t>
+        </is>
+      </c>
+      <c r="AC32" s="8" t="n"/>
       <c r="AD32" s="8" t="n"/>
       <c r="AE32" s="8" t="n"/>
       <c r="AF32" s="8" t="n"/>
@@ -3042,7 +3496,9 @@
       <c r="AO32" s="8" t="n"/>
       <c r="AP32" s="8" t="n"/>
       <c r="AQ32" s="8" t="n"/>
-      <c r="AR32" s="8" t="n"/>
+      <c r="AR32" s="17" t="n">
+        <v>70</v>
+      </c>
       <c r="AS32" s="8" t="n"/>
       <c r="AT32" s="8" t="n"/>
       <c r="AU32" s="8" t="n"/>
@@ -3052,58 +3508,76 @@
     </row>
     <row r="33">
       <c r="A33" s="8" t="n"/>
-      <c r="B33" s="8" t="n">
-        <v>22</v>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Half brick masonry with bricks of class designation ______ in foundation &amp; plinth in cement mortar 1:4 (1 cement : 4 coarse sand)</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr"/>
+          <t>Half brick masonry with bricks of class designation ____ in foundation &amp; plinth in cement mortar 1:4 (1 cement : 4 coarse sand)</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr"/>
-      <c r="I33" s="8" t="n"/>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>Burnt brick</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>Brick, Cement, Coarse sand</t>
+        </is>
+      </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
           <t>Masonry</t>
         </is>
       </c>
-      <c r="K33" s="8" t="n"/>
+      <c r="K33" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L33" s="8" t="n"/>
-      <c r="M33" s="8" t="n"/>
-      <c r="N33" s="8" t="n"/>
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="N33" s="17" t="n">
+        <v>4.8</v>
+      </c>
       <c r="O33" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P33" s="8" t="n"/>
-      <c r="Q33" s="8" t="n"/>
+      <c r="Q33" s="17" t="n">
+        <v>4.8</v>
+      </c>
       <c r="R33" s="8" t="n"/>
       <c r="S33" s="8" t="n"/>
       <c r="T33" s="8" t="n"/>
       <c r="U33" s="8" t="n"/>
       <c r="V33" s="8" t="n"/>
-      <c r="W33" s="8" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="W33" s="8" t="n"/>
       <c r="X33" s="8" t="n"/>
       <c r="Y33" s="8" t="n"/>
       <c r="Z33" s="8" t="n"/>
       <c r="AA33" s="8" t="n"/>
-      <c r="AB33" s="8" t="n"/>
-      <c r="AC33" s="8" t="inlineStr">
-        <is>
-          <t>6.18.4/6.21/6.5.1/6.5.2</t>
-        </is>
-      </c>
+      <c r="AB33" s="8" t="inlineStr">
+        <is>
+          <t>6.18.4/6.21 6.5.1/6.5.2</t>
+        </is>
+      </c>
+      <c r="AC33" s="8" t="n"/>
       <c r="AD33" s="8" t="n"/>
       <c r="AE33" s="8" t="n"/>
       <c r="AF33" s="8" t="n"/>
@@ -3128,58 +3602,76 @@
     </row>
     <row r="34">
       <c r="A34" s="8" t="n"/>
-      <c r="B34" s="8" t="n">
-        <v>23</v>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Half brick masonry with bricks of class designation ______ in super structure upto floor two level in cement mortar 1:4 (1 cement : 4 coarse sand).</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr"/>
+          <t>Half brick masonry with bricks of class designation ____ in super structure upto floor two level in cement mortar 1:4 (1 cement : 4 coarse sand).</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr"/>
-      <c r="I34" s="8" t="n"/>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Burnt brick</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>Brick, Cement, Coarse sand</t>
+        </is>
+      </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
           <t>Masonry</t>
         </is>
       </c>
-      <c r="K34" s="8" t="n"/>
+      <c r="K34" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L34" s="8" t="n"/>
-      <c r="M34" s="8" t="n"/>
-      <c r="N34" s="8" t="n"/>
+      <c r="M34" s="8" t="inlineStr">
+        <is>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="N34" s="17" t="n">
+        <v>18</v>
+      </c>
       <c r="O34" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P34" s="8" t="n"/>
-      <c r="Q34" s="8" t="n"/>
+      <c r="Q34" s="17" t="n">
+        <v>18</v>
+      </c>
       <c r="R34" s="8" t="n"/>
       <c r="S34" s="8" t="n"/>
       <c r="T34" s="8" t="n"/>
       <c r="U34" s="8" t="n"/>
       <c r="V34" s="8" t="n"/>
-      <c r="W34" s="8" t="n">
-        <v>18</v>
-      </c>
+      <c r="W34" s="8" t="n"/>
       <c r="X34" s="8" t="n"/>
       <c r="Y34" s="8" t="n"/>
       <c r="Z34" s="8" t="n"/>
       <c r="AA34" s="8" t="n"/>
-      <c r="AB34" s="8" t="n"/>
-      <c r="AC34" s="8" t="inlineStr">
-        <is>
-          <t>6.18.4/6.19.1/6.20/6.21.1/6.21.2</t>
-        </is>
-      </c>
+      <c r="AB34" s="8" t="inlineStr">
+        <is>
+          <t>6.18.4/6.19.1 6.20/6.21.1/ 6.21.2</t>
+        </is>
+      </c>
+      <c r="AC34" s="8" t="n"/>
       <c r="AD34" s="8" t="n"/>
       <c r="AE34" s="8" t="n"/>
       <c r="AF34" s="8" t="n"/>
@@ -3204,48 +3696,62 @@
     </row>
     <row r="35">
       <c r="A35" s="8" t="n"/>
-      <c r="B35" s="8" t="n">
-        <v>24</v>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Providing ______ wood work in frames of doors, windows, clerestory windows and other frames, wrought framed and fixed in position.</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr"/>
+          <t>Providing ________ wood work in frames of doors, windows, clerestory windows and other frames, wrought framed and fixed in position.</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr"/>
-      <c r="I35" s="8" t="n"/>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
       <c r="J35" s="8" t="inlineStr">
         <is>
           <t>Timber</t>
         </is>
       </c>
-      <c r="K35" s="8" t="n"/>
+      <c r="K35" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L35" s="8" t="n"/>
       <c r="M35" s="8" t="n"/>
-      <c r="N35" s="8" t="n"/>
+      <c r="N35" s="17" t="n">
+        <v>0.035</v>
+      </c>
       <c r="O35" s="8" t="inlineStr">
         <is>
-          <t>10 Cubic decimetre</t>
-        </is>
-      </c>
-      <c r="P35" s="8" t="n"/>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P35" s="17" t="n">
+        <v>0.035</v>
+      </c>
       <c r="Q35" s="8" t="n"/>
       <c r="R35" s="8" t="n"/>
       <c r="S35" s="8" t="n"/>
       <c r="T35" s="8" t="n"/>
       <c r="U35" s="8" t="n"/>
       <c r="V35" s="8" t="n"/>
-      <c r="W35" s="8" t="n">
-        <v>3.5</v>
-      </c>
+      <c r="W35" s="8" t="n"/>
       <c r="X35" s="8" t="n"/>
       <c r="Y35" s="8" t="n"/>
       <c r="Z35" s="8" t="n"/>
@@ -3276,48 +3782,62 @@
     </row>
     <row r="36">
       <c r="A36" s="8" t="n"/>
-      <c r="B36" s="8" t="n">
-        <v>25</v>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing 35 mm thick battended and framed door shutters of ______ wood including bright finished or/and black enamelled MS butt hinges with necessary screws.</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr"/>
+          <t>Providing and fixing 35 mm thick battened and framed door shutters of ________ wood including bright finished or/and black enamelled MS butt hinges with necessary screws.</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr"/>
-      <c r="I36" s="8" t="n"/>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>Wood, Mild steel</t>
+        </is>
+      </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
           <t>Timber</t>
         </is>
       </c>
-      <c r="K36" s="8" t="n"/>
+      <c r="K36" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L36" s="8" t="n"/>
       <c r="M36" s="8" t="n"/>
-      <c r="N36" s="8" t="n"/>
+      <c r="N36" s="17" t="n">
+        <v>18</v>
+      </c>
       <c r="O36" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P36" s="8" t="n"/>
-      <c r="Q36" s="8" t="n"/>
+      <c r="Q36" s="17" t="n">
+        <v>18</v>
+      </c>
       <c r="R36" s="8" t="n"/>
       <c r="S36" s="8" t="n"/>
       <c r="T36" s="8" t="n"/>
       <c r="U36" s="8" t="n"/>
       <c r="V36" s="8" t="n"/>
-      <c r="W36" s="8" t="n">
-        <v>18</v>
-      </c>
+      <c r="W36" s="8" t="n"/>
       <c r="X36" s="8" t="n"/>
       <c r="Y36" s="8" t="n"/>
       <c r="Z36" s="8" t="n"/>
@@ -3338,7 +3858,9 @@
       <c r="AO36" s="8" t="n"/>
       <c r="AP36" s="8" t="n"/>
       <c r="AQ36" s="8" t="n"/>
-      <c r="AR36" s="8" t="n"/>
+      <c r="AR36" s="17" t="n">
+        <v>35</v>
+      </c>
       <c r="AS36" s="8" t="n"/>
       <c r="AT36" s="8" t="n"/>
       <c r="AU36" s="8" t="n"/>
@@ -3348,58 +3870,72 @@
     </row>
     <row r="37">
       <c r="A37" s="8" t="n"/>
-      <c r="B37" s="8" t="n">
-        <v>26</v>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing 25 mm thick flush door (for cupboard) shutters core of block board construction with frame of 1st class hard wood and well matched 1st class teak ply veneering with vertical grains or cross bands and face veneer on one face and commercial ply veneering with vertical grains or cross bands and face veneer on other face of shutters, including nickel plated bright finished MS piano hinges with necessary screws.</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="inlineStr"/>
+          <t>Providing and fixing 25 mm thick flush door (for cupboard) shutters core of block board construction with frame of Ist class hard wood and well matched Ist class teak ply veneering with vertical grains or cross bands and face veneer on one face and commercial ply veneering with vertical grains or cross bands and face veneer on other face of shutters, including nickel plated bright finished MS piano hinges with necessary screws.</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr"/>
-      <c r="I37" s="8" t="n"/>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Flush door</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>Hard wood, Teak ply, Commercial ply, Mild steel</t>
+        </is>
+      </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
           <t>Timber</t>
         </is>
       </c>
-      <c r="K37" s="8" t="n"/>
+      <c r="K37" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L37" s="8" t="n"/>
       <c r="M37" s="8" t="n"/>
-      <c r="N37" s="8" t="n"/>
+      <c r="N37" s="17" t="n">
+        <v>4.7</v>
+      </c>
       <c r="O37" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P37" s="8" t="n"/>
-      <c r="Q37" s="8" t="n"/>
+      <c r="Q37" s="17" t="n">
+        <v>4.7</v>
+      </c>
       <c r="R37" s="8" t="n"/>
       <c r="S37" s="8" t="n"/>
       <c r="T37" s="8" t="n"/>
       <c r="U37" s="8" t="n"/>
       <c r="V37" s="8" t="n"/>
-      <c r="W37" s="8" t="n">
-        <v>4.7</v>
-      </c>
+      <c r="W37" s="8" t="n"/>
       <c r="X37" s="8" t="n"/>
       <c r="Y37" s="8" t="n"/>
       <c r="Z37" s="8" t="n"/>
       <c r="AA37" s="8" t="n"/>
-      <c r="AB37" s="8" t="n"/>
-      <c r="AC37" s="8" t="inlineStr">
+      <c r="AB37" s="8" t="inlineStr">
         <is>
           <t>9.26.4</t>
         </is>
       </c>
+      <c r="AC37" s="8" t="n"/>
       <c r="AD37" s="8" t="n"/>
       <c r="AE37" s="8" t="n"/>
       <c r="AF37" s="8" t="n"/>
@@ -3414,7 +3950,9 @@
       <c r="AO37" s="8" t="n"/>
       <c r="AP37" s="8" t="n"/>
       <c r="AQ37" s="8" t="n"/>
-      <c r="AR37" s="8" t="n"/>
+      <c r="AR37" s="17" t="n">
+        <v>25</v>
+      </c>
       <c r="AS37" s="8" t="n"/>
       <c r="AT37" s="8" t="n"/>
       <c r="AU37" s="8" t="n"/>
@@ -3424,56 +3962,76 @@
     </row>
     <row r="38">
       <c r="A38" s="8" t="n"/>
-      <c r="B38" s="8" t="n">
-        <v>27</v>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Providing 50x50x50 mm 2nd class Teak wood plugs including cutting brick work and fixing in cement mortar 1:3 (1 cement : 3 fine sand) and making good the walls etc.</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr"/>
+          <t>Providing 50x50x50 mm 2nd class Teak wood plugs including cutting brick work and fixing in cement mortar 1:3 (1 cement :3 fine sand) and making good the walls etc.</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr"/>
-      <c r="I38" s="8" t="n"/>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Teak wood</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>Teak wood, Cement, Fine sand</t>
+        </is>
+      </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
           <t>Timber</t>
         </is>
       </c>
-      <c r="K38" s="8" t="n"/>
+      <c r="K38" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L38" s="8" t="n"/>
-      <c r="M38" s="8" t="n"/>
-      <c r="N38" s="8" t="n"/>
+      <c r="M38" s="8" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="N38" s="17" t="n">
+        <v>20</v>
+      </c>
       <c r="O38" s="8" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P38" s="8" t="n"/>
       <c r="Q38" s="8" t="n"/>
       <c r="R38" s="8" t="n"/>
       <c r="S38" s="8" t="n"/>
-      <c r="T38" s="8" t="n"/>
+      <c r="T38" s="17" t="n">
+        <v>20</v>
+      </c>
       <c r="U38" s="8" t="n"/>
       <c r="V38" s="8" t="n"/>
-      <c r="W38" s="8" t="n">
-        <v>20</v>
-      </c>
+      <c r="W38" s="8" t="n"/>
       <c r="X38" s="8" t="n"/>
       <c r="Y38" s="8" t="n"/>
       <c r="Z38" s="8" t="n"/>
       <c r="AA38" s="8" t="n"/>
-      <c r="AB38" s="8" t="n"/>
-      <c r="AC38" s="8" t="n">
-        <v>9.51</v>
-      </c>
+      <c r="AB38" s="8" t="inlineStr">
+        <is>
+          <t>9.51</t>
+        </is>
+      </c>
+      <c r="AC38" s="8" t="n"/>
       <c r="AD38" s="8" t="n"/>
       <c r="AE38" s="8" t="n"/>
       <c r="AF38" s="8" t="n"/>
@@ -3498,48 +4056,62 @@
     </row>
     <row r="39">
       <c r="A39" s="8" t="n"/>
-      <c r="B39" s="8" t="n">
-        <v>28</v>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing M.S.oxidised fan light ventilator catch with necessary screws etc. complete.</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr"/>
+          <t>Providing and fixing M.S.oxidised fan light .ventilator catch with necessary screws etc. complete.</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr"/>
-      <c r="I39" s="8" t="n"/>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>Mild steel</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>Mild steel</t>
+        </is>
+      </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
           <t>Steel</t>
         </is>
       </c>
-      <c r="K39" s="8" t="n"/>
+      <c r="K39" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L39" s="8" t="n"/>
       <c r="M39" s="8" t="n"/>
-      <c r="N39" s="8" t="n"/>
+      <c r="N39" s="17" t="n">
+        <v>6</v>
+      </c>
       <c r="O39" s="8" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P39" s="8" t="n"/>
       <c r="Q39" s="8" t="n"/>
       <c r="R39" s="8" t="n"/>
       <c r="S39" s="8" t="n"/>
-      <c r="T39" s="8" t="n"/>
+      <c r="T39" s="17" t="n">
+        <v>6</v>
+      </c>
       <c r="U39" s="8" t="n"/>
       <c r="V39" s="8" t="n"/>
-      <c r="W39" s="8" t="n">
-        <v>6</v>
-      </c>
+      <c r="W39" s="8" t="n"/>
       <c r="X39" s="8" t="n"/>
       <c r="Y39" s="8" t="n"/>
       <c r="Z39" s="8" t="n"/>
@@ -3570,58 +4142,72 @@
     </row>
     <row r="40">
       <c r="A40" s="8" t="n"/>
-      <c r="B40" s="8" t="n">
-        <v>29</v>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing 90 mm oxidised M.S. hasp and staple (safety type) with necessary screws etc. complete.</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="inlineStr"/>
+          <t>Providing and fixing 90 mm oxidised M.S. hasp and staple (safety type) with necessaary screws etc. complete.</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr"/>
-      <c r="I40" s="8" t="n"/>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>Mild steel</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>Mild steel</t>
+        </is>
+      </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
           <t>Steel</t>
         </is>
       </c>
-      <c r="K40" s="8" t="n"/>
+      <c r="K40" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L40" s="8" t="n"/>
       <c r="M40" s="8" t="n"/>
-      <c r="N40" s="8" t="n"/>
+      <c r="N40" s="17" t="n">
+        <v>2</v>
+      </c>
       <c r="O40" s="8" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P40" s="8" t="n"/>
       <c r="Q40" s="8" t="n"/>
       <c r="R40" s="8" t="n"/>
       <c r="S40" s="8" t="n"/>
-      <c r="T40" s="8" t="n"/>
+      <c r="T40" s="17" t="n">
+        <v>2</v>
+      </c>
       <c r="U40" s="8" t="n"/>
       <c r="V40" s="8" t="n"/>
-      <c r="W40" s="8" t="n">
-        <v>2</v>
-      </c>
+      <c r="W40" s="8" t="n"/>
       <c r="X40" s="8" t="n"/>
       <c r="Y40" s="8" t="n"/>
       <c r="Z40" s="8" t="n"/>
       <c r="AA40" s="8" t="n"/>
-      <c r="AB40" s="8" t="n"/>
-      <c r="AC40" s="8" t="inlineStr">
+      <c r="AB40" s="8" t="inlineStr">
         <is>
           <t>9.127.3</t>
         </is>
       </c>
+      <c r="AC40" s="8" t="n"/>
       <c r="AD40" s="8" t="n"/>
       <c r="AE40" s="8" t="n"/>
       <c r="AF40" s="8" t="n"/>
@@ -3646,8 +4232,10 @@
     </row>
     <row r="41">
       <c r="A41" s="8" t="n"/>
-      <c r="B41" s="8" t="n">
-        <v>30</v>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="n"/>
@@ -3656,48 +4244,60 @@
           <t>Providing and fixing aluminium sliding door bolts 300 x 16 mm anodised transparent or dyed to required colour or shade with nuts and screws etc. complete.</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr"/>
+      <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr"/>
-      <c r="I41" s="8" t="n"/>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K41" s="8" t="n"/>
+      <c r="K41" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L41" s="8" t="n"/>
       <c r="M41" s="8" t="n"/>
-      <c r="N41" s="8" t="n"/>
+      <c r="N41" s="17" t="n">
+        <v>10</v>
+      </c>
       <c r="O41" s="8" t="inlineStr">
         <is>
-          <t>Each</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P41" s="8" t="n"/>
       <c r="Q41" s="8" t="n"/>
       <c r="R41" s="8" t="n"/>
       <c r="S41" s="8" t="n"/>
-      <c r="T41" s="8" t="n"/>
+      <c r="T41" s="17" t="n">
+        <v>10</v>
+      </c>
       <c r="U41" s="8" t="n"/>
       <c r="V41" s="8" t="n"/>
-      <c r="W41" s="8" t="n">
-        <v>10</v>
-      </c>
+      <c r="W41" s="8" t="n"/>
       <c r="X41" s="8" t="n"/>
       <c r="Y41" s="8" t="n"/>
       <c r="Z41" s="8" t="n"/>
       <c r="AA41" s="8" t="n"/>
-      <c r="AB41" s="8" t="n"/>
-      <c r="AC41" s="8" t="inlineStr">
+      <c r="AB41" s="8" t="inlineStr">
         <is>
           <t>9.218.1</t>
         </is>
       </c>
+      <c r="AC41" s="8" t="n"/>
       <c r="AD41" s="8" t="n"/>
       <c r="AE41" s="8" t="n"/>
       <c r="AF41" s="8" t="n"/>
@@ -3714,7 +4314,9 @@
       <c r="AQ41" s="8" t="n"/>
       <c r="AR41" s="8" t="n"/>
       <c r="AS41" s="8" t="n"/>
-      <c r="AT41" s="8" t="n"/>
+      <c r="AT41" s="17" t="n">
+        <v>16</v>
+      </c>
       <c r="AU41" s="8" t="n"/>
       <c r="AV41" s="8" t="n"/>
       <c r="AW41" s="8" t="n"/>
@@ -3724,58 +4326,70 @@
       <c r="A42" s="8" t="n"/>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>31a</t>
+          <t>31i</t>
         </is>
       </c>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. i) 200 x 10 mm</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr"/>
+          <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 200 x 10 mm</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr"/>
-      <c r="I42" s="8" t="n"/>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K42" s="8" t="n"/>
+      <c r="K42" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L42" s="8" t="n"/>
       <c r="M42" s="8" t="n"/>
-      <c r="N42" s="8" t="n"/>
+      <c r="N42" s="17" t="n">
+        <v>10</v>
+      </c>
       <c r="O42" s="8" t="inlineStr">
         <is>
-          <t>Each</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P42" s="8" t="n"/>
       <c r="Q42" s="8" t="n"/>
       <c r="R42" s="8" t="n"/>
       <c r="S42" s="8" t="n"/>
-      <c r="T42" s="8" t="n"/>
+      <c r="T42" s="17" t="n">
+        <v>10</v>
+      </c>
       <c r="U42" s="8" t="n"/>
       <c r="V42" s="8" t="n"/>
-      <c r="W42" s="8" t="n">
-        <v>10</v>
-      </c>
+      <c r="W42" s="8" t="n"/>
       <c r="X42" s="8" t="n"/>
       <c r="Y42" s="8" t="n"/>
       <c r="Z42" s="8" t="n"/>
       <c r="AA42" s="8" t="n"/>
-      <c r="AB42" s="8" t="n"/>
-      <c r="AC42" s="8" t="inlineStr">
+      <c r="AB42" s="8" t="inlineStr">
         <is>
           <t>9.219.3</t>
         </is>
       </c>
+      <c r="AC42" s="8" t="n"/>
       <c r="AD42" s="8" t="n"/>
       <c r="AE42" s="8" t="n"/>
       <c r="AF42" s="8" t="n"/>
@@ -3792,7 +4406,9 @@
       <c r="AQ42" s="8" t="n"/>
       <c r="AR42" s="8" t="n"/>
       <c r="AS42" s="8" t="n"/>
-      <c r="AT42" s="8" t="n"/>
+      <c r="AT42" s="17" t="n">
+        <v>10</v>
+      </c>
       <c r="AU42" s="8" t="n"/>
       <c r="AV42" s="8" t="n"/>
       <c r="AW42" s="8" t="n"/>
@@ -3802,58 +4418,70 @@
       <c r="A43" s="8" t="n"/>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>31b</t>
+          <t>31ii</t>
         </is>
       </c>
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. ii) 100 x 10 mm</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr"/>
+          <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 100 x 10 mm</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr"/>
-      <c r="I43" s="8" t="n"/>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K43" s="8" t="n"/>
+      <c r="K43" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L43" s="8" t="n"/>
       <c r="M43" s="8" t="n"/>
-      <c r="N43" s="8" t="n"/>
+      <c r="N43" s="17" t="n">
+        <v>8</v>
+      </c>
       <c r="O43" s="8" t="inlineStr">
         <is>
-          <t>Each</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P43" s="8" t="n"/>
       <c r="Q43" s="8" t="n"/>
       <c r="R43" s="8" t="n"/>
       <c r="S43" s="8" t="n"/>
-      <c r="T43" s="8" t="n"/>
+      <c r="T43" s="17" t="n">
+        <v>8</v>
+      </c>
       <c r="U43" s="8" t="n"/>
       <c r="V43" s="8" t="n"/>
-      <c r="W43" s="8" t="n">
-        <v>8</v>
-      </c>
+      <c r="W43" s="8" t="n"/>
       <c r="X43" s="8" t="n"/>
       <c r="Y43" s="8" t="n"/>
       <c r="Z43" s="8" t="n"/>
       <c r="AA43" s="8" t="n"/>
-      <c r="AB43" s="8" t="n"/>
-      <c r="AC43" s="8" t="inlineStr">
+      <c r="AB43" s="8" t="inlineStr">
         <is>
           <t>9.219.5</t>
         </is>
       </c>
+      <c r="AC43" s="8" t="n"/>
       <c r="AD43" s="8" t="n"/>
       <c r="AE43" s="8" t="n"/>
       <c r="AF43" s="8" t="n"/>
@@ -3870,7 +4498,9 @@
       <c r="AQ43" s="8" t="n"/>
       <c r="AR43" s="8" t="n"/>
       <c r="AS43" s="8" t="n"/>
-      <c r="AT43" s="8" t="n"/>
+      <c r="AT43" s="17" t="n">
+        <v>10</v>
+      </c>
       <c r="AU43" s="8" t="n"/>
       <c r="AV43" s="8" t="n"/>
       <c r="AW43" s="8" t="n"/>
@@ -3880,58 +4510,70 @@
       <c r="A44" s="8" t="n"/>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>32a</t>
+          <t>32i</t>
         </is>
       </c>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. i) 100 mm</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr"/>
+          <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 100 mm</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr"/>
-      <c r="I44" s="8" t="n"/>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K44" s="8" t="n"/>
+      <c r="K44" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L44" s="8" t="n"/>
       <c r="M44" s="8" t="n"/>
-      <c r="N44" s="8" t="n"/>
+      <c r="N44" s="17" t="n">
+        <v>20</v>
+      </c>
       <c r="O44" s="8" t="inlineStr">
         <is>
-          <t>Each</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P44" s="8" t="n"/>
       <c r="Q44" s="8" t="n"/>
       <c r="R44" s="8" t="n"/>
       <c r="S44" s="8" t="n"/>
-      <c r="T44" s="8" t="n"/>
+      <c r="T44" s="17" t="n">
+        <v>20</v>
+      </c>
       <c r="U44" s="8" t="n"/>
       <c r="V44" s="8" t="n"/>
-      <c r="W44" s="8" t="n">
-        <v>20</v>
-      </c>
+      <c r="W44" s="8" t="n"/>
       <c r="X44" s="8" t="n"/>
       <c r="Y44" s="8" t="n"/>
       <c r="Z44" s="8" t="n"/>
       <c r="AA44" s="8" t="n"/>
-      <c r="AB44" s="8" t="n"/>
-      <c r="AC44" s="8" t="inlineStr">
+      <c r="AB44" s="8" t="inlineStr">
         <is>
           <t>9.222.2</t>
         </is>
       </c>
+      <c r="AC44" s="8" t="n"/>
       <c r="AD44" s="8" t="n"/>
       <c r="AE44" s="8" t="n"/>
       <c r="AF44" s="8" t="n"/>
@@ -3958,58 +4600,70 @@
       <c r="A45" s="8" t="n"/>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>32b</t>
+          <t>32ii</t>
         </is>
       </c>
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. ii) 75 mm</t>
-        </is>
-      </c>
-      <c r="F45" s="8" t="inlineStr"/>
+          <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 75 mm</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr"/>
-      <c r="I45" s="8" t="n"/>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K45" s="8" t="n"/>
+      <c r="K45" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L45" s="8" t="n"/>
       <c r="M45" s="8" t="n"/>
-      <c r="N45" s="8" t="n"/>
+      <c r="N45" s="17" t="n">
+        <v>4</v>
+      </c>
       <c r="O45" s="8" t="inlineStr">
         <is>
-          <t>Each</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P45" s="8" t="n"/>
       <c r="Q45" s="8" t="n"/>
       <c r="R45" s="8" t="n"/>
       <c r="S45" s="8" t="n"/>
-      <c r="T45" s="8" t="n"/>
+      <c r="T45" s="17" t="n">
+        <v>4</v>
+      </c>
       <c r="U45" s="8" t="n"/>
       <c r="V45" s="8" t="n"/>
-      <c r="W45" s="8" t="n">
-        <v>4</v>
-      </c>
+      <c r="W45" s="8" t="n"/>
       <c r="X45" s="8" t="n"/>
       <c r="Y45" s="8" t="n"/>
       <c r="Z45" s="8" t="n"/>
       <c r="AA45" s="8" t="n"/>
-      <c r="AB45" s="8" t="n"/>
-      <c r="AC45" s="8" t="inlineStr">
+      <c r="AB45" s="8" t="inlineStr">
         <is>
           <t>9.222.3</t>
         </is>
       </c>
+      <c r="AC45" s="8" t="n"/>
       <c r="AD45" s="8" t="n"/>
       <c r="AE45" s="8" t="n"/>
       <c r="AF45" s="8" t="n"/>
@@ -4034,8 +4688,10 @@
     </row>
     <row r="46">
       <c r="A46" s="8" t="n"/>
-      <c r="B46" s="8" t="n">
-        <v>33</v>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="C46" s="8" t="n"/>
       <c r="D46" s="8" t="n"/>
@@ -4044,46 +4700,60 @@
           <t>Providing and fixing aluminium hanging floor door stopper anodised transparent or dyed to required colour &amp; shade with necessary screws etc. complete.</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr"/>
+      <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H46" s="8" t="inlineStr"/>
-      <c r="I46" s="8" t="n"/>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K46" s="8" t="n"/>
+      <c r="K46" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L46" s="8" t="n"/>
       <c r="M46" s="8" t="n"/>
-      <c r="N46" s="8" t="n"/>
+      <c r="N46" s="17" t="n">
+        <v>10</v>
+      </c>
       <c r="O46" s="8" t="inlineStr">
         <is>
-          <t>Each</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P46" s="8" t="n"/>
       <c r="Q46" s="8" t="n"/>
       <c r="R46" s="8" t="n"/>
       <c r="S46" s="8" t="n"/>
-      <c r="T46" s="8" t="n"/>
+      <c r="T46" s="17" t="n">
+        <v>10</v>
+      </c>
       <c r="U46" s="8" t="n"/>
       <c r="V46" s="8" t="n"/>
-      <c r="W46" s="8" t="n">
-        <v>10</v>
-      </c>
+      <c r="W46" s="8" t="n"/>
       <c r="X46" s="8" t="n"/>
       <c r="Y46" s="8" t="n"/>
       <c r="Z46" s="8" t="n"/>
       <c r="AA46" s="8" t="n"/>
-      <c r="AB46" s="8" t="n"/>
-      <c r="AC46" s="8" t="n">
-        <v>9.223000000000001</v>
-      </c>
+      <c r="AB46" s="8" t="inlineStr">
+        <is>
+          <t>9.223</t>
+        </is>
+      </c>
+      <c r="AC46" s="8" t="n"/>
       <c r="AD46" s="8" t="n"/>
       <c r="AE46" s="8" t="n"/>
       <c r="AF46" s="8" t="n"/>
@@ -4110,58 +4780,74 @@
       <c r="A47" s="8" t="n"/>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>34a</t>
+          <t>34i</t>
         </is>
       </c>
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. i) Windows - side hung</t>
-        </is>
-      </c>
-      <c r="F47" s="8" t="inlineStr"/>
+          <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. Windows - side hung</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H47" s="8" t="inlineStr"/>
-      <c r="I47" s="8" t="n"/>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>Steel, Cement, Coarse sand, Graded stone aggregate, Glass</t>
+        </is>
+      </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
           <t>Steel</t>
         </is>
       </c>
-      <c r="K47" s="8" t="n"/>
+      <c r="K47" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L47" s="8" t="n"/>
-      <c r="M47" s="8" t="n"/>
-      <c r="N47" s="8" t="n"/>
+      <c r="M47" s="8" t="inlineStr">
+        <is>
+          <t>1:3:6</t>
+        </is>
+      </c>
+      <c r="N47" s="17" t="n">
+        <v>11.3</v>
+      </c>
       <c r="O47" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P47" s="8" t="n"/>
-      <c r="Q47" s="8" t="n"/>
+      <c r="Q47" s="17" t="n">
+        <v>11.3</v>
+      </c>
       <c r="R47" s="8" t="n"/>
       <c r="S47" s="8" t="n"/>
       <c r="T47" s="8" t="n"/>
       <c r="U47" s="8" t="n"/>
       <c r="V47" s="8" t="n"/>
-      <c r="W47" s="8" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="W47" s="8" t="n"/>
       <c r="X47" s="8" t="n"/>
       <c r="Y47" s="8" t="n"/>
       <c r="Z47" s="8" t="n"/>
       <c r="AA47" s="8" t="n"/>
-      <c r="AB47" s="8" t="n"/>
-      <c r="AC47" s="8" t="inlineStr">
+      <c r="AB47" s="8" t="inlineStr">
         <is>
           <t>N.S.I.</t>
         </is>
       </c>
+      <c r="AC47" s="8" t="n"/>
       <c r="AD47" s="8" t="n"/>
       <c r="AE47" s="8" t="n"/>
       <c r="AF47" s="8" t="n"/>
@@ -4176,7 +4862,9 @@
       <c r="AO47" s="8" t="n"/>
       <c r="AP47" s="8" t="n"/>
       <c r="AQ47" s="8" t="n"/>
-      <c r="AR47" s="8" t="n"/>
+      <c r="AR47" s="17" t="n">
+        <v>3</v>
+      </c>
       <c r="AS47" s="8" t="n"/>
       <c r="AT47" s="8" t="n"/>
       <c r="AU47" s="8" t="n"/>
@@ -4188,58 +4876,74 @@
       <c r="A48" s="8" t="n"/>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>34b</t>
+          <t>34ii</t>
         </is>
       </c>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="n"/>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. ii) Ventilators - centre hung</t>
-        </is>
-      </c>
-      <c r="F48" s="8" t="inlineStr"/>
+          <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. Ventilators - centre hung</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr"/>
-      <c r="I48" s="8" t="n"/>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>Steel, Cement, Coarse sand, Graded stone aggregate, Glass</t>
+        </is>
+      </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
           <t>Steel</t>
         </is>
       </c>
-      <c r="K48" s="8" t="n"/>
+      <c r="K48" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L48" s="8" t="n"/>
-      <c r="M48" s="8" t="n"/>
-      <c r="N48" s="8" t="n"/>
+      <c r="M48" s="8" t="inlineStr">
+        <is>
+          <t>1:3:6</t>
+        </is>
+      </c>
+      <c r="N48" s="17" t="n">
+        <v>1</v>
+      </c>
       <c r="O48" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P48" s="8" t="n"/>
-      <c r="Q48" s="8" t="n"/>
+      <c r="Q48" s="17" t="n">
+        <v>1</v>
+      </c>
       <c r="R48" s="8" t="n"/>
       <c r="S48" s="8" t="n"/>
       <c r="T48" s="8" t="n"/>
       <c r="U48" s="8" t="n"/>
       <c r="V48" s="8" t="n"/>
-      <c r="W48" s="8" t="n">
-        <v>1</v>
-      </c>
+      <c r="W48" s="8" t="n"/>
       <c r="X48" s="8" t="n"/>
       <c r="Y48" s="8" t="n"/>
       <c r="Z48" s="8" t="n"/>
       <c r="AA48" s="8" t="n"/>
-      <c r="AB48" s="8" t="n"/>
-      <c r="AC48" s="8" t="inlineStr">
+      <c r="AB48" s="8" t="inlineStr">
         <is>
           <t>N.S.I.</t>
         </is>
       </c>
+      <c r="AC48" s="8" t="n"/>
       <c r="AD48" s="8" t="n"/>
       <c r="AE48" s="8" t="n"/>
       <c r="AF48" s="8" t="n"/>
@@ -4254,7 +4958,9 @@
       <c r="AO48" s="8" t="n"/>
       <c r="AP48" s="8" t="n"/>
       <c r="AQ48" s="8" t="n"/>
-      <c r="AR48" s="8" t="n"/>
+      <c r="AR48" s="17" t="n">
+        <v>3</v>
+      </c>
       <c r="AS48" s="8" t="n"/>
       <c r="AT48" s="8" t="n"/>
       <c r="AU48" s="8" t="n"/>
@@ -4264,8 +4970,10 @@
     </row>
     <row r="49">
       <c r="A49" s="8" t="n"/>
-      <c r="B49" s="8" t="n">
-        <v>35</v>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="n"/>
@@ -4274,48 +4982,60 @@
           <t>Providing and fixing oxidised mild steel casement window fastners of minimum weight 200 grams to side hung steel windows with necessary welding and machine screws etc. complete.</t>
         </is>
       </c>
-      <c r="F49" s="8" t="inlineStr"/>
+      <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr"/>
-      <c r="I49" s="8" t="n"/>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>Mild steel</t>
+        </is>
+      </c>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>Mild steel</t>
+        </is>
+      </c>
       <c r="J49" s="8" t="inlineStr">
         <is>
           <t>Steel</t>
         </is>
       </c>
-      <c r="K49" s="8" t="n"/>
+      <c r="K49" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L49" s="8" t="n"/>
       <c r="M49" s="8" t="n"/>
-      <c r="N49" s="8" t="n"/>
+      <c r="N49" s="17" t="n">
+        <v>21</v>
+      </c>
       <c r="O49" s="8" t="inlineStr">
         <is>
-          <t>Each</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P49" s="8" t="n"/>
       <c r="Q49" s="8" t="n"/>
       <c r="R49" s="8" t="n"/>
       <c r="S49" s="8" t="n"/>
-      <c r="T49" s="8" t="n"/>
+      <c r="T49" s="17" t="n">
+        <v>21</v>
+      </c>
       <c r="U49" s="8" t="n"/>
       <c r="V49" s="8" t="n"/>
-      <c r="W49" s="8" t="n">
-        <v>21</v>
-      </c>
+      <c r="W49" s="8" t="n"/>
       <c r="X49" s="8" t="n"/>
       <c r="Y49" s="8" t="n"/>
       <c r="Z49" s="8" t="n"/>
       <c r="AA49" s="8" t="n"/>
-      <c r="AB49" s="8" t="n"/>
-      <c r="AC49" s="8" t="inlineStr">
+      <c r="AB49" s="8" t="inlineStr">
         <is>
           <t>N.S.I.</t>
         </is>
       </c>
+      <c r="AC49" s="8" t="n"/>
       <c r="AD49" s="8" t="n"/>
       <c r="AE49" s="8" t="n"/>
       <c r="AF49" s="8" t="n"/>
@@ -4340,56 +5060,72 @@
     </row>
     <row r="50">
       <c r="A50" s="8" t="n"/>
-      <c r="B50" s="8" t="n">
-        <v>36</v>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium casement stays anodised transparent or dyed to required colour and shade with with necessary welding and machine screws etc. complete.</t>
-        </is>
-      </c>
-      <c r="F50" s="8" t="inlineStr"/>
+          <t>Providing and fixing aluminium casement stays anodised transparent or dyed to requird colour and shade with with necessary welding and machine screws etc. complete.</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H50" s="8" t="inlineStr"/>
-      <c r="I50" s="8" t="n"/>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K50" s="8" t="n"/>
+      <c r="K50" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L50" s="8" t="n"/>
       <c r="M50" s="8" t="n"/>
-      <c r="N50" s="8" t="n"/>
+      <c r="N50" s="17" t="n">
+        <v>21</v>
+      </c>
       <c r="O50" s="8" t="inlineStr">
         <is>
-          <t>Each</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P50" s="8" t="n"/>
       <c r="Q50" s="8" t="n"/>
       <c r="R50" s="8" t="n"/>
       <c r="S50" s="8" t="n"/>
-      <c r="T50" s="8" t="n"/>
+      <c r="T50" s="17" t="n">
+        <v>21</v>
+      </c>
       <c r="U50" s="8" t="n"/>
       <c r="V50" s="8" t="n"/>
-      <c r="W50" s="8" t="n">
-        <v>21</v>
-      </c>
+      <c r="W50" s="8" t="n"/>
       <c r="X50" s="8" t="n"/>
       <c r="Y50" s="8" t="n"/>
       <c r="Z50" s="8" t="n"/>
       <c r="AA50" s="8" t="n"/>
-      <c r="AB50" s="8" t="n"/>
-      <c r="AC50" s="8" t="n">
-        <v>9.224</v>
-      </c>
+      <c r="AB50" s="8" t="inlineStr">
+        <is>
+          <t>9.224</t>
+        </is>
+      </c>
+      <c r="AC50" s="8" t="n"/>
       <c r="AD50" s="8" t="n"/>
       <c r="AE50" s="8" t="n"/>
       <c r="AF50" s="8" t="n"/>
@@ -4414,58 +5150,72 @@
     </row>
     <row r="51">
       <c r="A51" s="8" t="n"/>
-      <c r="B51" s="8" t="n">
-        <v>37</v>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>Providing and welding 20x4 mm M S Guard Flats 10cm c/c in steel windows of standard rolled steel section including a coat of steel peimer as per drawing and specification complete in all respect.</t>
-        </is>
-      </c>
-      <c r="F51" s="8" t="inlineStr"/>
+          <t>Providing and welding 20x4 mm M S Guard Flats 10cm c/c in steel windows of standard rolled steel section including a coat of steel primer as per drawing and specification complete in all respect.</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H51" s="8" t="inlineStr"/>
-      <c r="I51" s="8" t="n"/>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>Mild steel</t>
+        </is>
+      </c>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>Mild steel, Steel primer</t>
+        </is>
+      </c>
       <c r="J51" s="8" t="inlineStr">
         <is>
           <t>Steel</t>
         </is>
       </c>
-      <c r="K51" s="8" t="n"/>
+      <c r="K51" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L51" s="8" t="n"/>
       <c r="M51" s="8" t="n"/>
-      <c r="N51" s="8" t="n"/>
+      <c r="N51" s="17" t="n">
+        <v>66</v>
+      </c>
       <c r="O51" s="8" t="inlineStr">
         <is>
-          <t>Kg.</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="P51" s="8" t="n"/>
       <c r="Q51" s="8" t="n"/>
       <c r="R51" s="8" t="n"/>
-      <c r="S51" s="8" t="n"/>
+      <c r="S51" s="17" t="n">
+        <v>66</v>
+      </c>
       <c r="T51" s="8" t="n"/>
       <c r="U51" s="8" t="n"/>
       <c r="V51" s="8" t="n"/>
-      <c r="W51" s="8" t="n">
-        <v>66</v>
-      </c>
+      <c r="W51" s="8" t="n"/>
       <c r="X51" s="8" t="n"/>
       <c r="Y51" s="8" t="n"/>
       <c r="Z51" s="8" t="n"/>
       <c r="AA51" s="8" t="n"/>
-      <c r="AB51" s="8" t="n"/>
-      <c r="AC51" s="8" t="inlineStr">
+      <c r="AB51" s="8" t="inlineStr">
         <is>
           <t>N.S.I.</t>
         </is>
       </c>
+      <c r="AC51" s="8" t="n"/>
       <c r="AD51" s="8" t="n"/>
       <c r="AE51" s="8" t="n"/>
       <c r="AF51" s="8" t="n"/>
@@ -4480,7 +5230,9 @@
       <c r="AO51" s="8" t="n"/>
       <c r="AP51" s="8" t="n"/>
       <c r="AQ51" s="8" t="n"/>
-      <c r="AR51" s="8" t="n"/>
+      <c r="AR51" s="17" t="n">
+        <v>4</v>
+      </c>
       <c r="AS51" s="8" t="n"/>
       <c r="AT51" s="8" t="n"/>
       <c r="AU51" s="8" t="n"/>
@@ -4490,8 +5242,10 @@
     </row>
     <row r="52">
       <c r="A52" s="8" t="n"/>
-      <c r="B52" s="8" t="n">
-        <v>38</v>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
       <c r="C52" s="8" t="n"/>
       <c r="D52" s="8" t="n"/>
@@ -4500,46 +5254,64 @@
           <t>Providing and fixing T - Iron frames for doors, windows and ventilators of mild steel Tee - sections, joints mitred and welded with 15x3 mm lugs 10 cm long embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including fixing of necessary butt hinges and screws and applying a priming coat of approved steel primer.</t>
         </is>
       </c>
-      <c r="F52" s="8" t="inlineStr"/>
+      <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr"/>
-      <c r="I52" s="8" t="n"/>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>Mild steel</t>
+        </is>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>Mild steel, Cement, Coarse sand, Graded stone aggregate</t>
+        </is>
+      </c>
       <c r="J52" s="8" t="inlineStr">
         <is>
           <t>Steel</t>
         </is>
       </c>
-      <c r="K52" s="8" t="n"/>
+      <c r="K52" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L52" s="8" t="n"/>
-      <c r="M52" s="8" t="n"/>
-      <c r="N52" s="8" t="n"/>
+      <c r="M52" s="8" t="inlineStr">
+        <is>
+          <t>1:3:6</t>
+        </is>
+      </c>
+      <c r="N52" s="17" t="n">
+        <v>187</v>
+      </c>
       <c r="O52" s="8" t="inlineStr">
         <is>
-          <t>Kg.</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="P52" s="8" t="n"/>
       <c r="Q52" s="8" t="n"/>
       <c r="R52" s="8" t="n"/>
-      <c r="S52" s="8" t="n"/>
+      <c r="S52" s="17" t="n">
+        <v>187</v>
+      </c>
       <c r="T52" s="8" t="n"/>
       <c r="U52" s="8" t="n"/>
       <c r="V52" s="8" t="n"/>
-      <c r="W52" s="8" t="n">
-        <v>187</v>
-      </c>
+      <c r="W52" s="8" t="n"/>
       <c r="X52" s="8" t="n"/>
       <c r="Y52" s="8" t="n"/>
       <c r="Z52" s="8" t="n"/>
       <c r="AA52" s="8" t="n"/>
-      <c r="AB52" s="8" t="n"/>
-      <c r="AC52" s="8" t="n">
-        <v>10.14</v>
-      </c>
+      <c r="AB52" s="8" t="inlineStr">
+        <is>
+          <t>10.14</t>
+        </is>
+      </c>
+      <c r="AC52" s="8" t="n"/>
       <c r="AD52" s="8" t="n"/>
       <c r="AE52" s="8" t="n"/>
       <c r="AF52" s="8" t="n"/>
@@ -4564,8 +5336,10 @@
     </row>
     <row r="53">
       <c r="A53" s="8" t="n"/>
-      <c r="B53" s="8" t="n">
-        <v>39</v>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
       </c>
       <c r="C53" s="8" t="n"/>
       <c r="D53" s="8" t="n"/>
@@ -4574,46 +5348,60 @@
           <t>Providing and fixing MS fan clamp type I of 16 mm dia MS bar bent to shape with hooked ends in RCC slabs during laying including painting the exposed portion of loop, all as per standard design complete.</t>
         </is>
       </c>
-      <c r="F53" s="8" t="inlineStr"/>
+      <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
       </c>
-      <c r="H53" s="8" t="inlineStr"/>
-      <c r="I53" s="8" t="n"/>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>Mild steel</t>
+        </is>
+      </c>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>Mild steel</t>
+        </is>
+      </c>
       <c r="J53" s="8" t="inlineStr">
         <is>
           <t>Steel</t>
         </is>
       </c>
-      <c r="K53" s="8" t="n"/>
+      <c r="K53" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L53" s="8" t="n"/>
       <c r="M53" s="8" t="n"/>
-      <c r="N53" s="8" t="n"/>
+      <c r="N53" s="17" t="n">
+        <v>5</v>
+      </c>
       <c r="O53" s="8" t="inlineStr">
         <is>
-          <t>Each</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P53" s="8" t="n"/>
       <c r="Q53" s="8" t="n"/>
       <c r="R53" s="8" t="n"/>
       <c r="S53" s="8" t="n"/>
-      <c r="T53" s="8" t="n"/>
+      <c r="T53" s="17" t="n">
+        <v>5</v>
+      </c>
       <c r="U53" s="8" t="n"/>
       <c r="V53" s="8" t="n"/>
-      <c r="W53" s="8" t="n">
-        <v>5</v>
-      </c>
+      <c r="W53" s="8" t="n"/>
       <c r="X53" s="8" t="n"/>
       <c r="Y53" s="8" t="n"/>
       <c r="Z53" s="8" t="n"/>
       <c r="AA53" s="8" t="n"/>
-      <c r="AB53" s="8" t="n"/>
-      <c r="AC53" s="8" t="n">
-        <v>10.19</v>
-      </c>
+      <c r="AB53" s="8" t="inlineStr">
+        <is>
+          <t>10.19</t>
+        </is>
+      </c>
+      <c r="AC53" s="8" t="n"/>
       <c r="AD53" s="8" t="n"/>
       <c r="AE53" s="8" t="n"/>
       <c r="AF53" s="8" t="n"/>
@@ -4630,7 +5418,9 @@
       <c r="AQ53" s="8" t="n"/>
       <c r="AR53" s="8" t="n"/>
       <c r="AS53" s="8" t="n"/>
-      <c r="AT53" s="8" t="n"/>
+      <c r="AT53" s="17" t="n">
+        <v>16</v>
+      </c>
       <c r="AU53" s="8" t="n"/>
       <c r="AV53" s="8" t="n"/>
       <c r="AW53" s="8" t="n"/>
@@ -4638,8 +5428,10 @@
     </row>
     <row r="54">
       <c r="A54" s="8" t="n"/>
-      <c r="B54" s="8" t="n">
-        <v>40</v>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="8" t="n"/>
@@ -4648,48 +5440,64 @@
           <t>40 mm thick cement concrete flooring 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20.0 mm nominal size) finished with a floating coat of neat cement including cement slurry, rounding off edges and strips etc. but excluding the cost of nosing of steps etc. complete.</t>
         </is>
       </c>
-      <c r="F54" s="8" t="inlineStr"/>
+      <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H54" s="8" t="inlineStr"/>
-      <c r="I54" s="8" t="n"/>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>Cement concrete</t>
+        </is>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
+        </is>
+      </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K54" s="8" t="n"/>
+      <c r="K54" s="17" t="n">
+        <v>0.98</v>
+      </c>
       <c r="L54" s="8" t="n"/>
-      <c r="M54" s="8" t="n"/>
-      <c r="N54" s="8" t="n"/>
+      <c r="M54" s="8" t="inlineStr">
+        <is>
+          <t>1:2:4</t>
+        </is>
+      </c>
+      <c r="N54" s="17" t="n">
+        <v>68</v>
+      </c>
       <c r="O54" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P54" s="8" t="n"/>
-      <c r="Q54" s="8" t="n"/>
+      <c r="Q54" s="17" t="n">
+        <v>68</v>
+      </c>
       <c r="R54" s="8" t="n"/>
       <c r="S54" s="8" t="n"/>
       <c r="T54" s="8" t="n"/>
       <c r="U54" s="8" t="n"/>
       <c r="V54" s="8" t="n"/>
-      <c r="W54" s="8" t="n">
-        <v>68</v>
-      </c>
+      <c r="W54" s="8" t="n"/>
       <c r="X54" s="8" t="n"/>
       <c r="Y54" s="8" t="n"/>
       <c r="Z54" s="8" t="n"/>
       <c r="AA54" s="8" t="n"/>
-      <c r="AB54" s="8" t="n"/>
-      <c r="AC54" s="8" t="inlineStr">
+      <c r="AB54" s="8" t="inlineStr">
         <is>
           <t>11.4.2</t>
         </is>
       </c>
+      <c r="AC54" s="8" t="n"/>
       <c r="AD54" s="8" t="n"/>
       <c r="AE54" s="8" t="n"/>
       <c r="AF54" s="8" t="n"/>
@@ -4704,7 +5512,9 @@
       <c r="AO54" s="8" t="n"/>
       <c r="AP54" s="8" t="n"/>
       <c r="AQ54" s="8" t="n"/>
-      <c r="AR54" s="8" t="n"/>
+      <c r="AR54" s="17" t="n">
+        <v>40</v>
+      </c>
       <c r="AS54" s="8" t="n"/>
       <c r="AT54" s="8" t="n"/>
       <c r="AU54" s="8" t="n"/>
@@ -4714,8 +5524,10 @@
     </row>
     <row r="55">
       <c r="A55" s="8" t="n"/>
-      <c r="B55" s="8" t="n">
-        <v>41</v>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
@@ -4724,48 +5536,64 @@
           <t>18 mm thick cement plaster skirting (upto 30 cm height) with cement mortar 1:3 (1 cement : 3 coarse sand) finished with a floating coat of neat cement including rounding of junctions with floors.</t>
         </is>
       </c>
-      <c r="F55" s="8" t="inlineStr"/>
+      <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H55" s="8" t="inlineStr"/>
-      <c r="I55" s="8" t="n"/>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>Cement plaster</t>
+        </is>
+      </c>
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>Cement, Coarse sand</t>
+        </is>
+      </c>
       <c r="J55" s="8" t="inlineStr">
         <is>
           <t>Paint/Finish</t>
         </is>
       </c>
-      <c r="K55" s="8" t="n"/>
+      <c r="K55" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L55" s="8" t="n"/>
-      <c r="M55" s="8" t="n"/>
-      <c r="N55" s="8" t="n"/>
+      <c r="M55" s="8" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="N55" s="17" t="n">
+        <v>11</v>
+      </c>
       <c r="O55" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P55" s="8" t="n"/>
-      <c r="Q55" s="8" t="n"/>
+      <c r="Q55" s="17" t="n">
+        <v>11</v>
+      </c>
       <c r="R55" s="8" t="n"/>
       <c r="S55" s="8" t="n"/>
       <c r="T55" s="8" t="n"/>
       <c r="U55" s="8" t="n"/>
       <c r="V55" s="8" t="n"/>
-      <c r="W55" s="8" t="n">
-        <v>11</v>
-      </c>
+      <c r="W55" s="8" t="n"/>
       <c r="X55" s="8" t="n"/>
       <c r="Y55" s="8" t="n"/>
       <c r="Z55" s="8" t="n"/>
       <c r="AA55" s="8" t="n"/>
-      <c r="AB55" s="8" t="n"/>
-      <c r="AC55" s="8" t="inlineStr">
+      <c r="AB55" s="8" t="inlineStr">
         <is>
           <t>11.10.1</t>
         </is>
       </c>
+      <c r="AC55" s="8" t="n"/>
       <c r="AD55" s="8" t="n"/>
       <c r="AE55" s="8" t="n"/>
       <c r="AF55" s="8" t="n"/>
@@ -4780,7 +5608,9 @@
       <c r="AO55" s="8" t="n"/>
       <c r="AP55" s="8" t="n"/>
       <c r="AQ55" s="8" t="n"/>
-      <c r="AR55" s="8" t="n"/>
+      <c r="AR55" s="17" t="n">
+        <v>18</v>
+      </c>
       <c r="AS55" s="8" t="n"/>
       <c r="AT55" s="8" t="n"/>
       <c r="AU55" s="8" t="n"/>
@@ -4790,8 +5620,10 @@
     </row>
     <row r="56">
       <c r="A56" s="8" t="n"/>
-      <c r="B56" s="8" t="n">
-        <v>42</v>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="C56" s="8" t="n"/>
       <c r="D56" s="8" t="n"/>
@@ -4800,48 +5632,64 @@
           <t>40 mm thick marble chips flooring, rubbed and polished to granolithic finish, under layer 31 mm thick cement concrete 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 12.5 mm nominal size) and top layer 9 mm thick with white black, chocolate, grey yellow or Baroda green marble chips of sizes from 4 mm to 7 mm nominal size laid in cement marble powder mix 3:1 (3 cement : 1 marble powder) by weight in proportion of 4:7 (4 cement marble powder mix : 7 marble chips) by volume including cement slurry etc., complete using dark shade pigment with ordinary cement.</t>
         </is>
       </c>
-      <c r="F56" s="8" t="inlineStr"/>
+      <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H56" s="8" t="inlineStr"/>
-      <c r="I56" s="8" t="n"/>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>Marble chips</t>
+        </is>
+      </c>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>Cement, Coarse sand, Graded stone aggregate, Marble chips, Marble powder</t>
+        </is>
+      </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
           <t>Paint/Finish</t>
         </is>
       </c>
-      <c r="K56" s="8" t="n"/>
+      <c r="K56" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L56" s="8" t="n"/>
-      <c r="M56" s="8" t="n"/>
-      <c r="N56" s="8" t="n"/>
+      <c r="M56" s="8" t="inlineStr">
+        <is>
+          <t>1:2:4</t>
+        </is>
+      </c>
+      <c r="N56" s="17" t="n">
+        <v>9</v>
+      </c>
       <c r="O56" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P56" s="8" t="n"/>
-      <c r="Q56" s="8" t="n"/>
+      <c r="Q56" s="17" t="n">
+        <v>9</v>
+      </c>
       <c r="R56" s="8" t="n"/>
       <c r="S56" s="8" t="n"/>
       <c r="T56" s="8" t="n"/>
       <c r="U56" s="8" t="n"/>
       <c r="V56" s="8" t="n"/>
-      <c r="W56" s="8" t="n">
-        <v>9</v>
-      </c>
+      <c r="W56" s="8" t="n"/>
       <c r="X56" s="8" t="n"/>
       <c r="Y56" s="8" t="n"/>
       <c r="Z56" s="8" t="n"/>
       <c r="AA56" s="8" t="n"/>
-      <c r="AB56" s="8" t="n"/>
-      <c r="AC56" s="8" t="inlineStr">
+      <c r="AB56" s="8" t="inlineStr">
         <is>
           <t>11.16.1</t>
         </is>
       </c>
+      <c r="AC56" s="8" t="n"/>
       <c r="AD56" s="8" t="n"/>
       <c r="AE56" s="8" t="n"/>
       <c r="AF56" s="8" t="n"/>
@@ -4856,7 +5704,9 @@
       <c r="AO56" s="8" t="n"/>
       <c r="AP56" s="8" t="n"/>
       <c r="AQ56" s="8" t="n"/>
-      <c r="AR56" s="8" t="n"/>
+      <c r="AR56" s="17" t="n">
+        <v>40</v>
+      </c>
       <c r="AS56" s="8" t="n"/>
       <c r="AT56" s="8" t="n"/>
       <c r="AU56" s="8" t="n"/>
@@ -4866,8 +5716,10 @@
     </row>
     <row r="57">
       <c r="A57" s="8" t="n"/>
-      <c r="B57" s="8" t="n">
-        <v>43</v>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
       </c>
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="n"/>
@@ -4876,48 +5728,60 @@
           <t>Add or deduct for providing and fixing glass strips in joints of terrazzo/cement concrete floors- 40 mm wide and 6 mm thick.</t>
         </is>
       </c>
-      <c r="F57" s="8" t="inlineStr"/>
+      <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H57" s="8" t="inlineStr"/>
-      <c r="I57" s="8" t="n"/>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>Glass</t>
+        </is>
+      </c>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>Glass</t>
+        </is>
+      </c>
       <c r="J57" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish</t>
-        </is>
-      </c>
-      <c r="K57" s="8" t="n"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="K57" s="17" t="n">
+        <v>0.9</v>
+      </c>
       <c r="L57" s="8" t="n"/>
       <c r="M57" s="8" t="n"/>
-      <c r="N57" s="8" t="n"/>
+      <c r="N57" s="17" t="n">
+        <v>18</v>
+      </c>
       <c r="O57" s="8" t="inlineStr">
         <is>
-          <t>Mtr.</t>
+          <t>m</t>
         </is>
       </c>
       <c r="P57" s="8" t="n"/>
       <c r="Q57" s="8" t="n"/>
-      <c r="R57" s="8" t="n"/>
+      <c r="R57" s="17" t="n">
+        <v>18</v>
+      </c>
       <c r="S57" s="8" t="n"/>
       <c r="T57" s="8" t="n"/>
       <c r="U57" s="8" t="n"/>
       <c r="V57" s="8" t="n"/>
-      <c r="W57" s="8" t="n">
-        <v>18</v>
-      </c>
+      <c r="W57" s="8" t="n"/>
       <c r="X57" s="8" t="n"/>
       <c r="Y57" s="8" t="n"/>
       <c r="Z57" s="8" t="n"/>
       <c r="AA57" s="8" t="n"/>
-      <c r="AB57" s="8" t="n"/>
-      <c r="AC57" s="8" t="inlineStr">
+      <c r="AB57" s="8" t="inlineStr">
         <is>
           <t>11.20.2</t>
         </is>
       </c>
+      <c r="AC57" s="8" t="n"/>
       <c r="AD57" s="8" t="n"/>
       <c r="AE57" s="8" t="n"/>
       <c r="AF57" s="8" t="n"/>
@@ -4932,7 +5796,9 @@
       <c r="AO57" s="8" t="n"/>
       <c r="AP57" s="8" t="n"/>
       <c r="AQ57" s="8" t="n"/>
-      <c r="AR57" s="8" t="n"/>
+      <c r="AR57" s="17" t="n">
+        <v>6</v>
+      </c>
       <c r="AS57" s="8" t="n"/>
       <c r="AT57" s="8" t="n"/>
       <c r="AU57" s="8" t="n"/>
@@ -4942,8 +5808,10 @@
     </row>
     <row r="58">
       <c r="A58" s="8" t="n"/>
-      <c r="B58" s="8" t="n">
-        <v>44</v>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="n"/>
@@ -4952,48 +5820,60 @@
           <t>Painting top of roofs with bitumen of approved quality at 17 Kg. per 10 square metre impregnated with a coat of coarse sand at 3/2 60 dm per 10 m including cleaning the slab surface with brushes and finally with a piece of cloth lightly soaked in kerosene oil complete with residual type petroleum bitumen of penetration 80/100.</t>
         </is>
       </c>
-      <c r="F58" s="8" t="inlineStr"/>
+      <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
-        </is>
-      </c>
-      <c r="H58" s="8" t="inlineStr"/>
-      <c r="I58" s="8" t="n"/>
+          <t>Finishes</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>Bitumen</t>
+        </is>
+      </c>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>Bitumen, Coarse sand, Kerosene oil</t>
+        </is>
+      </c>
       <c r="J58" s="8" t="inlineStr">
         <is>
           <t>Paint/Finish</t>
         </is>
       </c>
-      <c r="K58" s="8" t="n"/>
+      <c r="K58" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L58" s="8" t="n"/>
       <c r="M58" s="8" t="n"/>
-      <c r="N58" s="8" t="n"/>
+      <c r="N58" s="17" t="n">
+        <v>65</v>
+      </c>
       <c r="O58" s="8" t="inlineStr">
         <is>
-          <t>sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P58" s="8" t="n"/>
-      <c r="Q58" s="8" t="n"/>
+      <c r="Q58" s="17" t="n">
+        <v>65</v>
+      </c>
       <c r="R58" s="8" t="n"/>
       <c r="S58" s="8" t="n"/>
       <c r="T58" s="8" t="n"/>
       <c r="U58" s="8" t="n"/>
       <c r="V58" s="8" t="n"/>
-      <c r="W58" s="8" t="n">
-        <v>65</v>
-      </c>
+      <c r="W58" s="8" t="n"/>
       <c r="X58" s="8" t="n"/>
       <c r="Y58" s="8" t="n"/>
       <c r="Z58" s="8" t="n"/>
       <c r="AA58" s="8" t="n"/>
-      <c r="AB58" s="8" t="n"/>
-      <c r="AC58" s="8" t="inlineStr">
+      <c r="AB58" s="8" t="inlineStr">
         <is>
           <t>12.29.1</t>
         </is>
       </c>
+      <c r="AC58" s="8" t="n"/>
       <c r="AD58" s="8" t="n"/>
       <c r="AE58" s="8" t="n"/>
       <c r="AF58" s="8" t="n"/>
@@ -5018,8 +5898,10 @@
     </row>
     <row r="59">
       <c r="A59" s="8" t="n"/>
-      <c r="B59" s="8" t="n">
-        <v>45</v>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="n"/>
@@ -5028,48 +5910,64 @@
           <t>Lime concrete terracing on roofs, average thickness 10 cm laid to fall with 25 mm nominal size brick aggregate and 50% lime mortar 1:2 (1 lime putty : 2 surkhi) rammed and finished with gur and belgiri treatment complete and covered with flat FPS brick tiles of class designation 100 grouted with cement mortar 1:3 (1 cement : 3 fine sand) mixed with 5% crude oil by wt. of cement, over 12 mm layer of cement mortar 1:3 (1 cement : 3 fine sand) and finished neat.</t>
         </is>
       </c>
-      <c r="F59" s="8" t="inlineStr"/>
+      <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
-        </is>
-      </c>
-      <c r="H59" s="8" t="inlineStr"/>
-      <c r="I59" s="8" t="n"/>
+          <t>Finishes</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>Lime concrete</t>
+        </is>
+      </c>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>Lime, Brick aggregate, Surkhi, Brick tiles, Cement, Fine sand, Crude oil</t>
+        </is>
+      </c>
       <c r="J59" s="8" t="inlineStr">
         <is>
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K59" s="8" t="n"/>
+      <c r="K59" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L59" s="8" t="n"/>
-      <c r="M59" s="8" t="n"/>
-      <c r="N59" s="8" t="n"/>
+      <c r="M59" s="8" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="N59" s="17" t="n">
+        <v>65</v>
+      </c>
       <c r="O59" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P59" s="8" t="n"/>
-      <c r="Q59" s="8" t="n"/>
+      <c r="Q59" s="17" t="n">
+        <v>65</v>
+      </c>
       <c r="R59" s="8" t="n"/>
       <c r="S59" s="8" t="n"/>
       <c r="T59" s="8" t="n"/>
       <c r="U59" s="8" t="n"/>
       <c r="V59" s="8" t="n"/>
-      <c r="W59" s="8" t="n">
-        <v>65</v>
-      </c>
+      <c r="W59" s="8" t="n"/>
       <c r="X59" s="8" t="n"/>
       <c r="Y59" s="8" t="n"/>
       <c r="Z59" s="8" t="n"/>
       <c r="AA59" s="8" t="n"/>
-      <c r="AB59" s="8" t="n"/>
-      <c r="AC59" s="8" t="inlineStr">
+      <c r="AB59" s="8" t="inlineStr">
         <is>
           <t>12.35.2</t>
         </is>
       </c>
+      <c r="AC59" s="8" t="n"/>
       <c r="AD59" s="8" t="n"/>
       <c r="AE59" s="8" t="n"/>
       <c r="AF59" s="8" t="n"/>
@@ -5084,7 +5982,9 @@
       <c r="AO59" s="8" t="n"/>
       <c r="AP59" s="8" t="n"/>
       <c r="AQ59" s="8" t="n"/>
-      <c r="AR59" s="8" t="n"/>
+      <c r="AR59" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="AS59" s="8" t="n"/>
       <c r="AT59" s="8" t="n"/>
       <c r="AU59" s="8" t="n"/>
@@ -5094,8 +5994,10 @@
     </row>
     <row r="60">
       <c r="A60" s="8" t="n"/>
-      <c r="B60" s="8" t="n">
-        <v>46</v>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="n"/>
@@ -5104,48 +6006,64 @@
           <t>Providing and laying 25 mm thick burnt clay tiles 250x250x25 mm of approved quality over roofs with 1 cm side joints grouted with CM 1:3 (1 cement : 3 fine sand) over 15 mm thick bed of cement mortar 1:3 (1 cement : 3 fine sand) and finished neat.</t>
         </is>
       </c>
-      <c r="F60" s="8" t="inlineStr"/>
+      <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
-        </is>
-      </c>
-      <c r="H60" s="8" t="inlineStr"/>
-      <c r="I60" s="8" t="n"/>
+          <t>Finishes</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>Burnt clay tile</t>
+        </is>
+      </c>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>Burnt clay tile, Cement, Fine sand</t>
+        </is>
+      </c>
       <c r="J60" s="8" t="inlineStr">
         <is>
           <t>Masonry</t>
         </is>
       </c>
-      <c r="K60" s="8" t="n"/>
+      <c r="K60" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L60" s="8" t="n"/>
-      <c r="M60" s="8" t="n"/>
-      <c r="N60" s="8" t="n"/>
+      <c r="M60" s="8" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="N60" s="17" t="n">
+        <v>32</v>
+      </c>
       <c r="O60" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P60" s="8" t="n"/>
-      <c r="Q60" s="8" t="n"/>
+      <c r="Q60" s="17" t="n">
+        <v>32</v>
+      </c>
       <c r="R60" s="8" t="n"/>
       <c r="S60" s="8" t="n"/>
       <c r="T60" s="8" t="n"/>
       <c r="U60" s="8" t="n"/>
       <c r="V60" s="8" t="n"/>
-      <c r="W60" s="8" t="n">
-        <v>32</v>
-      </c>
+      <c r="W60" s="8" t="n"/>
       <c r="X60" s="8" t="n"/>
       <c r="Y60" s="8" t="n"/>
       <c r="Z60" s="8" t="n"/>
       <c r="AA60" s="8" t="n"/>
-      <c r="AB60" s="8" t="n"/>
-      <c r="AC60" s="8" t="inlineStr">
+      <c r="AB60" s="8" t="inlineStr">
         <is>
           <t>N.S.I.</t>
         </is>
       </c>
+      <c r="AC60" s="8" t="n"/>
       <c r="AD60" s="8" t="n"/>
       <c r="AE60" s="8" t="n"/>
       <c r="AF60" s="8" t="n"/>
@@ -5160,7 +6078,9 @@
       <c r="AO60" s="8" t="n"/>
       <c r="AP60" s="8" t="n"/>
       <c r="AQ60" s="8" t="n"/>
-      <c r="AR60" s="8" t="n"/>
+      <c r="AR60" s="17" t="n">
+        <v>25</v>
+      </c>
       <c r="AS60" s="8" t="n"/>
       <c r="AT60" s="8" t="n"/>
       <c r="AU60" s="8" t="n"/>
@@ -5170,8 +6090,10 @@
     </row>
     <row r="61">
       <c r="A61" s="8" t="n"/>
-      <c r="B61" s="8" t="n">
-        <v>47</v>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="n"/>
@@ -5180,48 +6102,64 @@
           <t>Providing gola 15x15 cm in size in cement concrete mix 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) covered with brick tiles in CM 1:3 (1 cement : 3 coarse sand) as per drawing and specifications complete in all respects.</t>
         </is>
       </c>
-      <c r="F61" s="8" t="inlineStr"/>
+      <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
         </is>
       </c>
-      <c r="H61" s="8" t="inlineStr"/>
-      <c r="I61" s="8" t="n"/>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>Cement concrete</t>
+        </is>
+      </c>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>Cement, Coarse sand, Graded stone aggregate, Brick tile</t>
+        </is>
+      </c>
       <c r="J61" s="8" t="inlineStr">
         <is>
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K61" s="8" t="n"/>
+      <c r="K61" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L61" s="8" t="n"/>
-      <c r="M61" s="8" t="n"/>
-      <c r="N61" s="8" t="n"/>
+      <c r="M61" s="8" t="inlineStr">
+        <is>
+          <t>1:3:6</t>
+        </is>
+      </c>
+      <c r="N61" s="17" t="n">
+        <v>46</v>
+      </c>
       <c r="O61" s="8" t="inlineStr">
         <is>
-          <t>Mtr.</t>
+          <t>m</t>
         </is>
       </c>
       <c r="P61" s="8" t="n"/>
       <c r="Q61" s="8" t="n"/>
-      <c r="R61" s="8" t="n"/>
+      <c r="R61" s="17" t="n">
+        <v>46</v>
+      </c>
       <c r="S61" s="8" t="n"/>
       <c r="T61" s="8" t="n"/>
       <c r="U61" s="8" t="n"/>
       <c r="V61" s="8" t="n"/>
-      <c r="W61" s="8" t="n">
-        <v>46</v>
-      </c>
+      <c r="W61" s="8" t="n"/>
       <c r="X61" s="8" t="n"/>
       <c r="Y61" s="8" t="n"/>
       <c r="Z61" s="8" t="n"/>
       <c r="AA61" s="8" t="n"/>
-      <c r="AB61" s="8" t="n"/>
-      <c r="AC61" s="8" t="inlineStr">
+      <c r="AB61" s="8" t="inlineStr">
         <is>
           <t>N.S.I.</t>
         </is>
       </c>
+      <c r="AC61" s="8" t="n"/>
       <c r="AD61" s="8" t="n"/>
       <c r="AE61" s="8" t="n"/>
       <c r="AF61" s="8" t="n"/>
@@ -5246,8 +6184,10 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n"/>
-      <c r="B62" s="8" t="n">
-        <v>48</v>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="8" t="n"/>
@@ -5256,46 +6196,64 @@
           <t>Making khurras 45 x 45 cm with average minimum thickness of 5 cm cement concrete 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size) over PVC sheet 1m x 1m x 400 micron, finished with 12 cement plaster 1:3 (1 cement : 3 coarse sand) and a coat of neat cement rounding the edges and making and finishing the outlet complete.</t>
         </is>
       </c>
-      <c r="F62" s="8" t="inlineStr"/>
+      <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>Plumbing &amp; Sanitary</t>
-        </is>
-      </c>
-      <c r="H62" s="8" t="inlineStr"/>
-      <c r="I62" s="8" t="n"/>
+          <t>Civil &amp; Sitework</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>Cement concrete</t>
+        </is>
+      </c>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>Cement, Coarse sand, Graded stone aggregate, PVC sheet</t>
+        </is>
+      </c>
       <c r="J62" s="8" t="inlineStr">
         <is>
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K62" s="8" t="n"/>
+      <c r="K62" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L62" s="8" t="n"/>
-      <c r="M62" s="8" t="n"/>
-      <c r="N62" s="8" t="n"/>
+      <c r="M62" s="8" t="inlineStr">
+        <is>
+          <t>1:2:4</t>
+        </is>
+      </c>
+      <c r="N62" s="17" t="n">
+        <v>3</v>
+      </c>
       <c r="O62" s="8" t="inlineStr">
         <is>
-          <t>Each</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P62" s="8" t="n"/>
       <c r="Q62" s="8" t="n"/>
       <c r="R62" s="8" t="n"/>
       <c r="S62" s="8" t="n"/>
-      <c r="T62" s="8" t="n"/>
+      <c r="T62" s="17" t="n">
+        <v>3</v>
+      </c>
       <c r="U62" s="8" t="n"/>
       <c r="V62" s="8" t="n"/>
-      <c r="W62" s="8" t="n">
-        <v>3</v>
-      </c>
+      <c r="W62" s="8" t="n"/>
       <c r="X62" s="8" t="n"/>
       <c r="Y62" s="8" t="n"/>
       <c r="Z62" s="8" t="n"/>
       <c r="AA62" s="8" t="n"/>
-      <c r="AB62" s="8" t="n"/>
-      <c r="AC62" s="8" t="n">
-        <v>12.39</v>
-      </c>
+      <c r="AB62" s="8" t="inlineStr">
+        <is>
+          <t>12.39</t>
+        </is>
+      </c>
+      <c r="AC62" s="8" t="n"/>
       <c r="AD62" s="8" t="n"/>
       <c r="AE62" s="8" t="n"/>
       <c r="AF62" s="8" t="n"/>
@@ -5310,7 +6268,9 @@
       <c r="AO62" s="8" t="n"/>
       <c r="AP62" s="8" t="n"/>
       <c r="AQ62" s="8" t="n"/>
-      <c r="AR62" s="8" t="n"/>
+      <c r="AR62" s="17" t="n">
+        <v>50</v>
+      </c>
       <c r="AS62" s="8" t="n"/>
       <c r="AT62" s="8" t="n"/>
       <c r="AU62" s="8" t="n"/>
@@ -5320,8 +6280,10 @@
     </row>
     <row r="63">
       <c r="A63" s="8" t="n"/>
-      <c r="B63" s="8" t="n">
-        <v>49</v>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="n"/>
@@ -5330,48 +6292,64 @@
           <t>Providing and fixing on wallface 100 mm diameter CI rain water pipe including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand)</t>
         </is>
       </c>
-      <c r="F63" s="8" t="inlineStr"/>
+      <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="inlineStr">
         <is>
           <t>Plumbing &amp; Sanitary</t>
         </is>
       </c>
-      <c r="H63" s="8" t="inlineStr"/>
-      <c r="I63" s="8" t="n"/>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>Cast iron</t>
+        </is>
+      </c>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>Cast iron, Cement, Fine sand</t>
+        </is>
+      </c>
       <c r="J63" s="8" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K63" s="8" t="n"/>
+      <c r="K63" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L63" s="8" t="n"/>
-      <c r="M63" s="8" t="n"/>
-      <c r="N63" s="8" t="n"/>
+      <c r="M63" s="8" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="N63" s="17" t="n">
+        <v>10</v>
+      </c>
       <c r="O63" s="8" t="inlineStr">
         <is>
-          <t>Mtr.</t>
+          <t>m</t>
         </is>
       </c>
       <c r="P63" s="8" t="n"/>
       <c r="Q63" s="8" t="n"/>
-      <c r="R63" s="8" t="n"/>
+      <c r="R63" s="17" t="n">
+        <v>10</v>
+      </c>
       <c r="S63" s="8" t="n"/>
       <c r="T63" s="8" t="n"/>
       <c r="U63" s="8" t="n"/>
       <c r="V63" s="8" t="n"/>
-      <c r="W63" s="8" t="n">
-        <v>10</v>
-      </c>
+      <c r="W63" s="8" t="n"/>
       <c r="X63" s="8" t="n"/>
       <c r="Y63" s="8" t="n"/>
       <c r="Z63" s="8" t="n"/>
       <c r="AA63" s="8" t="n"/>
-      <c r="AB63" s="8" t="n"/>
-      <c r="AC63" s="8" t="inlineStr">
+      <c r="AB63" s="8" t="inlineStr">
         <is>
           <t>12.69.2</t>
         </is>
       </c>
+      <c r="AC63" s="8" t="n"/>
       <c r="AD63" s="8" t="n"/>
       <c r="AE63" s="8" t="n"/>
       <c r="AF63" s="8" t="n"/>
@@ -5388,7 +6366,9 @@
       <c r="AQ63" s="8" t="n"/>
       <c r="AR63" s="8" t="n"/>
       <c r="AS63" s="8" t="n"/>
-      <c r="AT63" s="8" t="n"/>
+      <c r="AT63" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="AU63" s="8" t="n"/>
       <c r="AV63" s="8" t="n"/>
       <c r="AW63" s="8" t="n"/>
@@ -5396,8 +6376,10 @@
     </row>
     <row r="64">
       <c r="A64" s="8" t="n"/>
-      <c r="B64" s="8" t="n">
-        <v>50</v>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="n"/>
@@ -5406,48 +6388,64 @@
           <t>Providing and fixing 100 mm dia MS holderbat clamps of approved design to CI or SCI rain water pipes embedded in and including cement concrete blocks 10 x 10 x 10 cm of 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size) and cost of cutting holes and making good the walls etc.</t>
         </is>
       </c>
-      <c r="F64" s="8" t="inlineStr"/>
+      <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="inlineStr">
         <is>
           <t>Plumbing &amp; Sanitary</t>
         </is>
       </c>
-      <c r="H64" s="8" t="inlineStr"/>
-      <c r="I64" s="8" t="n"/>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>Mild steel</t>
+        </is>
+      </c>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>Mild steel, Cement, Coarse sand, Graded stone aggregate</t>
+        </is>
+      </c>
       <c r="J64" s="8" t="inlineStr">
         <is>
           <t>Steel</t>
         </is>
       </c>
-      <c r="K64" s="8" t="n"/>
+      <c r="K64" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L64" s="8" t="n"/>
-      <c r="M64" s="8" t="n"/>
-      <c r="N64" s="8" t="n"/>
+      <c r="M64" s="8" t="inlineStr">
+        <is>
+          <t>1:2:4</t>
+        </is>
+      </c>
+      <c r="N64" s="17" t="n">
+        <v>9</v>
+      </c>
       <c r="O64" s="8" t="inlineStr">
         <is>
-          <t>Each</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P64" s="8" t="n"/>
       <c r="Q64" s="8" t="n"/>
       <c r="R64" s="8" t="n"/>
       <c r="S64" s="8" t="n"/>
-      <c r="T64" s="8" t="n"/>
+      <c r="T64" s="17" t="n">
+        <v>9</v>
+      </c>
       <c r="U64" s="8" t="n"/>
       <c r="V64" s="8" t="n"/>
-      <c r="W64" s="8" t="n">
-        <v>9</v>
-      </c>
+      <c r="W64" s="8" t="n"/>
       <c r="X64" s="8" t="n"/>
       <c r="Y64" s="8" t="n"/>
       <c r="Z64" s="8" t="n"/>
       <c r="AA64" s="8" t="n"/>
-      <c r="AB64" s="8" t="n"/>
-      <c r="AC64" s="8" t="inlineStr">
+      <c r="AB64" s="8" t="inlineStr">
         <is>
           <t>12.71.2</t>
         </is>
       </c>
+      <c r="AC64" s="8" t="n"/>
       <c r="AD64" s="8" t="n"/>
       <c r="AE64" s="8" t="n"/>
       <c r="AF64" s="8" t="n"/>
@@ -5464,7 +6462,9 @@
       <c r="AQ64" s="8" t="n"/>
       <c r="AR64" s="8" t="n"/>
       <c r="AS64" s="8" t="n"/>
-      <c r="AT64" s="8" t="n"/>
+      <c r="AT64" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="AU64" s="8" t="n"/>
       <c r="AV64" s="8" t="n"/>
       <c r="AW64" s="8" t="n"/>
@@ -5474,58 +6474,74 @@
       <c r="A65" s="8" t="n"/>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>51a</t>
+          <t>51i</t>
         </is>
       </c>
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) i) CI plain head 100 mm dia</t>
-        </is>
-      </c>
-      <c r="F65" s="8" t="inlineStr"/>
+          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand). CI plain head 100 mm dia</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="inlineStr">
         <is>
           <t>Plumbing &amp; Sanitary</t>
         </is>
       </c>
-      <c r="H65" s="8" t="inlineStr"/>
-      <c r="I65" s="8" t="n"/>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>Cast iron</t>
+        </is>
+      </c>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>Cast iron, Cement, Fine sand</t>
+        </is>
+      </c>
       <c r="J65" s="8" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K65" s="8" t="n"/>
+      <c r="K65" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L65" s="8" t="n"/>
-      <c r="M65" s="8" t="n"/>
-      <c r="N65" s="8" t="n"/>
+      <c r="M65" s="8" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="N65" s="17" t="n">
+        <v>3</v>
+      </c>
       <c r="O65" s="8" t="inlineStr">
         <is>
-          <t>Each</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P65" s="8" t="n"/>
       <c r="Q65" s="8" t="n"/>
       <c r="R65" s="8" t="n"/>
       <c r="S65" s="8" t="n"/>
-      <c r="T65" s="8" t="n"/>
+      <c r="T65" s="17" t="n">
+        <v>3</v>
+      </c>
       <c r="U65" s="8" t="n"/>
       <c r="V65" s="8" t="n"/>
-      <c r="W65" s="8" t="n">
-        <v>3</v>
-      </c>
+      <c r="W65" s="8" t="n"/>
       <c r="X65" s="8" t="n"/>
       <c r="Y65" s="8" t="n"/>
       <c r="Z65" s="8" t="n"/>
       <c r="AA65" s="8" t="n"/>
-      <c r="AB65" s="8" t="n"/>
-      <c r="AC65" s="8" t="inlineStr">
+      <c r="AB65" s="8" t="inlineStr">
         <is>
           <t>12.72.2.2</t>
         </is>
       </c>
+      <c r="AC65" s="8" t="n"/>
       <c r="AD65" s="8" t="n"/>
       <c r="AE65" s="8" t="n"/>
       <c r="AF65" s="8" t="n"/>
@@ -5542,7 +6558,9 @@
       <c r="AQ65" s="8" t="n"/>
       <c r="AR65" s="8" t="n"/>
       <c r="AS65" s="8" t="n"/>
-      <c r="AT65" s="8" t="n"/>
+      <c r="AT65" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="AU65" s="8" t="n"/>
       <c r="AV65" s="8" t="n"/>
       <c r="AW65" s="8" t="n"/>
@@ -5552,58 +6570,74 @@
       <c r="A66" s="8" t="n"/>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>51b</t>
+          <t>51ii</t>
         </is>
       </c>
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) ii) CI plain shoe - 100 mm dia</t>
-        </is>
-      </c>
-      <c r="F66" s="8" t="inlineStr"/>
+          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand). CI plain shoe - 100 mm dia</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="inlineStr">
         <is>
           <t>Plumbing &amp; Sanitary</t>
         </is>
       </c>
-      <c r="H66" s="8" t="inlineStr"/>
-      <c r="I66" s="8" t="n"/>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>Cast iron</t>
+        </is>
+      </c>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>Cast iron, Cement, Fine sand</t>
+        </is>
+      </c>
       <c r="J66" s="8" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K66" s="8" t="n"/>
+      <c r="K66" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L66" s="8" t="n"/>
-      <c r="M66" s="8" t="n"/>
-      <c r="N66" s="8" t="n"/>
+      <c r="M66" s="8" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="N66" s="17" t="n">
+        <v>3</v>
+      </c>
       <c r="O66" s="8" t="inlineStr">
         <is>
-          <t>Each</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P66" s="8" t="n"/>
       <c r="Q66" s="8" t="n"/>
       <c r="R66" s="8" t="n"/>
       <c r="S66" s="8" t="n"/>
-      <c r="T66" s="8" t="n"/>
+      <c r="T66" s="17" t="n">
+        <v>3</v>
+      </c>
       <c r="U66" s="8" t="n"/>
       <c r="V66" s="8" t="n"/>
-      <c r="W66" s="8" t="n">
-        <v>3</v>
-      </c>
+      <c r="W66" s="8" t="n"/>
       <c r="X66" s="8" t="n"/>
       <c r="Y66" s="8" t="n"/>
       <c r="Z66" s="8" t="n"/>
       <c r="AA66" s="8" t="n"/>
-      <c r="AB66" s="8" t="n"/>
-      <c r="AC66" s="8" t="inlineStr">
+      <c r="AB66" s="8" t="inlineStr">
         <is>
           <t>12.72.3.2</t>
         </is>
       </c>
+      <c r="AC66" s="8" t="n"/>
       <c r="AD66" s="8" t="n"/>
       <c r="AE66" s="8" t="n"/>
       <c r="AF66" s="8" t="n"/>
@@ -5620,7 +6654,9 @@
       <c r="AQ66" s="8" t="n"/>
       <c r="AR66" s="8" t="n"/>
       <c r="AS66" s="8" t="n"/>
-      <c r="AT66" s="8" t="n"/>
+      <c r="AT66" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="AU66" s="8" t="n"/>
       <c r="AV66" s="8" t="n"/>
       <c r="AW66" s="8" t="n"/>
@@ -5630,58 +6666,74 @@
       <c r="A67" s="8" t="n"/>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>51c</t>
+          <t>51iii</t>
         </is>
       </c>
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) iii) CI plain bend - 100 mm dia</t>
-        </is>
-      </c>
-      <c r="F67" s="8" t="inlineStr"/>
+          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand). CI plain bend - 100 mm dia</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="inlineStr">
         <is>
           <t>Plumbing &amp; Sanitary</t>
         </is>
       </c>
-      <c r="H67" s="8" t="inlineStr"/>
-      <c r="I67" s="8" t="n"/>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>Cast iron</t>
+        </is>
+      </c>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>Cast iron, Cement, Fine sand</t>
+        </is>
+      </c>
       <c r="J67" s="8" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="K67" s="8" t="n"/>
+      <c r="K67" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L67" s="8" t="n"/>
-      <c r="M67" s="8" t="n"/>
-      <c r="N67" s="8" t="n"/>
+      <c r="M67" s="8" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="N67" s="17" t="n">
+        <v>3</v>
+      </c>
       <c r="O67" s="8" t="inlineStr">
         <is>
-          <t>Each</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P67" s="8" t="n"/>
       <c r="Q67" s="8" t="n"/>
       <c r="R67" s="8" t="n"/>
       <c r="S67" s="8" t="n"/>
-      <c r="T67" s="8" t="n"/>
+      <c r="T67" s="17" t="n">
+        <v>3</v>
+      </c>
       <c r="U67" s="8" t="n"/>
       <c r="V67" s="8" t="n"/>
-      <c r="W67" s="8" t="n">
-        <v>3</v>
-      </c>
+      <c r="W67" s="8" t="n"/>
       <c r="X67" s="8" t="n"/>
       <c r="Y67" s="8" t="n"/>
       <c r="Z67" s="8" t="n"/>
       <c r="AA67" s="8" t="n"/>
-      <c r="AB67" s="8" t="n"/>
-      <c r="AC67" s="8" t="inlineStr">
+      <c r="AB67" s="8" t="inlineStr">
         <is>
           <t>12.72.1.2</t>
         </is>
       </c>
+      <c r="AC67" s="8" t="n"/>
       <c r="AD67" s="8" t="n"/>
       <c r="AE67" s="8" t="n"/>
       <c r="AF67" s="8" t="n"/>
@@ -5698,7 +6750,9 @@
       <c r="AQ67" s="8" t="n"/>
       <c r="AR67" s="8" t="n"/>
       <c r="AS67" s="8" t="n"/>
-      <c r="AT67" s="8" t="n"/>
+      <c r="AT67" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="AU67" s="8" t="n"/>
       <c r="AV67" s="8" t="n"/>
       <c r="AW67" s="8" t="n"/>
@@ -5706,8 +6760,10 @@
     </row>
     <row r="68">
       <c r="A68" s="8" t="n"/>
-      <c r="B68" s="8" t="n">
-        <v>52</v>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="n"/>
@@ -5716,48 +6772,64 @@
           <t>12 mm cement plaster of mix 1:6 (1 cement : 6 fine sand)</t>
         </is>
       </c>
-      <c r="F68" s="8" t="inlineStr"/>
+      <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H68" s="8" t="inlineStr"/>
-      <c r="I68" s="8" t="n"/>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>Cement plaster</t>
+        </is>
+      </c>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>Cement, Fine sand</t>
+        </is>
+      </c>
       <c r="J68" s="8" t="inlineStr">
         <is>
           <t>Paint/Finish</t>
         </is>
       </c>
-      <c r="K68" s="8" t="n"/>
+      <c r="K68" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L68" s="8" t="n"/>
-      <c r="M68" s="8" t="n"/>
-      <c r="N68" s="8" t="n"/>
+      <c r="M68" s="8" t="inlineStr">
+        <is>
+          <t>1:6</t>
+        </is>
+      </c>
+      <c r="N68" s="17" t="n">
+        <v>220</v>
+      </c>
       <c r="O68" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P68" s="8" t="n"/>
-      <c r="Q68" s="8" t="n"/>
+      <c r="Q68" s="17" t="n">
+        <v>220</v>
+      </c>
       <c r="R68" s="8" t="n"/>
       <c r="S68" s="8" t="n"/>
       <c r="T68" s="8" t="n"/>
       <c r="U68" s="8" t="n"/>
       <c r="V68" s="8" t="n"/>
-      <c r="W68" s="8" t="n">
-        <v>220</v>
-      </c>
+      <c r="W68" s="8" t="n"/>
       <c r="X68" s="8" t="n"/>
       <c r="Y68" s="8" t="n"/>
       <c r="Z68" s="8" t="n"/>
       <c r="AA68" s="8" t="n"/>
-      <c r="AB68" s="8" t="n"/>
-      <c r="AC68" s="8" t="inlineStr">
+      <c r="AB68" s="8" t="inlineStr">
         <is>
           <t>13.8.4</t>
         </is>
       </c>
+      <c r="AC68" s="8" t="n"/>
       <c r="AD68" s="8" t="n"/>
       <c r="AE68" s="8" t="n"/>
       <c r="AF68" s="8" t="n"/>
@@ -5772,7 +6844,9 @@
       <c r="AO68" s="8" t="n"/>
       <c r="AP68" s="8" t="n"/>
       <c r="AQ68" s="8" t="n"/>
-      <c r="AR68" s="8" t="n"/>
+      <c r="AR68" s="17" t="n">
+        <v>12</v>
+      </c>
       <c r="AS68" s="8" t="n"/>
       <c r="AT68" s="8" t="n"/>
       <c r="AU68" s="8" t="n"/>
@@ -5782,8 +6856,10 @@
     </row>
     <row r="69">
       <c r="A69" s="8" t="n"/>
-      <c r="B69" s="8" t="n">
-        <v>53</v>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="n"/>
@@ -5792,48 +6868,64 @@
           <t>15 mm cement plaster on the rough side of single or half brick wall of mix 1:6 (1 cement : 6 fine sand)</t>
         </is>
       </c>
-      <c r="F69" s="8" t="inlineStr"/>
+      <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H69" s="8" t="inlineStr"/>
-      <c r="I69" s="8" t="n"/>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>Cement plaster</t>
+        </is>
+      </c>
+      <c r="I69" s="8" t="inlineStr">
+        <is>
+          <t>Cement, Fine sand</t>
+        </is>
+      </c>
       <c r="J69" s="8" t="inlineStr">
         <is>
           <t>Paint/Finish</t>
         </is>
       </c>
-      <c r="K69" s="8" t="n"/>
+      <c r="K69" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L69" s="8" t="n"/>
-      <c r="M69" s="8" t="n"/>
-      <c r="N69" s="8" t="n"/>
+      <c r="M69" s="8" t="inlineStr">
+        <is>
+          <t>1:6</t>
+        </is>
+      </c>
+      <c r="N69" s="17" t="n">
+        <v>220</v>
+      </c>
       <c r="O69" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P69" s="8" t="n"/>
-      <c r="Q69" s="8" t="n"/>
+      <c r="Q69" s="17" t="n">
+        <v>220</v>
+      </c>
       <c r="R69" s="8" t="n"/>
       <c r="S69" s="8" t="n"/>
       <c r="T69" s="8" t="n"/>
       <c r="U69" s="8" t="n"/>
       <c r="V69" s="8" t="n"/>
-      <c r="W69" s="8" t="n">
-        <v>220</v>
-      </c>
+      <c r="W69" s="8" t="n"/>
       <c r="X69" s="8" t="n"/>
       <c r="Y69" s="8" t="n"/>
       <c r="Z69" s="8" t="n"/>
       <c r="AA69" s="8" t="n"/>
-      <c r="AB69" s="8" t="n"/>
-      <c r="AC69" s="8" t="inlineStr">
+      <c r="AB69" s="8" t="inlineStr">
         <is>
           <t>13.9.4</t>
         </is>
       </c>
+      <c r="AC69" s="8" t="n"/>
       <c r="AD69" s="8" t="n"/>
       <c r="AE69" s="8" t="n"/>
       <c r="AF69" s="8" t="n"/>
@@ -5848,7 +6940,9 @@
       <c r="AO69" s="8" t="n"/>
       <c r="AP69" s="8" t="n"/>
       <c r="AQ69" s="8" t="n"/>
-      <c r="AR69" s="8" t="n"/>
+      <c r="AR69" s="17" t="n">
+        <v>15</v>
+      </c>
       <c r="AS69" s="8" t="n"/>
       <c r="AT69" s="8" t="n"/>
       <c r="AU69" s="8" t="n"/>
@@ -5858,8 +6952,10 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n"/>
-      <c r="B70" s="8" t="n">
-        <v>54</v>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="n"/>
@@ -5868,46 +6964,64 @@
           <t>6 mm cement plaster of mix 1:3 (1 cement : 3 fine sand) finished with a floating coat of neat cement and thick coat of lime wash on top of walls when dry for bearing of RCC slabs and beams.</t>
         </is>
       </c>
-      <c r="F70" s="8" t="inlineStr"/>
+      <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H70" s="8" t="inlineStr"/>
-      <c r="I70" s="8" t="n"/>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>Cement plaster</t>
+        </is>
+      </c>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>Cement, Fine sand, Lime wash</t>
+        </is>
+      </c>
       <c r="J70" s="8" t="inlineStr">
         <is>
           <t>Paint/Finish</t>
         </is>
       </c>
-      <c r="K70" s="8" t="n"/>
+      <c r="K70" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L70" s="8" t="n"/>
-      <c r="M70" s="8" t="n"/>
-      <c r="N70" s="8" t="n"/>
+      <c r="M70" s="8" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="N70" s="17" t="n">
+        <v>19</v>
+      </c>
       <c r="O70" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P70" s="8" t="n"/>
-      <c r="Q70" s="8" t="n"/>
+      <c r="Q70" s="17" t="n">
+        <v>19</v>
+      </c>
       <c r="R70" s="8" t="n"/>
       <c r="S70" s="8" t="n"/>
       <c r="T70" s="8" t="n"/>
       <c r="U70" s="8" t="n"/>
       <c r="V70" s="8" t="n"/>
-      <c r="W70" s="8" t="n">
-        <v>19</v>
-      </c>
+      <c r="W70" s="8" t="n"/>
       <c r="X70" s="8" t="n"/>
       <c r="Y70" s="8" t="n"/>
       <c r="Z70" s="8" t="n"/>
       <c r="AA70" s="8" t="n"/>
-      <c r="AB70" s="8" t="n"/>
-      <c r="AC70" s="8" t="n">
-        <v>13.25</v>
-      </c>
+      <c r="AB70" s="8" t="inlineStr">
+        <is>
+          <t>13.25</t>
+        </is>
+      </c>
+      <c r="AC70" s="8" t="n"/>
       <c r="AD70" s="8" t="n"/>
       <c r="AE70" s="8" t="n"/>
       <c r="AF70" s="8" t="n"/>
@@ -5922,7 +7036,9 @@
       <c r="AO70" s="8" t="n"/>
       <c r="AP70" s="8" t="n"/>
       <c r="AQ70" s="8" t="n"/>
-      <c r="AR70" s="8" t="n"/>
+      <c r="AR70" s="17" t="n">
+        <v>6</v>
+      </c>
       <c r="AS70" s="8" t="n"/>
       <c r="AT70" s="8" t="n"/>
       <c r="AU70" s="8" t="n"/>
@@ -5932,8 +7048,10 @@
     </row>
     <row r="71">
       <c r="A71" s="8" t="n"/>
-      <c r="B71" s="8" t="n">
-        <v>55</v>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="n"/>
@@ -5942,48 +7060,64 @@
           <t>18 mm plastering with terrazzo finish for dado rubbed and polished complete, under layer 12 mm thick cement plaster 1:3 (1 cement : 3 coarse sand) and top layer 6 mm thick white, black, chocolate, grey, yellow or Baroda green marble chips of 3 mm and down size laid in cement marble powder mix 3:1 (3 cement : 1 marble powder) by weight in proportion of 4:7 (4 cement marble powder mix : 7 marble chips) by volume.</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr"/>
+      <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H71" s="8" t="inlineStr"/>
-      <c r="I71" s="8" t="n"/>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>Terrazzo plaster</t>
+        </is>
+      </c>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>Cement, Coarse sand, Marble chips, Marble powder</t>
+        </is>
+      </c>
       <c r="J71" s="8" t="inlineStr">
         <is>
           <t>Paint/Finish</t>
         </is>
       </c>
-      <c r="K71" s="8" t="n"/>
+      <c r="K71" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L71" s="8" t="n"/>
-      <c r="M71" s="8" t="n"/>
-      <c r="N71" s="8" t="n"/>
+      <c r="M71" s="8" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="N71" s="17" t="n">
+        <v>20</v>
+      </c>
       <c r="O71" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P71" s="8" t="n"/>
-      <c r="Q71" s="8" t="n"/>
+      <c r="Q71" s="17" t="n">
+        <v>20</v>
+      </c>
       <c r="R71" s="8" t="n"/>
       <c r="S71" s="8" t="n"/>
       <c r="T71" s="8" t="n"/>
       <c r="U71" s="8" t="n"/>
       <c r="V71" s="8" t="n"/>
-      <c r="W71" s="8" t="n">
-        <v>20</v>
-      </c>
+      <c r="W71" s="8" t="n"/>
       <c r="X71" s="8" t="n"/>
       <c r="Y71" s="8" t="n"/>
       <c r="Z71" s="8" t="n"/>
       <c r="AA71" s="8" t="n"/>
-      <c r="AB71" s="8" t="n"/>
-      <c r="AC71" s="8" t="inlineStr">
+      <c r="AB71" s="8" t="inlineStr">
         <is>
           <t>5.31/13.24.1</t>
         </is>
       </c>
+      <c r="AC71" s="8" t="n"/>
       <c r="AD71" s="8" t="n"/>
       <c r="AE71" s="8" t="n"/>
       <c r="AF71" s="8" t="n"/>
@@ -5998,7 +7132,9 @@
       <c r="AO71" s="8" t="n"/>
       <c r="AP71" s="8" t="n"/>
       <c r="AQ71" s="8" t="n"/>
-      <c r="AR71" s="8" t="n"/>
+      <c r="AR71" s="17" t="n">
+        <v>18</v>
+      </c>
       <c r="AS71" s="8" t="n"/>
       <c r="AT71" s="8" t="n"/>
       <c r="AU71" s="8" t="n"/>
@@ -6008,8 +7144,10 @@
     </row>
     <row r="72">
       <c r="A72" s="8" t="n"/>
-      <c r="B72" s="8" t="n">
-        <v>56</v>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
       </c>
       <c r="C72" s="8" t="n"/>
       <c r="D72" s="8" t="n"/>
@@ -6018,48 +7156,64 @@
           <t>Finishing and plastering the exposed surface of RCC with cement mortar 1:3</t>
         </is>
       </c>
-      <c r="F72" s="8" t="inlineStr"/>
+      <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H72" s="8" t="inlineStr"/>
-      <c r="I72" s="8" t="n"/>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>Cement mortar</t>
+        </is>
+      </c>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>Cement, Sand</t>
+        </is>
+      </c>
       <c r="J72" s="8" t="inlineStr">
         <is>
           <t>Paint/Finish</t>
         </is>
       </c>
-      <c r="K72" s="8" t="n"/>
+      <c r="K72" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L72" s="8" t="n"/>
-      <c r="M72" s="8" t="n"/>
-      <c r="N72" s="8" t="n"/>
+      <c r="M72" s="8" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="N72" s="17" t="n">
+        <v>155</v>
+      </c>
       <c r="O72" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P72" s="8" t="n"/>
-      <c r="Q72" s="8" t="n"/>
+      <c r="Q72" s="17" t="n">
+        <v>155</v>
+      </c>
       <c r="R72" s="8" t="n"/>
       <c r="S72" s="8" t="n"/>
       <c r="T72" s="8" t="n"/>
       <c r="U72" s="8" t="n"/>
       <c r="V72" s="8" t="n"/>
-      <c r="W72" s="8" t="n">
-        <v>155</v>
-      </c>
+      <c r="W72" s="8" t="n"/>
       <c r="X72" s="8" t="n"/>
       <c r="Y72" s="8" t="n"/>
       <c r="Z72" s="8" t="n"/>
       <c r="AA72" s="8" t="n"/>
-      <c r="AB72" s="8" t="n"/>
-      <c r="AC72" s="8" t="inlineStr">
+      <c r="AB72" s="8" t="inlineStr">
         <is>
           <t>13.70.1</t>
         </is>
       </c>
+      <c r="AC72" s="8" t="n"/>
       <c r="AD72" s="8" t="n"/>
       <c r="AE72" s="8" t="n"/>
       <c r="AF72" s="8" t="n"/>
@@ -6084,8 +7238,10 @@
     </row>
     <row r="73">
       <c r="A73" s="8" t="n"/>
-      <c r="B73" s="8" t="n">
-        <v>57</v>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="C73" s="8" t="n"/>
       <c r="D73" s="8" t="n"/>
@@ -6094,48 +7250,60 @@
           <t>White washing with lime to give an even shade on new work (three or more coats).</t>
         </is>
       </c>
-      <c r="F73" s="8" t="inlineStr"/>
+      <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H73" s="8" t="inlineStr"/>
-      <c r="I73" s="8" t="n"/>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>Lime wash</t>
+        </is>
+      </c>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>Lime</t>
+        </is>
+      </c>
       <c r="J73" s="8" t="inlineStr">
         <is>
           <t>Paint/Finish</t>
         </is>
       </c>
-      <c r="K73" s="8" t="n"/>
+      <c r="K73" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L73" s="8" t="n"/>
       <c r="M73" s="8" t="n"/>
-      <c r="N73" s="8" t="n"/>
+      <c r="N73" s="17" t="n">
+        <v>285</v>
+      </c>
       <c r="O73" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P73" s="8" t="n"/>
-      <c r="Q73" s="8" t="n"/>
+      <c r="Q73" s="17" t="n">
+        <v>285</v>
+      </c>
       <c r="R73" s="8" t="n"/>
       <c r="S73" s="8" t="n"/>
       <c r="T73" s="8" t="n"/>
       <c r="U73" s="8" t="n"/>
       <c r="V73" s="8" t="n"/>
-      <c r="W73" s="8" t="n">
-        <v>285</v>
-      </c>
+      <c r="W73" s="8" t="n"/>
       <c r="X73" s="8" t="n"/>
       <c r="Y73" s="8" t="n"/>
       <c r="Z73" s="8" t="n"/>
       <c r="AA73" s="8" t="n"/>
-      <c r="AB73" s="8" t="n"/>
-      <c r="AC73" s="8" t="inlineStr">
+      <c r="AB73" s="8" t="inlineStr">
         <is>
           <t>13.73.1</t>
         </is>
       </c>
+      <c r="AC73" s="8" t="n"/>
       <c r="AD73" s="8" t="n"/>
       <c r="AE73" s="8" t="n"/>
       <c r="AF73" s="8" t="n"/>
@@ -6160,58 +7328,72 @@
     </row>
     <row r="74">
       <c r="A74" s="8" t="n"/>
-      <c r="B74" s="8" t="n">
-        <v>58</v>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
       </c>
       <c r="C74" s="8" t="n"/>
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Colour washing such as green, blue or buff to give an even shade on new work (two or more coats) with a base coat of white washing with lime.</t>
-        </is>
-      </c>
-      <c r="F74" s="8" t="inlineStr"/>
+          <t>Colour washing such as green, blue or buff to give an even shade on new work (two. or more coats) with a base coat of white washing with lime.</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H74" s="8" t="inlineStr"/>
-      <c r="I74" s="8" t="n"/>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>Colour wash</t>
+        </is>
+      </c>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>Lime</t>
+        </is>
+      </c>
       <c r="J74" s="8" t="inlineStr">
         <is>
           <t>Paint/Finish</t>
         </is>
       </c>
-      <c r="K74" s="8" t="n"/>
+      <c r="K74" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="L74" s="8" t="n"/>
       <c r="M74" s="8" t="n"/>
-      <c r="N74" s="8" t="n"/>
+      <c r="N74" s="17" t="n">
+        <v>285</v>
+      </c>
       <c r="O74" s="8" t="inlineStr">
         <is>
-          <t>Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P74" s="8" t="n"/>
-      <c r="Q74" s="8" t="n"/>
+      <c r="Q74" s="17" t="n">
+        <v>285</v>
+      </c>
       <c r="R74" s="8" t="n"/>
       <c r="S74" s="8" t="n"/>
       <c r="T74" s="8" t="n"/>
       <c r="U74" s="8" t="n"/>
       <c r="V74" s="8" t="n"/>
-      <c r="W74" s="8" t="n">
-        <v>285</v>
-      </c>
+      <c r="W74" s="8" t="n"/>
       <c r="X74" s="8" t="n"/>
       <c r="Y74" s="8" t="n"/>
       <c r="Z74" s="8" t="n"/>
       <c r="AA74" s="8" t="n"/>
-      <c r="AB74" s="8" t="n"/>
-      <c r="AC74" s="8" t="inlineStr">
+      <c r="AB74" s="8" t="inlineStr">
         <is>
           <t>13.81.1</t>
         </is>
       </c>
+      <c r="AC74" s="8" t="n"/>
       <c r="AD74" s="8" t="n"/>
       <c r="AE74" s="8" t="n"/>
       <c r="AF74" s="8" t="n"/>
@@ -6235,206 +7417,315 @@
       <c r="AX74" s="8" t="n"/>
     </row>
     <row r="75">
-      <c r="B75" t="n">
-        <v>59</v>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Applying priming coat with ready mixed pink or gray primer of approved brand and manufacture - on wood work (hard and soft wood)</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
+          <t>Applying priming coat with ready mixed pink or gray primer of approved brand and manufacture on wood work (hard and soft wood)</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Primer</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Primer</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr">
         <is>
           <t>Paint/Finish</t>
         </is>
       </c>
+      <c r="K75" s="18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N75" s="18" t="n">
+        <v>47</v>
+      </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Sq.m</t>
-        </is>
-      </c>
-      <c r="W75" t="n">
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="Q75" s="18" t="n">
         <v>47</v>
       </c>
-      <c r="AC75" t="inlineStr">
+      <c r="AB75" t="inlineStr">
         <is>
           <t>13.81.4</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="B76" t="n">
-        <v>60</v>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>Applying priming coat with readymixed zinc chromate yellow primer of approved brand and manufacture on steelwork (second coat)</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Zinc chromate primer</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Zinc chromate primer</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
           <t>Paint/Finish</t>
         </is>
       </c>
+      <c r="K76" s="18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N76" s="18" t="n">
+        <v>30</v>
+      </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Sq.m</t>
-        </is>
-      </c>
-      <c r="W76" t="n">
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="Q76" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="AC76" t="inlineStr">
+      <c r="AB76" t="inlineStr">
         <is>
           <t>13.84.3</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="B77" t="n">
-        <v>61</v>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>Painting (two or more coats) on rain water, soil, waste and vent pipes and fittings with black anticorrosive bitumastic paint of approved brand and manufacture over and including a priming coat of ready mixed zinc chromate yellow primer on new work on 100 mm diameter pipes.</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Bitumastic paint</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Bitumastic paint, Zinc chromate primer</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>Paint/Finish</t>
         </is>
       </c>
+      <c r="K77" s="18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N77" s="18" t="n">
+        <v>10</v>
+      </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Mtr.</t>
-        </is>
-      </c>
-      <c r="W77" t="n">
+          <t>m</t>
+        </is>
+      </c>
+      <c r="R77" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="AC77" t="inlineStr">
+      <c r="AB77" t="inlineStr">
         <is>
           <t>13.94.1</t>
         </is>
       </c>
+      <c r="AT77" s="18" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="78">
-      <c r="B78" t="n">
-        <v>62</v>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>Painting with synthetic enamel paint of approved brand and manufacture to give an even shade in two or more coats on new work in black or chocolate shade over an under coat of suitable shade with ordinary paint of approved brand and manufacture.</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Synthetic enamel paint</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Synthetic enamel paint</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>Paint/Finish</t>
         </is>
       </c>
+      <c r="K78" s="18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N78" s="18" t="n">
+        <v>77</v>
+      </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Sq.m</t>
-        </is>
-      </c>
-      <c r="W78" t="n">
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="Q78" s="18" t="n">
         <v>77</v>
       </c>
     </row>
     <row r="79">
-      <c r="B79" t="n">
-        <v>63</v>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>French spirit polishing two or more coats on new works including a coat of wood filler.</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>French polish</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>French polish, Wood filler</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
           <t>Paint/Finish</t>
         </is>
       </c>
+      <c r="K79" s="18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N79" s="18" t="n">
+        <v>13</v>
+      </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Sq.m</t>
-        </is>
-      </c>
-      <c r="W79" t="n">
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="Q79" s="18" t="n">
         <v>13</v>
       </c>
-      <c r="AC79" t="inlineStr">
+      <c r="AB79" t="inlineStr">
         <is>
           <t>13.101.1</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="B80" t="n">
-        <v>64</v>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>Making plinth protection 50 mm thick of cement concrete 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) over 75 mm bed of dry brick ballast 40 mm nominal size well rammed and consolidated and grouted with fine sand, including finishing the top smooth.</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Cement concrete</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Cement, Coarse sand, Graded stone aggregate, Brick ballast, Fine sand</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
           <t>Concrete</t>
         </is>
       </c>
+      <c r="K80" s="18" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>1:3:6</t>
+        </is>
+      </c>
+      <c r="N80" s="18" t="n">
+        <v>34.6</v>
+      </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Sq.m</t>
-        </is>
-      </c>
-      <c r="W80" t="n">
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="Q80" s="18" t="n">
         <v>34.6</v>
       </c>
-      <c r="AC80" t="n">
-        <v>16.1</v>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>16.1</t>
+        </is>
+      </c>
+      <c r="AR80" s="18" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/output/passport_filled.xlsx
+++ b/output/passport_filled.xlsx
@@ -1216,12 +1216,12 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Soil</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Soil</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
+          <t>Fine sand</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
           <t>Sand</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>Fine sand</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="K10" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L10" s="8" t="n"/>
       <c r="M10" s="8" t="n"/>
@@ -1577,7 +1577,7 @@
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Civil &amp; Sitework</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="K12" s="17" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="L12" s="8" t="n"/>
       <c r="M12" s="8" t="inlineStr">
@@ -1623,8 +1623,12 @@
       <c r="V12" s="8" t="n"/>
       <c r="W12" s="8" t="n"/>
       <c r="X12" s="8" t="n"/>
-      <c r="Y12" s="8" t="n"/>
-      <c r="Z12" s="8" t="n"/>
+      <c r="Y12" s="17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z12" s="17" t="n">
+        <v>0.149</v>
+      </c>
       <c r="AA12" s="8" t="n"/>
       <c r="AB12" s="8" t="inlineStr">
         <is>
@@ -1652,7 +1656,11 @@
       <c r="AU12" s="8" t="n"/>
       <c r="AV12" s="8" t="n"/>
       <c r="AW12" s="8" t="n"/>
-      <c r="AX12" s="8" t="n"/>
+      <c r="AX12" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n"/>
@@ -1671,7 +1679,7 @@
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Civil &amp; Sitework</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
@@ -1681,7 +1689,7 @@
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>Cement, Fine sand, Graded stone aggregate</t>
+          <t>Cement, Fine sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
@@ -1690,7 +1698,7 @@
         </is>
       </c>
       <c r="K13" s="17" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="L13" s="8" t="n"/>
       <c r="M13" s="8" t="inlineStr">
@@ -1717,8 +1725,12 @@
       <c r="V13" s="8" t="n"/>
       <c r="W13" s="8" t="n"/>
       <c r="X13" s="8" t="n"/>
-      <c r="Y13" s="8" t="n"/>
-      <c r="Z13" s="8" t="n"/>
+      <c r="Y13" s="17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z13" s="17" t="n">
+        <v>0.149</v>
+      </c>
       <c r="AA13" s="8" t="n"/>
       <c r="AB13" s="8" t="inlineStr">
         <is>
@@ -1746,7 +1758,11 @@
       <c r="AU13" s="8" t="n"/>
       <c r="AV13" s="8" t="n"/>
       <c r="AW13" s="8" t="n"/>
-      <c r="AX13" s="8" t="n"/>
+      <c r="AX13" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n"/>
@@ -1765,7 +1781,7 @@
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Civil &amp; Sitework</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -1775,7 +1791,7 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -1784,7 +1800,7 @@
         </is>
       </c>
       <c r="K14" s="17" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="L14" s="8" t="n"/>
       <c r="M14" s="8" t="inlineStr">
@@ -1811,8 +1827,12 @@
       <c r="V14" s="8" t="n"/>
       <c r="W14" s="8" t="n"/>
       <c r="X14" s="8" t="n"/>
-      <c r="Y14" s="8" t="n"/>
-      <c r="Z14" s="8" t="n"/>
+      <c r="Y14" s="17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Z14" s="17" t="n">
+        <v>0.149</v>
+      </c>
       <c r="AA14" s="8" t="n"/>
       <c r="AB14" s="8" t="inlineStr">
         <is>
@@ -1840,7 +1860,11 @@
       <c r="AU14" s="8" t="n"/>
       <c r="AV14" s="8" t="n"/>
       <c r="AW14" s="8" t="n"/>
-      <c r="AX14" s="8" t="n"/>
+      <c r="AX14" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n"/>
@@ -1869,7 +1893,7 @@
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J15" s="8" t="inlineStr">
@@ -1905,8 +1929,12 @@
       <c r="V15" s="8" t="n"/>
       <c r="W15" s="8" t="n"/>
       <c r="X15" s="8" t="n"/>
-      <c r="Y15" s="8" t="n"/>
-      <c r="Z15" s="8" t="n"/>
+      <c r="Y15" s="17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z15" s="17" t="n">
+        <v>0.149</v>
+      </c>
       <c r="AA15" s="8" t="n"/>
       <c r="AB15" s="8" t="inlineStr">
         <is>
@@ -1936,7 +1964,11 @@
       <c r="AU15" s="8" t="n"/>
       <c r="AV15" s="8" t="n"/>
       <c r="AW15" s="8" t="n"/>
-      <c r="AX15" s="8" t="n"/>
+      <c r="AX15" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n"/>
@@ -1965,7 +1997,7 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>Petroleum bitumen, Kerosene oil</t>
+          <t>Bitumen, Kerosene oil</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -2055,7 +2087,7 @@
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -2064,7 +2096,7 @@
         </is>
       </c>
       <c r="K17" s="17" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="L17" s="8" t="n"/>
       <c r="M17" s="8" t="inlineStr">
@@ -2091,8 +2123,12 @@
       <c r="V17" s="8" t="n"/>
       <c r="W17" s="8" t="n"/>
       <c r="X17" s="8" t="n"/>
-      <c r="Y17" s="8" t="n"/>
-      <c r="Z17" s="8" t="n"/>
+      <c r="Y17" s="17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z17" s="17" t="n">
+        <v>0.149</v>
+      </c>
       <c r="AA17" s="8" t="n"/>
       <c r="AB17" s="8" t="inlineStr">
         <is>
@@ -2120,7 +2156,11 @@
       <c r="AU17" s="8" t="n"/>
       <c r="AV17" s="8" t="n"/>
       <c r="AW17" s="8" t="n"/>
-      <c r="AX17" s="8" t="n"/>
+      <c r="AX17" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n"/>
@@ -2149,7 +2189,7 @@
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -2158,7 +2198,7 @@
         </is>
       </c>
       <c r="K18" s="17" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="L18" s="8" t="n"/>
       <c r="M18" s="8" t="inlineStr">
@@ -2185,8 +2225,12 @@
       <c r="V18" s="8" t="n"/>
       <c r="W18" s="8" t="n"/>
       <c r="X18" s="8" t="n"/>
-      <c r="Y18" s="8" t="n"/>
-      <c r="Z18" s="8" t="n"/>
+      <c r="Y18" s="17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Z18" s="17" t="n">
+        <v>0.149</v>
+      </c>
       <c r="AA18" s="8" t="n"/>
       <c r="AB18" s="8" t="inlineStr">
         <is>
@@ -2214,7 +2258,11 @@
       <c r="AU18" s="8" t="n"/>
       <c r="AV18" s="8" t="n"/>
       <c r="AW18" s="8" t="n"/>
-      <c r="AX18" s="8" t="n"/>
+      <c r="AX18" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n"/>
@@ -2243,7 +2291,7 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -2252,7 +2300,7 @@
         </is>
       </c>
       <c r="K19" s="17" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="L19" s="8" t="n"/>
       <c r="M19" s="8" t="inlineStr">
@@ -2279,8 +2327,12 @@
       <c r="V19" s="8" t="n"/>
       <c r="W19" s="8" t="n"/>
       <c r="X19" s="8" t="n"/>
-      <c r="Y19" s="8" t="n"/>
-      <c r="Z19" s="8" t="n"/>
+      <c r="Y19" s="17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Z19" s="17" t="n">
+        <v>0.149</v>
+      </c>
       <c r="AA19" s="8" t="n"/>
       <c r="AB19" s="8" t="inlineStr">
         <is>
@@ -2308,7 +2360,11 @@
       <c r="AU19" s="8" t="n"/>
       <c r="AV19" s="8" t="n"/>
       <c r="AW19" s="8" t="n"/>
-      <c r="AX19" s="8" t="n"/>
+      <c r="AX19" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n"/>
@@ -2337,7 +2393,7 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
@@ -2346,7 +2402,7 @@
         </is>
       </c>
       <c r="K20" s="17" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="L20" s="8" t="n"/>
       <c r="M20" s="8" t="inlineStr">
@@ -2373,8 +2429,12 @@
       <c r="V20" s="8" t="n"/>
       <c r="W20" s="8" t="n"/>
       <c r="X20" s="8" t="n"/>
-      <c r="Y20" s="8" t="n"/>
-      <c r="Z20" s="8" t="n"/>
+      <c r="Y20" s="17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z20" s="17" t="n">
+        <v>0.149</v>
+      </c>
       <c r="AA20" s="8" t="n"/>
       <c r="AB20" s="8" t="inlineStr">
         <is>
@@ -2402,7 +2462,11 @@
       <c r="AU20" s="8" t="n"/>
       <c r="AV20" s="8" t="n"/>
       <c r="AW20" s="8" t="n"/>
-      <c r="AX20" s="8" t="n"/>
+      <c r="AX20" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n"/>
@@ -2431,7 +2495,7 @@
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -2440,7 +2504,7 @@
         </is>
       </c>
       <c r="K21" s="17" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="L21" s="8" t="n"/>
       <c r="M21" s="8" t="inlineStr">
@@ -2467,8 +2531,12 @@
       <c r="V21" s="8" t="n"/>
       <c r="W21" s="8" t="n"/>
       <c r="X21" s="8" t="n"/>
-      <c r="Y21" s="8" t="n"/>
-      <c r="Z21" s="8" t="n"/>
+      <c r="Y21" s="17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Z21" s="17" t="n">
+        <v>0.149</v>
+      </c>
       <c r="AA21" s="8" t="n"/>
       <c r="AB21" s="8" t="inlineStr">
         <is>
@@ -2496,7 +2564,11 @@
       <c r="AU21" s="8" t="n"/>
       <c r="AV21" s="8" t="n"/>
       <c r="AW21" s="8" t="n"/>
-      <c r="AX21" s="8" t="n"/>
+      <c r="AX21" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n"/>
@@ -2515,7 +2587,7 @@
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Civil &amp; Sitework</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -2605,7 +2677,7 @@
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Civil &amp; Sitework</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -2695,7 +2767,7 @@
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Civil &amp; Sitework</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -2785,7 +2857,7 @@
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Civil &amp; Sitework</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -2875,7 +2947,7 @@
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Civil &amp; Sitework</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -2970,7 +3042,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>Mild steel bar</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
@@ -2984,7 +3056,7 @@
         </is>
       </c>
       <c r="K27" s="17" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="L27" s="8" t="n"/>
       <c r="M27" s="8" t="n"/>
@@ -3007,8 +3079,12 @@
       <c r="V27" s="8" t="n"/>
       <c r="W27" s="8" t="n"/>
       <c r="X27" s="8" t="n"/>
-      <c r="Y27" s="8" t="n"/>
-      <c r="Z27" s="8" t="n"/>
+      <c r="Y27" s="17" t="n">
+        <v>155</v>
+      </c>
+      <c r="Z27" s="17" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA27" s="8" t="n"/>
       <c r="AB27" s="8" t="inlineStr">
         <is>
@@ -3036,7 +3112,11 @@
       <c r="AU27" s="8" t="n"/>
       <c r="AV27" s="8" t="n"/>
       <c r="AW27" s="8" t="n"/>
-      <c r="AX27" s="8" t="n"/>
+      <c r="AX27" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n"/>
@@ -3060,7 +3140,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>Cold twisted steel</t>
+          <t>Cold twisted bar</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
@@ -3074,7 +3154,7 @@
         </is>
       </c>
       <c r="K28" s="17" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="L28" s="8" t="n"/>
       <c r="M28" s="8" t="n"/>
@@ -3097,8 +3177,12 @@
       <c r="V28" s="8" t="n"/>
       <c r="W28" s="8" t="n"/>
       <c r="X28" s="8" t="n"/>
-      <c r="Y28" s="8" t="n"/>
-      <c r="Z28" s="8" t="n"/>
+      <c r="Y28" s="17" t="n">
+        <v>2131.25</v>
+      </c>
+      <c r="Z28" s="17" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA28" s="8" t="n"/>
       <c r="AB28" s="8" t="inlineStr">
         <is>
@@ -3126,7 +3210,11 @@
       <c r="AU28" s="8" t="n"/>
       <c r="AV28" s="8" t="n"/>
       <c r="AW28" s="8" t="n"/>
-      <c r="AX28" s="8" t="n"/>
+      <c r="AX28" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n"/>
@@ -3155,7 +3243,7 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
@@ -3164,7 +3252,7 @@
         </is>
       </c>
       <c r="K29" s="17" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="L29" s="8" t="n"/>
       <c r="M29" s="8" t="inlineStr">
@@ -3191,8 +3279,12 @@
       <c r="V29" s="8" t="n"/>
       <c r="W29" s="8" t="n"/>
       <c r="X29" s="8" t="n"/>
-      <c r="Y29" s="8" t="n"/>
-      <c r="Z29" s="8" t="n"/>
+      <c r="Y29" s="17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Z29" s="17" t="n">
+        <v>0.149</v>
+      </c>
       <c r="AA29" s="8" t="n"/>
       <c r="AB29" s="8" t="inlineStr">
         <is>
@@ -3220,7 +3312,11 @@
       <c r="AU29" s="8" t="n"/>
       <c r="AV29" s="8" t="n"/>
       <c r="AW29" s="8" t="n"/>
-      <c r="AX29" s="8" t="n"/>
+      <c r="AX29" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n"/>
@@ -3233,7 +3329,7 @@
       <c r="D30" s="8" t="n"/>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Brick work with bricks of class designation___ in foundation and plinth in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
+          <t>Brick work with bricks of class designation in foundation and plinth in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
         </is>
       </c>
       <c r="F30" s="8" t="n"/>
@@ -3244,12 +3340,12 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>Burnt brick</t>
+          <t>Brick work</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>Brick, Cement, Coarse sand</t>
+          <t>Brick, Cement, Sand</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -3285,12 +3381,16 @@
       <c r="V30" s="8" t="n"/>
       <c r="W30" s="8" t="n"/>
       <c r="X30" s="8" t="n"/>
-      <c r="Y30" s="8" t="n"/>
-      <c r="Z30" s="8" t="n"/>
+      <c r="Y30" s="17" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="Z30" s="17" t="n">
+        <v>0.213</v>
+      </c>
       <c r="AA30" s="8" t="n"/>
       <c r="AB30" s="8" t="inlineStr">
         <is>
-          <t>6.1.14/6.5.1 6.5.2</t>
+          <t>6.1.14/6.5.1/6.5.2</t>
         </is>
       </c>
       <c r="AC30" s="8" t="n"/>
@@ -3314,7 +3414,11 @@
       <c r="AU30" s="8" t="n"/>
       <c r="AV30" s="8" t="n"/>
       <c r="AW30" s="8" t="n"/>
-      <c r="AX30" s="8" t="n"/>
+      <c r="AX30" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
@@ -3327,7 +3431,7 @@
       <c r="D31" s="8" t="n"/>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Brick work with bricks of class designation___ in super structure above plinth upto floor two level in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
+          <t>Brick work with bricks of class designation in super structure above plinth upto floor two level in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
         </is>
       </c>
       <c r="F31" s="8" t="n"/>
@@ -3338,12 +3442,12 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>Burnt brick</t>
+          <t>Brick work</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>Brick, Cement, Coarse sand</t>
+          <t>Brick, Cement, Sand</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -3379,12 +3483,16 @@
       <c r="V31" s="8" t="n"/>
       <c r="W31" s="8" t="n"/>
       <c r="X31" s="8" t="n"/>
-      <c r="Y31" s="8" t="n"/>
-      <c r="Z31" s="8" t="n"/>
+      <c r="Y31" s="17" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="Z31" s="17" t="n">
+        <v>0.213</v>
+      </c>
       <c r="AA31" s="8" t="n"/>
       <c r="AB31" s="8" t="inlineStr">
         <is>
-          <t>6.1.14/6.3 6.5.1/6.5.2</t>
+          <t>6.1.14/6.3/6.5.1/6.5.2</t>
         </is>
       </c>
       <c r="AC31" s="8" t="n"/>
@@ -3408,7 +3516,11 @@
       <c r="AU31" s="8" t="n"/>
       <c r="AV31" s="8" t="n"/>
       <c r="AW31" s="8" t="n"/>
-      <c r="AX31" s="8" t="n"/>
+      <c r="AX31" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n"/>
@@ -3421,7 +3533,7 @@
       <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Brick work 7 cm thick with bricks of class designation ------ in super structure upto floor two level in cement mortar 1:3 (1 cement : 3 coarse sand).</t>
+          <t>Brick work 7 cm thick with bricks of class designation in super structure upto floor two level in cement mortar 1:3 (1 cement : 3 coarse sand).</t>
         </is>
       </c>
       <c r="F32" s="8" t="n"/>
@@ -3432,12 +3544,12 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>Burnt brick</t>
+          <t>Brick work</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>Brick, Cement, Coarse sand</t>
+          <t>Brick, Cement, Sand</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
@@ -3473,12 +3585,16 @@
       <c r="V32" s="8" t="n"/>
       <c r="W32" s="8" t="n"/>
       <c r="X32" s="8" t="n"/>
-      <c r="Y32" s="8" t="n"/>
-      <c r="Z32" s="8" t="n"/>
+      <c r="Y32" s="17" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="Z32" s="17" t="n">
+        <v>0.213</v>
+      </c>
       <c r="AA32" s="8" t="n"/>
       <c r="AB32" s="8" t="inlineStr">
         <is>
-          <t>6.13/6.21/ 6.5.1/6.5.2</t>
+          <t>6.13/6.21/6.5.1/6.5.2</t>
         </is>
       </c>
       <c r="AC32" s="8" t="n"/>
@@ -3504,7 +3620,11 @@
       <c r="AU32" s="8" t="n"/>
       <c r="AV32" s="8" t="n"/>
       <c r="AW32" s="8" t="n"/>
-      <c r="AX32" s="8" t="n"/>
+      <c r="AX32" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n"/>
@@ -3517,7 +3637,7 @@
       <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Half brick masonry with bricks of class designation ____ in foundation &amp; plinth in cement mortar 1:4 (1 cement : 4 coarse sand)</t>
+          <t>Half brick masonry with bricks of class designation in foundation &amp; plinth in cement mortar 1:4 (1 cement : 4 coarse sand)</t>
         </is>
       </c>
       <c r="F33" s="8" t="n"/>
@@ -3528,12 +3648,12 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>Burnt brick</t>
+          <t>Brick masonry</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>Brick, Cement, Coarse sand</t>
+          <t>Brick, Cement, Sand</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
@@ -3569,12 +3689,16 @@
       <c r="V33" s="8" t="n"/>
       <c r="W33" s="8" t="n"/>
       <c r="X33" s="8" t="n"/>
-      <c r="Y33" s="8" t="n"/>
-      <c r="Z33" s="8" t="n"/>
+      <c r="Y33" s="17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z33" s="17" t="n">
+        <v>0.213</v>
+      </c>
       <c r="AA33" s="8" t="n"/>
       <c r="AB33" s="8" t="inlineStr">
         <is>
-          <t>6.18.4/6.21 6.5.1/6.5.2</t>
+          <t>6.18.4/6.21/6.5.1/6.5.2</t>
         </is>
       </c>
       <c r="AC33" s="8" t="n"/>
@@ -3598,7 +3722,11 @@
       <c r="AU33" s="8" t="n"/>
       <c r="AV33" s="8" t="n"/>
       <c r="AW33" s="8" t="n"/>
-      <c r="AX33" s="8" t="n"/>
+      <c r="AX33" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n"/>
@@ -3611,7 +3739,7 @@
       <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Half brick masonry with bricks of class designation ____ in super structure upto floor two level in cement mortar 1:4 (1 cement : 4 coarse sand).</t>
+          <t>Half brick masonry with bricks of class designation in super structure upto floor two level in cement mortar 1:4 (1 cement : 4 coarse sand).</t>
         </is>
       </c>
       <c r="F34" s="8" t="n"/>
@@ -3622,12 +3750,12 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>Burnt brick</t>
+          <t>Brick masonry</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>Brick, Cement, Coarse sand</t>
+          <t>Brick, Cement, Sand</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -3663,12 +3791,16 @@
       <c r="V34" s="8" t="n"/>
       <c r="W34" s="8" t="n"/>
       <c r="X34" s="8" t="n"/>
-      <c r="Y34" s="8" t="n"/>
-      <c r="Z34" s="8" t="n"/>
+      <c r="Y34" s="17" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="Z34" s="17" t="n">
+        <v>0.213</v>
+      </c>
       <c r="AA34" s="8" t="n"/>
       <c r="AB34" s="8" t="inlineStr">
         <is>
-          <t>6.18.4/6.19.1 6.20/6.21.1/ 6.21.2</t>
+          <t>6.18.4/6.19.1/6.20/6.21.1/6.21.2</t>
         </is>
       </c>
       <c r="AC34" s="8" t="n"/>
@@ -3692,7 +3824,11 @@
       <c r="AU34" s="8" t="n"/>
       <c r="AV34" s="8" t="n"/>
       <c r="AW34" s="8" t="n"/>
-      <c r="AX34" s="8" t="n"/>
+      <c r="AX34" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n"/>
@@ -3705,7 +3841,7 @@
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Providing ________ wood work in frames of doors, windows, clerestory windows and other frames, wrought framed and fixed in position.</t>
+          <t>Providing wood work in frames of doors, windows, clerestory windows and other frames, wrought framed and fixed in position.</t>
         </is>
       </c>
       <c r="F35" s="8" t="n"/>
@@ -3716,7 +3852,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Wood work</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
@@ -3753,8 +3889,12 @@
       <c r="V35" s="8" t="n"/>
       <c r="W35" s="8" t="n"/>
       <c r="X35" s="8" t="n"/>
-      <c r="Y35" s="8" t="n"/>
-      <c r="Z35" s="8" t="n"/>
+      <c r="Y35" s="17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Z35" s="17" t="n">
+        <v>0.306</v>
+      </c>
       <c r="AA35" s="8" t="n"/>
       <c r="AB35" s="8" t="n"/>
       <c r="AC35" s="8" t="n"/>
@@ -3778,7 +3918,11 @@
       <c r="AU35" s="8" t="n"/>
       <c r="AV35" s="8" t="n"/>
       <c r="AW35" s="8" t="n"/>
-      <c r="AX35" s="8" t="n"/>
+      <c r="AX35" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n"/>
@@ -3791,7 +3935,7 @@
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing 35 mm thick battened and framed door shutters of ________ wood including bright finished or/and black enamelled MS butt hinges with necessary screws.</t>
+          <t>Providing and fixing 35 mm thick battended and framed door shutters of wood including bright finished or/and black enamelled MS butt hinges with necessary screws.</t>
         </is>
       </c>
       <c r="F36" s="8" t="n"/>
@@ -3802,12 +3946,12 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Wood door shutters</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>Wood, Mild steel</t>
+          <t>Wood, MS butt hinges</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
@@ -3839,8 +3983,12 @@
       <c r="V36" s="8" t="n"/>
       <c r="W36" s="8" t="n"/>
       <c r="X36" s="8" t="n"/>
-      <c r="Y36" s="8" t="n"/>
-      <c r="Z36" s="8" t="n"/>
+      <c r="Y36" s="17" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="Z36" s="17" t="n">
+        <v>0.306</v>
+      </c>
       <c r="AA36" s="8" t="n"/>
       <c r="AB36" s="8" t="n"/>
       <c r="AC36" s="8" t="n"/>
@@ -3866,7 +4014,11 @@
       <c r="AU36" s="8" t="n"/>
       <c r="AV36" s="8" t="n"/>
       <c r="AW36" s="8" t="n"/>
-      <c r="AX36" s="8" t="n"/>
+      <c r="AX36" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n"/>
@@ -3890,12 +4042,12 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>Flush door</t>
+          <t>Flush door shutter</t>
         </is>
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>Hard wood, Teak ply, Commercial ply, Mild steel</t>
+          <t>Block board, Hard wood, Teak ply, Commercial ply, MS piano hinges</t>
         </is>
       </c>
       <c r="J37" s="8" t="inlineStr">
@@ -3927,8 +4079,12 @@
       <c r="V37" s="8" t="n"/>
       <c r="W37" s="8" t="n"/>
       <c r="X37" s="8" t="n"/>
-      <c r="Y37" s="8" t="n"/>
-      <c r="Z37" s="8" t="n"/>
+      <c r="Y37" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z37" s="17" t="n">
+        <v>0.306</v>
+      </c>
       <c r="AA37" s="8" t="n"/>
       <c r="AB37" s="8" t="inlineStr">
         <is>
@@ -3958,7 +4114,11 @@
       <c r="AU37" s="8" t="n"/>
       <c r="AV37" s="8" t="n"/>
       <c r="AW37" s="8" t="n"/>
-      <c r="AX37" s="8" t="n"/>
+      <c r="AX37" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n"/>
@@ -3977,12 +4137,12 @@
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>Finishes</t>
+          <t>Civil &amp; Sitework</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>Teak wood</t>
+          <t>Teak wood plugs</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
@@ -4023,8 +4183,12 @@
       <c r="V38" s="8" t="n"/>
       <c r="W38" s="8" t="n"/>
       <c r="X38" s="8" t="n"/>
-      <c r="Y38" s="8" t="n"/>
-      <c r="Z38" s="8" t="n"/>
+      <c r="Y38" s="17" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="Z38" s="17" t="n">
+        <v>0.306</v>
+      </c>
       <c r="AA38" s="8" t="n"/>
       <c r="AB38" s="8" t="inlineStr">
         <is>
@@ -4052,7 +4216,11 @@
       <c r="AU38" s="8" t="n"/>
       <c r="AV38" s="8" t="n"/>
       <c r="AW38" s="8" t="n"/>
-      <c r="AX38" s="8" t="n"/>
+      <c r="AX38" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n"/>
@@ -4065,7 +4233,7 @@
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing M.S.oxidised fan light .ventilator catch with necessary screws etc. complete.</t>
+          <t>Providing and fixing M.S.oxidised fan light ventilator catch with necessary screws etc. complete.</t>
         </is>
       </c>
       <c r="F39" s="8" t="n"/>
@@ -4076,12 +4244,12 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>M.S. oxidised fan light ventilator catch</t>
         </is>
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>M.S.</t>
         </is>
       </c>
       <c r="J39" s="8" t="inlineStr">
@@ -4090,7 +4258,7 @@
         </is>
       </c>
       <c r="K39" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L39" s="8" t="n"/>
       <c r="M39" s="8" t="n"/>
@@ -4113,8 +4281,12 @@
       <c r="V39" s="8" t="n"/>
       <c r="W39" s="8" t="n"/>
       <c r="X39" s="8" t="n"/>
-      <c r="Y39" s="8" t="n"/>
-      <c r="Z39" s="8" t="n"/>
+      <c r="Y39" s="17" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z39" s="17" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA39" s="8" t="n"/>
       <c r="AB39" s="8" t="n"/>
       <c r="AC39" s="8" t="n"/>
@@ -4138,7 +4310,11 @@
       <c r="AU39" s="8" t="n"/>
       <c r="AV39" s="8" t="n"/>
       <c r="AW39" s="8" t="n"/>
-      <c r="AX39" s="8" t="n"/>
+      <c r="AX39" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n"/>
@@ -4151,7 +4327,7 @@
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing 90 mm oxidised M.S. hasp and staple (safety type) with necessaary screws etc. complete.</t>
+          <t>Providing and fixing 90 mm oxidised M.S. hasp and staple (safety type) with necessary screws etc. complete.</t>
         </is>
       </c>
       <c r="F40" s="8" t="n"/>
@@ -4162,12 +4338,12 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>Oxidised M.S. hasp and staple</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>M.S.</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
@@ -4176,7 +4352,7 @@
         </is>
       </c>
       <c r="K40" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L40" s="8" t="n"/>
       <c r="M40" s="8" t="n"/>
@@ -4199,8 +4375,12 @@
       <c r="V40" s="8" t="n"/>
       <c r="W40" s="8" t="n"/>
       <c r="X40" s="8" t="n"/>
-      <c r="Y40" s="8" t="n"/>
-      <c r="Z40" s="8" t="n"/>
+      <c r="Y40" s="17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Z40" s="17" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA40" s="8" t="n"/>
       <c r="AB40" s="8" t="inlineStr">
         <is>
@@ -4228,7 +4408,11 @@
       <c r="AU40" s="8" t="n"/>
       <c r="AV40" s="8" t="n"/>
       <c r="AW40" s="8" t="n"/>
-      <c r="AX40" s="8" t="n"/>
+      <c r="AX40" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n"/>
@@ -4252,7 +4436,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Aluminium sliding door bolts</t>
         </is>
       </c>
       <c r="I41" s="8" t="inlineStr">
@@ -4344,7 +4528,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Aluminium tower bolts</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
@@ -4436,7 +4620,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Aluminium tower bolts</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
@@ -4528,7 +4712,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Aluminium handles</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">
@@ -4618,7 +4802,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Aluminium handles</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
@@ -4708,7 +4892,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Aluminium door stopper</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
@@ -4798,12 +4982,12 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Steel glazed windows</t>
         </is>
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>Steel, Cement, Coarse sand, Graded stone aggregate, Glass</t>
+          <t>Steel, Cement, Coarse sand, Stone aggregate, Glass, Putty</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
@@ -4839,8 +5023,12 @@
       <c r="V47" s="8" t="n"/>
       <c r="W47" s="8" t="n"/>
       <c r="X47" s="8" t="n"/>
-      <c r="Y47" s="8" t="n"/>
-      <c r="Z47" s="8" t="n"/>
+      <c r="Y47" s="17" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="Z47" s="17" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA47" s="8" t="n"/>
       <c r="AB47" s="8" t="inlineStr">
         <is>
@@ -4870,7 +5058,11 @@
       <c r="AU47" s="8" t="n"/>
       <c r="AV47" s="8" t="n"/>
       <c r="AW47" s="8" t="n"/>
-      <c r="AX47" s="8" t="n"/>
+      <c r="AX47" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n"/>
@@ -4894,12 +5086,12 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Steel glazed ventilators</t>
         </is>
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>Steel, Cement, Coarse sand, Graded stone aggregate, Glass</t>
+          <t>Steel, Cement, Coarse sand, Stone aggregate, Glass, Putty</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
@@ -4935,8 +5127,12 @@
       <c r="V48" s="8" t="n"/>
       <c r="W48" s="8" t="n"/>
       <c r="X48" s="8" t="n"/>
-      <c r="Y48" s="8" t="n"/>
-      <c r="Z48" s="8" t="n"/>
+      <c r="Y48" s="17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z48" s="17" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA48" s="8" t="n"/>
       <c r="AB48" s="8" t="inlineStr">
         <is>
@@ -4966,7 +5162,11 @@
       <c r="AU48" s="8" t="n"/>
       <c r="AV48" s="8" t="n"/>
       <c r="AW48" s="8" t="n"/>
-      <c r="AX48" s="8" t="n"/>
+      <c r="AX48" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n"/>
@@ -4990,7 +5190,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>Mild steel casement window fastners</t>
         </is>
       </c>
       <c r="I49" s="8" t="inlineStr">
@@ -5027,8 +5227,12 @@
       <c r="V49" s="8" t="n"/>
       <c r="W49" s="8" t="n"/>
       <c r="X49" s="8" t="n"/>
-      <c r="Y49" s="8" t="n"/>
-      <c r="Z49" s="8" t="n"/>
+      <c r="Y49" s="17" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="Z49" s="17" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA49" s="8" t="n"/>
       <c r="AB49" s="8" t="inlineStr">
         <is>
@@ -5056,7 +5260,11 @@
       <c r="AU49" s="8" t="n"/>
       <c r="AV49" s="8" t="n"/>
       <c r="AW49" s="8" t="n"/>
-      <c r="AX49" s="8" t="n"/>
+      <c r="AX49" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n"/>
@@ -5069,7 +5277,7 @@
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium casement stays anodised transparent or dyed to requird colour and shade with with necessary welding and machine screws etc. complete.</t>
+          <t>Providing and fixing aluminium casement stays anodised transparent or dyed to required colour and shade with with necessary welding and machine screws etc. complete.</t>
         </is>
       </c>
       <c r="F50" s="8" t="n"/>
@@ -5080,7 +5288,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Aluminium casement stays</t>
         </is>
       </c>
       <c r="I50" s="8" t="inlineStr">
@@ -5170,12 +5378,12 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>M S Guard Flats</t>
         </is>
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>Mild steel, Steel primer</t>
+          <t>MS, Steel primer</t>
         </is>
       </c>
       <c r="J51" s="8" t="inlineStr">
@@ -5207,8 +5415,12 @@
       <c r="V51" s="8" t="n"/>
       <c r="W51" s="8" t="n"/>
       <c r="X51" s="8" t="n"/>
-      <c r="Y51" s="8" t="n"/>
-      <c r="Z51" s="8" t="n"/>
+      <c r="Y51" s="17" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="Z51" s="17" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA51" s="8" t="n"/>
       <c r="AB51" s="8" t="inlineStr">
         <is>
@@ -5238,7 +5450,11 @@
       <c r="AU51" s="8" t="n"/>
       <c r="AV51" s="8" t="n"/>
       <c r="AW51" s="8" t="n"/>
-      <c r="AX51" s="8" t="n"/>
+      <c r="AX51" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="n"/>
@@ -5262,12 +5478,12 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>T-Iron frames</t>
         </is>
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>Mild steel, Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Mild steel, Cement, Sand, Stone aggregate, Steel primer</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr">
@@ -5303,8 +5519,12 @@
       <c r="V52" s="8" t="n"/>
       <c r="W52" s="8" t="n"/>
       <c r="X52" s="8" t="n"/>
-      <c r="Y52" s="8" t="n"/>
-      <c r="Z52" s="8" t="n"/>
+      <c r="Y52" s="17" t="n">
+        <v>289.85</v>
+      </c>
+      <c r="Z52" s="17" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA52" s="8" t="n"/>
       <c r="AB52" s="8" t="inlineStr">
         <is>
@@ -5332,7 +5552,11 @@
       <c r="AU52" s="8" t="n"/>
       <c r="AV52" s="8" t="n"/>
       <c r="AW52" s="8" t="n"/>
-      <c r="AX52" s="8" t="n"/>
+      <c r="AX52" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n"/>
@@ -5356,12 +5580,12 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>MS fan clamp</t>
         </is>
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>MS bar, Paint</t>
         </is>
       </c>
       <c r="J53" s="8" t="inlineStr">
@@ -5393,8 +5617,12 @@
       <c r="V53" s="8" t="n"/>
       <c r="W53" s="8" t="n"/>
       <c r="X53" s="8" t="n"/>
-      <c r="Y53" s="8" t="n"/>
-      <c r="Z53" s="8" t="n"/>
+      <c r="Y53" s="17" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="Z53" s="17" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA53" s="8" t="n"/>
       <c r="AB53" s="8" t="inlineStr">
         <is>
@@ -5424,7 +5652,11 @@
       <c r="AU53" s="8" t="n"/>
       <c r="AV53" s="8" t="n"/>
       <c r="AW53" s="8" t="n"/>
-      <c r="AX53" s="8" t="n"/>
+      <c r="AX53" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="n"/>
@@ -5448,12 +5680,12 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>Cement concrete</t>
+          <t>Cement concrete flooring</t>
         </is>
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
@@ -5462,7 +5694,7 @@
         </is>
       </c>
       <c r="K54" s="17" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="L54" s="8" t="n"/>
       <c r="M54" s="8" t="inlineStr">
@@ -5489,8 +5721,12 @@
       <c r="V54" s="8" t="n"/>
       <c r="W54" s="8" t="n"/>
       <c r="X54" s="8" t="n"/>
-      <c r="Y54" s="8" t="n"/>
-      <c r="Z54" s="8" t="n"/>
+      <c r="Y54" s="17" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="Z54" s="17" t="n">
+        <v>0.149</v>
+      </c>
       <c r="AA54" s="8" t="n"/>
       <c r="AB54" s="8" t="inlineStr">
         <is>
@@ -5520,7 +5756,11 @@
       <c r="AU54" s="8" t="n"/>
       <c r="AV54" s="8" t="n"/>
       <c r="AW54" s="8" t="n"/>
-      <c r="AX54" s="8" t="n"/>
+      <c r="AX54" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n"/>
@@ -5544,7 +5784,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>Cement plaster</t>
+          <t>Cement plaster skirting</t>
         </is>
       </c>
       <c r="I55" s="8" t="inlineStr">
@@ -5585,8 +5825,12 @@
       <c r="V55" s="8" t="n"/>
       <c r="W55" s="8" t="n"/>
       <c r="X55" s="8" t="n"/>
-      <c r="Y55" s="8" t="n"/>
-      <c r="Z55" s="8" t="n"/>
+      <c r="Y55" s="17" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="Z55" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="AA55" s="8" t="n"/>
       <c r="AB55" s="8" t="inlineStr">
         <is>
@@ -5616,7 +5860,11 @@
       <c r="AU55" s="8" t="n"/>
       <c r="AV55" s="8" t="n"/>
       <c r="AW55" s="8" t="n"/>
-      <c r="AX55" s="8" t="n"/>
+      <c r="AX55" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n"/>
@@ -5640,17 +5888,17 @@
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>Marble chips</t>
+          <t>Marble chips flooring</t>
         </is>
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate, Marble chips, Marble powder</t>
+          <t>Cement, Sand, Stone aggregate, Marble chips, Marble powder, Pigment</t>
         </is>
       </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish</t>
+          <t>Finishes</t>
         </is>
       </c>
       <c r="K56" s="17" t="n">
@@ -5736,21 +5984,21 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
+          <t>Glass strips</t>
+        </is>
+      </c>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
           <t>Glass</t>
         </is>
       </c>
-      <c r="I57" s="8" t="inlineStr">
-        <is>
-          <t>Glass</t>
-        </is>
-      </c>
       <c r="J57" s="8" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
       <c r="K57" s="17" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L57" s="8" t="n"/>
       <c r="M57" s="8" t="n"/>
@@ -5817,13 +6065,13 @@
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>Painting top of roofs with bitumen of approved quality at 17 Kg. per 10 square metre impregnated with a coat of coarse sand at 3/2 60 dm per 10 m including cleaning the slab surface with brushes and finally with a piece of cloth lightly soaked in kerosene oil complete with residual type petroleum bitumen of penetration 80/100.</t>
+          <t>Painting top of roofs with bitumen of approved quality at 17 Kg. per 10 square metre impregnated with a coat of coarse sand at 3/60 dm3 per 10 m2 including cleaning the slab surface with brushes and finally with a piece of cloth lightly soaked in kerosene oil complete with residual type petroleum bitumen of penetration 80/100.</t>
         </is>
       </c>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>Finishes</t>
+          <t>Civil &amp; Sitework</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
@@ -5842,7 +6090,7 @@
         </is>
       </c>
       <c r="K58" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L58" s="8" t="n"/>
       <c r="M58" s="8" t="n"/>
@@ -5865,8 +6113,12 @@
       <c r="V58" s="8" t="n"/>
       <c r="W58" s="8" t="n"/>
       <c r="X58" s="8" t="n"/>
-      <c r="Y58" s="8" t="n"/>
-      <c r="Z58" s="8" t="n"/>
+      <c r="Y58" s="17" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="Z58" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="AA58" s="8" t="n"/>
       <c r="AB58" s="8" t="inlineStr">
         <is>
@@ -5894,7 +6146,11 @@
       <c r="AU58" s="8" t="n"/>
       <c r="AV58" s="8" t="n"/>
       <c r="AW58" s="8" t="n"/>
-      <c r="AX58" s="8" t="n"/>
+      <c r="AX58" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n"/>
@@ -5913,17 +6169,17 @@
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>Finishes</t>
+          <t>Civil &amp; Sitework</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>Lime concrete</t>
+          <t>Lime concrete terracing</t>
         </is>
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>Lime, Brick aggregate, Surkhi, Brick tiles, Cement, Fine sand, Crude oil</t>
+          <t>Brick aggregate, Lime putty, Surkhi, Gur, Belgiri, Brick tiles, Cement, Fine sand, Crude oil</t>
         </is>
       </c>
       <c r="J59" s="8" t="inlineStr">
@@ -5959,8 +6215,12 @@
       <c r="V59" s="8" t="n"/>
       <c r="W59" s="8" t="n"/>
       <c r="X59" s="8" t="n"/>
-      <c r="Y59" s="8" t="n"/>
-      <c r="Z59" s="8" t="n"/>
+      <c r="Y59" s="17" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="Z59" s="17" t="n">
+        <v>0.149</v>
+      </c>
       <c r="AA59" s="8" t="n"/>
       <c r="AB59" s="8" t="inlineStr">
         <is>
@@ -5990,7 +6250,11 @@
       <c r="AU59" s="8" t="n"/>
       <c r="AV59" s="8" t="n"/>
       <c r="AW59" s="8" t="n"/>
-      <c r="AX59" s="8" t="n"/>
+      <c r="AX59" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n"/>
@@ -6014,12 +6278,12 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>Burnt clay tile</t>
+          <t>Burnt clay tiles</t>
         </is>
       </c>
       <c r="I60" s="8" t="inlineStr">
         <is>
-          <t>Burnt clay tile, Cement, Fine sand</t>
+          <t>Clay tiles, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J60" s="8" t="inlineStr">
@@ -6055,8 +6319,12 @@
       <c r="V60" s="8" t="n"/>
       <c r="W60" s="8" t="n"/>
       <c r="X60" s="8" t="n"/>
-      <c r="Y60" s="8" t="n"/>
-      <c r="Z60" s="8" t="n"/>
+      <c r="Y60" s="17" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="Z60" s="17" t="n">
+        <v>0.213</v>
+      </c>
       <c r="AA60" s="8" t="n"/>
       <c r="AB60" s="8" t="inlineStr">
         <is>
@@ -6086,7 +6354,11 @@
       <c r="AU60" s="8" t="n"/>
       <c r="AV60" s="8" t="n"/>
       <c r="AW60" s="8" t="n"/>
-      <c r="AX60" s="8" t="n"/>
+      <c r="AX60" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n"/>
@@ -6110,12 +6382,12 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>Cement concrete</t>
+          <t>Cement concrete gola</t>
         </is>
       </c>
       <c r="I61" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate, Brick tile</t>
+          <t>Cement, Coarse sand, Stone aggregate, Brick tiles</t>
         </is>
       </c>
       <c r="J61" s="8" t="inlineStr">
@@ -6151,8 +6423,12 @@
       <c r="V61" s="8" t="n"/>
       <c r="W61" s="8" t="n"/>
       <c r="X61" s="8" t="n"/>
-      <c r="Y61" s="8" t="n"/>
-      <c r="Z61" s="8" t="n"/>
+      <c r="Y61" s="17" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="Z61" s="17" t="n">
+        <v>0.149</v>
+      </c>
       <c r="AA61" s="8" t="n"/>
       <c r="AB61" s="8" t="inlineStr">
         <is>
@@ -6180,7 +6456,11 @@
       <c r="AU61" s="8" t="n"/>
       <c r="AV61" s="8" t="n"/>
       <c r="AW61" s="8" t="n"/>
-      <c r="AX61" s="8" t="n"/>
+      <c r="AX61" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="n"/>
@@ -6204,12 +6484,12 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>Cement concrete</t>
+          <t>Cement concrete khurras</t>
         </is>
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate, PVC sheet</t>
+          <t>Cement, Coarse sand, Stone aggregate, PVC sheet</t>
         </is>
       </c>
       <c r="J62" s="8" t="inlineStr">
@@ -6245,8 +6525,12 @@
       <c r="V62" s="8" t="n"/>
       <c r="W62" s="8" t="n"/>
       <c r="X62" s="8" t="n"/>
-      <c r="Y62" s="8" t="n"/>
-      <c r="Z62" s="8" t="n"/>
+      <c r="Y62" s="17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Z62" s="17" t="n">
+        <v>0.149</v>
+      </c>
       <c r="AA62" s="8" t="n"/>
       <c r="AB62" s="8" t="inlineStr">
         <is>
@@ -6276,7 +6560,11 @@
       <c r="AU62" s="8" t="n"/>
       <c r="AV62" s="8" t="n"/>
       <c r="AW62" s="8" t="n"/>
-      <c r="AX62" s="8" t="n"/>
+      <c r="AX62" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n"/>
@@ -6300,12 +6588,12 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>Cast iron</t>
+          <t>CI rain water pipe</t>
         </is>
       </c>
       <c r="I63" s="8" t="inlineStr">
         <is>
-          <t>Cast iron, Cement, Fine sand</t>
+          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J63" s="8" t="inlineStr">
@@ -6396,12 +6684,12 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>MS holderbat clamps</t>
         </is>
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>Mild steel, Cement, Coarse sand, Graded stone aggregate</t>
+          <t>MS, Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J64" s="8" t="inlineStr">
@@ -6437,8 +6725,12 @@
       <c r="V64" s="8" t="n"/>
       <c r="W64" s="8" t="n"/>
       <c r="X64" s="8" t="n"/>
-      <c r="Y64" s="8" t="n"/>
-      <c r="Z64" s="8" t="n"/>
+      <c r="Y64" s="17" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="Z64" s="17" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA64" s="8" t="n"/>
       <c r="AB64" s="8" t="inlineStr">
         <is>
@@ -6468,7 +6760,11 @@
       <c r="AU64" s="8" t="n"/>
       <c r="AV64" s="8" t="n"/>
       <c r="AW64" s="8" t="n"/>
-      <c r="AX64" s="8" t="n"/>
+      <c r="AX64" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n"/>
@@ -6481,7 +6777,7 @@
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand). CI plain head 100 mm dia</t>
+          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) CI plain head 100 mm dia</t>
         </is>
       </c>
       <c r="F65" s="8" t="n"/>
@@ -6492,12 +6788,12 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>Cast iron</t>
+          <t>CI plain head</t>
         </is>
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>Cast iron, Cement, Fine sand</t>
+          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J65" s="8" t="inlineStr">
@@ -6577,7 +6873,7 @@
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand). CI plain shoe - 100 mm dia</t>
+          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) CI plain shoe - 100 mm dia</t>
         </is>
       </c>
       <c r="F66" s="8" t="n"/>
@@ -6588,12 +6884,12 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>Cast iron</t>
+          <t>CI plain shoe</t>
         </is>
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>Cast iron, Cement, Fine sand</t>
+          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J66" s="8" t="inlineStr">
@@ -6673,7 +6969,7 @@
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand). CI plain bend - 100 mm dia</t>
+          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) CI plain bend - 100 mm dia</t>
         </is>
       </c>
       <c r="F67" s="8" t="n"/>
@@ -6684,12 +6980,12 @@
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>Cast iron</t>
+          <t>CI plain bend</t>
         </is>
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>Cast iron, Cement, Fine sand</t>
+          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J67" s="8" t="inlineStr">
@@ -6821,8 +7117,12 @@
       <c r="V68" s="8" t="n"/>
       <c r="W68" s="8" t="n"/>
       <c r="X68" s="8" t="n"/>
-      <c r="Y68" s="8" t="n"/>
-      <c r="Z68" s="8" t="n"/>
+      <c r="Y68" s="17" t="n">
+        <v>209</v>
+      </c>
+      <c r="Z68" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="AA68" s="8" t="n"/>
       <c r="AB68" s="8" t="inlineStr">
         <is>
@@ -6852,7 +7152,11 @@
       <c r="AU68" s="8" t="n"/>
       <c r="AV68" s="8" t="n"/>
       <c r="AW68" s="8" t="n"/>
-      <c r="AX68" s="8" t="n"/>
+      <c r="AX68" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n"/>
@@ -6917,8 +7221,12 @@
       <c r="V69" s="8" t="n"/>
       <c r="W69" s="8" t="n"/>
       <c r="X69" s="8" t="n"/>
-      <c r="Y69" s="8" t="n"/>
-      <c r="Z69" s="8" t="n"/>
+      <c r="Y69" s="17" t="n">
+        <v>209</v>
+      </c>
+      <c r="Z69" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="AA69" s="8" t="n"/>
       <c r="AB69" s="8" t="inlineStr">
         <is>
@@ -6948,7 +7256,11 @@
       <c r="AU69" s="8" t="n"/>
       <c r="AV69" s="8" t="n"/>
       <c r="AW69" s="8" t="n"/>
-      <c r="AX69" s="8" t="n"/>
+      <c r="AX69" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="n"/>
@@ -7013,8 +7325,12 @@
       <c r="V70" s="8" t="n"/>
       <c r="W70" s="8" t="n"/>
       <c r="X70" s="8" t="n"/>
-      <c r="Y70" s="8" t="n"/>
-      <c r="Z70" s="8" t="n"/>
+      <c r="Y70" s="17" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="Z70" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="AA70" s="8" t="n"/>
       <c r="AB70" s="8" t="inlineStr">
         <is>
@@ -7044,7 +7360,11 @@
       <c r="AU70" s="8" t="n"/>
       <c r="AV70" s="8" t="n"/>
       <c r="AW70" s="8" t="n"/>
-      <c r="AX70" s="8" t="n"/>
+      <c r="AX70" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n"/>
@@ -7068,12 +7388,12 @@
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>Terrazzo plaster</t>
+          <t>Terrazzo plastering</t>
         </is>
       </c>
       <c r="I71" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Marble chips, Marble powder</t>
+          <t>Cement, Sand, Marble chips, Marble powder</t>
         </is>
       </c>
       <c r="J71" s="8" t="inlineStr">
@@ -7109,12 +7429,16 @@
       <c r="V71" s="8" t="n"/>
       <c r="W71" s="8" t="n"/>
       <c r="X71" s="8" t="n"/>
-      <c r="Y71" s="8" t="n"/>
-      <c r="Z71" s="8" t="n"/>
+      <c r="Y71" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z71" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="AA71" s="8" t="n"/>
       <c r="AB71" s="8" t="inlineStr">
         <is>
-          <t>5.31/13.24.1</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AC71" s="8" t="n"/>
@@ -7140,7 +7464,11 @@
       <c r="AU71" s="8" t="n"/>
       <c r="AV71" s="8" t="n"/>
       <c r="AW71" s="8" t="n"/>
-      <c r="AX71" s="8" t="n"/>
+      <c r="AX71" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n"/>
@@ -7164,7 +7492,7 @@
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>Cement mortar</t>
+          <t>Cement mortar plaster</t>
         </is>
       </c>
       <c r="I72" s="8" t="inlineStr">
@@ -7205,12 +7533,16 @@
       <c r="V72" s="8" t="n"/>
       <c r="W72" s="8" t="n"/>
       <c r="X72" s="8" t="n"/>
-      <c r="Y72" s="8" t="n"/>
-      <c r="Z72" s="8" t="n"/>
+      <c r="Y72" s="17" t="n">
+        <v>147.25</v>
+      </c>
+      <c r="Z72" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="AA72" s="8" t="n"/>
       <c r="AB72" s="8" t="inlineStr">
         <is>
-          <t>13.70.1</t>
+          <t>5.31/13.24.1</t>
         </is>
       </c>
       <c r="AC72" s="8" t="n"/>
@@ -7234,7 +7566,11 @@
       <c r="AU72" s="8" t="n"/>
       <c r="AV72" s="8" t="n"/>
       <c r="AW72" s="8" t="n"/>
-      <c r="AX72" s="8" t="n"/>
+      <c r="AX72" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n"/>
@@ -7258,7 +7594,7 @@
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>Lime wash</t>
+          <t>Lime white wash</t>
         </is>
       </c>
       <c r="I73" s="8" t="inlineStr">
@@ -7295,12 +7631,16 @@
       <c r="V73" s="8" t="n"/>
       <c r="W73" s="8" t="n"/>
       <c r="X73" s="8" t="n"/>
-      <c r="Y73" s="8" t="n"/>
-      <c r="Z73" s="8" t="n"/>
+      <c r="Y73" s="17" t="n">
+        <v>270.75</v>
+      </c>
+      <c r="Z73" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="AA73" s="8" t="n"/>
       <c r="AB73" s="8" t="inlineStr">
         <is>
-          <t>13.73.1</t>
+          <t>13.70.1</t>
         </is>
       </c>
       <c r="AC73" s="8" t="n"/>
@@ -7324,7 +7664,11 @@
       <c r="AU73" s="8" t="n"/>
       <c r="AV73" s="8" t="n"/>
       <c r="AW73" s="8" t="n"/>
-      <c r="AX73" s="8" t="n"/>
+      <c r="AX73" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="n"/>
@@ -7337,7 +7681,7 @@
       <c r="D74" s="8" t="n"/>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Colour washing such as green, blue or buff to give an even shade on new work (two. or more coats) with a base coat of white washing with lime.</t>
+          <t>Colour washing such as green, blue or buff to give an even shade on new work (two or more coats) with a base coat of white washing with lime.</t>
         </is>
       </c>
       <c r="F74" s="8" t="n"/>
@@ -7353,7 +7697,7 @@
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
-          <t>Lime</t>
+          <t>Lime, Colour wash</t>
         </is>
       </c>
       <c r="J74" s="8" t="inlineStr">
@@ -7385,12 +7729,16 @@
       <c r="V74" s="8" t="n"/>
       <c r="W74" s="8" t="n"/>
       <c r="X74" s="8" t="n"/>
-      <c r="Y74" s="8" t="n"/>
-      <c r="Z74" s="8" t="n"/>
+      <c r="Y74" s="17" t="n">
+        <v>270.75</v>
+      </c>
+      <c r="Z74" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="AA74" s="8" t="n"/>
       <c r="AB74" s="8" t="inlineStr">
         <is>
-          <t>13.81.1</t>
+          <t>13.73.1</t>
         </is>
       </c>
       <c r="AC74" s="8" t="n"/>
@@ -7414,7 +7762,11 @@
       <c r="AU74" s="8" t="n"/>
       <c r="AV74" s="8" t="n"/>
       <c r="AW74" s="8" t="n"/>
-      <c r="AX74" s="8" t="n"/>
+      <c r="AX74" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="B75" t="inlineStr">
@@ -7424,7 +7776,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Applying priming coat with ready mixed pink or gray primer of approved brand and manufacture on wood work (hard and soft wood)</t>
+          <t>Applying priming coat with ready mixed pink or gray primer of approved brand and manufacture - on wood work (hard and soft wood)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -7434,7 +7786,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Primer</t>
+          <t>Wood primer</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7461,9 +7813,20 @@
       <c r="Q75" s="18" t="n">
         <v>47</v>
       </c>
+      <c r="Y75" s="18" t="n">
+        <v>44.65</v>
+      </c>
+      <c r="Z75" s="18" t="n">
+        <v>0.95</v>
+      </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13.81.4</t>
+          <t>13.81.1</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
         </is>
       </c>
     </row>
@@ -7512,9 +7875,20 @@
       <c r="Q76" s="18" t="n">
         <v>30</v>
       </c>
+      <c r="Y76" s="18" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="Z76" s="18" t="n">
+        <v>0.95</v>
+      </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13.84.3</t>
+          <t>13.81.4</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
         </is>
       </c>
     </row>
@@ -7563,14 +7937,25 @@
       <c r="R77" s="18" t="n">
         <v>10</v>
       </c>
+      <c r="Y77" s="18" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z77" s="18" t="n">
+        <v>0.95</v>
+      </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13.94.1</t>
+          <t>13.84.3</t>
         </is>
       </c>
       <c r="AT77" s="18" t="n">
         <v>100</v>
       </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="B78" t="inlineStr">
@@ -7617,6 +8002,22 @@
       <c r="Q78" s="18" t="n">
         <v>77</v>
       </c>
+      <c r="Y78" s="18" t="n">
+        <v>73.15000000000001</v>
+      </c>
+      <c r="Z78" s="18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13.94.1</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="B79" t="inlineStr">
@@ -7636,12 +8037,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>French polish</t>
+          <t>French spirit polish</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>French polish, Wood filler</t>
+          <t>French spirit polish, Wood filler</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -7663,9 +8064,20 @@
       <c r="Q79" s="18" t="n">
         <v>13</v>
       </c>
+      <c r="Y79" s="18" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="Z79" s="18" t="n">
+        <v>0.95</v>
+      </c>
       <c r="AB79" t="inlineStr">
         <is>
           <t>13.101.1</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
         </is>
       </c>
     </row>
@@ -7687,12 +8099,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Cement concrete</t>
+          <t>Cement concrete plinth protection</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate, Brick ballast, Fine sand</t>
+          <t>Cement, Coarse sand, Stone aggregate, Brick ballast, Fine sand</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7701,7 +8113,7 @@
         </is>
       </c>
       <c r="K80" s="18" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -7719,6 +8131,12 @@
       <c r="Q80" s="18" t="n">
         <v>34.6</v>
       </c>
+      <c r="Y80" s="18" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="Z80" s="18" t="n">
+        <v>0.149</v>
+      </c>
       <c r="AB80" t="inlineStr">
         <is>
           <t>16.1</t>
@@ -7726,6 +8144,11 @@
       </c>
       <c r="AR80" s="18" t="n">
         <v>50</v>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/output/passport_filled.xlsx
+++ b/output/passport_filled.xlsx
@@ -1097,7 +1097,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n"/>
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0001</t>
+        </is>
+      </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
           <t>1</t>
@@ -1161,14 +1165,22 @@
       <c r="X7" s="8" t="n"/>
       <c r="Y7" s="8" t="n"/>
       <c r="Z7" s="8" t="n"/>
-      <c r="AA7" s="8" t="n"/>
+      <c r="AA7" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB7" s="8" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
       <c r="AC7" s="8" t="n"/>
-      <c r="AD7" s="8" t="n"/>
+      <c r="AD7" s="8" t="inlineStr">
+        <is>
+          <t>Earthwork &gt; Soil</t>
+        </is>
+      </c>
       <c r="AE7" s="8" t="n"/>
       <c r="AF7" s="8" t="n"/>
       <c r="AG7" s="8" t="n"/>
@@ -1191,7 +1203,11 @@
       <c r="AX7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n"/>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0002</t>
+        </is>
+      </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
           <t>2</t>
@@ -1216,12 +1232,12 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Soil</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Soil</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -1255,14 +1271,22 @@
       <c r="X8" s="8" t="n"/>
       <c r="Y8" s="8" t="n"/>
       <c r="Z8" s="8" t="n"/>
-      <c r="AA8" s="8" t="n"/>
+      <c r="AA8" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB8" s="8" t="inlineStr">
         <is>
           <t>2.26</t>
         </is>
       </c>
       <c r="AC8" s="8" t="n"/>
-      <c r="AD8" s="8" t="n"/>
+      <c r="AD8" s="8" t="inlineStr">
+        <is>
+          <t>Earthwork &gt; Earth</t>
+        </is>
+      </c>
       <c r="AE8" s="8" t="n"/>
       <c r="AF8" s="8" t="n"/>
       <c r="AG8" s="8" t="n"/>
@@ -1277,7 +1301,9 @@
       <c r="AP8" s="8" t="n"/>
       <c r="AQ8" s="8" t="n"/>
       <c r="AR8" s="8" t="n"/>
-      <c r="AS8" s="8" t="n"/>
+      <c r="AS8" s="17" t="n">
+        <v>200</v>
+      </c>
       <c r="AT8" s="8" t="n"/>
       <c r="AU8" s="8" t="n"/>
       <c r="AV8" s="8" t="n"/>
@@ -1285,7 +1311,11 @@
       <c r="AX8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n"/>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0003</t>
+        </is>
+      </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
           <t>3</t>
@@ -1315,7 +1345,7 @@
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Sand</t>
+          <t>Fine sand</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -1324,7 +1354,7 @@
         </is>
       </c>
       <c r="K9" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L9" s="8" t="n"/>
       <c r="M9" s="8" t="n"/>
@@ -1349,14 +1379,22 @@
       <c r="X9" s="8" t="n"/>
       <c r="Y9" s="8" t="n"/>
       <c r="Z9" s="8" t="n"/>
-      <c r="AA9" s="8" t="n"/>
+      <c r="AA9" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB9" s="8" t="inlineStr">
         <is>
           <t>2.28</t>
         </is>
       </c>
       <c r="AC9" s="8" t="n"/>
-      <c r="AD9" s="8" t="n"/>
+      <c r="AD9" s="8" t="inlineStr">
+        <is>
+          <t>Earthwork &gt; Fine sand</t>
+        </is>
+      </c>
       <c r="AE9" s="8" t="n"/>
       <c r="AF9" s="8" t="n"/>
       <c r="AG9" s="8" t="n"/>
@@ -1379,7 +1417,11 @@
       <c r="AX9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n"/>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0004</t>
+        </is>
+      </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
           <t>4</t>
@@ -1423,15 +1465,17 @@
       <c r="L10" s="8" t="n"/>
       <c r="M10" s="8" t="n"/>
       <c r="N10" s="17" t="n">
-        <v>1.4</v>
+        <v>540</v>
       </c>
       <c r="O10" s="8" t="inlineStr">
         <is>
-          <t>100 Sq.m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P10" s="8" t="n"/>
-      <c r="Q10" s="8" t="n"/>
+      <c r="Q10" s="17" t="n">
+        <v>540</v>
+      </c>
       <c r="R10" s="8" t="n"/>
       <c r="S10" s="8" t="n"/>
       <c r="T10" s="8" t="n"/>
@@ -1441,14 +1485,22 @@
       <c r="X10" s="8" t="n"/>
       <c r="Y10" s="8" t="n"/>
       <c r="Z10" s="8" t="n"/>
-      <c r="AA10" s="8" t="n"/>
+      <c r="AA10" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB10" s="8" t="inlineStr">
         <is>
           <t>2.29.1</t>
         </is>
       </c>
       <c r="AC10" s="8" t="n"/>
-      <c r="AD10" s="8" t="n"/>
+      <c r="AD10" s="8" t="inlineStr">
+        <is>
+          <t>Earthwork &gt; Soil</t>
+        </is>
+      </c>
       <c r="AE10" s="8" t="n"/>
       <c r="AF10" s="8" t="n"/>
       <c r="AG10" s="8" t="n"/>
@@ -1463,7 +1515,9 @@
       <c r="AP10" s="8" t="n"/>
       <c r="AQ10" s="8" t="n"/>
       <c r="AR10" s="8" t="n"/>
-      <c r="AS10" s="8" t="n"/>
+      <c r="AS10" s="17" t="n">
+        <v>150</v>
+      </c>
       <c r="AT10" s="8" t="n"/>
       <c r="AU10" s="8" t="n"/>
       <c r="AV10" s="8" t="n"/>
@@ -1471,7 +1525,11 @@
       <c r="AX10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n"/>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0005</t>
+        </is>
+      </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
           <t>5</t>
@@ -1484,7 +1542,11 @@
           <t>Providing and injecting chemical emulsion for PRECONSTRUCTIONAL anti termite treatment and creating a chemical barrier under and alround the column pits, wall trenches, basement excavation, top surface of plinth filling junction of wall and floor, along the external perimetre of building, expansion joints, surroundings of pipes &amp; conduits etc. complete (plinth area of the building at ground floor only shall be measured) with Aldrin Emulsifiable Concentrate (0.5%)</t>
         </is>
       </c>
-      <c r="F11" s="8" t="n"/>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
@@ -1492,21 +1554,21 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
+          <t>Aldrin Chemical Emulsion</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
           <t>Aldrin Emulsifiable Concentrate</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>Chemical emulsion, Aldrin</t>
-        </is>
-      </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
       <c r="K11" s="17" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L11" s="8" t="n"/>
       <c r="M11" s="8" t="n"/>
@@ -1531,14 +1593,22 @@
       <c r="X11" s="8" t="n"/>
       <c r="Y11" s="8" t="n"/>
       <c r="Z11" s="8" t="n"/>
-      <c r="AA11" s="8" t="n"/>
+      <c r="AA11" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB11" s="8" t="inlineStr">
         <is>
           <t>2.35.2</t>
         </is>
       </c>
       <c r="AC11" s="8" t="n"/>
-      <c r="AD11" s="8" t="n"/>
+      <c r="AD11" s="8" t="inlineStr">
+        <is>
+          <t>Other &gt; Aldrin Chemical Emulsion</t>
+        </is>
+      </c>
       <c r="AE11" s="8" t="n"/>
       <c r="AF11" s="8" t="n"/>
       <c r="AG11" s="8" t="n"/>
@@ -1561,7 +1631,11 @@
       <c r="AX11" s="8" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n"/>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0006</t>
+        </is>
+      </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
           <t>6</t>
@@ -1574,10 +1648,14 @@
           <t>Providing and laying cement concrete in footings and bases for columns, excluding the cost of centring and shuttering with 1:5:10 (1 cement : 5 coarse sand : 10 graded stone aggregate 40 mm nominal size).</t>
         </is>
       </c>
-      <c r="F12" s="8" t="n"/>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
@@ -1598,7 +1676,11 @@
       <c r="K12" s="17" t="n">
         <v>0.95</v>
       </c>
-      <c r="L12" s="8" t="n"/>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
           <t>1:5:10</t>
@@ -1629,14 +1711,22 @@
       <c r="Z12" s="17" t="n">
         <v>0.149</v>
       </c>
-      <c r="AA12" s="8" t="n"/>
+      <c r="AA12" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB12" s="8" t="inlineStr">
         <is>
           <t>4.5.10</t>
         </is>
       </c>
       <c r="AC12" s="8" t="n"/>
-      <c r="AD12" s="8" t="n"/>
+      <c r="AD12" s="8" t="inlineStr">
+        <is>
+          <t>Concrete &gt; Cement concrete &gt; M5</t>
+        </is>
+      </c>
       <c r="AE12" s="8" t="n"/>
       <c r="AF12" s="8" t="n"/>
       <c r="AG12" s="8" t="n"/>
@@ -1658,12 +1748,16 @@
       <c r="AW12" s="8" t="n"/>
       <c r="AX12" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M5 inferred from nominal mix 1:5:10 (IS 456); not printed in BoQ</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n"/>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0007</t>
+        </is>
+      </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
           <t>7</t>
@@ -1676,10 +1770,14 @@
           <t>Providing and laying cement concrete in retaining walls, return walls, walls (any thickness) including attached pilasters, buttresses, plinth, string courses, fillets etc. upto floor two level, excluding the cost of centring and shuttering with 1:5:10 (1 cement : 5 fine sand : 10 graded stone aggregate 40 mm nominal size)</t>
         </is>
       </c>
-      <c r="F13" s="8" t="n"/>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
@@ -1700,7 +1798,11 @@
       <c r="K13" s="17" t="n">
         <v>0.95</v>
       </c>
-      <c r="L13" s="8" t="n"/>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
       <c r="M13" s="8" t="inlineStr">
         <is>
           <t>1:5:10</t>
@@ -1731,14 +1833,22 @@
       <c r="Z13" s="17" t="n">
         <v>0.149</v>
       </c>
-      <c r="AA13" s="8" t="n"/>
+      <c r="AA13" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB13" s="8" t="inlineStr">
         <is>
           <t>4.6.11</t>
         </is>
       </c>
       <c r="AC13" s="8" t="n"/>
-      <c r="AD13" s="8" t="n"/>
+      <c r="AD13" s="8" t="inlineStr">
+        <is>
+          <t>Concrete &gt; Cement concrete &gt; M5</t>
+        </is>
+      </c>
       <c r="AE13" s="8" t="n"/>
       <c r="AF13" s="8" t="n"/>
       <c r="AG13" s="8" t="n"/>
@@ -1760,12 +1870,16 @@
       <c r="AW13" s="8" t="n"/>
       <c r="AX13" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M5 inferred from nominal mix 1:5:10 (IS 456); not printed in BoQ</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n"/>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0008</t>
+        </is>
+      </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>8</t>
@@ -1778,10 +1892,14 @@
           <t>Providing and laying upto floor two level cement concrete in string or lacing courses, parapets, copings, bed blocks anchor blocks, plain window sills and the like excluding centring and shuttering, etc. with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
         </is>
       </c>
-      <c r="F14" s="8" t="n"/>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -1802,7 +1920,11 @@
       <c r="K14" s="17" t="n">
         <v>0.95</v>
       </c>
-      <c r="L14" s="8" t="n"/>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
           <t>1:2:4</t>
@@ -1833,14 +1955,22 @@
       <c r="Z14" s="17" t="n">
         <v>0.149</v>
       </c>
-      <c r="AA14" s="8" t="n"/>
+      <c r="AA14" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB14" s="8" t="inlineStr">
         <is>
           <t>4.11.1</t>
         </is>
       </c>
       <c r="AC14" s="8" t="n"/>
-      <c r="AD14" s="8" t="n"/>
+      <c r="AD14" s="8" t="inlineStr">
+        <is>
+          <t>Concrete &gt; Cement concrete &gt; M15</t>
+        </is>
+      </c>
       <c r="AE14" s="8" t="n"/>
       <c r="AF14" s="8" t="n"/>
       <c r="AG14" s="8" t="n"/>
@@ -1862,12 +1992,16 @@
       <c r="AW14" s="8" t="n"/>
       <c r="AX14" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456); not printed in BoQ</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n"/>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0009</t>
+        </is>
+      </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>9</t>
@@ -1880,7 +2014,11 @@
           <t>Providing and laying damp-proof course 40 mm thick with cement concrete 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 12.5 mm nominal size)</t>
         </is>
       </c>
-      <c r="F15" s="8" t="n"/>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
@@ -1904,7 +2042,11 @@
       <c r="K15" s="17" t="n">
         <v>0.95</v>
       </c>
-      <c r="L15" s="8" t="n"/>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
           <t>1:2:4</t>
@@ -1925,9 +2067,19 @@
       <c r="R15" s="8" t="n"/>
       <c r="S15" s="8" t="n"/>
       <c r="T15" s="8" t="n"/>
-      <c r="U15" s="8" t="n"/>
-      <c r="V15" s="8" t="n"/>
-      <c r="W15" s="8" t="n"/>
+      <c r="U15" s="17" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (40.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X15" s="8" t="n"/>
       <c r="Y15" s="17" t="n">
         <v>2.15</v>
@@ -1935,14 +2087,22 @@
       <c r="Z15" s="17" t="n">
         <v>0.149</v>
       </c>
-      <c r="AA15" s="8" t="n"/>
+      <c r="AA15" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB15" s="8" t="inlineStr">
         <is>
           <t>4.24</t>
         </is>
       </c>
       <c r="AC15" s="8" t="n"/>
-      <c r="AD15" s="8" t="n"/>
+      <c r="AD15" s="8" t="inlineStr">
+        <is>
+          <t>Concrete &gt; Cement concrete &gt; M15</t>
+        </is>
+      </c>
       <c r="AE15" s="8" t="n"/>
       <c r="AF15" s="8" t="n"/>
       <c r="AG15" s="8" t="n"/>
@@ -1966,12 +2126,16 @@
       <c r="AW15" s="8" t="n"/>
       <c r="AX15" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456); not printed in BoQ</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n"/>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0010</t>
+        </is>
+      </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
           <t>10</t>
@@ -1984,7 +2148,11 @@
           <t>Applying a coat of residual petroleum bitumen of penetration 80/100 of approved quality using 1.7 Kg. per square metre on damp proof course after cleaning the surface with brushes and finally with a piece of cloth lightly soaked in kerosene oil.</t>
         </is>
       </c>
-      <c r="F16" s="8" t="n"/>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
@@ -1992,12 +2160,12 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>Petroleum bitumen</t>
+          <t>Bitumen</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>Bitumen, Kerosene oil</t>
+          <t>Residual petroleum bitumen, Kerosene oil</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -2031,14 +2199,22 @@
       <c r="X16" s="8" t="n"/>
       <c r="Y16" s="8" t="n"/>
       <c r="Z16" s="8" t="n"/>
-      <c r="AA16" s="8" t="n"/>
+      <c r="AA16" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB16" s="8" t="inlineStr">
         <is>
           <t>4.27</t>
         </is>
       </c>
       <c r="AC16" s="8" t="n"/>
-      <c r="AD16" s="8" t="n"/>
+      <c r="AD16" s="8" t="inlineStr">
+        <is>
+          <t>Other &gt; Bitumen</t>
+        </is>
+      </c>
       <c r="AE16" s="8" t="n"/>
       <c r="AF16" s="8" t="n"/>
       <c r="AG16" s="8" t="n"/>
@@ -2061,7 +2237,11 @@
       <c r="AX16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n"/>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0011</t>
+        </is>
+      </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
           <t>11</t>
@@ -2074,7 +2254,11 @@
           <t>Reinforced cement concrete work in suspended floors, roofs, landings and balconies upto floor two level excluding cost of centring, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size)</t>
         </is>
       </c>
-      <c r="F17" s="8" t="n"/>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
@@ -2098,7 +2282,11 @@
       <c r="K17" s="17" t="n">
         <v>0.95</v>
       </c>
-      <c r="L17" s="8" t="n"/>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
           <t>1:2:4</t>
@@ -2129,14 +2317,22 @@
       <c r="Z17" s="17" t="n">
         <v>0.149</v>
       </c>
-      <c r="AA17" s="8" t="n"/>
+      <c r="AA17" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB17" s="8" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
       </c>
       <c r="AC17" s="8" t="n"/>
-      <c r="AD17" s="8" t="n"/>
+      <c r="AD17" s="8" t="inlineStr">
+        <is>
+          <t>Concrete &gt; Reinforced cement concrete &gt; M15</t>
+        </is>
+      </c>
       <c r="AE17" s="8" t="n"/>
       <c r="AF17" s="8" t="n"/>
       <c r="AG17" s="8" t="n"/>
@@ -2158,12 +2354,16 @@
       <c r="AW17" s="8" t="n"/>
       <c r="AX17" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456); not printed in BoQ</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n"/>
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0012</t>
+        </is>
+      </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
           <t>12</t>
@@ -2176,7 +2376,11 @@
           <t>Reinforced cement concrete work in shelves upto floor two level excluding the cost of centering and shuttering and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
         </is>
       </c>
-      <c r="F18" s="8" t="n"/>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
@@ -2200,7 +2404,11 @@
       <c r="K18" s="17" t="n">
         <v>0.95</v>
       </c>
-      <c r="L18" s="8" t="n"/>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
           <t>1:2:4</t>
@@ -2231,14 +2439,22 @@
       <c r="Z18" s="17" t="n">
         <v>0.149</v>
       </c>
-      <c r="AA18" s="8" t="n"/>
+      <c r="AA18" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB18" s="8" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
       </c>
       <c r="AC18" s="8" t="n"/>
-      <c r="AD18" s="8" t="n"/>
+      <c r="AD18" s="8" t="inlineStr">
+        <is>
+          <t>Concrete &gt; Reinforced cement concrete &gt; M15</t>
+        </is>
+      </c>
       <c r="AE18" s="8" t="n"/>
       <c r="AF18" s="8" t="n"/>
       <c r="AG18" s="8" t="n"/>
@@ -2260,12 +2476,16 @@
       <c r="AW18" s="8" t="n"/>
       <c r="AX18" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456); not printed in BoQ</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n"/>
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0013</t>
+        </is>
+      </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
           <t>13</t>
@@ -2278,7 +2498,11 @@
           <t>Reinforced cement concrete work in chajjas facias and gutters upto floor two level including throating of plastered drip and moulding excluding cost of centring, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
         </is>
       </c>
-      <c r="F19" s="8" t="n"/>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
@@ -2302,7 +2526,11 @@
       <c r="K19" s="17" t="n">
         <v>0.95</v>
       </c>
-      <c r="L19" s="8" t="n"/>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
           <t>1:2:4</t>
@@ -2333,14 +2561,22 @@
       <c r="Z19" s="17" t="n">
         <v>0.149</v>
       </c>
-      <c r="AA19" s="8" t="n"/>
+      <c r="AA19" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB19" s="8" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
       <c r="AC19" s="8" t="n"/>
-      <c r="AD19" s="8" t="n"/>
+      <c r="AD19" s="8" t="inlineStr">
+        <is>
+          <t>Concrete &gt; Reinforced cement concrete &gt; M15</t>
+        </is>
+      </c>
       <c r="AE19" s="8" t="n"/>
       <c r="AF19" s="8" t="n"/>
       <c r="AG19" s="8" t="n"/>
@@ -2362,12 +2598,16 @@
       <c r="AW19" s="8" t="n"/>
       <c r="AX19" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456); not printed in BoQ</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n"/>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0014</t>
+        </is>
+      </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
           <t>14</t>
@@ -2380,7 +2620,11 @@
           <t>Reinforced cement concrete work in lintels, beams, plinth beams and bresummers upto floor two level excluding the cost of centring, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
         </is>
       </c>
-      <c r="F20" s="8" t="n"/>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
@@ -2404,7 +2648,11 @@
       <c r="K20" s="17" t="n">
         <v>0.95</v>
       </c>
-      <c r="L20" s="8" t="n"/>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
           <t>1:2:4</t>
@@ -2435,14 +2683,22 @@
       <c r="Z20" s="17" t="n">
         <v>0.149</v>
       </c>
-      <c r="AA20" s="8" t="n"/>
+      <c r="AA20" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB20" s="8" t="inlineStr">
         <is>
           <t>5.6.3</t>
         </is>
       </c>
       <c r="AC20" s="8" t="n"/>
-      <c r="AD20" s="8" t="n"/>
+      <c r="AD20" s="8" t="inlineStr">
+        <is>
+          <t>Concrete &gt; Reinforced cement concrete &gt; M15</t>
+        </is>
+      </c>
       <c r="AE20" s="8" t="n"/>
       <c r="AF20" s="8" t="n"/>
       <c r="AG20" s="8" t="n"/>
@@ -2464,12 +2720,16 @@
       <c r="AW20" s="8" t="n"/>
       <c r="AX20" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456); not printed in BoQ</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n"/>
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0015</t>
+        </is>
+      </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
           <t>15</t>
@@ -2482,7 +2742,11 @@
           <t>Reinforced cement concrete work in columns, pillars, piers, abutments, posts and struts upto floor two level excluding the cost of centring, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
         </is>
       </c>
-      <c r="F21" s="8" t="n"/>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
@@ -2506,7 +2770,11 @@
       <c r="K21" s="17" t="n">
         <v>0.95</v>
       </c>
-      <c r="L21" s="8" t="n"/>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
           <t>1:2:4</t>
@@ -2537,14 +2805,22 @@
       <c r="Z21" s="17" t="n">
         <v>0.149</v>
       </c>
-      <c r="AA21" s="8" t="n"/>
+      <c r="AA21" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB21" s="8" t="inlineStr">
         <is>
           <t>5.7.3</t>
         </is>
       </c>
       <c r="AC21" s="8" t="n"/>
-      <c r="AD21" s="8" t="n"/>
+      <c r="AD21" s="8" t="inlineStr">
+        <is>
+          <t>Concrete &gt; Reinforced cement concrete &gt; M15</t>
+        </is>
+      </c>
       <c r="AE21" s="8" t="n"/>
       <c r="AF21" s="8" t="n"/>
       <c r="AG21" s="8" t="n"/>
@@ -2566,12 +2842,16 @@
       <c r="AW21" s="8" t="n"/>
       <c r="AX21" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456); not printed in BoQ</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n"/>
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0016</t>
+        </is>
+      </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
           <t>16i</t>
@@ -2581,13 +2861,17 @@
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Suspended floors,roofs,landings balconies and chajjas.</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n"/>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Suspended floors, roofs, landings balconies and chajjas.</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -2606,7 +2890,7 @@
         </is>
       </c>
       <c r="K22" s="17" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
@@ -2631,14 +2915,22 @@
       <c r="X22" s="8" t="n"/>
       <c r="Y22" s="8" t="n"/>
       <c r="Z22" s="8" t="n"/>
-      <c r="AA22" s="8" t="n"/>
+      <c r="AA22" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB22" s="8" t="inlineStr">
         <is>
           <t>5.14</t>
         </is>
       </c>
       <c r="AC22" s="8" t="n"/>
-      <c r="AD22" s="8" t="n"/>
+      <c r="AD22" s="8" t="inlineStr">
+        <is>
+          <t>Other &gt; Formwork</t>
+        </is>
+      </c>
       <c r="AE22" s="8" t="n"/>
       <c r="AF22" s="8" t="n"/>
       <c r="AG22" s="8" t="n"/>
@@ -2661,7 +2953,11 @@
       <c r="AX22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n"/>
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0017</t>
+        </is>
+      </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
           <t>16ii</t>
@@ -2674,10 +2970,14 @@
           <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Shelves</t>
         </is>
       </c>
-      <c r="F23" s="8" t="n"/>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -2696,7 +2996,7 @@
         </is>
       </c>
       <c r="K23" s="17" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L23" s="8" t="n"/>
       <c r="M23" s="8" t="n"/>
@@ -2721,14 +3021,22 @@
       <c r="X23" s="8" t="n"/>
       <c r="Y23" s="8" t="n"/>
       <c r="Z23" s="8" t="n"/>
-      <c r="AA23" s="8" t="n"/>
+      <c r="AA23" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB23" s="8" t="inlineStr">
         <is>
           <t>5.14</t>
         </is>
       </c>
       <c r="AC23" s="8" t="n"/>
-      <c r="AD23" s="8" t="n"/>
+      <c r="AD23" s="8" t="inlineStr">
+        <is>
+          <t>Other &gt; Formwork</t>
+        </is>
+      </c>
       <c r="AE23" s="8" t="n"/>
       <c r="AF23" s="8" t="n"/>
       <c r="AG23" s="8" t="n"/>
@@ -2751,7 +3059,11 @@
       <c r="AX23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n"/>
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0018</t>
+        </is>
+      </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
           <t>16iii</t>
@@ -2764,10 +3076,14 @@
           <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Lintels, beams, plinth beams, girders bressumers and cantilever.</t>
         </is>
       </c>
-      <c r="F24" s="8" t="n"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -2786,7 +3102,7 @@
         </is>
       </c>
       <c r="K24" s="17" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
@@ -2811,14 +3127,22 @@
       <c r="X24" s="8" t="n"/>
       <c r="Y24" s="8" t="n"/>
       <c r="Z24" s="8" t="n"/>
-      <c r="AA24" s="8" t="n"/>
+      <c r="AA24" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB24" s="8" t="inlineStr">
         <is>
           <t>5.14</t>
         </is>
       </c>
       <c r="AC24" s="8" t="n"/>
-      <c r="AD24" s="8" t="n"/>
+      <c r="AD24" s="8" t="inlineStr">
+        <is>
+          <t>Other &gt; Formwork</t>
+        </is>
+      </c>
       <c r="AE24" s="8" t="n"/>
       <c r="AF24" s="8" t="n"/>
       <c r="AG24" s="8" t="n"/>
@@ -2841,7 +3165,11 @@
       <c r="AX24" s="8" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="n"/>
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0019</t>
+        </is>
+      </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
           <t>16iv</t>
@@ -2854,10 +3182,14 @@
           <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Columns, pillars, posts and struts.</t>
         </is>
       </c>
-      <c r="F25" s="8" t="n"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -2876,7 +3208,7 @@
         </is>
       </c>
       <c r="K25" s="17" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L25" s="8" t="n"/>
       <c r="M25" s="8" t="n"/>
@@ -2901,14 +3233,22 @@
       <c r="X25" s="8" t="n"/>
       <c r="Y25" s="8" t="n"/>
       <c r="Z25" s="8" t="n"/>
-      <c r="AA25" s="8" t="n"/>
+      <c r="AA25" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB25" s="8" t="inlineStr">
         <is>
           <t>5.14</t>
         </is>
       </c>
       <c r="AC25" s="8" t="n"/>
-      <c r="AD25" s="8" t="n"/>
+      <c r="AD25" s="8" t="inlineStr">
+        <is>
+          <t>Other &gt; Formwork</t>
+        </is>
+      </c>
       <c r="AE25" s="8" t="n"/>
       <c r="AF25" s="8" t="n"/>
       <c r="AG25" s="8" t="n"/>
@@ -2931,7 +3271,11 @@
       <c r="AX25" s="8" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n"/>
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0020</t>
+        </is>
+      </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
           <t>16v</t>
@@ -2944,10 +3288,14 @@
           <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Vertical and horizontal fins individually or forming box louvers hand and facias.</t>
         </is>
       </c>
-      <c r="F26" s="8" t="n"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -2966,7 +3314,7 @@
         </is>
       </c>
       <c r="K26" s="17" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L26" s="8" t="n"/>
       <c r="M26" s="8" t="n"/>
@@ -2991,14 +3339,22 @@
       <c r="X26" s="8" t="n"/>
       <c r="Y26" s="8" t="n"/>
       <c r="Z26" s="8" t="n"/>
-      <c r="AA26" s="8" t="n"/>
+      <c r="AA26" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB26" s="8" t="inlineStr">
         <is>
           <t>5.14</t>
         </is>
       </c>
       <c r="AC26" s="8" t="n"/>
-      <c r="AD26" s="8" t="n"/>
+      <c r="AD26" s="8" t="inlineStr">
+        <is>
+          <t>Other &gt; Formwork</t>
+        </is>
+      </c>
       <c r="AE26" s="8" t="n"/>
       <c r="AF26" s="8" t="n"/>
       <c r="AG26" s="8" t="n"/>
@@ -3021,7 +3377,11 @@
       <c r="AX26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n"/>
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0021</t>
+        </is>
+      </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
           <t>17i</t>
@@ -3034,7 +3394,11 @@
           <t>Reinforcement for RCC work including bending binding and placing in position complete. Mild steel and medium tensile steel bars.</t>
         </is>
       </c>
-      <c r="F27" s="8" t="n"/>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
@@ -3047,7 +3411,7 @@
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Mild steel, Medium tensile steel</t>
         </is>
       </c>
       <c r="J27" s="8" t="inlineStr">
@@ -3085,14 +3449,22 @@
       <c r="Z27" s="17" t="n">
         <v>1.55</v>
       </c>
-      <c r="AA27" s="8" t="n"/>
+      <c r="AA27" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB27" s="8" t="inlineStr">
         <is>
           <t>5.29</t>
         </is>
       </c>
       <c r="AC27" s="8" t="n"/>
-      <c r="AD27" s="8" t="n"/>
+      <c r="AD27" s="8" t="inlineStr">
+        <is>
+          <t>Steel &gt; Mild steel bar</t>
+        </is>
+      </c>
       <c r="AE27" s="8" t="n"/>
       <c r="AF27" s="8" t="n"/>
       <c r="AG27" s="8" t="n"/>
@@ -3119,7 +3491,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n"/>
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0022</t>
+        </is>
+      </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
           <t>17ii</t>
@@ -3132,7 +3508,11 @@
           <t>Reinforcement for RCC work including bending binding and placing in position complete. Cold twisted bars</t>
         </is>
       </c>
-      <c r="F28" s="8" t="n"/>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
@@ -3145,7 +3525,7 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Cold twisted steel</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -3183,14 +3563,22 @@
       <c r="Z28" s="17" t="n">
         <v>1.55</v>
       </c>
-      <c r="AA28" s="8" t="n"/>
+      <c r="AA28" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB28" s="8" t="inlineStr">
         <is>
           <t>5.29</t>
         </is>
       </c>
       <c r="AC28" s="8" t="n"/>
-      <c r="AD28" s="8" t="n"/>
+      <c r="AD28" s="8" t="inlineStr">
+        <is>
+          <t>Steel &gt; Cold twisted bar</t>
+        </is>
+      </c>
       <c r="AE28" s="8" t="n"/>
       <c r="AF28" s="8" t="n"/>
       <c r="AG28" s="8" t="n"/>
@@ -3217,7 +3605,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n"/>
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0023</t>
+        </is>
+      </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
           <t>18</t>
@@ -3230,7 +3622,11 @@
           <t>Providing and laying upto floor two level RCC in string courses, bands, copings, bed plates, anchor blocks, plain window sills and the like excluding the cost of centering, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
         </is>
       </c>
-      <c r="F29" s="8" t="n"/>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
           <t>Structural</t>
@@ -3254,7 +3650,11 @@
       <c r="K29" s="17" t="n">
         <v>0.95</v>
       </c>
-      <c r="L29" s="8" t="n"/>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
           <t>1:2:4</t>
@@ -3285,14 +3685,22 @@
       <c r="Z29" s="17" t="n">
         <v>0.149</v>
       </c>
-      <c r="AA29" s="8" t="n"/>
+      <c r="AA29" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB29" s="8" t="inlineStr">
         <is>
           <t>5.16</t>
         </is>
       </c>
       <c r="AC29" s="8" t="n"/>
-      <c r="AD29" s="8" t="n"/>
+      <c r="AD29" s="8" t="inlineStr">
+        <is>
+          <t>Concrete &gt; Reinforced cement concrete &gt; M15</t>
+        </is>
+      </c>
       <c r="AE29" s="8" t="n"/>
       <c r="AF29" s="8" t="n"/>
       <c r="AG29" s="8" t="n"/>
@@ -3314,12 +3722,16 @@
       <c r="AW29" s="8" t="n"/>
       <c r="AX29" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456); not printed in BoQ</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n"/>
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0024</t>
+        </is>
+      </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
           <t>19</t>
@@ -3329,10 +3741,14 @@
       <c r="D30" s="8" t="n"/>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Brick work with bricks of class designation in foundation and plinth in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="n"/>
+          <t>Brick work with bricks of class designation___ in foundation and plinth in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
@@ -3340,12 +3756,12 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>Brick work</t>
+          <t>Brick masonry</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>Brick, Cement, Sand</t>
+          <t>Bricks, Cement, Coarse sand</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -3387,14 +3803,22 @@
       <c r="Z30" s="17" t="n">
         <v>0.213</v>
       </c>
-      <c r="AA30" s="8" t="n"/>
+      <c r="AA30" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB30" s="8" t="inlineStr">
         <is>
-          <t>6.1.14/6.5.1/6.5.2</t>
+          <t>6.1.14/6.5.1 6.5.2</t>
         </is>
       </c>
       <c r="AC30" s="8" t="n"/>
-      <c r="AD30" s="8" t="n"/>
+      <c r="AD30" s="8" t="inlineStr">
+        <is>
+          <t>Masonry &gt; Brick masonry &gt; 1:6</t>
+        </is>
+      </c>
       <c r="AE30" s="8" t="n"/>
       <c r="AF30" s="8" t="n"/>
       <c r="AG30" s="8" t="n"/>
@@ -3421,7 +3845,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="n"/>
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0025</t>
+        </is>
+      </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
           <t>20</t>
@@ -3431,10 +3859,14 @@
       <c r="D31" s="8" t="n"/>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Brick work with bricks of class designation in super structure above plinth upto floor two level in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="n"/>
+          <t>Brick work with bricks of class designation___ in super structure above plinth upto floor two level in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
@@ -3442,12 +3874,12 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>Brick work</t>
+          <t>Brick masonry</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>Brick, Cement, Sand</t>
+          <t>Bricks, Cement, Coarse sand</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -3489,14 +3921,22 @@
       <c r="Z31" s="17" t="n">
         <v>0.213</v>
       </c>
-      <c r="AA31" s="8" t="n"/>
+      <c r="AA31" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB31" s="8" t="inlineStr">
         <is>
-          <t>6.1.14/6.3/6.5.1/6.5.2</t>
+          <t>6.1.14/6.3 6.5.1/6.5.2</t>
         </is>
       </c>
       <c r="AC31" s="8" t="n"/>
-      <c r="AD31" s="8" t="n"/>
+      <c r="AD31" s="8" t="inlineStr">
+        <is>
+          <t>Masonry &gt; Brick masonry &gt; 1:6</t>
+        </is>
+      </c>
       <c r="AE31" s="8" t="n"/>
       <c r="AF31" s="8" t="n"/>
       <c r="AG31" s="8" t="n"/>
@@ -3523,7 +3963,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="n"/>
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0026</t>
+        </is>
+      </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
           <t>21</t>
@@ -3533,10 +3977,14 @@
       <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Brick work 7 cm thick with bricks of class designation in super structure upto floor two level in cement mortar 1:3 (1 cement : 3 coarse sand).</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="n"/>
+          <t>Brick work 7 cm thick with bricks of class designation ______ in super structure upto floor two level in cement mortar 1:3 (1 cement : 3 coarse sand).</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
@@ -3544,12 +3992,12 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>Brick work</t>
+          <t>Brick masonry</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>Brick, Cement, Sand</t>
+          <t>Bricks, Cement, Coarse sand</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
@@ -3581,9 +4029,19 @@
       <c r="R32" s="8" t="n"/>
       <c r="S32" s="8" t="n"/>
       <c r="T32" s="8" t="n"/>
-      <c r="U32" s="8" t="n"/>
-      <c r="V32" s="8" t="n"/>
-      <c r="W32" s="8" t="n"/>
+      <c r="U32" s="17" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W32" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (70.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X32" s="8" t="n"/>
       <c r="Y32" s="17" t="n">
         <v>0.19</v>
@@ -3591,14 +4049,22 @@
       <c r="Z32" s="17" t="n">
         <v>0.213</v>
       </c>
-      <c r="AA32" s="8" t="n"/>
+      <c r="AA32" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB32" s="8" t="inlineStr">
         <is>
           <t>6.13/6.21/6.5.1/6.5.2</t>
         </is>
       </c>
       <c r="AC32" s="8" t="n"/>
-      <c r="AD32" s="8" t="n"/>
+      <c r="AD32" s="8" t="inlineStr">
+        <is>
+          <t>Masonry &gt; Brick masonry &gt; 1:3</t>
+        </is>
+      </c>
       <c r="AE32" s="8" t="n"/>
       <c r="AF32" s="8" t="n"/>
       <c r="AG32" s="8" t="n"/>
@@ -3627,7 +4093,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="n"/>
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0027</t>
+        </is>
+      </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
           <t>22</t>
@@ -3637,10 +4107,14 @@
       <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Half brick masonry with bricks of class designation in foundation &amp; plinth in cement mortar 1:4 (1 cement : 4 coarse sand)</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="n"/>
+          <t>Half brick masonry with bricks of class designation _______ in foundation &amp; plinth in cement mortar 1:4 (1 cement : 4 coarse sand)</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
@@ -3653,7 +4127,7 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>Brick, Cement, Sand</t>
+          <t>Bricks, Cement, Coarse sand</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
@@ -3695,14 +4169,22 @@
       <c r="Z33" s="17" t="n">
         <v>0.213</v>
       </c>
-      <c r="AA33" s="8" t="n"/>
+      <c r="AA33" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB33" s="8" t="inlineStr">
         <is>
-          <t>6.18.4/6.21/6.5.1/6.5.2</t>
+          <t>6.18.4/6.21 6.5.1/6.5.2</t>
         </is>
       </c>
       <c r="AC33" s="8" t="n"/>
-      <c r="AD33" s="8" t="n"/>
+      <c r="AD33" s="8" t="inlineStr">
+        <is>
+          <t>Masonry &gt; Brick masonry &gt; 1:4</t>
+        </is>
+      </c>
       <c r="AE33" s="8" t="n"/>
       <c r="AF33" s="8" t="n"/>
       <c r="AG33" s="8" t="n"/>
@@ -3729,7 +4211,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="n"/>
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0028</t>
+        </is>
+      </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
           <t>23</t>
@@ -3739,10 +4225,14 @@
       <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Half brick masonry with bricks of class designation in super structure upto floor two level in cement mortar 1:4 (1 cement : 4 coarse sand).</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="n"/>
+          <t>Half brick masonry with bricks of class designation ________ in super structure upto floor two level in cement mortar 1:4 (1 cement : 4 coarse sand).</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
@@ -3755,7 +4245,7 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>Brick, Cement, Sand</t>
+          <t>Bricks, Cement, Coarse sand</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -3797,14 +4287,22 @@
       <c r="Z34" s="17" t="n">
         <v>0.213</v>
       </c>
-      <c r="AA34" s="8" t="n"/>
+      <c r="AA34" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB34" s="8" t="inlineStr">
         <is>
-          <t>6.18.4/6.19.1/6.20/6.21.1/6.21.2</t>
+          <t>6.18.4/6.19.1 6.20/6.21.1/6.21.2</t>
         </is>
       </c>
       <c r="AC34" s="8" t="n"/>
-      <c r="AD34" s="8" t="n"/>
+      <c r="AD34" s="8" t="inlineStr">
+        <is>
+          <t>Masonry &gt; Brick masonry &gt; 1:4</t>
+        </is>
+      </c>
       <c r="AE34" s="8" t="n"/>
       <c r="AF34" s="8" t="n"/>
       <c r="AG34" s="8" t="n"/>
@@ -3831,7 +4329,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="n"/>
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0029</t>
+        </is>
+      </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
           <t>24</t>
@@ -3841,10 +4343,14 @@
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Providing wood work in frames of doors, windows, clerestory windows and other frames, wrought framed and fixed in position.</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="n"/>
+          <t>Providing _______ wood work in frames of doors, windows, clerestory windows and other frames, wrought framed and fixed in position.</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -3852,7 +4358,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>Wood work</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
@@ -3866,7 +4372,7 @@
         </is>
       </c>
       <c r="K35" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L35" s="8" t="n"/>
       <c r="M35" s="8" t="n"/>
@@ -3895,10 +4401,18 @@
       <c r="Z35" s="17" t="n">
         <v>0.306</v>
       </c>
-      <c r="AA35" s="8" t="n"/>
+      <c r="AA35" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB35" s="8" t="n"/>
       <c r="AC35" s="8" t="n"/>
-      <c r="AD35" s="8" t="n"/>
+      <c r="AD35" s="8" t="inlineStr">
+        <is>
+          <t>Timber &gt; Wood</t>
+        </is>
+      </c>
       <c r="AE35" s="8" t="n"/>
       <c r="AF35" s="8" t="n"/>
       <c r="AG35" s="8" t="n"/>
@@ -3925,7 +4439,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="n"/>
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0030</t>
+        </is>
+      </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
           <t>25</t>
@@ -3935,10 +4453,14 @@
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing 35 mm thick battended and framed door shutters of wood including bright finished or/and black enamelled MS butt hinges with necessary screws.</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="n"/>
+          <t>Providing and fixing 35 mm thick battended and framed door shutters of ________ wood including bright finished or/and black enamelled MS butt hinges with necessary screws.</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -3946,12 +4468,12 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>Wood door shutters</t>
+          <t>Wood door shutter</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>Wood, MS butt hinges</t>
+          <t>Wood, Mild steel</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
@@ -3960,7 +4482,7 @@
         </is>
       </c>
       <c r="K36" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L36" s="8" t="n"/>
       <c r="M36" s="8" t="n"/>
@@ -3979,9 +4501,19 @@
       <c r="R36" s="8" t="n"/>
       <c r="S36" s="8" t="n"/>
       <c r="T36" s="8" t="n"/>
-      <c r="U36" s="8" t="n"/>
-      <c r="V36" s="8" t="n"/>
-      <c r="W36" s="8" t="n"/>
+      <c r="U36" s="17" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W36" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (35.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X36" s="8" t="n"/>
       <c r="Y36" s="17" t="n">
         <v>5.51</v>
@@ -3989,10 +4521,22 @@
       <c r="Z36" s="17" t="n">
         <v>0.306</v>
       </c>
-      <c r="AA36" s="8" t="n"/>
-      <c r="AB36" s="8" t="n"/>
+      <c r="AA36" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
+      <c r="AB36" s="8" t="inlineStr">
+        <is>
+          <t>9.26.4</t>
+        </is>
+      </c>
       <c r="AC36" s="8" t="n"/>
-      <c r="AD36" s="8" t="n"/>
+      <c r="AD36" s="8" t="inlineStr">
+        <is>
+          <t>Timber &gt; Wood door shutter</t>
+        </is>
+      </c>
       <c r="AE36" s="8" t="n"/>
       <c r="AF36" s="8" t="n"/>
       <c r="AG36" s="8" t="n"/>
@@ -4021,7 +4565,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="n"/>
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0031</t>
+        </is>
+      </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
           <t>26</t>
@@ -4031,10 +4579,14 @@
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing 25 mm thick flush door (for cupboard) shutters core of block board construction with frame of Ist class hard wood and well matched Ist class teak ply veneering with vertical grains or cross bands and face veneer on one face and commercial ply veneering with vertical grains or cross bands and face veneer on other face of shutters, including nickel plated bright finished MS piano hinges with necessary screws.</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="n"/>
+          <t>Providing and fixing 25 mm thick flush door (for cupboard) shutters core of block board construction with frame of 1st class hard wood and well matched 1st class teak ply veneering with vertical grains or cross bands and face veneer on one face and commercial ply veneering with vertical grains or cross bands and face veneer on other face of shutters, including nickel plated bright finished MS piano hinges with necessary screws.</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -4047,7 +4599,7 @@
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>Block board, Hard wood, Teak ply, Commercial ply, MS piano hinges</t>
+          <t>Block board, Hardwood, Teak ply, Commercial ply, Mild steel</t>
         </is>
       </c>
       <c r="J37" s="8" t="inlineStr">
@@ -4056,7 +4608,7 @@
         </is>
       </c>
       <c r="K37" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L37" s="8" t="n"/>
       <c r="M37" s="8" t="n"/>
@@ -4075,9 +4627,19 @@
       <c r="R37" s="8" t="n"/>
       <c r="S37" s="8" t="n"/>
       <c r="T37" s="8" t="n"/>
-      <c r="U37" s="8" t="n"/>
-      <c r="V37" s="8" t="n"/>
-      <c r="W37" s="8" t="n"/>
+      <c r="U37" s="17" t="n">
+        <v>0.1175</v>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W37" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (25.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X37" s="8" t="n"/>
       <c r="Y37" s="17" t="n">
         <v>1.44</v>
@@ -4085,14 +4647,22 @@
       <c r="Z37" s="17" t="n">
         <v>0.306</v>
       </c>
-      <c r="AA37" s="8" t="n"/>
+      <c r="AA37" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB37" s="8" t="inlineStr">
         <is>
-          <t>9.26.4</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="AC37" s="8" t="n"/>
-      <c r="AD37" s="8" t="n"/>
+      <c r="AD37" s="8" t="inlineStr">
+        <is>
+          <t>Timber &gt; Flush door shutter</t>
+        </is>
+      </c>
       <c r="AE37" s="8" t="n"/>
       <c r="AF37" s="8" t="n"/>
       <c r="AG37" s="8" t="n"/>
@@ -4121,7 +4691,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="n"/>
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0032</t>
+        </is>
+      </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
           <t>27</t>
@@ -4131,10 +4705,14 @@
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Providing 50x50x50 mm 2nd class Teak wood plugs including cutting brick work and fixing in cement mortar 1:3 (1 cement :3 fine sand) and making good the walls etc.</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="n"/>
+          <t>Providing 50x50x50 mm 2nd class Teak wood plugs including cutting brick work and fixing in cement mortar 1:3 (1 cement : 3 fine sand) and making good the walls etc.</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
@@ -4142,7 +4720,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>Teak wood plugs</t>
+          <t>Teak wood plug</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
@@ -4156,7 +4734,7 @@
         </is>
       </c>
       <c r="K38" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L38" s="8" t="n"/>
       <c r="M38" s="8" t="inlineStr">
@@ -4189,14 +4767,18 @@
       <c r="Z38" s="17" t="n">
         <v>0.306</v>
       </c>
-      <c r="AA38" s="8" t="n"/>
-      <c r="AB38" s="8" t="inlineStr">
-        <is>
-          <t>9.51</t>
-        </is>
-      </c>
+      <c r="AA38" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
+      <c r="AB38" s="8" t="n"/>
       <c r="AC38" s="8" t="n"/>
-      <c r="AD38" s="8" t="n"/>
+      <c r="AD38" s="8" t="inlineStr">
+        <is>
+          <t>Timber &gt; Teak wood plug &gt; 1:3</t>
+        </is>
+      </c>
       <c r="AE38" s="8" t="n"/>
       <c r="AF38" s="8" t="n"/>
       <c r="AG38" s="8" t="n"/>
@@ -4207,9 +4789,15 @@
       <c r="AL38" s="8" t="n"/>
       <c r="AM38" s="8" t="n"/>
       <c r="AN38" s="8" t="n"/>
-      <c r="AO38" s="8" t="n"/>
-      <c r="AP38" s="8" t="n"/>
-      <c r="AQ38" s="8" t="n"/>
+      <c r="AO38" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP38" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AQ38" s="17" t="n">
+        <v>50</v>
+      </c>
       <c r="AR38" s="8" t="n"/>
       <c r="AS38" s="8" t="n"/>
       <c r="AT38" s="8" t="n"/>
@@ -4223,7 +4811,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="n"/>
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0033</t>
+        </is>
+      </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
           <t>28</t>
@@ -4233,10 +4825,14 @@
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing M.S.oxidised fan light ventilator catch with necessary screws etc. complete.</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="n"/>
+          <t>Providing and fixing M.S.oxidised fan light .vantilator catch with necessary screws etc. complete.</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -4244,12 +4840,12 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>M.S. oxidised fan light ventilator catch</t>
+          <t>Mild steel ventilator catch</t>
         </is>
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>M.S.</t>
+          <t>Mild steel</t>
         </is>
       </c>
       <c r="J39" s="8" t="inlineStr">
@@ -4287,10 +4883,22 @@
       <c r="Z39" s="17" t="n">
         <v>1.55</v>
       </c>
-      <c r="AA39" s="8" t="n"/>
-      <c r="AB39" s="8" t="n"/>
+      <c r="AA39" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
+      <c r="AB39" s="8" t="inlineStr">
+        <is>
+          <t>9.127.3</t>
+        </is>
+      </c>
       <c r="AC39" s="8" t="n"/>
-      <c r="AD39" s="8" t="n"/>
+      <c r="AD39" s="8" t="inlineStr">
+        <is>
+          <t>Steel &gt; Mild steel ventilator catch</t>
+        </is>
+      </c>
       <c r="AE39" s="8" t="n"/>
       <c r="AF39" s="8" t="n"/>
       <c r="AG39" s="8" t="n"/>
@@ -4317,7 +4925,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="n"/>
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0034</t>
+        </is>
+      </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
           <t>29</t>
@@ -4330,7 +4942,11 @@
           <t>Providing and fixing 90 mm oxidised M.S. hasp and staple (safety type) with necessary screws etc. complete.</t>
         </is>
       </c>
-      <c r="F40" s="8" t="n"/>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -4338,12 +4954,12 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>Oxidised M.S. hasp and staple</t>
+          <t>Mild steel hasp and staple</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>M.S.</t>
+          <t>Mild steel</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
@@ -4381,14 +4997,22 @@
       <c r="Z40" s="17" t="n">
         <v>1.55</v>
       </c>
-      <c r="AA40" s="8" t="n"/>
+      <c r="AA40" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB40" s="8" t="inlineStr">
         <is>
-          <t>9.127.3</t>
+          <t>9.218.1</t>
         </is>
       </c>
       <c r="AC40" s="8" t="n"/>
-      <c r="AD40" s="8" t="n"/>
+      <c r="AD40" s="8" t="inlineStr">
+        <is>
+          <t>Steel &gt; Mild steel hasp and staple</t>
+        </is>
+      </c>
       <c r="AE40" s="8" t="n"/>
       <c r="AF40" s="8" t="n"/>
       <c r="AG40" s="8" t="n"/>
@@ -4399,7 +5023,9 @@
       <c r="AL40" s="8" t="n"/>
       <c r="AM40" s="8" t="n"/>
       <c r="AN40" s="8" t="n"/>
-      <c r="AO40" s="8" t="n"/>
+      <c r="AO40" s="17" t="n">
+        <v>90</v>
+      </c>
       <c r="AP40" s="8" t="n"/>
       <c r="AQ40" s="8" t="n"/>
       <c r="AR40" s="8" t="n"/>
@@ -4415,7 +5041,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="n"/>
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0035</t>
+        </is>
+      </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
           <t>30</t>
@@ -4428,7 +5058,11 @@
           <t>Providing and fixing aluminium sliding door bolts 300 x 16 mm anodised transparent or dyed to required colour or shade with nuts and screws etc. complete.</t>
         </is>
       </c>
-      <c r="F41" s="8" t="n"/>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -4436,7 +5070,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>Aluminium sliding door bolts</t>
+          <t>Aluminium sliding door bolt</t>
         </is>
       </c>
       <c r="I41" s="8" t="inlineStr">
@@ -4450,7 +5084,7 @@
         </is>
       </c>
       <c r="K41" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L41" s="8" t="n"/>
       <c r="M41" s="8" t="n"/>
@@ -4475,14 +5109,18 @@
       <c r="X41" s="8" t="n"/>
       <c r="Y41" s="8" t="n"/>
       <c r="Z41" s="8" t="n"/>
-      <c r="AA41" s="8" t="n"/>
-      <c r="AB41" s="8" t="inlineStr">
-        <is>
-          <t>9.218.1</t>
-        </is>
-      </c>
+      <c r="AA41" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
+      <c r="AB41" s="8" t="n"/>
       <c r="AC41" s="8" t="n"/>
-      <c r="AD41" s="8" t="n"/>
+      <c r="AD41" s="8" t="inlineStr">
+        <is>
+          <t>Other &gt; Aluminium sliding door bolt</t>
+        </is>
+      </c>
       <c r="AE41" s="8" t="n"/>
       <c r="AF41" s="8" t="n"/>
       <c r="AG41" s="8" t="n"/>
@@ -4493,7 +5131,9 @@
       <c r="AL41" s="8" t="n"/>
       <c r="AM41" s="8" t="n"/>
       <c r="AN41" s="8" t="n"/>
-      <c r="AO41" s="8" t="n"/>
+      <c r="AO41" s="17" t="n">
+        <v>300</v>
+      </c>
       <c r="AP41" s="8" t="n"/>
       <c r="AQ41" s="8" t="n"/>
       <c r="AR41" s="8" t="n"/>
@@ -4507,7 +5147,11 @@
       <c r="AX41" s="8" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="n"/>
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0036</t>
+        </is>
+      </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
           <t>31i</t>
@@ -4520,7 +5164,11 @@
           <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 200 x 10 mm</t>
         </is>
       </c>
-      <c r="F42" s="8" t="n"/>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -4528,7 +5176,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>Aluminium tower bolts</t>
+          <t>Aluminium tower bolt</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
@@ -4542,7 +5190,7 @@
         </is>
       </c>
       <c r="K42" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L42" s="8" t="n"/>
       <c r="M42" s="8" t="n"/>
@@ -4567,14 +5215,22 @@
       <c r="X42" s="8" t="n"/>
       <c r="Y42" s="8" t="n"/>
       <c r="Z42" s="8" t="n"/>
-      <c r="AA42" s="8" t="n"/>
+      <c r="AA42" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB42" s="8" t="inlineStr">
         <is>
           <t>9.219.3</t>
         </is>
       </c>
       <c r="AC42" s="8" t="n"/>
-      <c r="AD42" s="8" t="n"/>
+      <c r="AD42" s="8" t="inlineStr">
+        <is>
+          <t>Other &gt; Aluminium tower bolt</t>
+        </is>
+      </c>
       <c r="AE42" s="8" t="n"/>
       <c r="AF42" s="8" t="n"/>
       <c r="AG42" s="8" t="n"/>
@@ -4585,7 +5241,9 @@
       <c r="AL42" s="8" t="n"/>
       <c r="AM42" s="8" t="n"/>
       <c r="AN42" s="8" t="n"/>
-      <c r="AO42" s="8" t="n"/>
+      <c r="AO42" s="17" t="n">
+        <v>200</v>
+      </c>
       <c r="AP42" s="8" t="n"/>
       <c r="AQ42" s="8" t="n"/>
       <c r="AR42" s="8" t="n"/>
@@ -4599,7 +5257,11 @@
       <c r="AX42" s="8" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="n"/>
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0037</t>
+        </is>
+      </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
           <t>31ii</t>
@@ -4612,7 +5274,11 @@
           <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 100 x 10 mm</t>
         </is>
       </c>
-      <c r="F43" s="8" t="n"/>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -4620,7 +5286,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>Aluminium tower bolts</t>
+          <t>Aluminium tower bolt</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
@@ -4634,7 +5300,7 @@
         </is>
       </c>
       <c r="K43" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L43" s="8" t="n"/>
       <c r="M43" s="8" t="n"/>
@@ -4659,14 +5325,22 @@
       <c r="X43" s="8" t="n"/>
       <c r="Y43" s="8" t="n"/>
       <c r="Z43" s="8" t="n"/>
-      <c r="AA43" s="8" t="n"/>
+      <c r="AA43" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB43" s="8" t="inlineStr">
         <is>
           <t>9.219.5</t>
         </is>
       </c>
       <c r="AC43" s="8" t="n"/>
-      <c r="AD43" s="8" t="n"/>
+      <c r="AD43" s="8" t="inlineStr">
+        <is>
+          <t>Other &gt; Aluminium tower bolt</t>
+        </is>
+      </c>
       <c r="AE43" s="8" t="n"/>
       <c r="AF43" s="8" t="n"/>
       <c r="AG43" s="8" t="n"/>
@@ -4677,7 +5351,9 @@
       <c r="AL43" s="8" t="n"/>
       <c r="AM43" s="8" t="n"/>
       <c r="AN43" s="8" t="n"/>
-      <c r="AO43" s="8" t="n"/>
+      <c r="AO43" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="AP43" s="8" t="n"/>
       <c r="AQ43" s="8" t="n"/>
       <c r="AR43" s="8" t="n"/>
@@ -4691,7 +5367,11 @@
       <c r="AX43" s="8" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="n"/>
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0038</t>
+        </is>
+      </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
           <t>32i</t>
@@ -4704,7 +5384,11 @@
           <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 100 mm</t>
         </is>
       </c>
-      <c r="F44" s="8" t="n"/>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -4712,7 +5396,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>Aluminium handles</t>
+          <t>Aluminium handle</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">
@@ -4726,7 +5410,7 @@
         </is>
       </c>
       <c r="K44" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L44" s="8" t="n"/>
       <c r="M44" s="8" t="n"/>
@@ -4751,14 +5435,22 @@
       <c r="X44" s="8" t="n"/>
       <c r="Y44" s="8" t="n"/>
       <c r="Z44" s="8" t="n"/>
-      <c r="AA44" s="8" t="n"/>
+      <c r="AA44" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB44" s="8" t="inlineStr">
         <is>
           <t>9.222.2</t>
         </is>
       </c>
       <c r="AC44" s="8" t="n"/>
-      <c r="AD44" s="8" t="n"/>
+      <c r="AD44" s="8" t="inlineStr">
+        <is>
+          <t>Other &gt; Aluminium handle</t>
+        </is>
+      </c>
       <c r="AE44" s="8" t="n"/>
       <c r="AF44" s="8" t="n"/>
       <c r="AG44" s="8" t="n"/>
@@ -4769,7 +5461,9 @@
       <c r="AL44" s="8" t="n"/>
       <c r="AM44" s="8" t="n"/>
       <c r="AN44" s="8" t="n"/>
-      <c r="AO44" s="8" t="n"/>
+      <c r="AO44" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="AP44" s="8" t="n"/>
       <c r="AQ44" s="8" t="n"/>
       <c r="AR44" s="8" t="n"/>
@@ -4781,7 +5475,11 @@
       <c r="AX44" s="8" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="n"/>
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0039</t>
+        </is>
+      </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
           <t>32ii</t>
@@ -4794,7 +5492,11 @@
           <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 75 mm</t>
         </is>
       </c>
-      <c r="F45" s="8" t="n"/>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -4802,7 +5504,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>Aluminium handles</t>
+          <t>Aluminium handle</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
@@ -4816,7 +5518,7 @@
         </is>
       </c>
       <c r="K45" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L45" s="8" t="n"/>
       <c r="M45" s="8" t="n"/>
@@ -4841,14 +5543,22 @@
       <c r="X45" s="8" t="n"/>
       <c r="Y45" s="8" t="n"/>
       <c r="Z45" s="8" t="n"/>
-      <c r="AA45" s="8" t="n"/>
+      <c r="AA45" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB45" s="8" t="inlineStr">
         <is>
           <t>9.222.3</t>
         </is>
       </c>
       <c r="AC45" s="8" t="n"/>
-      <c r="AD45" s="8" t="n"/>
+      <c r="AD45" s="8" t="inlineStr">
+        <is>
+          <t>Other &gt; Aluminium handle</t>
+        </is>
+      </c>
       <c r="AE45" s="8" t="n"/>
       <c r="AF45" s="8" t="n"/>
       <c r="AG45" s="8" t="n"/>
@@ -4859,7 +5569,9 @@
       <c r="AL45" s="8" t="n"/>
       <c r="AM45" s="8" t="n"/>
       <c r="AN45" s="8" t="n"/>
-      <c r="AO45" s="8" t="n"/>
+      <c r="AO45" s="17" t="n">
+        <v>75</v>
+      </c>
       <c r="AP45" s="8" t="n"/>
       <c r="AQ45" s="8" t="n"/>
       <c r="AR45" s="8" t="n"/>
@@ -4871,7 +5583,11 @@
       <c r="AX45" s="8" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="n"/>
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0040</t>
+        </is>
+      </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
           <t>33</t>
@@ -4884,7 +5600,11 @@
           <t>Providing and fixing aluminium hanging floor door stopper anodised transparent or dyed to required colour &amp; shade with necessary screws etc. complete.</t>
         </is>
       </c>
-      <c r="F46" s="8" t="n"/>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -4906,7 +5626,7 @@
         </is>
       </c>
       <c r="K46" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L46" s="8" t="n"/>
       <c r="M46" s="8" t="n"/>
@@ -4931,14 +5651,22 @@
       <c r="X46" s="8" t="n"/>
       <c r="Y46" s="8" t="n"/>
       <c r="Z46" s="8" t="n"/>
-      <c r="AA46" s="8" t="n"/>
+      <c r="AA46" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB46" s="8" t="inlineStr">
         <is>
           <t>9.223</t>
         </is>
       </c>
       <c r="AC46" s="8" t="n"/>
-      <c r="AD46" s="8" t="n"/>
+      <c r="AD46" s="8" t="inlineStr">
+        <is>
+          <t>Other &gt; Aluminium door stopper</t>
+        </is>
+      </c>
       <c r="AE46" s="8" t="n"/>
       <c r="AF46" s="8" t="n"/>
       <c r="AG46" s="8" t="n"/>
@@ -4961,7 +5689,11 @@
       <c r="AX46" s="8" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="n"/>
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0041</t>
+        </is>
+      </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
           <t>34i</t>
@@ -4974,7 +5706,11 @@
           <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. Windows - side hung</t>
         </is>
       </c>
-      <c r="F47" s="8" t="n"/>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -4982,12 +5718,12 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>Steel glazed windows</t>
+          <t>Steel glazed window</t>
         </is>
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>Steel, Cement, Coarse sand, Stone aggregate, Glass, Putty</t>
+          <t>Steel, Glass, Cement concrete, Putty</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
@@ -4996,7 +5732,7 @@
         </is>
       </c>
       <c r="K47" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L47" s="8" t="n"/>
       <c r="M47" s="8" t="inlineStr">
@@ -5019,9 +5755,19 @@
       <c r="R47" s="8" t="n"/>
       <c r="S47" s="8" t="n"/>
       <c r="T47" s="8" t="n"/>
-      <c r="U47" s="8" t="n"/>
-      <c r="V47" s="8" t="n"/>
-      <c r="W47" s="8" t="n"/>
+      <c r="U47" s="17" t="n">
+        <v>0.0339</v>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W47" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (3.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X47" s="8" t="n"/>
       <c r="Y47" s="17" t="n">
         <v>17.52</v>
@@ -5029,14 +5775,22 @@
       <c r="Z47" s="17" t="n">
         <v>1.55</v>
       </c>
-      <c r="AA47" s="8" t="n"/>
+      <c r="AA47" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB47" s="8" t="inlineStr">
         <is>
           <t>N.S.I.</t>
         </is>
       </c>
       <c r="AC47" s="8" t="n"/>
-      <c r="AD47" s="8" t="n"/>
+      <c r="AD47" s="8" t="inlineStr">
+        <is>
+          <t>Steel &gt; Steel glazed window &gt; 1:3:6</t>
+        </is>
+      </c>
       <c r="AE47" s="8" t="n"/>
       <c r="AF47" s="8" t="n"/>
       <c r="AG47" s="8" t="n"/>
@@ -5065,7 +5819,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="n"/>
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0042</t>
+        </is>
+      </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
           <t>34ii</t>
@@ -5078,7 +5836,11 @@
           <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. Ventilators - centre hung</t>
         </is>
       </c>
-      <c r="F48" s="8" t="n"/>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -5086,12 +5848,12 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>Steel glazed ventilators</t>
+          <t>Steel glazed ventilator</t>
         </is>
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>Steel, Cement, Coarse sand, Stone aggregate, Glass, Putty</t>
+          <t>Steel, Glass, Cement concrete, Putty</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
@@ -5100,7 +5862,7 @@
         </is>
       </c>
       <c r="K48" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L48" s="8" t="n"/>
       <c r="M48" s="8" t="inlineStr">
@@ -5123,9 +5885,19 @@
       <c r="R48" s="8" t="n"/>
       <c r="S48" s="8" t="n"/>
       <c r="T48" s="8" t="n"/>
-      <c r="U48" s="8" t="n"/>
-      <c r="V48" s="8" t="n"/>
-      <c r="W48" s="8" t="n"/>
+      <c r="U48" s="17" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W48" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (3.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X48" s="8" t="n"/>
       <c r="Y48" s="17" t="n">
         <v>1.55</v>
@@ -5133,14 +5905,22 @@
       <c r="Z48" s="17" t="n">
         <v>1.55</v>
       </c>
-      <c r="AA48" s="8" t="n"/>
+      <c r="AA48" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB48" s="8" t="inlineStr">
         <is>
           <t>N.S.I.</t>
         </is>
       </c>
       <c r="AC48" s="8" t="n"/>
-      <c r="AD48" s="8" t="n"/>
+      <c r="AD48" s="8" t="inlineStr">
+        <is>
+          <t>Steel &gt; Steel glazed ventilator &gt; 1:3:6</t>
+        </is>
+      </c>
       <c r="AE48" s="8" t="n"/>
       <c r="AF48" s="8" t="n"/>
       <c r="AG48" s="8" t="n"/>
@@ -5169,7 +5949,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="n"/>
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0043</t>
+        </is>
+      </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
           <t>35</t>
@@ -5182,7 +5966,11 @@
           <t>Providing and fixing oxidised mild steel casement window fastners of minimum weight 200 grams to side hung steel windows with necessary welding and machine screws etc. complete.</t>
         </is>
       </c>
-      <c r="F49" s="8" t="n"/>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -5190,7 +5978,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>Mild steel casement window fastners</t>
+          <t>Mild steel casement fastener</t>
         </is>
       </c>
       <c r="I49" s="8" t="inlineStr">
@@ -5204,7 +5992,7 @@
         </is>
       </c>
       <c r="K49" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L49" s="8" t="n"/>
       <c r="M49" s="8" t="n"/>
@@ -5233,14 +6021,22 @@
       <c r="Z49" s="17" t="n">
         <v>1.55</v>
       </c>
-      <c r="AA49" s="8" t="n"/>
+      <c r="AA49" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB49" s="8" t="inlineStr">
         <is>
           <t>N.S.I.</t>
         </is>
       </c>
       <c r="AC49" s="8" t="n"/>
-      <c r="AD49" s="8" t="n"/>
+      <c r="AD49" s="8" t="inlineStr">
+        <is>
+          <t>Steel &gt; Mild steel casement fastener</t>
+        </is>
+      </c>
       <c r="AE49" s="8" t="n"/>
       <c r="AF49" s="8" t="n"/>
       <c r="AG49" s="8" t="n"/>
@@ -5267,7 +6063,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="n"/>
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0044</t>
+        </is>
+      </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
           <t>36</t>
@@ -5280,7 +6080,11 @@
           <t>Providing and fixing aluminium casement stays anodised transparent or dyed to required colour and shade with with necessary welding and machine screws etc. complete.</t>
         </is>
       </c>
-      <c r="F50" s="8" t="n"/>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -5288,7 +6092,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>Aluminium casement stays</t>
+          <t>Aluminium casement stay</t>
         </is>
       </c>
       <c r="I50" s="8" t="inlineStr">
@@ -5302,7 +6106,7 @@
         </is>
       </c>
       <c r="K50" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L50" s="8" t="n"/>
       <c r="M50" s="8" t="n"/>
@@ -5327,14 +6131,22 @@
       <c r="X50" s="8" t="n"/>
       <c r="Y50" s="8" t="n"/>
       <c r="Z50" s="8" t="n"/>
-      <c r="AA50" s="8" t="n"/>
+      <c r="AA50" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB50" s="8" t="inlineStr">
         <is>
           <t>9.224</t>
         </is>
       </c>
       <c r="AC50" s="8" t="n"/>
-      <c r="AD50" s="8" t="n"/>
+      <c r="AD50" s="8" t="inlineStr">
+        <is>
+          <t>Other &gt; Aluminium casement stay</t>
+        </is>
+      </c>
       <c r="AE50" s="8" t="n"/>
       <c r="AF50" s="8" t="n"/>
       <c r="AG50" s="8" t="n"/>
@@ -5357,7 +6169,11 @@
       <c r="AX50" s="8" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="n"/>
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0045</t>
+        </is>
+      </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
           <t>37</t>
@@ -5370,7 +6186,11 @@
           <t>Providing and welding 20x4 mm M S Guard Flats 10cm c/c in steel windows of standard rolled steel section including a coat of steel primer as per drawing and specification complete in all respect.</t>
         </is>
       </c>
-      <c r="F51" s="8" t="n"/>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -5378,12 +6198,12 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>M S Guard Flats</t>
+          <t>Mild steel flat</t>
         </is>
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>MS, Steel primer</t>
+          <t>Mild steel, Steel primer</t>
         </is>
       </c>
       <c r="J51" s="8" t="inlineStr">
@@ -5421,14 +6241,22 @@
       <c r="Z51" s="17" t="n">
         <v>1.55</v>
       </c>
-      <c r="AA51" s="8" t="n"/>
+      <c r="AA51" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB51" s="8" t="inlineStr">
         <is>
           <t>N.S.I.</t>
         </is>
       </c>
       <c r="AC51" s="8" t="n"/>
-      <c r="AD51" s="8" t="n"/>
+      <c r="AD51" s="8" t="inlineStr">
+        <is>
+          <t>Steel &gt; Mild steel flat</t>
+        </is>
+      </c>
       <c r="AE51" s="8" t="n"/>
       <c r="AF51" s="8" t="n"/>
       <c r="AG51" s="8" t="n"/>
@@ -5440,7 +6268,9 @@
       <c r="AM51" s="8" t="n"/>
       <c r="AN51" s="8" t="n"/>
       <c r="AO51" s="8" t="n"/>
-      <c r="AP51" s="8" t="n"/>
+      <c r="AP51" s="17" t="n">
+        <v>20</v>
+      </c>
       <c r="AQ51" s="8" t="n"/>
       <c r="AR51" s="17" t="n">
         <v>4</v>
@@ -5457,7 +6287,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="n"/>
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0046</t>
+        </is>
+      </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
           <t>38</t>
@@ -5470,7 +6304,11 @@
           <t>Providing and fixing T - Iron frames for doors, windows and ventilators of mild steel Tee - sections, joints mitred and welded with 15x3 mm lugs 10 cm long embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including fixing of necessary butt hinges and screws and applying a priming coat of approved steel primer.</t>
         </is>
       </c>
-      <c r="F52" s="8" t="n"/>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -5478,12 +6316,12 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>T-Iron frames</t>
+          <t>Mild steel T-Iron frame</t>
         </is>
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>Mild steel, Cement, Sand, Stone aggregate, Steel primer</t>
+          <t>Mild steel, Cement concrete, Wood, Steel primer</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr">
@@ -5525,14 +6363,22 @@
       <c r="Z52" s="17" t="n">
         <v>1.55</v>
       </c>
-      <c r="AA52" s="8" t="n"/>
+      <c r="AA52" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB52" s="8" t="inlineStr">
         <is>
           <t>10.14</t>
         </is>
       </c>
       <c r="AC52" s="8" t="n"/>
-      <c r="AD52" s="8" t="n"/>
+      <c r="AD52" s="8" t="inlineStr">
+        <is>
+          <t>Steel &gt; Mild steel T-Iron frame &gt; 1:3:6</t>
+        </is>
+      </c>
       <c r="AE52" s="8" t="n"/>
       <c r="AF52" s="8" t="n"/>
       <c r="AG52" s="8" t="n"/>
@@ -5559,7 +6405,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="n"/>
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0047</t>
+        </is>
+      </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
           <t>39</t>
@@ -5572,7 +6422,11 @@
           <t>Providing and fixing MS fan clamp type I of 16 mm dia MS bar bent to shape with hooked ends in RCC slabs during laying including painting the exposed portion of loop, all as per standard design complete.</t>
         </is>
       </c>
-      <c r="F53" s="8" t="n"/>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
           <t>Electrical</t>
@@ -5580,12 +6434,12 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>MS fan clamp</t>
+          <t>Mild steel fan clamp</t>
         </is>
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>MS bar, Paint</t>
+          <t>Mild steel</t>
         </is>
       </c>
       <c r="J53" s="8" t="inlineStr">
@@ -5594,7 +6448,7 @@
         </is>
       </c>
       <c r="K53" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L53" s="8" t="n"/>
       <c r="M53" s="8" t="n"/>
@@ -5623,14 +6477,22 @@
       <c r="Z53" s="17" t="n">
         <v>1.55</v>
       </c>
-      <c r="AA53" s="8" t="n"/>
+      <c r="AA53" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB53" s="8" t="inlineStr">
         <is>
           <t>10.19</t>
         </is>
       </c>
       <c r="AC53" s="8" t="n"/>
-      <c r="AD53" s="8" t="n"/>
+      <c r="AD53" s="8" t="inlineStr">
+        <is>
+          <t>Steel &gt; Mild steel fan clamp</t>
+        </is>
+      </c>
       <c r="AE53" s="8" t="n"/>
       <c r="AF53" s="8" t="n"/>
       <c r="AG53" s="8" t="n"/>
@@ -5659,7 +6521,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="n"/>
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0048</t>
+        </is>
+      </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
           <t>40</t>
@@ -5672,7 +6538,11 @@
           <t>40 mm thick cement concrete flooring 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20.0 mm nominal size) finished with a floating coat of neat cement including cement slurry, rounding off edges and strips etc. but excluding the cost of nosing of steps etc. complete.</t>
         </is>
       </c>
-      <c r="F54" s="8" t="n"/>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -5696,7 +6566,11 @@
       <c r="K54" s="17" t="n">
         <v>0.95</v>
       </c>
-      <c r="L54" s="8" t="n"/>
+      <c r="L54" s="8" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
       <c r="M54" s="8" t="inlineStr">
         <is>
           <t>1:2:4</t>
@@ -5717,9 +6591,19 @@
       <c r="R54" s="8" t="n"/>
       <c r="S54" s="8" t="n"/>
       <c r="T54" s="8" t="n"/>
-      <c r="U54" s="8" t="n"/>
-      <c r="V54" s="8" t="n"/>
-      <c r="W54" s="8" t="n"/>
+      <c r="U54" s="17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="V54" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W54" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (40.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X54" s="8" t="n"/>
       <c r="Y54" s="17" t="n">
         <v>10.13</v>
@@ -5727,14 +6611,22 @@
       <c r="Z54" s="17" t="n">
         <v>0.149</v>
       </c>
-      <c r="AA54" s="8" t="n"/>
+      <c r="AA54" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB54" s="8" t="inlineStr">
         <is>
           <t>11.4.2</t>
         </is>
       </c>
       <c r="AC54" s="8" t="n"/>
-      <c r="AD54" s="8" t="n"/>
+      <c r="AD54" s="8" t="inlineStr">
+        <is>
+          <t>Concrete &gt; Cement concrete flooring &gt; M15</t>
+        </is>
+      </c>
       <c r="AE54" s="8" t="n"/>
       <c r="AF54" s="8" t="n"/>
       <c r="AG54" s="8" t="n"/>
@@ -5758,12 +6650,16 @@
       <c r="AW54" s="8" t="n"/>
       <c r="AX54" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456); not printed in BoQ</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="n"/>
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0049</t>
+        </is>
+      </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
           <t>41</t>
@@ -5776,7 +6672,11 @@
           <t>18 mm thick cement plaster skirting (upto 30 cm height) with cement mortar 1:3 (1 cement : 3 coarse sand) finished with a floating coat of neat cement including rounding of junctions with floors.</t>
         </is>
       </c>
-      <c r="F55" s="8" t="n"/>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -5798,7 +6698,7 @@
         </is>
       </c>
       <c r="K55" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L55" s="8" t="n"/>
       <c r="M55" s="8" t="inlineStr">
@@ -5821,9 +6721,19 @@
       <c r="R55" s="8" t="n"/>
       <c r="S55" s="8" t="n"/>
       <c r="T55" s="8" t="n"/>
-      <c r="U55" s="8" t="n"/>
-      <c r="V55" s="8" t="n"/>
-      <c r="W55" s="8" t="n"/>
+      <c r="U55" s="17" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W55" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (18.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X55" s="8" t="n"/>
       <c r="Y55" s="17" t="n">
         <v>10.45</v>
@@ -5831,14 +6741,22 @@
       <c r="Z55" s="17" t="n">
         <v>0.95</v>
       </c>
-      <c r="AA55" s="8" t="n"/>
+      <c r="AA55" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB55" s="8" t="inlineStr">
         <is>
           <t>11.10.1</t>
         </is>
       </c>
       <c r="AC55" s="8" t="n"/>
-      <c r="AD55" s="8" t="n"/>
+      <c r="AD55" s="8" t="inlineStr">
+        <is>
+          <t>Paint/Finish &gt; Cement plaster skirting &gt; 1:3</t>
+        </is>
+      </c>
       <c r="AE55" s="8" t="n"/>
       <c r="AF55" s="8" t="n"/>
       <c r="AG55" s="8" t="n"/>
@@ -5851,7 +6769,9 @@
       <c r="AN55" s="8" t="n"/>
       <c r="AO55" s="8" t="n"/>
       <c r="AP55" s="8" t="n"/>
-      <c r="AQ55" s="8" t="n"/>
+      <c r="AQ55" s="17" t="n">
+        <v>300</v>
+      </c>
       <c r="AR55" s="17" t="n">
         <v>18</v>
       </c>
@@ -5867,7 +6787,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="n"/>
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0050</t>
+        </is>
+      </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
           <t>42</t>
@@ -5880,7 +6804,11 @@
           <t>40 mm thick marble chips flooring, rubbed and polished to granolithic finish, under layer 31 mm thick cement concrete 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 12.5 mm nominal size) and top layer 9 mm thick with white black, chocolate, grey yellow or Baroda green marble chips of sizes from 4 mm to 7 mm nominal size laid in cement marble powder mix 3:1 (3 cement : 1 marble powder) by weight in proportion of 4:7 (4 cement marble powder mix : 7 marble chips) by volume including cement slurry etc., complete using dark shade pigment with ordinary cement.</t>
         </is>
       </c>
-      <c r="F56" s="8" t="n"/>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -5893,12 +6821,12 @@
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>Cement, Sand, Stone aggregate, Marble chips, Marble powder, Pigment</t>
+          <t>Marble chips, Cement, Coarse sand, Stone aggregate, Marble powder, Pigment</t>
         </is>
       </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
-          <t>Finishes</t>
+          <t>Paint/Finish</t>
         </is>
       </c>
       <c r="K56" s="17" t="n">
@@ -5925,20 +6853,42 @@
       <c r="R56" s="8" t="n"/>
       <c r="S56" s="8" t="n"/>
       <c r="T56" s="8" t="n"/>
-      <c r="U56" s="8" t="n"/>
-      <c r="V56" s="8" t="n"/>
-      <c r="W56" s="8" t="n"/>
+      <c r="U56" s="17" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W56" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (40.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X56" s="8" t="n"/>
-      <c r="Y56" s="8" t="n"/>
-      <c r="Z56" s="8" t="n"/>
-      <c r="AA56" s="8" t="n"/>
+      <c r="Y56" s="17" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="Z56" s="17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AA56" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB56" s="8" t="inlineStr">
         <is>
           <t>11.16.1</t>
         </is>
       </c>
       <c r="AC56" s="8" t="n"/>
-      <c r="AD56" s="8" t="n"/>
+      <c r="AD56" s="8" t="inlineStr">
+        <is>
+          <t>Paint/Finish &gt; Marble chips flooring &gt; 1:2:4</t>
+        </is>
+      </c>
       <c r="AE56" s="8" t="n"/>
       <c r="AF56" s="8" t="n"/>
       <c r="AG56" s="8" t="n"/>
@@ -5960,10 +6910,18 @@
       <c r="AU56" s="8" t="n"/>
       <c r="AV56" s="8" t="n"/>
       <c r="AW56" s="8" t="n"/>
-      <c r="AX56" s="8" t="n"/>
+      <c r="AX56" s="8" t="inlineStr">
+        <is>
+          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="n"/>
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0051</t>
+        </is>
+      </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
           <t>43</t>
@@ -5976,7 +6934,11 @@
           <t>Add or deduct for providing and fixing glass strips in joints of terrazzo/cement concrete floors- 40 mm wide and 6 mm thick.</t>
         </is>
       </c>
-      <c r="F57" s="8" t="n"/>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -5984,7 +6946,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>Glass strips</t>
+          <t>Glass strip</t>
         </is>
       </c>
       <c r="I57" s="8" t="inlineStr">
@@ -5998,7 +6960,7 @@
         </is>
       </c>
       <c r="K57" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L57" s="8" t="n"/>
       <c r="M57" s="8" t="n"/>
@@ -6023,14 +6985,22 @@
       <c r="X57" s="8" t="n"/>
       <c r="Y57" s="8" t="n"/>
       <c r="Z57" s="8" t="n"/>
-      <c r="AA57" s="8" t="n"/>
+      <c r="AA57" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB57" s="8" t="inlineStr">
         <is>
           <t>11.20.2</t>
         </is>
       </c>
       <c r="AC57" s="8" t="n"/>
-      <c r="AD57" s="8" t="n"/>
+      <c r="AD57" s="8" t="inlineStr">
+        <is>
+          <t>Other &gt; Glass strip</t>
+        </is>
+      </c>
       <c r="AE57" s="8" t="n"/>
       <c r="AF57" s="8" t="n"/>
       <c r="AG57" s="8" t="n"/>
@@ -6042,7 +7012,9 @@
       <c r="AM57" s="8" t="n"/>
       <c r="AN57" s="8" t="n"/>
       <c r="AO57" s="8" t="n"/>
-      <c r="AP57" s="8" t="n"/>
+      <c r="AP57" s="17" t="n">
+        <v>40</v>
+      </c>
       <c r="AQ57" s="8" t="n"/>
       <c r="AR57" s="17" t="n">
         <v>6</v>
@@ -6055,7 +7027,11 @@
       <c r="AX57" s="8" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="n"/>
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0052</t>
+        </is>
+      </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
           <t>44</t>
@@ -6065,10 +7041,14 @@
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>Painting top of roofs with bitumen of approved quality at 17 Kg. per 10 square metre impregnated with a coat of coarse sand at 3/60 dm3 per 10 m2 including cleaning the slab surface with brushes and finally with a piece of cloth lightly soaked in kerosene oil complete with residual type petroleum bitumen of penetration 80/100.</t>
-        </is>
-      </c>
-      <c r="F58" s="8" t="n"/>
+          <t>Painting top of roofs with bitumen of approved quality at 17 Kg. per 10 square metre impregnated with a coat of coarse sand at 3/2 60 dm per 10 m including cleaning the slab surface with brushes and finally with a piece of cloth lightly soaked in kerosene oil complete with residual type petroleum bitumen of penetration 80/100.</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
@@ -6119,14 +7099,22 @@
       <c r="Z58" s="17" t="n">
         <v>0.95</v>
       </c>
-      <c r="AA58" s="8" t="n"/>
+      <c r="AA58" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB58" s="8" t="inlineStr">
         <is>
           <t>12.29.1</t>
         </is>
       </c>
       <c r="AC58" s="8" t="n"/>
-      <c r="AD58" s="8" t="n"/>
+      <c r="AD58" s="8" t="inlineStr">
+        <is>
+          <t>Paint/Finish &gt; Bitumen</t>
+        </is>
+      </c>
       <c r="AE58" s="8" t="n"/>
       <c r="AF58" s="8" t="n"/>
       <c r="AG58" s="8" t="n"/>
@@ -6153,7 +7141,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="n"/>
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0053</t>
+        </is>
+      </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
           <t>45</t>
@@ -6166,7 +7158,11 @@
           <t>Lime concrete terracing on roofs, average thickness 10 cm laid to fall with 25 mm nominal size brick aggregate and 50% lime mortar 1:2 (1 lime putty : 2 surkhi) rammed and finished with gur and belgiri treatment complete and covered with flat FPS brick tiles of class designation 100 grouted with cement mortar 1:3 (1 cement : 3 fine sand) mixed with 5% crude oil by wt. of cement, over 12 mm layer of cement mortar 1:3 (1 cement : 3 fine sand) and finished neat.</t>
         </is>
       </c>
-      <c r="F59" s="8" t="n"/>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
@@ -6179,7 +7175,7 @@
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>Brick aggregate, Lime putty, Surkhi, Gur, Belgiri, Brick tiles, Cement, Fine sand, Crude oil</t>
+          <t>Brick aggregate, Lime putty, Surkhi, Brick tiles, Cement, Fine sand, Crude oil</t>
         </is>
       </c>
       <c r="J59" s="8" t="inlineStr">
@@ -6188,7 +7184,7 @@
         </is>
       </c>
       <c r="K59" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L59" s="8" t="n"/>
       <c r="M59" s="8" t="inlineStr">
@@ -6211,9 +7207,19 @@
       <c r="R59" s="8" t="n"/>
       <c r="S59" s="8" t="n"/>
       <c r="T59" s="8" t="n"/>
-      <c r="U59" s="8" t="n"/>
-      <c r="V59" s="8" t="n"/>
-      <c r="W59" s="8" t="n"/>
+      <c r="U59" s="17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V59" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W59" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (100.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X59" s="8" t="n"/>
       <c r="Y59" s="17" t="n">
         <v>9.68</v>
@@ -6221,14 +7227,22 @@
       <c r="Z59" s="17" t="n">
         <v>0.149</v>
       </c>
-      <c r="AA59" s="8" t="n"/>
+      <c r="AA59" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB59" s="8" t="inlineStr">
         <is>
           <t>12.35.2</t>
         </is>
       </c>
       <c r="AC59" s="8" t="n"/>
-      <c r="AD59" s="8" t="n"/>
+      <c r="AD59" s="8" t="inlineStr">
+        <is>
+          <t>Concrete &gt; Lime concrete terracing &gt; 1:2</t>
+        </is>
+      </c>
       <c r="AE59" s="8" t="n"/>
       <c r="AF59" s="8" t="n"/>
       <c r="AG59" s="8" t="n"/>
@@ -6257,7 +7271,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="n"/>
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0054</t>
+        </is>
+      </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
           <t>46</t>
@@ -6270,7 +7288,11 @@
           <t>Providing and laying 25 mm thick burnt clay tiles 250x250x25 mm of approved quality over roofs with 1 cm side joints grouted with CM 1:3 (1 cement : 3 fine sand) over 15 mm thick bed of cement mortar 1:3 (1 cement : 3 fine sand) and finished neat.</t>
         </is>
       </c>
-      <c r="F60" s="8" t="n"/>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -6278,12 +7300,12 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>Burnt clay tiles</t>
+          <t>Burnt clay tile</t>
         </is>
       </c>
       <c r="I60" s="8" t="inlineStr">
         <is>
-          <t>Clay tiles, Cement, Fine sand</t>
+          <t>Burnt clay tiles, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J60" s="8" t="inlineStr">
@@ -6292,7 +7314,7 @@
         </is>
       </c>
       <c r="K60" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L60" s="8" t="n"/>
       <c r="M60" s="8" t="inlineStr">
@@ -6315,9 +7337,19 @@
       <c r="R60" s="8" t="n"/>
       <c r="S60" s="8" t="n"/>
       <c r="T60" s="8" t="n"/>
-      <c r="U60" s="8" t="n"/>
-      <c r="V60" s="8" t="n"/>
-      <c r="W60" s="8" t="n"/>
+      <c r="U60" s="17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V60" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W60" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (25.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X60" s="8" t="n"/>
       <c r="Y60" s="17" t="n">
         <v>6.82</v>
@@ -6325,14 +7357,22 @@
       <c r="Z60" s="17" t="n">
         <v>0.213</v>
       </c>
-      <c r="AA60" s="8" t="n"/>
+      <c r="AA60" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB60" s="8" t="inlineStr">
         <is>
           <t>N.S.I.</t>
         </is>
       </c>
       <c r="AC60" s="8" t="n"/>
-      <c r="AD60" s="8" t="n"/>
+      <c r="AD60" s="8" t="inlineStr">
+        <is>
+          <t>Masonry &gt; Burnt clay tile &gt; 1:3</t>
+        </is>
+      </c>
       <c r="AE60" s="8" t="n"/>
       <c r="AF60" s="8" t="n"/>
       <c r="AG60" s="8" t="n"/>
@@ -6343,8 +7383,12 @@
       <c r="AL60" s="8" t="n"/>
       <c r="AM60" s="8" t="n"/>
       <c r="AN60" s="8" t="n"/>
-      <c r="AO60" s="8" t="n"/>
-      <c r="AP60" s="8" t="n"/>
+      <c r="AO60" s="17" t="n">
+        <v>250</v>
+      </c>
+      <c r="AP60" s="17" t="n">
+        <v>250</v>
+      </c>
       <c r="AQ60" s="8" t="n"/>
       <c r="AR60" s="17" t="n">
         <v>25</v>
@@ -6361,7 +7405,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="n"/>
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0055</t>
+        </is>
+      </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
           <t>47</t>
@@ -6374,7 +7422,11 @@
           <t>Providing gola 15x15 cm in size in cement concrete mix 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) covered with brick tiles in CM 1:3 (1 cement : 3 coarse sand) as per drawing and specifications complete in all respects.</t>
         </is>
       </c>
-      <c r="F61" s="8" t="n"/>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
@@ -6396,9 +7448,13 @@
         </is>
       </c>
       <c r="K61" s="17" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L61" s="8" t="n"/>
+        <v>0.9</v>
+      </c>
+      <c r="L61" s="8" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
       <c r="M61" s="8" t="inlineStr">
         <is>
           <t>1:3:6</t>
@@ -6429,14 +7485,22 @@
       <c r="Z61" s="17" t="n">
         <v>0.149</v>
       </c>
-      <c r="AA61" s="8" t="n"/>
+      <c r="AA61" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB61" s="8" t="inlineStr">
         <is>
           <t>N.S.I.</t>
         </is>
       </c>
       <c r="AC61" s="8" t="n"/>
-      <c r="AD61" s="8" t="n"/>
+      <c r="AD61" s="8" t="inlineStr">
+        <is>
+          <t>Concrete &gt; Cement concrete gola &gt; M10</t>
+        </is>
+      </c>
       <c r="AE61" s="8" t="n"/>
       <c r="AF61" s="8" t="n"/>
       <c r="AG61" s="8" t="n"/>
@@ -6447,8 +7511,12 @@
       <c r="AL61" s="8" t="n"/>
       <c r="AM61" s="8" t="n"/>
       <c r="AN61" s="8" t="n"/>
-      <c r="AO61" s="8" t="n"/>
-      <c r="AP61" s="8" t="n"/>
+      <c r="AO61" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP61" s="17" t="n">
+        <v>150</v>
+      </c>
       <c r="AQ61" s="8" t="n"/>
       <c r="AR61" s="8" t="n"/>
       <c r="AS61" s="8" t="n"/>
@@ -6458,12 +7526,16 @@
       <c r="AW61" s="8" t="n"/>
       <c r="AX61" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M10 inferred from nominal mix 1:3:6 (IS 456); not printed in BoQ</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="n"/>
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0056</t>
+        </is>
+      </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
           <t>48</t>
@@ -6476,7 +7548,11 @@
           <t>Making khurras 45 x 45 cm with average minimum thickness of 5 cm cement concrete 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size) over PVC sheet 1m x 1m x 400 micron, finished with 12 cement plaster 1:3 (1 cement : 3 coarse sand) and a coat of neat cement rounding the edges and making and finishing the outlet complete.</t>
         </is>
       </c>
-      <c r="F62" s="8" t="n"/>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
@@ -6484,7 +7560,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>Cement concrete khurras</t>
+          <t>Cement concrete khurra</t>
         </is>
       </c>
       <c r="I62" s="8" t="inlineStr">
@@ -6498,9 +7574,13 @@
         </is>
       </c>
       <c r="K62" s="17" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L62" s="8" t="n"/>
+        <v>0.9</v>
+      </c>
+      <c r="L62" s="8" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
       <c r="M62" s="8" t="inlineStr">
         <is>
           <t>1:2:4</t>
@@ -6531,14 +7611,22 @@
       <c r="Z62" s="17" t="n">
         <v>0.149</v>
       </c>
-      <c r="AA62" s="8" t="n"/>
+      <c r="AA62" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB62" s="8" t="inlineStr">
         <is>
           <t>12.39</t>
         </is>
       </c>
       <c r="AC62" s="8" t="n"/>
-      <c r="AD62" s="8" t="n"/>
+      <c r="AD62" s="8" t="inlineStr">
+        <is>
+          <t>Concrete &gt; Cement concrete khurra &gt; M15</t>
+        </is>
+      </c>
       <c r="AE62" s="8" t="n"/>
       <c r="AF62" s="8" t="n"/>
       <c r="AG62" s="8" t="n"/>
@@ -6549,8 +7637,12 @@
       <c r="AL62" s="8" t="n"/>
       <c r="AM62" s="8" t="n"/>
       <c r="AN62" s="8" t="n"/>
-      <c r="AO62" s="8" t="n"/>
-      <c r="AP62" s="8" t="n"/>
+      <c r="AO62" s="17" t="n">
+        <v>450</v>
+      </c>
+      <c r="AP62" s="17" t="n">
+        <v>450</v>
+      </c>
       <c r="AQ62" s="8" t="n"/>
       <c r="AR62" s="17" t="n">
         <v>50</v>
@@ -6562,12 +7654,16 @@
       <c r="AW62" s="8" t="n"/>
       <c r="AX62" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456); not printed in BoQ</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="n"/>
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0057</t>
+        </is>
+      </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
           <t>49</t>
@@ -6580,7 +7676,11 @@
           <t>Providing and fixing on wallface 100 mm diameter CI rain water pipe including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand)</t>
         </is>
       </c>
-      <c r="F63" s="8" t="n"/>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
           <t>Plumbing &amp; Sanitary</t>
@@ -6588,12 +7688,12 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>CI rain water pipe</t>
+          <t>Cast iron rain water pipe</t>
         </is>
       </c>
       <c r="I63" s="8" t="inlineStr">
         <is>
-          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
+          <t>Cast iron, Spun yarn, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J63" s="8" t="inlineStr">
@@ -6631,14 +7731,22 @@
       <c r="X63" s="8" t="n"/>
       <c r="Y63" s="8" t="n"/>
       <c r="Z63" s="8" t="n"/>
-      <c r="AA63" s="8" t="n"/>
+      <c r="AA63" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB63" s="8" t="inlineStr">
         <is>
           <t>12.69.2</t>
         </is>
       </c>
       <c r="AC63" s="8" t="n"/>
-      <c r="AD63" s="8" t="n"/>
+      <c r="AD63" s="8" t="inlineStr">
+        <is>
+          <t>Other &gt; Cast iron rain water pipe &gt; 1:2</t>
+        </is>
+      </c>
       <c r="AE63" s="8" t="n"/>
       <c r="AF63" s="8" t="n"/>
       <c r="AG63" s="8" t="n"/>
@@ -6663,7 +7771,11 @@
       <c r="AX63" s="8" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="n"/>
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0058</t>
+        </is>
+      </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
           <t>50</t>
@@ -6676,7 +7788,11 @@
           <t>Providing and fixing 100 mm dia MS holderbat clamps of approved design to CI or SCI rain water pipes embedded in and including cement concrete blocks 10 x 10 x 10 cm of 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size) and cost of cutting holes and making good the walls etc.</t>
         </is>
       </c>
-      <c r="F64" s="8" t="n"/>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
           <t>Plumbing &amp; Sanitary</t>
@@ -6684,12 +7800,12 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>MS holderbat clamps</t>
+          <t>Mild steel holderbat clamp</t>
         </is>
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>MS, Cement, Coarse sand, Stone aggregate</t>
+          <t>Mild steel, Cement concrete</t>
         </is>
       </c>
       <c r="J64" s="8" t="inlineStr">
@@ -6698,7 +7814,7 @@
         </is>
       </c>
       <c r="K64" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L64" s="8" t="n"/>
       <c r="M64" s="8" t="inlineStr">
@@ -6731,14 +7847,22 @@
       <c r="Z64" s="17" t="n">
         <v>1.55</v>
       </c>
-      <c r="AA64" s="8" t="n"/>
+      <c r="AA64" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB64" s="8" t="inlineStr">
         <is>
           <t>12.71.2</t>
         </is>
       </c>
       <c r="AC64" s="8" t="n"/>
-      <c r="AD64" s="8" t="n"/>
+      <c r="AD64" s="8" t="inlineStr">
+        <is>
+          <t>Steel &gt; Mild steel holderbat clamp &gt; 1:2:4</t>
+        </is>
+      </c>
       <c r="AE64" s="8" t="n"/>
       <c r="AF64" s="8" t="n"/>
       <c r="AG64" s="8" t="n"/>
@@ -6767,7 +7891,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="n"/>
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0059</t>
+        </is>
+      </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
           <t>51i</t>
@@ -6780,7 +7908,11 @@
           <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) CI plain head 100 mm dia</t>
         </is>
       </c>
-      <c r="F65" s="8" t="n"/>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
           <t>Plumbing &amp; Sanitary</t>
@@ -6788,12 +7920,12 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>CI plain head</t>
+          <t>Cast iron plain head</t>
         </is>
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
+          <t>Cast iron, Spun yarn, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J65" s="8" t="inlineStr">
@@ -6802,7 +7934,7 @@
         </is>
       </c>
       <c r="K65" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L65" s="8" t="n"/>
       <c r="M65" s="8" t="inlineStr">
@@ -6831,14 +7963,22 @@
       <c r="X65" s="8" t="n"/>
       <c r="Y65" s="8" t="n"/>
       <c r="Z65" s="8" t="n"/>
-      <c r="AA65" s="8" t="n"/>
+      <c r="AA65" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB65" s="8" t="inlineStr">
         <is>
           <t>12.72.2.2</t>
         </is>
       </c>
       <c r="AC65" s="8" t="n"/>
-      <c r="AD65" s="8" t="n"/>
+      <c r="AD65" s="8" t="inlineStr">
+        <is>
+          <t>Other &gt; Cast iron plain head &gt; 1:2</t>
+        </is>
+      </c>
       <c r="AE65" s="8" t="n"/>
       <c r="AF65" s="8" t="n"/>
       <c r="AG65" s="8" t="n"/>
@@ -6863,7 +8003,11 @@
       <c r="AX65" s="8" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="n"/>
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0060</t>
+        </is>
+      </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
           <t>51ii</t>
@@ -6876,7 +8020,11 @@
           <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) CI plain shoe - 100 mm dia</t>
         </is>
       </c>
-      <c r="F66" s="8" t="n"/>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
           <t>Plumbing &amp; Sanitary</t>
@@ -6884,12 +8032,12 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>CI plain shoe</t>
+          <t>Cast iron plain shoe</t>
         </is>
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
+          <t>Cast iron, Spun yarn, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J66" s="8" t="inlineStr">
@@ -6898,7 +8046,7 @@
         </is>
       </c>
       <c r="K66" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L66" s="8" t="n"/>
       <c r="M66" s="8" t="inlineStr">
@@ -6927,14 +8075,22 @@
       <c r="X66" s="8" t="n"/>
       <c r="Y66" s="8" t="n"/>
       <c r="Z66" s="8" t="n"/>
-      <c r="AA66" s="8" t="n"/>
+      <c r="AA66" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB66" s="8" t="inlineStr">
         <is>
           <t>12.72.3.2</t>
         </is>
       </c>
       <c r="AC66" s="8" t="n"/>
-      <c r="AD66" s="8" t="n"/>
+      <c r="AD66" s="8" t="inlineStr">
+        <is>
+          <t>Other &gt; Cast iron plain shoe &gt; 1:2</t>
+        </is>
+      </c>
       <c r="AE66" s="8" t="n"/>
       <c r="AF66" s="8" t="n"/>
       <c r="AG66" s="8" t="n"/>
@@ -6959,7 +8115,11 @@
       <c r="AX66" s="8" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="n"/>
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0061</t>
+        </is>
+      </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
           <t>51iii</t>
@@ -6972,7 +8132,11 @@
           <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) CI plain bend - 100 mm dia</t>
         </is>
       </c>
-      <c r="F67" s="8" t="n"/>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
           <t>Plumbing &amp; Sanitary</t>
@@ -6980,12 +8144,12 @@
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>CI plain bend</t>
+          <t>Cast iron plain bend</t>
         </is>
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
+          <t>Cast iron, Spun yarn, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J67" s="8" t="inlineStr">
@@ -6994,7 +8158,7 @@
         </is>
       </c>
       <c r="K67" s="17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L67" s="8" t="n"/>
       <c r="M67" s="8" t="inlineStr">
@@ -7023,14 +8187,22 @@
       <c r="X67" s="8" t="n"/>
       <c r="Y67" s="8" t="n"/>
       <c r="Z67" s="8" t="n"/>
-      <c r="AA67" s="8" t="n"/>
+      <c r="AA67" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB67" s="8" t="inlineStr">
         <is>
           <t>12.72.1.2</t>
         </is>
       </c>
       <c r="AC67" s="8" t="n"/>
-      <c r="AD67" s="8" t="n"/>
+      <c r="AD67" s="8" t="inlineStr">
+        <is>
+          <t>Other &gt; Cast iron plain bend &gt; 1:2</t>
+        </is>
+      </c>
       <c r="AE67" s="8" t="n"/>
       <c r="AF67" s="8" t="n"/>
       <c r="AG67" s="8" t="n"/>
@@ -7055,7 +8227,11 @@
       <c r="AX67" s="8" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="n"/>
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0062</t>
+        </is>
+      </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
           <t>52</t>
@@ -7068,7 +8244,11 @@
           <t>12 mm cement plaster of mix 1:6 (1 cement : 6 fine sand)</t>
         </is>
       </c>
-      <c r="F68" s="8" t="n"/>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -7113,9 +8293,19 @@
       <c r="R68" s="8" t="n"/>
       <c r="S68" s="8" t="n"/>
       <c r="T68" s="8" t="n"/>
-      <c r="U68" s="8" t="n"/>
-      <c r="V68" s="8" t="n"/>
-      <c r="W68" s="8" t="n"/>
+      <c r="U68" s="17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V68" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W68" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (12.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X68" s="8" t="n"/>
       <c r="Y68" s="17" t="n">
         <v>209</v>
@@ -7123,14 +8313,22 @@
       <c r="Z68" s="17" t="n">
         <v>0.95</v>
       </c>
-      <c r="AA68" s="8" t="n"/>
+      <c r="AA68" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB68" s="8" t="inlineStr">
         <is>
           <t>13.8.4</t>
         </is>
       </c>
       <c r="AC68" s="8" t="n"/>
-      <c r="AD68" s="8" t="n"/>
+      <c r="AD68" s="8" t="inlineStr">
+        <is>
+          <t>Paint/Finish &gt; Cement plaster &gt; 1:6</t>
+        </is>
+      </c>
       <c r="AE68" s="8" t="n"/>
       <c r="AF68" s="8" t="n"/>
       <c r="AG68" s="8" t="n"/>
@@ -7159,7 +8357,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="n"/>
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0063</t>
+        </is>
+      </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
           <t>53</t>
@@ -7172,7 +8374,11 @@
           <t>15 mm cement plaster on the rough side of single or half brick wall of mix 1:6 (1 cement : 6 fine sand)</t>
         </is>
       </c>
-      <c r="F69" s="8" t="n"/>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -7217,9 +8423,19 @@
       <c r="R69" s="8" t="n"/>
       <c r="S69" s="8" t="n"/>
       <c r="T69" s="8" t="n"/>
-      <c r="U69" s="8" t="n"/>
-      <c r="V69" s="8" t="n"/>
-      <c r="W69" s="8" t="n"/>
+      <c r="U69" s="17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V69" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W69" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (15.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X69" s="8" t="n"/>
       <c r="Y69" s="17" t="n">
         <v>209</v>
@@ -7227,14 +8443,22 @@
       <c r="Z69" s="17" t="n">
         <v>0.95</v>
       </c>
-      <c r="AA69" s="8" t="n"/>
+      <c r="AA69" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB69" s="8" t="inlineStr">
         <is>
           <t>13.9.4</t>
         </is>
       </c>
       <c r="AC69" s="8" t="n"/>
-      <c r="AD69" s="8" t="n"/>
+      <c r="AD69" s="8" t="inlineStr">
+        <is>
+          <t>Paint/Finish &gt; Cement plaster &gt; 1:6</t>
+        </is>
+      </c>
       <c r="AE69" s="8" t="n"/>
       <c r="AF69" s="8" t="n"/>
       <c r="AG69" s="8" t="n"/>
@@ -7263,7 +8487,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="n"/>
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0064</t>
+        </is>
+      </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
           <t>54</t>
@@ -7276,7 +8504,11 @@
           <t>6 mm cement plaster of mix 1:3 (1 cement : 3 fine sand) finished with a floating coat of neat cement and thick coat of lime wash on top of walls when dry for bearing of RCC slabs and beams.</t>
         </is>
       </c>
-      <c r="F70" s="8" t="n"/>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -7321,9 +8553,19 @@
       <c r="R70" s="8" t="n"/>
       <c r="S70" s="8" t="n"/>
       <c r="T70" s="8" t="n"/>
-      <c r="U70" s="8" t="n"/>
-      <c r="V70" s="8" t="n"/>
-      <c r="W70" s="8" t="n"/>
+      <c r="U70" s="17" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="V70" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W70" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (6.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X70" s="8" t="n"/>
       <c r="Y70" s="17" t="n">
         <v>18.05</v>
@@ -7331,14 +8573,22 @@
       <c r="Z70" s="17" t="n">
         <v>0.95</v>
       </c>
-      <c r="AA70" s="8" t="n"/>
+      <c r="AA70" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB70" s="8" t="inlineStr">
         <is>
           <t>13.25</t>
         </is>
       </c>
       <c r="AC70" s="8" t="n"/>
-      <c r="AD70" s="8" t="n"/>
+      <c r="AD70" s="8" t="inlineStr">
+        <is>
+          <t>Paint/Finish &gt; Cement plaster &gt; 1:3</t>
+        </is>
+      </c>
       <c r="AE70" s="8" t="n"/>
       <c r="AF70" s="8" t="n"/>
       <c r="AG70" s="8" t="n"/>
@@ -7367,7 +8617,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="n"/>
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0065</t>
+        </is>
+      </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
           <t>55</t>
@@ -7380,7 +8634,11 @@
           <t>18 mm plastering with terrazzo finish for dado rubbed and polished complete, under layer 12 mm thick cement plaster 1:3 (1 cement : 3 coarse sand) and top layer 6 mm thick white, black, chocolate, grey, yellow or Baroda green marble chips of 3 mm and down size laid in cement marble powder mix 3:1 (3 cement : 1 marble powder) by weight in proportion of 4:7 (4 cement marble powder mix : 7 marble chips) by volume.</t>
         </is>
       </c>
-      <c r="F71" s="8" t="n"/>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -7393,7 +8651,7 @@
       </c>
       <c r="I71" s="8" t="inlineStr">
         <is>
-          <t>Cement, Sand, Marble chips, Marble powder</t>
+          <t>Cement, Coarse sand, Marble chips, Marble powder</t>
         </is>
       </c>
       <c r="J71" s="8" t="inlineStr">
@@ -7425,9 +8683,19 @@
       <c r="R71" s="8" t="n"/>
       <c r="S71" s="8" t="n"/>
       <c r="T71" s="8" t="n"/>
-      <c r="U71" s="8" t="n"/>
-      <c r="V71" s="8" t="n"/>
-      <c r="W71" s="8" t="n"/>
+      <c r="U71" s="17" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="V71" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W71" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (18.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X71" s="8" t="n"/>
       <c r="Y71" s="17" t="n">
         <v>19</v>
@@ -7435,14 +8703,22 @@
       <c r="Z71" s="17" t="n">
         <v>0.95</v>
       </c>
-      <c r="AA71" s="8" t="n"/>
+      <c r="AA71" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB71" s="8" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>5.31/13.24.1</t>
         </is>
       </c>
       <c r="AC71" s="8" t="n"/>
-      <c r="AD71" s="8" t="n"/>
+      <c r="AD71" s="8" t="inlineStr">
+        <is>
+          <t>Paint/Finish &gt; Terrazzo plastering &gt; 1:3</t>
+        </is>
+      </c>
       <c r="AE71" s="8" t="n"/>
       <c r="AF71" s="8" t="n"/>
       <c r="AG71" s="8" t="n"/>
@@ -7471,7 +8747,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="n"/>
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0066</t>
+        </is>
+      </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
           <t>56</t>
@@ -7484,7 +8764,11 @@
           <t>Finishing and plastering the exposed surface of RCC with cement mortar 1:3</t>
         </is>
       </c>
-      <c r="F72" s="8" t="n"/>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -7492,12 +8776,12 @@
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>Cement mortar plaster</t>
+          <t>Cement plaster</t>
         </is>
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>Cement, Sand</t>
+          <t>Cement mortar</t>
         </is>
       </c>
       <c r="J72" s="8" t="inlineStr">
@@ -7539,14 +8823,22 @@
       <c r="Z72" s="17" t="n">
         <v>0.95</v>
       </c>
-      <c r="AA72" s="8" t="n"/>
+      <c r="AA72" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB72" s="8" t="inlineStr">
         <is>
-          <t>5.31/13.24.1</t>
+          <t>13.70.1</t>
         </is>
       </c>
       <c r="AC72" s="8" t="n"/>
-      <c r="AD72" s="8" t="n"/>
+      <c r="AD72" s="8" t="inlineStr">
+        <is>
+          <t>Paint/Finish &gt; Cement plaster &gt; 1:3</t>
+        </is>
+      </c>
       <c r="AE72" s="8" t="n"/>
       <c r="AF72" s="8" t="n"/>
       <c r="AG72" s="8" t="n"/>
@@ -7573,7 +8865,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="n"/>
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0067</t>
+        </is>
+      </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
           <t>57</t>
@@ -7586,7 +8882,11 @@
           <t>White washing with lime to give an even shade on new work (three or more coats).</t>
         </is>
       </c>
-      <c r="F73" s="8" t="n"/>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -7594,7 +8894,7 @@
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>Lime white wash</t>
+          <t>Lime wash</t>
         </is>
       </c>
       <c r="I73" s="8" t="inlineStr">
@@ -7637,14 +8937,22 @@
       <c r="Z73" s="17" t="n">
         <v>0.95</v>
       </c>
-      <c r="AA73" s="8" t="n"/>
+      <c r="AA73" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB73" s="8" t="inlineStr">
         <is>
-          <t>13.70.1</t>
+          <t>13.73.1</t>
         </is>
       </c>
       <c r="AC73" s="8" t="n"/>
-      <c r="AD73" s="8" t="n"/>
+      <c r="AD73" s="8" t="inlineStr">
+        <is>
+          <t>Paint/Finish &gt; Lime wash</t>
+        </is>
+      </c>
       <c r="AE73" s="8" t="n"/>
       <c r="AF73" s="8" t="n"/>
       <c r="AG73" s="8" t="n"/>
@@ -7671,7 +8979,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="n"/>
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0068</t>
+        </is>
+      </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
           <t>58</t>
@@ -7684,7 +8996,11 @@
           <t>Colour washing such as green, blue or buff to give an even shade on new work (two or more coats) with a base coat of white washing with lime.</t>
         </is>
       </c>
-      <c r="F74" s="8" t="n"/>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -7697,7 +9013,7 @@
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
-          <t>Lime, Colour wash</t>
+          <t>Lime wash</t>
         </is>
       </c>
       <c r="J74" s="8" t="inlineStr">
@@ -7735,14 +9051,22 @@
       <c r="Z74" s="17" t="n">
         <v>0.95</v>
       </c>
-      <c r="AA74" s="8" t="n"/>
+      <c r="AA74" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB74" s="8" t="inlineStr">
         <is>
-          <t>13.73.1</t>
+          <t>13.81.1</t>
         </is>
       </c>
       <c r="AC74" s="8" t="n"/>
-      <c r="AD74" s="8" t="n"/>
+      <c r="AD74" s="8" t="inlineStr">
+        <is>
+          <t>Paint/Finish &gt; Colour wash</t>
+        </is>
+      </c>
       <c r="AE74" s="8" t="n"/>
       <c r="AF74" s="8" t="n"/>
       <c r="AG74" s="8" t="n"/>
@@ -7769,6 +9093,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>GMAP-0069</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>59</t>
@@ -7779,6 +9108,11 @@
           <t>Applying priming coat with ready mixed pink or gray primer of approved brand and manufacture - on wood work (hard and soft wood)</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -7786,12 +9120,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Wood primer</t>
+          <t>Primer</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Primer</t>
+          <t>Pink primer, Gray primer, Wood</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7819,9 +9153,19 @@
       <c r="Z75" s="18" t="n">
         <v>0.95</v>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13.81.1</t>
+          <t>13.81.4</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>Paint/Finish &gt; Primer</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
@@ -7831,6 +9175,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>GMAP-0070</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>60</t>
@@ -7841,6 +9190,11 @@
           <t>Applying priming coat with readymixed zinc chromate yellow primer of approved brand and manufacture on steelwork (second coat)</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -7848,12 +9202,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Zinc chromate primer</t>
+          <t>Zinc chromate yellow primer</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Zinc chromate primer</t>
+          <t>Zinc chromate yellow primer</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7881,9 +9235,19 @@
       <c r="Z76" s="18" t="n">
         <v>0.95</v>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13.81.4</t>
+          <t>13.84.3</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>Paint/Finish &gt; Zinc chromate yellow primer</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
@@ -7893,6 +9257,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>GMAP-0071</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>61</t>
@@ -7903,6 +9272,11 @@
           <t>Painting (two or more coats) on rain water, soil, waste and vent pipes and fittings with black anticorrosive bitumastic paint of approved brand and manufacture over and including a priming coat of ready mixed zinc chromate yellow primer on new work on 100 mm diameter pipes.</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>Finishes</t>
@@ -7915,7 +9289,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Bitumastic paint, Zinc chromate primer</t>
+          <t>Bitumastic paint, Zinc chromate yellow primer</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7943,9 +9317,19 @@
       <c r="Z77" s="18" t="n">
         <v>0.95</v>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13.84.3</t>
+          <t>13.94.1</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>Paint/Finish &gt; Bitumastic paint</t>
         </is>
       </c>
       <c r="AT77" s="18" t="n">
@@ -7958,6 +9342,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>GMAP-0072</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>62</t>
@@ -7966,6 +9355,11 @@
       <c r="E78" t="inlineStr">
         <is>
           <t>Painting with synthetic enamel paint of approved brand and manufacture to give an even shade in two or more coats on new work in black or chocolate shade over an under coat of suitable shade with ordinary paint of approved brand and manufacture.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -8008,9 +9402,14 @@
       <c r="Z78" s="18" t="n">
         <v>0.95</v>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>13.94.1</t>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>Paint/Finish &gt; Synthetic enamel paint</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
@@ -8020,6 +9419,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>GMAP-0073</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>63</t>
@@ -8028,6 +9432,11 @@
       <c r="E79" t="inlineStr">
         <is>
           <t>French spirit polishing two or more coats on new works including a coat of wood filler.</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -8070,11 +9479,21 @@
       <c r="Z79" s="18" t="n">
         <v>0.95</v>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB79" t="inlineStr">
         <is>
           <t>13.101.1</t>
         </is>
       </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>Paint/Finish &gt; French spirit polish</t>
+        </is>
+      </c>
       <c r="AX79" t="inlineStr">
         <is>
           <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
@@ -8082,6 +9501,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>GMAP-0074</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>64</t>
@@ -8090,6 +9514,11 @@
       <c r="E80" t="inlineStr">
         <is>
           <t>Making plinth protection 50 mm thick of cement concrete 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) over 75 mm bed of dry brick ballast 40 mm nominal size well rammed and consolidated and grouted with fine sand, including finishing the top smooth.</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Schedule 'A'</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -8115,6 +9544,11 @@
       <c r="K80" s="18" t="n">
         <v>0.95</v>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr">
         <is>
           <t>1:3:6</t>
@@ -8131,15 +9565,38 @@
       <c r="Q80" s="18" t="n">
         <v>34.6</v>
       </c>
+      <c r="U80" s="18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Area x thickness (50.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="Y80" s="18" t="n">
         <v>5.16</v>
       </c>
       <c r="Z80" s="18" t="n">
         <v>0.149</v>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
       <c r="AB80" t="inlineStr">
         <is>
           <t>16.1</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>Concrete &gt; Cement concrete plinth protection &gt; M10</t>
         </is>
       </c>
       <c r="AR80" s="18" t="n">
@@ -8147,7 +9604,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M10 inferred from nominal mix 1:3:6 (IS 456); not printed in BoQ</t>
         </is>
       </c>
     </row>

--- a/output/passport_filled.xlsx
+++ b/output/passport_filled.xlsx
@@ -1748,7 +1748,7 @@
       <c r="AW12" s="8" t="n"/>
       <c r="AX12" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M5 inferred from nominal mix 1:5:10 (IS 456); not printed in BoQ</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M5 inferred from nominal mix 1:5:10 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       <c r="AW13" s="8" t="n"/>
       <c r="AX13" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M5 inferred from nominal mix 1:5:10 (IS 456); not printed in BoQ</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M5 inferred from nominal mix 1:5:10 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -1992,7 +1992,7 @@
       <c r="AW14" s="8" t="n"/>
       <c r="AX14" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456); not printed in BoQ</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       <c r="AW15" s="8" t="n"/>
       <c r="AX15" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456); not printed in BoQ</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
       <c r="AW17" s="8" t="n"/>
       <c r="AX17" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456); not printed in BoQ</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       <c r="AW18" s="8" t="n"/>
       <c r="AX18" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456); not printed in BoQ</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       <c r="AW19" s="8" t="n"/>
       <c r="AX19" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456); not printed in BoQ</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       <c r="AW20" s="8" t="n"/>
       <c r="AX20" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456); not printed in BoQ</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       <c r="AW21" s="8" t="n"/>
       <c r="AX21" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456); not printed in BoQ</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       <c r="AW29" s="8" t="n"/>
       <c r="AX29" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456); not printed in BoQ</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       <c r="AW54" s="8" t="n"/>
       <c r="AX54" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456); not printed in BoQ</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7526,7 @@
       <c r="AW61" s="8" t="n"/>
       <c r="AX61" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M10 inferred from nominal mix 1:3:6 (IS 456); not printed in BoQ</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M10 inferred from nominal mix 1:3:6 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       <c r="AW62" s="8" t="n"/>
       <c r="AX62" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456); not printed in BoQ</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -9604,7 +9604,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M10 inferred from nominal mix 1:3:6 (IS 456); not printed in BoQ</t>
+          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M10 inferred from nominal mix 1:3:6 (IS 456)</t>
         </is>
       </c>
     </row>

--- a/output/passport_filled.xlsx
+++ b/output/passport_filled.xlsx
@@ -1116,7 +1116,7 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - I, Earth Work</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -1126,21 +1126,23 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
+          <t>Earth/Soil</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
           <t>Soil</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>Soil</t>
-        </is>
-      </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
           <t>Earthwork</t>
         </is>
       </c>
-      <c r="K7" s="17" t="n">
-        <v>0.95</v>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L7" s="8" t="n"/>
       <c r="M7" s="8" t="n"/>
@@ -1178,7 +1180,7 @@
       <c r="AC7" s="8" t="n"/>
       <c r="AD7" s="8" t="inlineStr">
         <is>
-          <t>Earthwork &gt; Soil</t>
+          <t>Earthwork &gt; Earth/Soil</t>
         </is>
       </c>
       <c r="AE7" s="8" t="n"/>
@@ -1200,7 +1202,11 @@
       <c r="AU7" s="8" t="n"/>
       <c r="AV7" s="8" t="n"/>
       <c r="AW7" s="8" t="n"/>
-      <c r="AX7" s="8" t="n"/>
+      <c r="AX7" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Earth/Soil — earthwork/excavated soil; negligible embodied material carbon</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -1222,7 +1228,7 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - I, Earth Work</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1232,21 +1238,23 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
+          <t>Earth/Soil</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
           <t>Earth</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>Earth</t>
-        </is>
-      </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
           <t>Earthwork</t>
         </is>
       </c>
-      <c r="K8" s="17" t="n">
-        <v>0.95</v>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L8" s="8" t="n"/>
       <c r="M8" s="8" t="n"/>
@@ -1284,7 +1292,7 @@
       <c r="AC8" s="8" t="n"/>
       <c r="AD8" s="8" t="inlineStr">
         <is>
-          <t>Earthwork &gt; Earth</t>
+          <t>Earthwork &gt; Earth/Soil</t>
         </is>
       </c>
       <c r="AE8" s="8" t="n"/>
@@ -1301,14 +1309,16 @@
       <c r="AP8" s="8" t="n"/>
       <c r="AQ8" s="8" t="n"/>
       <c r="AR8" s="8" t="n"/>
-      <c r="AS8" s="17" t="n">
-        <v>200</v>
-      </c>
+      <c r="AS8" s="8" t="n"/>
       <c r="AT8" s="8" t="n"/>
       <c r="AU8" s="8" t="n"/>
       <c r="AV8" s="8" t="n"/>
       <c r="AW8" s="8" t="n"/>
-      <c r="AX8" s="8" t="n"/>
+      <c r="AX8" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Earth/Soil — earthwork/excavated soil; negligible embodied material carbon</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -1330,7 +1340,7 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - I, Earth Work</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -1340,12 +1350,12 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Fine sand</t>
+          <t>Sand</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Fine sand</t>
+          <t>Sand</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -1353,8 +1363,10 @@
           <t>Earthwork</t>
         </is>
       </c>
-      <c r="K9" s="17" t="n">
-        <v>0.9</v>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L9" s="8" t="n"/>
       <c r="M9" s="8" t="n"/>
@@ -1392,7 +1404,7 @@
       <c r="AC9" s="8" t="n"/>
       <c r="AD9" s="8" t="inlineStr">
         <is>
-          <t>Earthwork &gt; Fine sand</t>
+          <t>Earthwork &gt; Sand</t>
         </is>
       </c>
       <c r="AE9" s="8" t="n"/>
@@ -1414,7 +1426,11 @@
       <c r="AU9" s="8" t="n"/>
       <c r="AV9" s="8" t="n"/>
       <c r="AW9" s="8" t="n"/>
-      <c r="AX9" s="8" t="n"/>
+      <c r="AX9" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Sand — earthwork/excavated soil; negligible embodied material carbon</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -1436,7 +1452,7 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - I, Earth Work</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1459,13 +1475,15 @@
           <t>Earthwork</t>
         </is>
       </c>
-      <c r="K10" s="17" t="n">
-        <v>0.9</v>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L10" s="8" t="n"/>
       <c r="M10" s="8" t="n"/>
       <c r="N10" s="17" t="n">
-        <v>540</v>
+        <v>140</v>
       </c>
       <c r="O10" s="8" t="inlineStr">
         <is>
@@ -1474,7 +1492,7 @@
       </c>
       <c r="P10" s="8" t="n"/>
       <c r="Q10" s="17" t="n">
-        <v>540</v>
+        <v>140</v>
       </c>
       <c r="R10" s="8" t="n"/>
       <c r="S10" s="8" t="n"/>
@@ -1515,14 +1533,16 @@
       <c r="AP10" s="8" t="n"/>
       <c r="AQ10" s="8" t="n"/>
       <c r="AR10" s="8" t="n"/>
-      <c r="AS10" s="17" t="n">
-        <v>150</v>
-      </c>
+      <c r="AS10" s="8" t="n"/>
       <c r="AT10" s="8" t="n"/>
       <c r="AU10" s="8" t="n"/>
       <c r="AV10" s="8" t="n"/>
       <c r="AW10" s="8" t="n"/>
-      <c r="AX10" s="8" t="n"/>
+      <c r="AX10" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Soil — earthwork/excavated soil; negligible embodied material carbon</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -1544,7 +1564,7 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - I, Earth Work</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -1554,12 +1574,12 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Aldrin Chemical Emulsion</t>
+          <t>Aldrin Emulsifiable Concentrate</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>Aldrin Emulsifiable Concentrate</t>
+          <t>Aldrin Emulsifiable Concentrate, Chemical emulsion</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
@@ -1567,8 +1587,10 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="K11" s="17" t="n">
-        <v>0.85</v>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L11" s="8" t="n"/>
       <c r="M11" s="8" t="n"/>
@@ -1606,7 +1628,7 @@
       <c r="AC11" s="8" t="n"/>
       <c r="AD11" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aldrin Chemical Emulsion</t>
+          <t>Other &gt; Aldrin Emulsifiable Concentrate</t>
         </is>
       </c>
       <c r="AE11" s="8" t="n"/>
@@ -1628,7 +1650,11 @@
       <c r="AU11" s="8" t="n"/>
       <c r="AV11" s="8" t="n"/>
       <c r="AW11" s="8" t="n"/>
-      <c r="AX11" s="8" t="n"/>
+      <c r="AX11" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Aldrin Emulsifiable Concentrate — category 'Other' not in current EPD database; carbon not estimated</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -1650,7 +1676,7 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - II, Cement Concrete Work</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1665,7 +1691,7 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Stone aggregate</t>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -1673,8 +1699,10 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K12" s="17" t="n">
-        <v>0.95</v>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
@@ -1704,9 +1732,11 @@
       <c r="U12" s="8" t="n"/>
       <c r="V12" s="8" t="n"/>
       <c r="W12" s="8" t="n"/>
-      <c r="X12" s="8" t="n"/>
+      <c r="X12" s="17" t="n">
+        <v>2400</v>
+      </c>
       <c r="Y12" s="17" t="n">
-        <v>1.19</v>
+        <v>2860.8</v>
       </c>
       <c r="Z12" s="17" t="n">
         <v>0.149</v>
@@ -1748,7 +1778,7 @@
       <c r="AW12" s="8" t="n"/>
       <c r="AX12" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M5 inferred from nominal mix 1:5:10 (IS 456)</t>
+          <t>[OK] material: Cement concrete — mass 19200.0 kg [direct volume] × 0.149 kgCO2e/kg = 2860.8 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M5 inferred from nominal mix 1:5:10 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1802,7 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - II, Cement Concrete Work</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -1787,7 +1817,7 @@
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>Cement, Fine sand, Stone aggregate</t>
+          <t>Cement, Fine sand, Graded stone aggregate</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
@@ -1795,8 +1825,10 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K13" s="17" t="n">
-        <v>0.95</v>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
@@ -1826,9 +1858,11 @@
       <c r="U13" s="8" t="n"/>
       <c r="V13" s="8" t="n"/>
       <c r="W13" s="8" t="n"/>
-      <c r="X13" s="8" t="n"/>
+      <c r="X13" s="17" t="n">
+        <v>2400</v>
+      </c>
       <c r="Y13" s="17" t="n">
-        <v>1.09</v>
+        <v>2610.48</v>
       </c>
       <c r="Z13" s="17" t="n">
         <v>0.149</v>
@@ -1870,7 +1904,7 @@
       <c r="AW13" s="8" t="n"/>
       <c r="AX13" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M5 inferred from nominal mix 1:5:10 (IS 456)</t>
+          <t>[OK] material: Cement concrete — mass 17520.0 kg [direct volume] × 0.149 kgCO2e/kg = 2610.48 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M5 inferred from nominal mix 1:5:10 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1928,7 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - II, Cement Concrete Work</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
@@ -1909,7 +1943,7 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Stone aggregate</t>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -1917,8 +1951,10 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K14" s="17" t="n">
-        <v>0.95</v>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
@@ -1948,9 +1984,11 @@
       <c r="U14" s="8" t="n"/>
       <c r="V14" s="8" t="n"/>
       <c r="W14" s="8" t="n"/>
-      <c r="X14" s="8" t="n"/>
+      <c r="X14" s="17" t="n">
+        <v>2400</v>
+      </c>
       <c r="Y14" s="17" t="n">
-        <v>0.01</v>
+        <v>35.76</v>
       </c>
       <c r="Z14" s="17" t="n">
         <v>0.149</v>
@@ -1992,7 +2030,7 @@
       <c r="AW14" s="8" t="n"/>
       <c r="AX14" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[OK] material: Cement concrete — mass 240.0 kg [direct volume] × 0.149 kgCO2e/kg = 35.76 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2054,7 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - II, Cement Concrete Work</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -2031,7 +2069,7 @@
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Stone aggregate</t>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
         </is>
       </c>
       <c r="J15" s="8" t="inlineStr">
@@ -2039,8 +2077,10 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K15" s="17" t="n">
-        <v>0.95</v>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
@@ -2080,9 +2120,11 @@
           <t>Area x thickness (40.0 mm, from description)</t>
         </is>
       </c>
-      <c r="X15" s="8" t="n"/>
+      <c r="X15" s="17" t="n">
+        <v>2400</v>
+      </c>
       <c r="Y15" s="17" t="n">
-        <v>2.15</v>
+        <v>205.98</v>
       </c>
       <c r="Z15" s="17" t="n">
         <v>0.149</v>
@@ -2126,7 +2168,7 @@
       <c r="AW15" s="8" t="n"/>
       <c r="AX15" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[OK] material: Cement concrete — mass 1382.4 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 205.98 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2192,7 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - II, Cement Concrete Work</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
@@ -2170,11 +2212,13 @@
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="n">
-        <v>0.9</v>
+          <t>Paint/Finish</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L16" s="8" t="n"/>
       <c r="M16" s="8" t="n"/>
@@ -2196,9 +2240,13 @@
       <c r="U16" s="8" t="n"/>
       <c r="V16" s="8" t="n"/>
       <c r="W16" s="8" t="n"/>
-      <c r="X16" s="8" t="n"/>
+      <c r="X16" s="17" t="n">
+        <v>1300</v>
+      </c>
       <c r="Y16" s="8" t="n"/>
-      <c r="Z16" s="8" t="n"/>
+      <c r="Z16" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="AA16" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -2212,7 +2260,7 @@
       <c r="AC16" s="8" t="n"/>
       <c r="AD16" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Bitumen</t>
+          <t>Paint/Finish &gt; Bitumen</t>
         </is>
       </c>
       <c r="AE16" s="8" t="n"/>
@@ -2234,7 +2282,11 @@
       <c r="AU16" s="8" t="n"/>
       <c r="AV16" s="8" t="n"/>
       <c r="AW16" s="8" t="n"/>
-      <c r="AX16" s="8" t="n"/>
+      <c r="AX16" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Bitumen — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -2256,7 +2308,7 @@
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - III, R.C.C. Work</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
@@ -2271,7 +2323,7 @@
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Stone aggregate</t>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -2279,8 +2331,10 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K17" s="17" t="n">
-        <v>0.95</v>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
@@ -2310,9 +2364,11 @@
       <c r="U17" s="8" t="n"/>
       <c r="V17" s="8" t="n"/>
       <c r="W17" s="8" t="n"/>
-      <c r="X17" s="8" t="n"/>
+      <c r="X17" s="17" t="n">
+        <v>2400</v>
+      </c>
       <c r="Y17" s="17" t="n">
-        <v>1.68</v>
+        <v>4040.88</v>
       </c>
       <c r="Z17" s="17" t="n">
         <v>0.149</v>
@@ -2354,7 +2410,7 @@
       <c r="AW17" s="8" t="n"/>
       <c r="AX17" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[OK] material: Reinforced cement concrete — mass 27120.0 kg [direct volume] × 0.149 kgCO2e/kg = 4040.88 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2434,7 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - III, R.C.C. Work</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
@@ -2393,7 +2449,7 @@
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Stone aggregate</t>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -2401,8 +2457,10 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K18" s="17" t="n">
-        <v>0.95</v>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
@@ -2432,9 +2490,11 @@
       <c r="U18" s="8" t="n"/>
       <c r="V18" s="8" t="n"/>
       <c r="W18" s="8" t="n"/>
-      <c r="X18" s="8" t="n"/>
+      <c r="X18" s="17" t="n">
+        <v>2400</v>
+      </c>
       <c r="Y18" s="17" t="n">
-        <v>0.15</v>
+        <v>357.6</v>
       </c>
       <c r="Z18" s="17" t="n">
         <v>0.149</v>
@@ -2476,7 +2536,7 @@
       <c r="AW18" s="8" t="n"/>
       <c r="AX18" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[OK] material: Reinforced cement concrete — mass 2400.0 kg [direct volume] × 0.149 kgCO2e/kg = 357.6 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2560,7 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - III, R.C.C. Work</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -2515,7 +2575,7 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Stone aggregate</t>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -2523,8 +2583,10 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K19" s="17" t="n">
-        <v>0.95</v>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
@@ -2554,9 +2616,11 @@
       <c r="U19" s="8" t="n"/>
       <c r="V19" s="8" t="n"/>
       <c r="W19" s="8" t="n"/>
-      <c r="X19" s="8" t="n"/>
+      <c r="X19" s="17" t="n">
+        <v>2400</v>
+      </c>
       <c r="Y19" s="17" t="n">
-        <v>0.09</v>
+        <v>214.56</v>
       </c>
       <c r="Z19" s="17" t="n">
         <v>0.149</v>
@@ -2598,7 +2662,7 @@
       <c r="AW19" s="8" t="n"/>
       <c r="AX19" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[OK] material: Reinforced cement concrete — mass 1440.0 kg [direct volume] × 0.149 kgCO2e/kg = 214.56 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2686,7 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - III, R.C.C. Work</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
@@ -2637,7 +2701,7 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Stone aggregate</t>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
@@ -2645,8 +2709,10 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K20" s="17" t="n">
-        <v>0.95</v>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
@@ -2676,9 +2742,11 @@
       <c r="U20" s="8" t="n"/>
       <c r="V20" s="8" t="n"/>
       <c r="W20" s="8" t="n"/>
-      <c r="X20" s="8" t="n"/>
+      <c r="X20" s="17" t="n">
+        <v>2400</v>
+      </c>
       <c r="Y20" s="17" t="n">
-        <v>0.25</v>
+        <v>607.92</v>
       </c>
       <c r="Z20" s="17" t="n">
         <v>0.149</v>
@@ -2720,7 +2788,7 @@
       <c r="AW20" s="8" t="n"/>
       <c r="AX20" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[OK] material: Reinforced cement concrete — mass 4080.0 kg [direct volume] × 0.149 kgCO2e/kg = 607.92 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2812,7 @@
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - III, R.C.C. Work</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -2759,7 +2827,7 @@
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Stone aggregate</t>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -2767,8 +2835,10 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K21" s="17" t="n">
-        <v>0.95</v>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -2798,9 +2868,11 @@
       <c r="U21" s="8" t="n"/>
       <c r="V21" s="8" t="n"/>
       <c r="W21" s="8" t="n"/>
-      <c r="X21" s="8" t="n"/>
+      <c r="X21" s="17" t="n">
+        <v>2400</v>
+      </c>
       <c r="Y21" s="17" t="n">
-        <v>0.01</v>
+        <v>35.76</v>
       </c>
       <c r="Z21" s="17" t="n">
         <v>0.149</v>
@@ -2842,7 +2914,7 @@
       <c r="AW21" s="8" t="n"/>
       <c r="AX21" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[OK] material: Reinforced cement concrete — mass 240.0 kg [direct volume] × 0.149 kgCO2e/kg = 35.76 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -2854,19 +2926,19 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>16i</t>
+          <t>16a</t>
         </is>
       </c>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Suspended floors, roofs, landings balconies and chajjas.</t>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : i) Suspended floors, roofs, landings balconies and chajjas.</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - III, R.C.C. Work</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
@@ -2881,7 +2953,7 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>Formwork</t>
+          <t>Timber, Steel</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -2889,8 +2961,10 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="K22" s="17" t="n">
-        <v>0.85</v>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
@@ -2950,7 +3024,11 @@
       <c r="AU22" s="8" t="n"/>
       <c r="AV22" s="8" t="n"/>
       <c r="AW22" s="8" t="n"/>
-      <c r="AX22" s="8" t="n"/>
+      <c r="AX22" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Formwork — category 'Other' not in current EPD database; carbon not estimated</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -2960,19 +3038,19 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>16ii</t>
+          <t>16b</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Shelves</t>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : ii) Shelves</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - III, R.C.C. Work</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -2987,7 +3065,7 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>Formwork</t>
+          <t>Timber, Steel</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
@@ -2995,8 +3073,10 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="K23" s="17" t="n">
-        <v>0.85</v>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L23" s="8" t="n"/>
       <c r="M23" s="8" t="n"/>
@@ -3056,7 +3136,11 @@
       <c r="AU23" s="8" t="n"/>
       <c r="AV23" s="8" t="n"/>
       <c r="AW23" s="8" t="n"/>
-      <c r="AX23" s="8" t="n"/>
+      <c r="AX23" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Formwork — category 'Other' not in current EPD database; carbon not estimated</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -3066,19 +3150,19 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>16iii</t>
+          <t>16c</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Lintels, beams, plinth beams, girders bressumers and cantilever.</t>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : iii) Lintels, beams, plinth beams, girders bressumers and cantilever.</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - III, R.C.C. Work</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
@@ -3093,7 +3177,7 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>Formwork</t>
+          <t>Timber, Steel</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
@@ -3101,8 +3185,10 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="K24" s="17" t="n">
-        <v>0.85</v>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
@@ -3162,7 +3248,11 @@
       <c r="AU24" s="8" t="n"/>
       <c r="AV24" s="8" t="n"/>
       <c r="AW24" s="8" t="n"/>
-      <c r="AX24" s="8" t="n"/>
+      <c r="AX24" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Formwork — category 'Other' not in current EPD database; carbon not estimated</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -3172,19 +3262,19 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>16iv</t>
+          <t>16d</t>
         </is>
       </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Columns, pillars, posts and struts.</t>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : iv) Columns, pillars, posts and struts.</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - III, R.C.C. Work</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
@@ -3199,7 +3289,7 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>Formwork</t>
+          <t>Timber, Steel</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
@@ -3207,8 +3297,10 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="K25" s="17" t="n">
-        <v>0.85</v>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L25" s="8" t="n"/>
       <c r="M25" s="8" t="n"/>
@@ -3268,7 +3360,11 @@
       <c r="AU25" s="8" t="n"/>
       <c r="AV25" s="8" t="n"/>
       <c r="AW25" s="8" t="n"/>
-      <c r="AX25" s="8" t="n"/>
+      <c r="AX25" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Formwork — category 'Other' not in current EPD database; carbon not estimated</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -3278,19 +3374,19 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>16v</t>
+          <t>16e</t>
         </is>
       </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Vertical and horizontal fins individually or forming box louvers hand and facias.</t>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : v) Vertical and horizontal fins individually or forming box louvers hand and facias.</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - III, R.C.C. Work</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
@@ -3305,7 +3401,7 @@
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>Formwork</t>
+          <t>Timber, Steel</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -3313,8 +3409,10 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="K26" s="17" t="n">
-        <v>0.85</v>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L26" s="8" t="n"/>
       <c r="M26" s="8" t="n"/>
@@ -3374,7 +3472,11 @@
       <c r="AU26" s="8" t="n"/>
       <c r="AV26" s="8" t="n"/>
       <c r="AW26" s="8" t="n"/>
-      <c r="AX26" s="8" t="n"/>
+      <c r="AX26" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Formwork — category 'Other' not in current EPD database; carbon not estimated</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -3384,19 +3486,19 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>17i</t>
+          <t>17a</t>
         </is>
       </c>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Reinforcement for RCC work including bending binding and placing in position complete. Mild steel and medium tensile steel bars.</t>
+          <t>Reinforcement for RCC work including bending binding and placing in position complete. i) Mild steel and medium tensile steel bars.</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - III, R.C.C. Work</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -3406,7 +3508,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>Mild steel bar</t>
+          <t>Steel reinforcement</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
@@ -3419,8 +3521,10 @@
           <t>Steel</t>
         </is>
       </c>
-      <c r="K27" s="17" t="n">
-        <v>0.95</v>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="L27" s="8" t="n"/>
       <c r="M27" s="8" t="n"/>
@@ -3442,7 +3546,9 @@
       <c r="U27" s="8" t="n"/>
       <c r="V27" s="8" t="n"/>
       <c r="W27" s="8" t="n"/>
-      <c r="X27" s="8" t="n"/>
+      <c r="X27" s="17" t="n">
+        <v>7850</v>
+      </c>
       <c r="Y27" s="17" t="n">
         <v>155</v>
       </c>
@@ -3462,7 +3568,7 @@
       <c r="AC27" s="8" t="n"/>
       <c r="AD27" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Mild steel bar</t>
+          <t>Steel &gt; Steel reinforcement</t>
         </is>
       </c>
       <c r="AE27" s="8" t="n"/>
@@ -3486,7 +3592,7 @@
       <c r="AW27" s="8" t="n"/>
       <c r="AX27" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[OK] material: Steel reinforcement — mass 100.0 kg [direct weight] × 1.55 kgCO2e/kg = 155.0 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -3498,19 +3604,19 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>17ii</t>
+          <t>17b</t>
         </is>
       </c>
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Reinforcement for RCC work including bending binding and placing in position complete. Cold twisted bars</t>
+          <t>Reinforcement for RCC work including bending binding and placing in position complete. ii) Cold twisted bars</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - III, R.C.C. Work</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
@@ -3520,7 +3626,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>Cold twisted bar</t>
+          <t>Cold twisted steel bars</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
@@ -3533,8 +3639,10 @@
           <t>Steel</t>
         </is>
       </c>
-      <c r="K28" s="17" t="n">
-        <v>0.95</v>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="L28" s="8" t="n"/>
       <c r="M28" s="8" t="n"/>
@@ -3556,7 +3664,9 @@
       <c r="U28" s="8" t="n"/>
       <c r="V28" s="8" t="n"/>
       <c r="W28" s="8" t="n"/>
-      <c r="X28" s="8" t="n"/>
+      <c r="X28" s="17" t="n">
+        <v>7850</v>
+      </c>
       <c r="Y28" s="17" t="n">
         <v>2131.25</v>
       </c>
@@ -3576,7 +3686,7 @@
       <c r="AC28" s="8" t="n"/>
       <c r="AD28" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Cold twisted bar</t>
+          <t>Steel &gt; Cold twisted steel bars</t>
         </is>
       </c>
       <c r="AE28" s="8" t="n"/>
@@ -3600,7 +3710,7 @@
       <c r="AW28" s="8" t="n"/>
       <c r="AX28" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[OK] material: Cold twisted steel bars — mass 1375.0 kg [direct weight] × 1.55 kgCO2e/kg = 2131.25 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3734,7 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - III, R.C.C. Work</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
@@ -3639,7 +3749,7 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Stone aggregate</t>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
@@ -3647,8 +3757,10 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K29" s="17" t="n">
-        <v>0.95</v>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
@@ -3678,9 +3790,11 @@
       <c r="U29" s="8" t="n"/>
       <c r="V29" s="8" t="n"/>
       <c r="W29" s="8" t="n"/>
-      <c r="X29" s="8" t="n"/>
+      <c r="X29" s="17" t="n">
+        <v>2400</v>
+      </c>
       <c r="Y29" s="17" t="n">
-        <v>0.12</v>
+        <v>286.08</v>
       </c>
       <c r="Z29" s="17" t="n">
         <v>0.149</v>
@@ -3722,7 +3836,7 @@
       <c r="AW29" s="8" t="n"/>
       <c r="AX29" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[OK] material: Reinforced cement concrete — mass 1920.0 kg [direct volume] × 0.149 kgCO2e/kg = 286.08 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -3741,12 +3855,12 @@
       <c r="D30" s="8" t="n"/>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Brick work with bricks of class designation___ in foundation and plinth in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
+          <t>Brick work with bricks of class designation _____ in foundation and plinth in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - IV, Brick Work</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
@@ -3756,7 +3870,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>Brick masonry</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
@@ -3769,8 +3883,10 @@
           <t>Masonry</t>
         </is>
       </c>
-      <c r="K30" s="17" t="n">
-        <v>0.95</v>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="L30" s="8" t="n"/>
       <c r="M30" s="8" t="inlineStr">
@@ -3796,9 +3912,11 @@
       <c r="U30" s="8" t="n"/>
       <c r="V30" s="8" t="n"/>
       <c r="W30" s="8" t="n"/>
-      <c r="X30" s="8" t="n"/>
+      <c r="X30" s="17" t="n">
+        <v>1800</v>
+      </c>
       <c r="Y30" s="17" t="n">
-        <v>3.62</v>
+        <v>6517.8</v>
       </c>
       <c r="Z30" s="17" t="n">
         <v>0.213</v>
@@ -3810,13 +3928,13 @@
       </c>
       <c r="AB30" s="8" t="inlineStr">
         <is>
-          <t>6.1.14/6.5.1 6.5.2</t>
+          <t>6.1.14/6.5.1/6.5.2</t>
         </is>
       </c>
       <c r="AC30" s="8" t="n"/>
       <c r="AD30" s="8" t="inlineStr">
         <is>
-          <t>Masonry &gt; Brick masonry &gt; 1:6</t>
+          <t>Masonry &gt; Brick &gt; 1:6</t>
         </is>
       </c>
       <c r="AE30" s="8" t="n"/>
@@ -3840,7 +3958,7 @@
       <c r="AW30" s="8" t="n"/>
       <c r="AX30" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
+          <t>[OK] material: Brick — mass 30600.0 kg [direct volume] × 0.213 kgCO2e/kg = 6517.8 kgCO2e — ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -3859,12 +3977,12 @@
       <c r="D31" s="8" t="n"/>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Brick work with bricks of class designation___ in super structure above plinth upto floor two level in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
+          <t>Brick work with bricks of class designation _____ in super structure above plinth upto floor two level in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - IV, Brick Work</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
@@ -3874,7 +3992,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>Brick masonry</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
@@ -3887,8 +4005,10 @@
           <t>Masonry</t>
         </is>
       </c>
-      <c r="K31" s="17" t="n">
-        <v>0.95</v>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="L31" s="8" t="n"/>
       <c r="M31" s="8" t="inlineStr">
@@ -3914,9 +4034,11 @@
       <c r="U31" s="8" t="n"/>
       <c r="V31" s="8" t="n"/>
       <c r="W31" s="8" t="n"/>
-      <c r="X31" s="8" t="n"/>
+      <c r="X31" s="17" t="n">
+        <v>1800</v>
+      </c>
       <c r="Y31" s="17" t="n">
-        <v>8.58</v>
+        <v>15451.02</v>
       </c>
       <c r="Z31" s="17" t="n">
         <v>0.213</v>
@@ -3928,13 +4050,13 @@
       </c>
       <c r="AB31" s="8" t="inlineStr">
         <is>
-          <t>6.1.14/6.3 6.5.1/6.5.2</t>
+          <t>6.1.14/6.3/6.5.1/6.5.2</t>
         </is>
       </c>
       <c r="AC31" s="8" t="n"/>
       <c r="AD31" s="8" t="inlineStr">
         <is>
-          <t>Masonry &gt; Brick masonry &gt; 1:6</t>
+          <t>Masonry &gt; Brick &gt; 1:6</t>
         </is>
       </c>
       <c r="AE31" s="8" t="n"/>
@@ -3958,7 +4080,7 @@
       <c r="AW31" s="8" t="n"/>
       <c r="AX31" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
+          <t>[OK] material: Brick — mass 72540.0 kg [direct volume] × 0.213 kgCO2e/kg = 15451.02 kgCO2e — ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -3977,12 +4099,12 @@
       <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Brick work 7 cm thick with bricks of class designation ______ in super structure upto floor two level in cement mortar 1:3 (1 cement : 3 coarse sand).</t>
+          <t>Brick work 7 cm thick with bricks of class designation _____ in super structure upto floor two level in cement mortar 1:3 (1 cement : 3 coarse sand).</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - IV, Brick Work</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
@@ -3992,7 +4114,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>Brick masonry</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
@@ -4005,8 +4127,10 @@
           <t>Masonry</t>
         </is>
       </c>
-      <c r="K32" s="17" t="n">
-        <v>0.95</v>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L32" s="8" t="n"/>
       <c r="M32" s="8" t="inlineStr">
@@ -4042,9 +4166,11 @@
           <t>Area x thickness (70.0 mm, from description)</t>
         </is>
       </c>
-      <c r="X32" s="8" t="n"/>
+      <c r="X32" s="17" t="n">
+        <v>1800</v>
+      </c>
       <c r="Y32" s="17" t="n">
-        <v>0.19</v>
+        <v>24.15</v>
       </c>
       <c r="Z32" s="17" t="n">
         <v>0.213</v>
@@ -4062,7 +4188,7 @@
       <c r="AC32" s="8" t="n"/>
       <c r="AD32" s="8" t="inlineStr">
         <is>
-          <t>Masonry &gt; Brick masonry &gt; 1:3</t>
+          <t>Masonry &gt; Brick &gt; 1:3</t>
         </is>
       </c>
       <c r="AE32" s="8" t="n"/>
@@ -4088,7 +4214,7 @@
       <c r="AW32" s="8" t="n"/>
       <c r="AX32" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
+          <t>[OK] material: Brick — mass 113.4 kg [area × thickness (derived)] × 0.213 kgCO2e/kg = 24.15 kgCO2e — ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -4107,12 +4233,12 @@
       <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Half brick masonry with bricks of class designation _______ in foundation &amp; plinth in cement mortar 1:4 (1 cement : 4 coarse sand)</t>
+          <t>Half brick masonry with bricks of class designation _____ in foundation &amp; plinth in cement mortar 1:4 (1 cement : 4 coarse sand)</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - IV, Brick Work</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -4122,7 +4248,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>Brick masonry</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
@@ -4135,8 +4261,10 @@
           <t>Masonry</t>
         </is>
       </c>
-      <c r="K33" s="17" t="n">
-        <v>0.95</v>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L33" s="8" t="n"/>
       <c r="M33" s="8" t="inlineStr">
@@ -4162,10 +4290,10 @@
       <c r="U33" s="8" t="n"/>
       <c r="V33" s="8" t="n"/>
       <c r="W33" s="8" t="n"/>
-      <c r="X33" s="8" t="n"/>
-      <c r="Y33" s="17" t="n">
-        <v>1.02</v>
-      </c>
+      <c r="X33" s="17" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Y33" s="8" t="n"/>
       <c r="Z33" s="17" t="n">
         <v>0.213</v>
       </c>
@@ -4176,13 +4304,13 @@
       </c>
       <c r="AB33" s="8" t="inlineStr">
         <is>
-          <t>6.18.4/6.21 6.5.1/6.5.2</t>
+          <t>6.18.4/6.21/6.5.1/6.5.2</t>
         </is>
       </c>
       <c r="AC33" s="8" t="n"/>
       <c r="AD33" s="8" t="inlineStr">
         <is>
-          <t>Masonry &gt; Brick masonry &gt; 1:4</t>
+          <t>Masonry &gt; Brick &gt; 1:4</t>
         </is>
       </c>
       <c r="AE33" s="8" t="n"/>
@@ -4206,7 +4334,7 @@
       <c r="AW33" s="8" t="n"/>
       <c r="AX33" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
+          <t>[EXCLUDED] material: Brick — category 'Masonry' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -4225,12 +4353,12 @@
       <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Half brick masonry with bricks of class designation ________ in super structure upto floor two level in cement mortar 1:4 (1 cement : 4 coarse sand).</t>
+          <t>Half brick masonry with bricks of class designation _____ in super structure upto floor two level in cement mortar 1:4 (1 cement : 4 coarse sand).</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - IV, Brick Work</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
@@ -4240,7 +4368,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>Brick masonry</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
@@ -4253,8 +4381,10 @@
           <t>Masonry</t>
         </is>
       </c>
-      <c r="K34" s="17" t="n">
-        <v>0.95</v>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L34" s="8" t="n"/>
       <c r="M34" s="8" t="inlineStr">
@@ -4280,10 +4410,10 @@
       <c r="U34" s="8" t="n"/>
       <c r="V34" s="8" t="n"/>
       <c r="W34" s="8" t="n"/>
-      <c r="X34" s="8" t="n"/>
-      <c r="Y34" s="17" t="n">
-        <v>3.83</v>
-      </c>
+      <c r="X34" s="17" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Y34" s="8" t="n"/>
       <c r="Z34" s="17" t="n">
         <v>0.213</v>
       </c>
@@ -4294,13 +4424,13 @@
       </c>
       <c r="AB34" s="8" t="inlineStr">
         <is>
-          <t>6.18.4/6.19.1 6.20/6.21.1/6.21.2</t>
+          <t>6.18.4/6.19.1/6.20/6.21.1/6.21.2</t>
         </is>
       </c>
       <c r="AC34" s="8" t="n"/>
       <c r="AD34" s="8" t="inlineStr">
         <is>
-          <t>Masonry &gt; Brick masonry &gt; 1:4</t>
+          <t>Masonry &gt; Brick &gt; 1:4</t>
         </is>
       </c>
       <c r="AE34" s="8" t="n"/>
@@ -4324,7 +4454,7 @@
       <c r="AW34" s="8" t="n"/>
       <c r="AX34" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
+          <t>[EXCLUDED] material: Brick — category 'Masonry' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4473,12 @@
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Providing _______ wood work in frames of doors, windows, clerestory windows and other frames, wrought framed and fixed in position.</t>
+          <t>Providing wood work in frames of doors, windows, clerestory windows and other frames, wrought framed and fixed in position.</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - V, Wood Work</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
@@ -4371,8 +4501,10 @@
           <t>Timber</t>
         </is>
       </c>
-      <c r="K35" s="17" t="n">
-        <v>0.9</v>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="L35" s="8" t="n"/>
       <c r="M35" s="8" t="n"/>
@@ -4394,9 +4526,11 @@
       <c r="U35" s="8" t="n"/>
       <c r="V35" s="8" t="n"/>
       <c r="W35" s="8" t="n"/>
-      <c r="X35" s="8" t="n"/>
+      <c r="X35" s="17" t="n">
+        <v>750</v>
+      </c>
       <c r="Y35" s="17" t="n">
-        <v>0.01</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Z35" s="17" t="n">
         <v>0.306</v>
@@ -4434,7 +4568,7 @@
       <c r="AW35" s="8" t="n"/>
       <c r="AX35" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
+          <t>[OK] material: Wood — mass 26.25 kg [direct volume] × 0.306 kgCO2e/kg = 8.03 kgCO2e — ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -4453,12 +4587,12 @@
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing 35 mm thick battended and framed door shutters of ________ wood including bright finished or/and black enamelled MS butt hinges with necessary screws.</t>
+          <t>Providing and fixing 35 mm thick battended and framed door shutters of wood including bright finished or/and black enamelled MS butt hinges with necessary screws.</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - V, Wood Work</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
@@ -4468,12 +4602,12 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>Wood door shutter</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>Wood, Mild steel</t>
+          <t>Wood, MS butt hinges</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
@@ -4481,8 +4615,10 @@
           <t>Timber</t>
         </is>
       </c>
-      <c r="K36" s="17" t="n">
-        <v>0.9</v>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L36" s="8" t="n"/>
       <c r="M36" s="8" t="n"/>
@@ -4514,9 +4650,11 @@
           <t>Area x thickness (35.0 mm, from description)</t>
         </is>
       </c>
-      <c r="X36" s="8" t="n"/>
+      <c r="X36" s="17" t="n">
+        <v>750</v>
+      </c>
       <c r="Y36" s="17" t="n">
-        <v>5.51</v>
+        <v>144.59</v>
       </c>
       <c r="Z36" s="17" t="n">
         <v>0.306</v>
@@ -4534,7 +4672,7 @@
       <c r="AC36" s="8" t="n"/>
       <c r="AD36" s="8" t="inlineStr">
         <is>
-          <t>Timber &gt; Wood door shutter</t>
+          <t>Timber &gt; Wood</t>
         </is>
       </c>
       <c r="AE36" s="8" t="n"/>
@@ -4560,7 +4698,7 @@
       <c r="AW36" s="8" t="n"/>
       <c r="AX36" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
+          <t>[OK] material: Wood — mass 472.5 kg [area × thickness (derived)] × 0.306 kgCO2e/kg = 144.59 kgCO2e — ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4722,7 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - V, Wood Work</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
@@ -4599,7 +4737,7 @@
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>Block board, Hardwood, Teak ply, Commercial ply, Mild steel</t>
+          <t>Block board, Hard wood, Teak ply veneer, Commercial ply veneer, MS piano hinges</t>
         </is>
       </c>
       <c r="J37" s="8" t="inlineStr">
@@ -4607,8 +4745,10 @@
           <t>Timber</t>
         </is>
       </c>
-      <c r="K37" s="17" t="n">
-        <v>0.9</v>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L37" s="8" t="n"/>
       <c r="M37" s="8" t="n"/>
@@ -4640,9 +4780,11 @@
           <t>Area x thickness (25.0 mm, from description)</t>
         </is>
       </c>
-      <c r="X37" s="8" t="n"/>
+      <c r="X37" s="17" t="n">
+        <v>750</v>
+      </c>
       <c r="Y37" s="17" t="n">
-        <v>1.44</v>
+        <v>26.97</v>
       </c>
       <c r="Z37" s="17" t="n">
         <v>0.306</v>
@@ -4686,7 +4828,7 @@
       <c r="AW37" s="8" t="n"/>
       <c r="AX37" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
+          <t>[OK] material: Flush door shutter — mass 88.12 kg [area × thickness (derived)] × 0.306 kgCO2e/kg = 26.97 kgCO2e — ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4852,7 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - V, Wood Work</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
@@ -4733,8 +4875,10 @@
           <t>Timber</t>
         </is>
       </c>
-      <c r="K38" s="17" t="n">
-        <v>0.9</v>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L38" s="8" t="n"/>
       <c r="M38" s="8" t="inlineStr">
@@ -4760,10 +4904,10 @@
       <c r="U38" s="8" t="n"/>
       <c r="V38" s="8" t="n"/>
       <c r="W38" s="8" t="n"/>
-      <c r="X38" s="8" t="n"/>
-      <c r="Y38" s="17" t="n">
-        <v>6.12</v>
-      </c>
+      <c r="X38" s="17" t="n">
+        <v>750</v>
+      </c>
+      <c r="Y38" s="8" t="n"/>
       <c r="Z38" s="17" t="n">
         <v>0.306</v>
       </c>
@@ -4806,7 +4950,7 @@
       <c r="AW38" s="8" t="n"/>
       <c r="AX38" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
+          <t>[EXCLUDED] material: Teak wood plug — category 'Timber' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4969,12 @@
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing M.S.oxidised fan light .vantilator catch with necessary screws etc. complete.</t>
+          <t>Providing and fixing M.S. oxidised fan light ventilator catch with necessary screws etc. complete.</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
@@ -4840,12 +4984,12 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>Mild steel ventilator catch</t>
+          <t>M.S. oxidised ventilator catch</t>
         </is>
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>M.S. oxidised steel</t>
         </is>
       </c>
       <c r="J39" s="8" t="inlineStr">
@@ -4853,8 +4997,10 @@
           <t>Steel</t>
         </is>
       </c>
-      <c r="K39" s="17" t="n">
-        <v>0.9</v>
+      <c r="K39" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L39" s="8" t="n"/>
       <c r="M39" s="8" t="n"/>
@@ -4876,10 +5022,10 @@
       <c r="U39" s="8" t="n"/>
       <c r="V39" s="8" t="n"/>
       <c r="W39" s="8" t="n"/>
-      <c r="X39" s="8" t="n"/>
-      <c r="Y39" s="17" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="X39" s="17" t="n">
+        <v>7850</v>
+      </c>
+      <c r="Y39" s="8" t="n"/>
       <c r="Z39" s="17" t="n">
         <v>1.55</v>
       </c>
@@ -4896,7 +5042,7 @@
       <c r="AC39" s="8" t="n"/>
       <c r="AD39" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Mild steel ventilator catch</t>
+          <t>Steel &gt; M.S. oxidised ventilator catch</t>
         </is>
       </c>
       <c r="AE39" s="8" t="n"/>
@@ -4920,7 +5066,7 @@
       <c r="AW39" s="8" t="n"/>
       <c r="AX39" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[EXCLUDED] material: M.S. oxidised ventilator catch — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -4944,7 +5090,7 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
@@ -4954,12 +5100,12 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>Mild steel hasp and staple</t>
+          <t>Oxidised M.S. hasp and staple</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>M.S. oxidised steel</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
@@ -4967,8 +5113,10 @@
           <t>Steel</t>
         </is>
       </c>
-      <c r="K40" s="17" t="n">
-        <v>0.9</v>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L40" s="8" t="n"/>
       <c r="M40" s="8" t="n"/>
@@ -4990,10 +5138,10 @@
       <c r="U40" s="8" t="n"/>
       <c r="V40" s="8" t="n"/>
       <c r="W40" s="8" t="n"/>
-      <c r="X40" s="8" t="n"/>
-      <c r="Y40" s="17" t="n">
-        <v>3.1</v>
-      </c>
+      <c r="X40" s="17" t="n">
+        <v>7850</v>
+      </c>
+      <c r="Y40" s="8" t="n"/>
       <c r="Z40" s="17" t="n">
         <v>1.55</v>
       </c>
@@ -5010,7 +5158,7 @@
       <c r="AC40" s="8" t="n"/>
       <c r="AD40" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Mild steel hasp and staple</t>
+          <t>Steel &gt; Oxidised M.S. hasp and staple</t>
         </is>
       </c>
       <c r="AE40" s="8" t="n"/>
@@ -5036,7 +5184,7 @@
       <c r="AW40" s="8" t="n"/>
       <c r="AX40" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[EXCLUDED] material: Oxidised M.S. hasp and staple — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5208,7 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
@@ -5083,8 +5231,10 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="K41" s="17" t="n">
-        <v>0.9</v>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L41" s="8" t="n"/>
       <c r="M41" s="8" t="n"/>
@@ -5144,7 +5294,11 @@
       <c r="AU41" s="8" t="n"/>
       <c r="AV41" s="8" t="n"/>
       <c r="AW41" s="8" t="n"/>
-      <c r="AX41" s="8" t="n"/>
+      <c r="AX41" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Aluminium sliding door bolt — category 'Other' not in current EPD database; carbon not estimated</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -5154,19 +5308,19 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>31i</t>
+          <t>31a</t>
         </is>
       </c>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 200 x 10 mm</t>
+          <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. i) 200 x 10 mm</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
@@ -5189,8 +5343,10 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="K42" s="17" t="n">
-        <v>0.9</v>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L42" s="8" t="n"/>
       <c r="M42" s="8" t="n"/>
@@ -5254,7 +5410,11 @@
       <c r="AU42" s="8" t="n"/>
       <c r="AV42" s="8" t="n"/>
       <c r="AW42" s="8" t="n"/>
-      <c r="AX42" s="8" t="n"/>
+      <c r="AX42" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Aluminium tower bolt — category 'Other' not in current EPD database; carbon not estimated</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -5264,19 +5424,19 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>31ii</t>
+          <t>31b</t>
         </is>
       </c>
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 100 x 10 mm</t>
+          <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. ii) 100 x 10 mm</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
@@ -5299,8 +5459,10 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="K43" s="17" t="n">
-        <v>0.9</v>
+      <c r="K43" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L43" s="8" t="n"/>
       <c r="M43" s="8" t="n"/>
@@ -5364,7 +5526,11 @@
       <c r="AU43" s="8" t="n"/>
       <c r="AV43" s="8" t="n"/>
       <c r="AW43" s="8" t="n"/>
-      <c r="AX43" s="8" t="n"/>
+      <c r="AX43" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Aluminium tower bolt — category 'Other' not in current EPD database; carbon not estimated</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -5374,19 +5540,19 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>32i</t>
+          <t>32a</t>
         </is>
       </c>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 100 mm</t>
+          <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. i) 100 mm</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
@@ -5409,8 +5575,10 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="K44" s="17" t="n">
-        <v>0.9</v>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L44" s="8" t="n"/>
       <c r="M44" s="8" t="n"/>
@@ -5472,7 +5640,11 @@
       <c r="AU44" s="8" t="n"/>
       <c r="AV44" s="8" t="n"/>
       <c r="AW44" s="8" t="n"/>
-      <c r="AX44" s="8" t="n"/>
+      <c r="AX44" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Aluminium handle — category 'Other' not in current EPD database; carbon not estimated</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -5482,19 +5654,19 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>32ii</t>
+          <t>32b</t>
         </is>
       </c>
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 75 mm</t>
+          <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. ii) 75 mm</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
@@ -5517,8 +5689,10 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="K45" s="17" t="n">
-        <v>0.9</v>
+      <c r="K45" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L45" s="8" t="n"/>
       <c r="M45" s="8" t="n"/>
@@ -5580,7 +5754,11 @@
       <c r="AU45" s="8" t="n"/>
       <c r="AV45" s="8" t="n"/>
       <c r="AW45" s="8" t="n"/>
-      <c r="AX45" s="8" t="n"/>
+      <c r="AX45" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Aluminium handle — category 'Other' not in current EPD database; carbon not estimated</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -5602,7 +5780,7 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
@@ -5612,7 +5790,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>Aluminium door stopper</t>
+          <t>Aluminium hanging floor door stopper</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
@@ -5625,8 +5803,10 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="K46" s="17" t="n">
-        <v>0.9</v>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L46" s="8" t="n"/>
       <c r="M46" s="8" t="n"/>
@@ -5664,7 +5844,7 @@
       <c r="AC46" s="8" t="n"/>
       <c r="AD46" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium door stopper</t>
+          <t>Other &gt; Aluminium hanging floor door stopper</t>
         </is>
       </c>
       <c r="AE46" s="8" t="n"/>
@@ -5686,7 +5866,11 @@
       <c r="AU46" s="8" t="n"/>
       <c r="AV46" s="8" t="n"/>
       <c r="AW46" s="8" t="n"/>
-      <c r="AX46" s="8" t="n"/>
+      <c r="AX46" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Aluminium hanging floor door stopper — category 'Other' not in current EPD database; carbon not estimated</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -5696,19 +5880,19 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>34i</t>
+          <t>34a</t>
         </is>
       </c>
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. Windows - side hung</t>
+          <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. i) Windows - side hung</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
@@ -5723,7 +5907,7 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>Steel, Glass, Cement concrete, Putty</t>
+          <t>Steel, Cement, Coarse sand, Graded stone aggregate, Glass, Putty, Primer</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
@@ -5731,8 +5915,10 @@
           <t>Steel</t>
         </is>
       </c>
-      <c r="K47" s="17" t="n">
-        <v>0.9</v>
+      <c r="K47" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L47" s="8" t="n"/>
       <c r="M47" s="8" t="inlineStr">
@@ -5768,9 +5954,11 @@
           <t>Area x thickness (3.0 mm, from description)</t>
         </is>
       </c>
-      <c r="X47" s="8" t="n"/>
+      <c r="X47" s="17" t="n">
+        <v>7850</v>
+      </c>
       <c r="Y47" s="17" t="n">
-        <v>17.52</v>
+        <v>412.48</v>
       </c>
       <c r="Z47" s="17" t="n">
         <v>1.55</v>
@@ -5814,7 +6002,7 @@
       <c r="AW47" s="8" t="n"/>
       <c r="AX47" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[OK] material: Steel glazed window — mass 266.12 kg [area × thickness (derived)] × 1.55 kgCO2e/kg = 412.48 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -5826,19 +6014,19 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>34ii</t>
+          <t>34b</t>
         </is>
       </c>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="n"/>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. Ventilators - centre hung</t>
+          <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. ii) Ventilators - centre hung</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
@@ -5853,7 +6041,7 @@
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>Steel, Glass, Cement concrete, Putty</t>
+          <t>Steel, Cement, Coarse sand, Graded stone aggregate, Glass, Putty, Primer</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
@@ -5861,8 +6049,10 @@
           <t>Steel</t>
         </is>
       </c>
-      <c r="K48" s="17" t="n">
-        <v>0.9</v>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L48" s="8" t="n"/>
       <c r="M48" s="8" t="inlineStr">
@@ -5898,9 +6088,11 @@
           <t>Area x thickness (3.0 mm, from description)</t>
         </is>
       </c>
-      <c r="X48" s="8" t="n"/>
+      <c r="X48" s="17" t="n">
+        <v>7850</v>
+      </c>
       <c r="Y48" s="17" t="n">
-        <v>1.55</v>
+        <v>36.5</v>
       </c>
       <c r="Z48" s="17" t="n">
         <v>1.55</v>
@@ -5944,7 +6136,7 @@
       <c r="AW48" s="8" t="n"/>
       <c r="AX48" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[OK] material: Steel glazed ventilator — mass 23.55 kg [area × thickness (derived)] × 1.55 kgCO2e/kg = 36.5 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -5968,7 +6160,7 @@
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
@@ -5978,7 +6170,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>Mild steel casement fastener</t>
+          <t>Oxidised mild steel casement window fastener</t>
         </is>
       </c>
       <c r="I49" s="8" t="inlineStr">
@@ -5991,8 +6183,10 @@
           <t>Steel</t>
         </is>
       </c>
-      <c r="K49" s="17" t="n">
-        <v>0.9</v>
+      <c r="K49" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L49" s="8" t="n"/>
       <c r="M49" s="8" t="n"/>
@@ -6014,10 +6208,10 @@
       <c r="U49" s="8" t="n"/>
       <c r="V49" s="8" t="n"/>
       <c r="W49" s="8" t="n"/>
-      <c r="X49" s="8" t="n"/>
-      <c r="Y49" s="17" t="n">
-        <v>32.55</v>
-      </c>
+      <c r="X49" s="17" t="n">
+        <v>7850</v>
+      </c>
+      <c r="Y49" s="8" t="n"/>
       <c r="Z49" s="17" t="n">
         <v>1.55</v>
       </c>
@@ -6034,7 +6228,7 @@
       <c r="AC49" s="8" t="n"/>
       <c r="AD49" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Mild steel casement fastener</t>
+          <t>Steel &gt; Oxidised mild steel casement window fastener</t>
         </is>
       </c>
       <c r="AE49" s="8" t="n"/>
@@ -6058,7 +6252,7 @@
       <c r="AW49" s="8" t="n"/>
       <c r="AX49" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[EXCLUDED] material: Oxidised mild steel casement window fastener — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6276,7 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
@@ -6105,8 +6299,10 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="K50" s="17" t="n">
-        <v>0.9</v>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L50" s="8" t="n"/>
       <c r="M50" s="8" t="n"/>
@@ -6166,7 +6362,11 @@
       <c r="AU50" s="8" t="n"/>
       <c r="AV50" s="8" t="n"/>
       <c r="AW50" s="8" t="n"/>
-      <c r="AX50" s="8" t="n"/>
+      <c r="AX50" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Aluminium casement stay — category 'Other' not in current EPD database; carbon not estimated</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -6183,27 +6383,27 @@
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>Providing and welding 20x4 mm M S Guard Flats 10cm c/c in steel windows of standard rolled steel section including a coat of steel primer as per drawing and specification complete in all respect.</t>
+          <t>Providing and welding 20x4 mm MS Guard Flats 10cm c/c in steel windows of standard rolled steel section including a coat of steel primer as per drawing and specification complete in all respect.</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>Finishes</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>Mild steel flat</t>
+          <t>MS Guard Flats</t>
         </is>
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>Mild steel, Steel primer</t>
+          <t>Mild steel, Primer</t>
         </is>
       </c>
       <c r="J51" s="8" t="inlineStr">
@@ -6211,8 +6411,10 @@
           <t>Steel</t>
         </is>
       </c>
-      <c r="K51" s="17" t="n">
-        <v>0.95</v>
+      <c r="K51" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="L51" s="8" t="n"/>
       <c r="M51" s="8" t="n"/>
@@ -6234,7 +6436,9 @@
       <c r="U51" s="8" t="n"/>
       <c r="V51" s="8" t="n"/>
       <c r="W51" s="8" t="n"/>
-      <c r="X51" s="8" t="n"/>
+      <c r="X51" s="17" t="n">
+        <v>7850</v>
+      </c>
       <c r="Y51" s="17" t="n">
         <v>102.3</v>
       </c>
@@ -6254,7 +6458,7 @@
       <c r="AC51" s="8" t="n"/>
       <c r="AD51" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Mild steel flat</t>
+          <t>Steel &gt; MS Guard Flats</t>
         </is>
       </c>
       <c r="AE51" s="8" t="n"/>
@@ -6282,7 +6486,7 @@
       <c r="AW51" s="8" t="n"/>
       <c r="AX51" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[OK] material: MS Guard Flats — mass 66.0 kg [direct weight] × 1.55 kgCO2e/kg = 102.3 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -6306,22 +6510,22 @@
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>Finishes</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>Mild steel T-Iron frame</t>
+          <t>T-Iron frame</t>
         </is>
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>Mild steel, Cement concrete, Wood, Steel primer</t>
+          <t>Mild steel, Cement, Coarse sand, Graded stone aggregate, Steel primer</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr">
@@ -6329,8 +6533,10 @@
           <t>Steel</t>
         </is>
       </c>
-      <c r="K52" s="17" t="n">
-        <v>0.95</v>
+      <c r="K52" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
       </c>
       <c r="L52" s="8" t="n"/>
       <c r="M52" s="8" t="inlineStr">
@@ -6356,7 +6562,9 @@
       <c r="U52" s="8" t="n"/>
       <c r="V52" s="8" t="n"/>
       <c r="W52" s="8" t="n"/>
-      <c r="X52" s="8" t="n"/>
+      <c r="X52" s="17" t="n">
+        <v>7850</v>
+      </c>
       <c r="Y52" s="17" t="n">
         <v>289.85</v>
       </c>
@@ -6376,7 +6584,7 @@
       <c r="AC52" s="8" t="n"/>
       <c r="AD52" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Mild steel T-Iron frame &gt; 1:3:6</t>
+          <t>Steel &gt; T-Iron frame &gt; 1:3:6</t>
         </is>
       </c>
       <c r="AE52" s="8" t="n"/>
@@ -6400,7 +6608,7 @@
       <c r="AW52" s="8" t="n"/>
       <c r="AX52" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[OK] material: T-Iron frame — mass 187.0 kg [direct weight] × 1.55 kgCO2e/kg = 289.85 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -6424,22 +6632,22 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>Mild steel fan clamp</t>
+          <t>MS fan clamp</t>
         </is>
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>MS bar, Paint</t>
         </is>
       </c>
       <c r="J53" s="8" t="inlineStr">
@@ -6447,8 +6655,10 @@
           <t>Steel</t>
         </is>
       </c>
-      <c r="K53" s="17" t="n">
-        <v>0.9</v>
+      <c r="K53" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L53" s="8" t="n"/>
       <c r="M53" s="8" t="n"/>
@@ -6470,10 +6680,10 @@
       <c r="U53" s="8" t="n"/>
       <c r="V53" s="8" t="n"/>
       <c r="W53" s="8" t="n"/>
-      <c r="X53" s="8" t="n"/>
-      <c r="Y53" s="17" t="n">
-        <v>7.75</v>
-      </c>
+      <c r="X53" s="17" t="n">
+        <v>7850</v>
+      </c>
+      <c r="Y53" s="8" t="n"/>
       <c r="Z53" s="17" t="n">
         <v>1.55</v>
       </c>
@@ -6490,7 +6700,7 @@
       <c r="AC53" s="8" t="n"/>
       <c r="AD53" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Mild steel fan clamp</t>
+          <t>Steel &gt; MS fan clamp</t>
         </is>
       </c>
       <c r="AE53" s="8" t="n"/>
@@ -6516,7 +6726,7 @@
       <c r="AW53" s="8" t="n"/>
       <c r="AX53" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[EXCLUDED] material: MS fan clamp — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6750,7 @@
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
@@ -6555,7 +6765,7 @@
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Stone aggregate</t>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
@@ -6563,8 +6773,10 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K54" s="17" t="n">
-        <v>0.95</v>
+      <c r="K54" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
@@ -6604,9 +6816,11 @@
           <t>Area x thickness (40.0 mm, from description)</t>
         </is>
       </c>
-      <c r="X54" s="8" t="n"/>
+      <c r="X54" s="17" t="n">
+        <v>2400</v>
+      </c>
       <c r="Y54" s="17" t="n">
-        <v>10.13</v>
+        <v>972.67</v>
       </c>
       <c r="Z54" s="17" t="n">
         <v>0.149</v>
@@ -6650,7 +6864,7 @@
       <c r="AW54" s="8" t="n"/>
       <c r="AX54" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[OK] material: Cement concrete flooring — mass 6528.0 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 972.67 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6888,7 @@
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
@@ -6694,11 +6908,13 @@
       </c>
       <c r="J55" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish</t>
-        </is>
-      </c>
-      <c r="K55" s="17" t="n">
-        <v>0.9</v>
+          <t>Plaster</t>
+        </is>
+      </c>
+      <c r="K55" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L55" s="8" t="n"/>
       <c r="M55" s="8" t="inlineStr">
@@ -6734,12 +6950,14 @@
           <t>Area x thickness (18.0 mm, from description)</t>
         </is>
       </c>
-      <c r="X55" s="8" t="n"/>
+      <c r="X55" s="17" t="n">
+        <v>1900</v>
+      </c>
       <c r="Y55" s="17" t="n">
-        <v>10.45</v>
+        <v>61.32</v>
       </c>
       <c r="Z55" s="17" t="n">
-        <v>0.95</v>
+        <v>0.163</v>
       </c>
       <c r="AA55" s="8" t="inlineStr">
         <is>
@@ -6754,7 +6972,7 @@
       <c r="AC55" s="8" t="n"/>
       <c r="AD55" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish &gt; Cement plaster skirting &gt; 1:3</t>
+          <t>Plaster &gt; Cement plaster skirting &gt; 1:3</t>
         </is>
       </c>
       <c r="AE55" s="8" t="n"/>
@@ -6782,7 +7000,7 @@
       <c r="AW55" s="8" t="n"/>
       <c r="AX55" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+          <t>[OK] material: Cement plaster skirting — mass 376.2 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 61.32 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -6806,7 +7024,7 @@
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
@@ -6821,18 +7039,24 @@
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>Marble chips, Cement, Coarse sand, Stone aggregate, Marble powder, Pigment</t>
+          <t>Marble chips, Cement, Coarse sand, Graded stone aggregate, Marble powder, Pigment</t>
         </is>
       </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish</t>
-        </is>
-      </c>
-      <c r="K56" s="17" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L56" s="8" t="n"/>
+          <t>Concrete</t>
+        </is>
+      </c>
+      <c r="K56" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L56" s="8" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
       <c r="M56" s="8" t="inlineStr">
         <is>
           <t>1:2:4</t>
@@ -6866,12 +7090,14 @@
           <t>Area x thickness (40.0 mm, from description)</t>
         </is>
       </c>
-      <c r="X56" s="8" t="n"/>
+      <c r="X56" s="17" t="n">
+        <v>2400</v>
+      </c>
       <c r="Y56" s="17" t="n">
-        <v>8.550000000000001</v>
+        <v>128.74</v>
       </c>
       <c r="Z56" s="17" t="n">
-        <v>0.95</v>
+        <v>0.149</v>
       </c>
       <c r="AA56" s="8" t="inlineStr">
         <is>
@@ -6886,7 +7112,7 @@
       <c r="AC56" s="8" t="n"/>
       <c r="AD56" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish &gt; Marble chips flooring &gt; 1:2:4</t>
+          <t>Concrete &gt; Marble chips flooring &gt; M15</t>
         </is>
       </c>
       <c r="AE56" s="8" t="n"/>
@@ -6912,7 +7138,7 @@
       <c r="AW56" s="8" t="n"/>
       <c r="AX56" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+          <t>[OK] material: Marble chips flooring — mass 864.0 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 128.74 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -6936,7 +7162,7 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
@@ -6946,7 +7172,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>Glass strip</t>
+          <t>Glass strips</t>
         </is>
       </c>
       <c r="I57" s="8" t="inlineStr">
@@ -6959,8 +7185,10 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="K57" s="17" t="n">
-        <v>0.9</v>
+      <c r="K57" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L57" s="8" t="n"/>
       <c r="M57" s="8" t="n"/>
@@ -6998,7 +7226,7 @@
       <c r="AC57" s="8" t="n"/>
       <c r="AD57" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Glass strip</t>
+          <t>Other &gt; Glass strips</t>
         </is>
       </c>
       <c r="AE57" s="8" t="n"/>
@@ -7024,7 +7252,11 @@
       <c r="AU57" s="8" t="n"/>
       <c r="AV57" s="8" t="n"/>
       <c r="AW57" s="8" t="n"/>
-      <c r="AX57" s="8" t="n"/>
+      <c r="AX57" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Glass strips — category 'Other' not in current EPD database; carbon not estimated</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
@@ -7041,12 +7273,12 @@
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>Painting top of roofs with bitumen of approved quality at 17 Kg. per 10 square metre impregnated with a coat of coarse sand at 3/2 60 dm per 10 m including cleaning the slab surface with brushes and finally with a piece of cloth lightly soaked in kerosene oil complete with residual type petroleum bitumen of penetration 80/100.</t>
+          <t>Painting top of roofs with bitumen of approved quality at 17 Kg. per 10 square metre impregnated with a coat of coarse sand at 60 dm3 per 10 m2 including cleaning the slab surface with brushes and finally with a piece of cloth lightly soaked in kerosene oil complete with residual type petroleum bitumen of penetration 80/100.</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
@@ -7061,7 +7293,7 @@
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>Bitumen, Coarse sand, Kerosene oil</t>
+          <t>Petroleum bitumen, Coarse sand, Kerosene oil</t>
         </is>
       </c>
       <c r="J58" s="8" t="inlineStr">
@@ -7069,8 +7301,10 @@
           <t>Paint/Finish</t>
         </is>
       </c>
-      <c r="K58" s="17" t="n">
-        <v>0.9</v>
+      <c r="K58" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L58" s="8" t="n"/>
       <c r="M58" s="8" t="n"/>
@@ -7092,10 +7326,10 @@
       <c r="U58" s="8" t="n"/>
       <c r="V58" s="8" t="n"/>
       <c r="W58" s="8" t="n"/>
-      <c r="X58" s="8" t="n"/>
-      <c r="Y58" s="17" t="n">
-        <v>61.75</v>
-      </c>
+      <c r="X58" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="Y58" s="8" t="n"/>
       <c r="Z58" s="17" t="n">
         <v>0.95</v>
       </c>
@@ -7136,7 +7370,7 @@
       <c r="AW58" s="8" t="n"/>
       <c r="AX58" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+          <t>[EXCLUDED] material: Bitumen — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7394,7 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
@@ -7170,12 +7404,12 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>Lime concrete terracing</t>
+          <t>Lime concrete</t>
         </is>
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>Brick aggregate, Lime putty, Surkhi, Brick tiles, Cement, Fine sand, Crude oil</t>
+          <t>Brick aggregate, Lime putty, Surkhi, FPS brick tiles, Cement, Fine sand, Crude oil</t>
         </is>
       </c>
       <c r="J59" s="8" t="inlineStr">
@@ -7183,8 +7417,10 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K59" s="17" t="n">
-        <v>0.9</v>
+      <c r="K59" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L59" s="8" t="n"/>
       <c r="M59" s="8" t="inlineStr">
@@ -7220,9 +7456,11 @@
           <t>Area x thickness (100.0 mm, from description)</t>
         </is>
       </c>
-      <c r="X59" s="8" t="n"/>
+      <c r="X59" s="17" t="n">
+        <v>2400</v>
+      </c>
       <c r="Y59" s="17" t="n">
-        <v>9.68</v>
+        <v>2324.4</v>
       </c>
       <c r="Z59" s="17" t="n">
         <v>0.149</v>
@@ -7240,7 +7478,7 @@
       <c r="AC59" s="8" t="n"/>
       <c r="AD59" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Lime concrete terracing &gt; 1:2</t>
+          <t>Concrete &gt; Lime concrete &gt; 1:2</t>
         </is>
       </c>
       <c r="AE59" s="8" t="n"/>
@@ -7266,7 +7504,7 @@
       <c r="AW59" s="8" t="n"/>
       <c r="AX59" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+          <t>[OK] material: Lime concrete — mass 15600.0 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 2324.4 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -7290,7 +7528,7 @@
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
@@ -7300,7 +7538,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>Burnt clay tile</t>
+          <t>Burnt clay tiles</t>
         </is>
       </c>
       <c r="I60" s="8" t="inlineStr">
@@ -7313,8 +7551,10 @@
           <t>Masonry</t>
         </is>
       </c>
-      <c r="K60" s="17" t="n">
-        <v>0.9</v>
+      <c r="K60" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L60" s="8" t="n"/>
       <c r="M60" s="8" t="inlineStr">
@@ -7350,9 +7590,11 @@
           <t>Area x thickness (25.0 mm, from description)</t>
         </is>
       </c>
-      <c r="X60" s="8" t="n"/>
+      <c r="X60" s="17" t="n">
+        <v>1800</v>
+      </c>
       <c r="Y60" s="17" t="n">
-        <v>6.82</v>
+        <v>306.72</v>
       </c>
       <c r="Z60" s="17" t="n">
         <v>0.213</v>
@@ -7370,7 +7612,7 @@
       <c r="AC60" s="8" t="n"/>
       <c r="AD60" s="8" t="inlineStr">
         <is>
-          <t>Masonry &gt; Burnt clay tile &gt; 1:3</t>
+          <t>Masonry &gt; Burnt clay tiles &gt; 1:3</t>
         </is>
       </c>
       <c r="AE60" s="8" t="n"/>
@@ -7400,7 +7642,7 @@
       <c r="AW60" s="8" t="n"/>
       <c r="AX60" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
+          <t>[OK] material: Burnt clay tiles — mass 1440.0 kg [area × thickness (derived)] × 0.213 kgCO2e/kg = 306.72 kgCO2e — ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7666,7 @@
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
@@ -7439,7 +7681,7 @@
       </c>
       <c r="I61" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Stone aggregate, Brick tiles</t>
+          <t>Cement, Coarse sand, Graded stone aggregate, Brick tiles</t>
         </is>
       </c>
       <c r="J61" s="8" t="inlineStr">
@@ -7447,8 +7689,10 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K61" s="17" t="n">
-        <v>0.9</v>
+      <c r="K61" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L61" s="8" t="inlineStr">
         <is>
@@ -7478,10 +7722,10 @@
       <c r="U61" s="8" t="n"/>
       <c r="V61" s="8" t="n"/>
       <c r="W61" s="8" t="n"/>
-      <c r="X61" s="8" t="n"/>
-      <c r="Y61" s="17" t="n">
-        <v>6.85</v>
-      </c>
+      <c r="X61" s="17" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Y61" s="8" t="n"/>
       <c r="Z61" s="17" t="n">
         <v>0.149</v>
       </c>
@@ -7511,13 +7755,13 @@
       <c r="AL61" s="8" t="n"/>
       <c r="AM61" s="8" t="n"/>
       <c r="AN61" s="8" t="n"/>
-      <c r="AO61" s="17" t="n">
-        <v>150</v>
-      </c>
+      <c r="AO61" s="8" t="n"/>
       <c r="AP61" s="17" t="n">
         <v>150</v>
       </c>
-      <c r="AQ61" s="8" t="n"/>
+      <c r="AQ61" s="17" t="n">
+        <v>150</v>
+      </c>
       <c r="AR61" s="8" t="n"/>
       <c r="AS61" s="8" t="n"/>
       <c r="AT61" s="8" t="n"/>
@@ -7526,7 +7770,7 @@
       <c r="AW61" s="8" t="n"/>
       <c r="AX61" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M10 inferred from nominal mix 1:3:6 (IS 456)</t>
+          <t>[EXCLUDED] material: Cement concrete gola — category 'Concrete' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7794,7 @@
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
@@ -7560,12 +7804,12 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>Cement concrete khurra</t>
+          <t>Cement concrete khurras</t>
         </is>
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Stone aggregate, PVC sheet</t>
+          <t>Cement, Coarse sand, Graded stone aggregate, PVC sheet</t>
         </is>
       </c>
       <c r="J62" s="8" t="inlineStr">
@@ -7573,8 +7817,10 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K62" s="17" t="n">
-        <v>0.9</v>
+      <c r="K62" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L62" s="8" t="inlineStr">
         <is>
@@ -7604,10 +7850,10 @@
       <c r="U62" s="8" t="n"/>
       <c r="V62" s="8" t="n"/>
       <c r="W62" s="8" t="n"/>
-      <c r="X62" s="8" t="n"/>
-      <c r="Y62" s="17" t="n">
-        <v>0.45</v>
-      </c>
+      <c r="X62" s="17" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Y62" s="8" t="n"/>
       <c r="Z62" s="17" t="n">
         <v>0.149</v>
       </c>
@@ -7624,7 +7870,7 @@
       <c r="AC62" s="8" t="n"/>
       <c r="AD62" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Cement concrete khurra &gt; M15</t>
+          <t>Concrete &gt; Cement concrete khurras &gt; M15</t>
         </is>
       </c>
       <c r="AE62" s="8" t="n"/>
@@ -7654,7 +7900,7 @@
       <c r="AW62" s="8" t="n"/>
       <c r="AX62" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[EXCLUDED] material: Cement concrete khurras — category 'Concrete' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7924,7 @@
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VIII, Sanitary Installation (Rain Water Pipes)</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
@@ -7688,21 +7934,23 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>Cast iron rain water pipe</t>
+          <t>Cast Iron rain water pipe</t>
         </is>
       </c>
       <c r="I63" s="8" t="inlineStr">
         <is>
-          <t>Cast iron, Spun yarn, Cement, Fine sand</t>
+          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J63" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="K63" s="17" t="n">
-        <v>0.95</v>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="K63" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L63" s="8" t="n"/>
       <c r="M63" s="8" t="inlineStr">
@@ -7728,9 +7976,13 @@
       <c r="U63" s="8" t="n"/>
       <c r="V63" s="8" t="n"/>
       <c r="W63" s="8" t="n"/>
-      <c r="X63" s="8" t="n"/>
+      <c r="X63" s="17" t="n">
+        <v>7850</v>
+      </c>
       <c r="Y63" s="8" t="n"/>
-      <c r="Z63" s="8" t="n"/>
+      <c r="Z63" s="17" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA63" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -7744,7 +7996,7 @@
       <c r="AC63" s="8" t="n"/>
       <c r="AD63" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Cast iron rain water pipe &gt; 1:2</t>
+          <t>Steel &gt; Cast Iron rain water pipe &gt; 1:2</t>
         </is>
       </c>
       <c r="AE63" s="8" t="n"/>
@@ -7768,7 +8020,11 @@
       <c r="AU63" s="8" t="n"/>
       <c r="AV63" s="8" t="n"/>
       <c r="AW63" s="8" t="n"/>
-      <c r="AX63" s="8" t="n"/>
+      <c r="AX63" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Cast Iron rain water pipe — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
@@ -7790,7 +8046,7 @@
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VIII, Sanitary Installation (Rain Water Pipes)</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
@@ -7800,12 +8056,12 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>Mild steel holderbat clamp</t>
+          <t>MS holderbat clamps</t>
         </is>
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>Mild steel, Cement concrete</t>
+          <t>Mild steel, Cement, Coarse sand, Graded stone aggregate</t>
         </is>
       </c>
       <c r="J64" s="8" t="inlineStr">
@@ -7813,8 +8069,10 @@
           <t>Steel</t>
         </is>
       </c>
-      <c r="K64" s="17" t="n">
-        <v>0.9</v>
+      <c r="K64" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L64" s="8" t="n"/>
       <c r="M64" s="8" t="inlineStr">
@@ -7840,10 +8098,10 @@
       <c r="U64" s="8" t="n"/>
       <c r="V64" s="8" t="n"/>
       <c r="W64" s="8" t="n"/>
-      <c r="X64" s="8" t="n"/>
-      <c r="Y64" s="17" t="n">
-        <v>13.95</v>
-      </c>
+      <c r="X64" s="17" t="n">
+        <v>7850</v>
+      </c>
+      <c r="Y64" s="8" t="n"/>
       <c r="Z64" s="17" t="n">
         <v>1.55</v>
       </c>
@@ -7860,7 +8118,7 @@
       <c r="AC64" s="8" t="n"/>
       <c r="AD64" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Mild steel holderbat clamp &gt; 1:2:4</t>
+          <t>Steel &gt; MS holderbat clamps &gt; 1:2:4</t>
         </is>
       </c>
       <c r="AE64" s="8" t="n"/>
@@ -7886,7 +8144,7 @@
       <c r="AW64" s="8" t="n"/>
       <c r="AX64" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[EXCLUDED] material: MS holderbat clamps — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -7898,19 +8156,19 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>51i</t>
+          <t>51a</t>
         </is>
       </c>
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) CI plain head 100 mm dia</t>
+          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) i) CI plain head 100 mm dia</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VIII, Sanitary Installation (Rain Water Pipes)</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
@@ -7920,21 +8178,23 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>Cast iron plain head</t>
+          <t>CI plain head</t>
         </is>
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>Cast iron, Spun yarn, Cement, Fine sand</t>
+          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J65" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="K65" s="17" t="n">
-        <v>0.9</v>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="K65" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L65" s="8" t="n"/>
       <c r="M65" s="8" t="inlineStr">
@@ -7960,9 +8220,13 @@
       <c r="U65" s="8" t="n"/>
       <c r="V65" s="8" t="n"/>
       <c r="W65" s="8" t="n"/>
-      <c r="X65" s="8" t="n"/>
+      <c r="X65" s="17" t="n">
+        <v>7850</v>
+      </c>
       <c r="Y65" s="8" t="n"/>
-      <c r="Z65" s="8" t="n"/>
+      <c r="Z65" s="17" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA65" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -7976,7 +8240,7 @@
       <c r="AC65" s="8" t="n"/>
       <c r="AD65" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Cast iron plain head &gt; 1:2</t>
+          <t>Steel &gt; CI plain head &gt; 1:2</t>
         </is>
       </c>
       <c r="AE65" s="8" t="n"/>
@@ -8000,7 +8264,11 @@
       <c r="AU65" s="8" t="n"/>
       <c r="AV65" s="8" t="n"/>
       <c r="AW65" s="8" t="n"/>
-      <c r="AX65" s="8" t="n"/>
+      <c r="AX65" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: CI plain head — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
@@ -8010,19 +8278,19 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>51ii</t>
+          <t>51b</t>
         </is>
       </c>
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) CI plain shoe - 100 mm dia</t>
+          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) ii) CI plain shoe - 100 mm dia</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VIII, Sanitary Installation (Rain Water Pipes)</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
@@ -8032,21 +8300,23 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>Cast iron plain shoe</t>
+          <t>CI plain shoe</t>
         </is>
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>Cast iron, Spun yarn, Cement, Fine sand</t>
+          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J66" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="K66" s="17" t="n">
-        <v>0.9</v>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="K66" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L66" s="8" t="n"/>
       <c r="M66" s="8" t="inlineStr">
@@ -8072,9 +8342,13 @@
       <c r="U66" s="8" t="n"/>
       <c r="V66" s="8" t="n"/>
       <c r="W66" s="8" t="n"/>
-      <c r="X66" s="8" t="n"/>
+      <c r="X66" s="17" t="n">
+        <v>7850</v>
+      </c>
       <c r="Y66" s="8" t="n"/>
-      <c r="Z66" s="8" t="n"/>
+      <c r="Z66" s="17" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA66" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -8088,7 +8362,7 @@
       <c r="AC66" s="8" t="n"/>
       <c r="AD66" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Cast iron plain shoe &gt; 1:2</t>
+          <t>Steel &gt; CI plain shoe &gt; 1:2</t>
         </is>
       </c>
       <c r="AE66" s="8" t="n"/>
@@ -8112,7 +8386,11 @@
       <c r="AU66" s="8" t="n"/>
       <c r="AV66" s="8" t="n"/>
       <c r="AW66" s="8" t="n"/>
-      <c r="AX66" s="8" t="n"/>
+      <c r="AX66" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: CI plain shoe — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
@@ -8122,19 +8400,19 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>51iii</t>
+          <t>51c</t>
         </is>
       </c>
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) CI plain bend - 100 mm dia</t>
+          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) iii) CI plain bend - 100 mm dia</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - VIII, Sanitary Installation (Rain Water Pipes)</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
@@ -8144,21 +8422,23 @@
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>Cast iron plain bend</t>
+          <t>CI plain bend</t>
         </is>
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>Cast iron, Spun yarn, Cement, Fine sand</t>
+          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J67" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="K67" s="17" t="n">
-        <v>0.9</v>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="K67" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L67" s="8" t="n"/>
       <c r="M67" s="8" t="inlineStr">
@@ -8184,9 +8464,13 @@
       <c r="U67" s="8" t="n"/>
       <c r="V67" s="8" t="n"/>
       <c r="W67" s="8" t="n"/>
-      <c r="X67" s="8" t="n"/>
+      <c r="X67" s="17" t="n">
+        <v>7850</v>
+      </c>
       <c r="Y67" s="8" t="n"/>
-      <c r="Z67" s="8" t="n"/>
+      <c r="Z67" s="17" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA67" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -8200,7 +8484,7 @@
       <c r="AC67" s="8" t="n"/>
       <c r="AD67" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Cast iron plain bend &gt; 1:2</t>
+          <t>Steel &gt; CI plain bend &gt; 1:2</t>
         </is>
       </c>
       <c r="AE67" s="8" t="n"/>
@@ -8224,7 +8508,11 @@
       <c r="AU67" s="8" t="n"/>
       <c r="AV67" s="8" t="n"/>
       <c r="AW67" s="8" t="n"/>
-      <c r="AX67" s="8" t="n"/>
+      <c r="AX67" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: CI plain bend — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
@@ -8246,7 +8534,7 @@
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - IX, Plastering</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
@@ -8266,11 +8554,13 @@
       </c>
       <c r="J68" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish</t>
-        </is>
-      </c>
-      <c r="K68" s="17" t="n">
-        <v>0.95</v>
+          <t>Plaster</t>
+        </is>
+      </c>
+      <c r="K68" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L68" s="8" t="n"/>
       <c r="M68" s="8" t="inlineStr">
@@ -8306,12 +8596,14 @@
           <t>Area x thickness (12.0 mm, from description)</t>
         </is>
       </c>
-      <c r="X68" s="8" t="n"/>
+      <c r="X68" s="17" t="n">
+        <v>1900</v>
+      </c>
       <c r="Y68" s="17" t="n">
-        <v>209</v>
+        <v>817.61</v>
       </c>
       <c r="Z68" s="17" t="n">
-        <v>0.95</v>
+        <v>0.163</v>
       </c>
       <c r="AA68" s="8" t="inlineStr">
         <is>
@@ -8326,7 +8618,7 @@
       <c r="AC68" s="8" t="n"/>
       <c r="AD68" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish &gt; Cement plaster &gt; 1:6</t>
+          <t>Plaster &gt; Cement plaster &gt; 1:6</t>
         </is>
       </c>
       <c r="AE68" s="8" t="n"/>
@@ -8352,7 +8644,7 @@
       <c r="AW68" s="8" t="n"/>
       <c r="AX68" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+          <t>[OK] material: Cement plaster — mass 5016.0 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 817.61 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8668,7 @@
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - IX, Plastering</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
@@ -8396,11 +8688,13 @@
       </c>
       <c r="J69" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish</t>
-        </is>
-      </c>
-      <c r="K69" s="17" t="n">
-        <v>0.95</v>
+          <t>Plaster</t>
+        </is>
+      </c>
+      <c r="K69" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L69" s="8" t="n"/>
       <c r="M69" s="8" t="inlineStr">
@@ -8436,12 +8730,14 @@
           <t>Area x thickness (15.0 mm, from description)</t>
         </is>
       </c>
-      <c r="X69" s="8" t="n"/>
+      <c r="X69" s="17" t="n">
+        <v>1900</v>
+      </c>
       <c r="Y69" s="17" t="n">
-        <v>209</v>
+        <v>1022.01</v>
       </c>
       <c r="Z69" s="17" t="n">
-        <v>0.95</v>
+        <v>0.163</v>
       </c>
       <c r="AA69" s="8" t="inlineStr">
         <is>
@@ -8456,7 +8752,7 @@
       <c r="AC69" s="8" t="n"/>
       <c r="AD69" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish &gt; Cement plaster &gt; 1:6</t>
+          <t>Plaster &gt; Cement plaster &gt; 1:6</t>
         </is>
       </c>
       <c r="AE69" s="8" t="n"/>
@@ -8482,7 +8778,7 @@
       <c r="AW69" s="8" t="n"/>
       <c r="AX69" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+          <t>[OK] material: Cement plaster — mass 6270.0 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 1022.01 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -8506,7 +8802,7 @@
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - IX, Plastering</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
@@ -8526,11 +8822,13 @@
       </c>
       <c r="J70" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish</t>
-        </is>
-      </c>
-      <c r="K70" s="17" t="n">
-        <v>0.95</v>
+          <t>Plaster</t>
+        </is>
+      </c>
+      <c r="K70" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L70" s="8" t="n"/>
       <c r="M70" s="8" t="inlineStr">
@@ -8566,12 +8864,14 @@
           <t>Area x thickness (6.0 mm, from description)</t>
         </is>
       </c>
-      <c r="X70" s="8" t="n"/>
+      <c r="X70" s="17" t="n">
+        <v>1900</v>
+      </c>
       <c r="Y70" s="17" t="n">
-        <v>18.05</v>
+        <v>35.31</v>
       </c>
       <c r="Z70" s="17" t="n">
-        <v>0.95</v>
+        <v>0.163</v>
       </c>
       <c r="AA70" s="8" t="inlineStr">
         <is>
@@ -8586,7 +8886,7 @@
       <c r="AC70" s="8" t="n"/>
       <c r="AD70" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish &gt; Cement plaster &gt; 1:3</t>
+          <t>Plaster &gt; Cement plaster &gt; 1:3</t>
         </is>
       </c>
       <c r="AE70" s="8" t="n"/>
@@ -8612,7 +8912,7 @@
       <c r="AW70" s="8" t="n"/>
       <c r="AX70" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+          <t>[OK] material: Cement plaster — mass 216.6 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 35.31 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -8636,7 +8936,7 @@
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - IX, Plastering</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
@@ -8646,7 +8946,7 @@
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>Terrazzo plastering</t>
+          <t>Terrazzo plaster</t>
         </is>
       </c>
       <c r="I71" s="8" t="inlineStr">
@@ -8656,11 +8956,13 @@
       </c>
       <c r="J71" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish</t>
-        </is>
-      </c>
-      <c r="K71" s="17" t="n">
-        <v>0.95</v>
+          <t>Plaster</t>
+        </is>
+      </c>
+      <c r="K71" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L71" s="8" t="n"/>
       <c r="M71" s="8" t="inlineStr">
@@ -8696,12 +8998,14 @@
           <t>Area x thickness (18.0 mm, from description)</t>
         </is>
       </c>
-      <c r="X71" s="8" t="n"/>
+      <c r="X71" s="17" t="n">
+        <v>1900</v>
+      </c>
       <c r="Y71" s="17" t="n">
-        <v>19</v>
+        <v>111.49</v>
       </c>
       <c r="Z71" s="17" t="n">
-        <v>0.95</v>
+        <v>0.163</v>
       </c>
       <c r="AA71" s="8" t="inlineStr">
         <is>
@@ -8716,7 +9020,7 @@
       <c r="AC71" s="8" t="n"/>
       <c r="AD71" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish &gt; Terrazzo plastering &gt; 1:3</t>
+          <t>Plaster &gt; Terrazzo plaster &gt; 1:3</t>
         </is>
       </c>
       <c r="AE71" s="8" t="n"/>
@@ -8742,7 +9046,7 @@
       <c r="AW71" s="8" t="n"/>
       <c r="AX71" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+          <t>[OK] material: Terrazzo plaster — mass 684.0 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 111.49 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -8766,7 +9070,7 @@
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - IX, Plastering</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
@@ -8781,16 +9085,18 @@
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>Cement mortar</t>
+          <t>Cement, Sand</t>
         </is>
       </c>
       <c r="J72" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish</t>
-        </is>
-      </c>
-      <c r="K72" s="17" t="n">
-        <v>0.95</v>
+          <t>Plaster</t>
+        </is>
+      </c>
+      <c r="K72" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L72" s="8" t="n"/>
       <c r="M72" s="8" t="inlineStr">
@@ -8816,12 +9122,12 @@
       <c r="U72" s="8" t="n"/>
       <c r="V72" s="8" t="n"/>
       <c r="W72" s="8" t="n"/>
-      <c r="X72" s="8" t="n"/>
-      <c r="Y72" s="17" t="n">
-        <v>147.25</v>
-      </c>
+      <c r="X72" s="17" t="n">
+        <v>1900</v>
+      </c>
+      <c r="Y72" s="8" t="n"/>
       <c r="Z72" s="17" t="n">
-        <v>0.95</v>
+        <v>0.163</v>
       </c>
       <c r="AA72" s="8" t="inlineStr">
         <is>
@@ -8836,7 +9142,7 @@
       <c r="AC72" s="8" t="n"/>
       <c r="AD72" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish &gt; Cement plaster &gt; 1:3</t>
+          <t>Plaster &gt; Cement plaster &gt; 1:3</t>
         </is>
       </c>
       <c r="AE72" s="8" t="n"/>
@@ -8860,7 +9166,7 @@
       <c r="AW72" s="8" t="n"/>
       <c r="AX72" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+          <t>[EXCLUDED] material: Cement plaster — category 'Plaster' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -8884,7 +9190,7 @@
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - X, White/Colour Washing &amp; Painting</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
@@ -8894,7 +9200,7 @@
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>Lime wash</t>
+          <t>Lime white wash</t>
         </is>
       </c>
       <c r="I73" s="8" t="inlineStr">
@@ -8907,8 +9213,10 @@
           <t>Paint/Finish</t>
         </is>
       </c>
-      <c r="K73" s="17" t="n">
-        <v>0.95</v>
+      <c r="K73" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L73" s="8" t="n"/>
       <c r="M73" s="8" t="n"/>
@@ -8930,10 +9238,10 @@
       <c r="U73" s="8" t="n"/>
       <c r="V73" s="8" t="n"/>
       <c r="W73" s="8" t="n"/>
-      <c r="X73" s="8" t="n"/>
-      <c r="Y73" s="17" t="n">
-        <v>270.75</v>
-      </c>
+      <c r="X73" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="Y73" s="8" t="n"/>
       <c r="Z73" s="17" t="n">
         <v>0.95</v>
       </c>
@@ -8950,7 +9258,7 @@
       <c r="AC73" s="8" t="n"/>
       <c r="AD73" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish &gt; Lime wash</t>
+          <t>Paint/Finish &gt; Lime white wash</t>
         </is>
       </c>
       <c r="AE73" s="8" t="n"/>
@@ -8974,7 +9282,7 @@
       <c r="AW73" s="8" t="n"/>
       <c r="AX73" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+          <t>[EXCLUDED] material: Lime white wash — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -8998,7 +9306,7 @@
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - X, White/Colour Washing &amp; Painting</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
@@ -9013,7 +9321,7 @@
       </c>
       <c r="I74" s="8" t="inlineStr">
         <is>
-          <t>Lime wash</t>
+          <t>Lime, Pigment</t>
         </is>
       </c>
       <c r="J74" s="8" t="inlineStr">
@@ -9021,8 +9329,10 @@
           <t>Paint/Finish</t>
         </is>
       </c>
-      <c r="K74" s="17" t="n">
-        <v>0.95</v>
+      <c r="K74" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="L74" s="8" t="n"/>
       <c r="M74" s="8" t="n"/>
@@ -9044,10 +9354,10 @@
       <c r="U74" s="8" t="n"/>
       <c r="V74" s="8" t="n"/>
       <c r="W74" s="8" t="n"/>
-      <c r="X74" s="8" t="n"/>
-      <c r="Y74" s="17" t="n">
-        <v>270.75</v>
-      </c>
+      <c r="X74" s="17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="Y74" s="8" t="n"/>
       <c r="Z74" s="17" t="n">
         <v>0.95</v>
       </c>
@@ -9088,7 +9398,7 @@
       <c r="AW74" s="8" t="n"/>
       <c r="AX74" s="8" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+          <t>[EXCLUDED] material: Colour wash — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -9110,7 +9420,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - X, White/Colour Washing &amp; Painting</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -9120,12 +9430,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Primer</t>
+          <t>Wood primer</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Pink primer, Gray primer, Wood</t>
+          <t>Pink primer, Gray primer</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9133,8 +9443,10 @@
           <t>Paint/Finish</t>
         </is>
       </c>
-      <c r="K75" s="18" t="n">
-        <v>0.95</v>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="N75" s="18" t="n">
         <v>47</v>
@@ -9147,8 +9459,8 @@
       <c r="Q75" s="18" t="n">
         <v>47</v>
       </c>
-      <c r="Y75" s="18" t="n">
-        <v>44.65</v>
+      <c r="X75" s="18" t="n">
+        <v>1300</v>
       </c>
       <c r="Z75" s="18" t="n">
         <v>0.95</v>
@@ -9165,12 +9477,12 @@
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>Paint/Finish &gt; Primer</t>
+          <t>Paint/Finish &gt; Wood primer</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+          <t>[EXCLUDED] material: Wood primer — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -9192,7 +9504,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - X, White/Colour Washing &amp; Painting</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -9215,8 +9527,10 @@
           <t>Paint/Finish</t>
         </is>
       </c>
-      <c r="K76" s="18" t="n">
-        <v>0.95</v>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="N76" s="18" t="n">
         <v>30</v>
@@ -9229,8 +9543,8 @@
       <c r="Q76" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="Y76" s="18" t="n">
-        <v>28.5</v>
+      <c r="X76" s="18" t="n">
+        <v>1300</v>
       </c>
       <c r="Z76" s="18" t="n">
         <v>0.95</v>
@@ -9252,7 +9566,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+          <t>[EXCLUDED] material: Zinc chromate yellow primer — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9588,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - X, White/Colour Washing &amp; Painting</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -9297,8 +9611,10 @@
           <t>Paint/Finish</t>
         </is>
       </c>
-      <c r="K77" s="18" t="n">
-        <v>0.95</v>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="N77" s="18" t="n">
         <v>10</v>
@@ -9311,8 +9627,8 @@
       <c r="R77" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="Y77" s="18" t="n">
-        <v>9.5</v>
+      <c r="X77" s="18" t="n">
+        <v>1300</v>
       </c>
       <c r="Z77" s="18" t="n">
         <v>0.95</v>
@@ -9337,7 +9653,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+          <t>[EXCLUDED] material: Bitumastic paint — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9675,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - X, White/Colour Washing &amp; Painting</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -9382,8 +9698,10 @@
           <t>Paint/Finish</t>
         </is>
       </c>
-      <c r="K78" s="18" t="n">
-        <v>0.95</v>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="N78" s="18" t="n">
         <v>77</v>
@@ -9396,8 +9714,8 @@
       <c r="Q78" s="18" t="n">
         <v>77</v>
       </c>
-      <c r="Y78" s="18" t="n">
-        <v>73.15000000000001</v>
+      <c r="X78" s="18" t="n">
+        <v>1300</v>
       </c>
       <c r="Z78" s="18" t="n">
         <v>0.95</v>
@@ -9414,7 +9732,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+          <t>[EXCLUDED] material: Synthetic enamel paint — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -9436,7 +9754,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - X, White/Colour Washing &amp; Painting</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -9451,7 +9769,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>French spirit polish, Wood filler</t>
+          <t>French spirit, Wood filler</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9459,8 +9777,10 @@
           <t>Paint/Finish</t>
         </is>
       </c>
-      <c r="K79" s="18" t="n">
-        <v>0.95</v>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="N79" s="18" t="n">
         <v>13</v>
@@ -9473,8 +9793,8 @@
       <c r="Q79" s="18" t="n">
         <v>13</v>
       </c>
-      <c r="Y79" s="18" t="n">
-        <v>12.35</v>
+      <c r="X79" s="18" t="n">
+        <v>1300</v>
       </c>
       <c r="Z79" s="18" t="n">
         <v>0.95</v>
@@ -9496,7 +9816,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V3.0 (Generic Assumed)</t>
+          <t>[EXCLUDED] material: French spirit polish — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -9518,7 +9838,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Schedule 'A'</t>
+          <t>Sub-Head - XI, Sundry Items / Site Development</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -9533,7 +9853,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Stone aggregate, Brick ballast, Fine sand</t>
+          <t>Cement, Coarse sand, Graded stone aggregate, Brick ballast, Fine sand</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9541,8 +9861,10 @@
           <t>Concrete</t>
         </is>
       </c>
-      <c r="K80" s="18" t="n">
-        <v>0.95</v>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -9578,8 +9900,11 @@
           <t>Area x thickness (50.0 mm, from description)</t>
         </is>
       </c>
+      <c r="X80" s="18" t="n">
+        <v>2400</v>
+      </c>
       <c r="Y80" s="18" t="n">
-        <v>5.16</v>
+        <v>618.65</v>
       </c>
       <c r="Z80" s="18" t="n">
         <v>0.149</v>
@@ -9604,7 +9929,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>EPD Source: ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M10 inferred from nominal mix 1:3:6 (IS 456)</t>
+          <t>[OK] material: Cement concrete plinth protection — mass 4152.0 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 618.65 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M10 inferred from nominal mix 1:3:6 (IS 456)</t>
         </is>
       </c>
     </row>

--- a/output/passport_filled.xlsx
+++ b/output/passport_filled.xlsx
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX80"/>
+  <dimension ref="A1:AX77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -911,207 +911,361 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>EXAMPLE 1</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>1.1.1</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Earth work in excavation by mechanical means (Hydraulic excavator)/manual means over areas (exceeding 30 cm in depth, 1.5 m in width as well as 10 sqm on plan) including getting out and disposal of excavated earth within campus and all lifts, as directed by Engineer-in-charge. All kinds of soil</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Sub- Head - I , Earth Work</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0001</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Earth work in excavation in foundation trenches or drains not exceeding 1.5 m in width or 10 Sq.m on plan including dressing of sides and ramming of bottoms, lift upto 1.5 m including getting out the excavated soil and disposal of surplus excavated soil as directed within a lead of 50 m in all types of soil except rocks.</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Sub-Head - I, Earth Work</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Civil &amp; Sitework</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Earthwork (excavation/filling/anti-termite)</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Excavated soil</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>Soil</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Earthwork</t>
         </is>
       </c>
-      <c r="N4" s="7" t="n">
-        <v>390.8</v>
-      </c>
-      <c r="O4" s="7" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="n"/>
+      <c r="M4" s="8" t="n"/>
+      <c r="N4" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="O4" s="8" t="inlineStr">
         <is>
           <t>cum</t>
         </is>
       </c>
-      <c r="P4" s="7" t="n">
-        <v>390.8</v>
-      </c>
-      <c r="Y4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="7" t="inlineStr">
-        <is>
-          <t>2.6.1</t>
-        </is>
-      </c>
-      <c r="AX4" s="7" t="inlineStr">
-        <is>
-          <t>[EXCLUDED] earth + labour; negligible embodied material carbon</t>
+      <c r="P4" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q4" s="8" t="n"/>
+      <c r="R4" s="8" t="n"/>
+      <c r="S4" s="8" t="n"/>
+      <c r="T4" s="8" t="n"/>
+      <c r="U4" s="8" t="n"/>
+      <c r="V4" s="8" t="n"/>
+      <c r="W4" s="8" t="n"/>
+      <c r="X4" s="8" t="n"/>
+      <c r="Y4" s="8" t="n"/>
+      <c r="Z4" s="8" t="n"/>
+      <c r="AA4" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
+      <c r="AB4" s="8" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="AC4" s="8" t="n"/>
+      <c r="AD4" s="8" t="inlineStr">
+        <is>
+          <t>Earthwork &gt; Excavated soil</t>
+        </is>
+      </c>
+      <c r="AE4" s="8" t="n"/>
+      <c r="AF4" s="8" t="n"/>
+      <c r="AG4" s="8" t="n"/>
+      <c r="AH4" s="8" t="n"/>
+      <c r="AI4" s="8" t="n"/>
+      <c r="AJ4" s="8" t="n"/>
+      <c r="AK4" s="8" t="n"/>
+      <c r="AL4" s="8" t="n"/>
+      <c r="AM4" s="8" t="n"/>
+      <c r="AN4" s="8" t="n"/>
+      <c r="AO4" s="8" t="n"/>
+      <c r="AP4" s="17" t="n">
+        <v>1500</v>
+      </c>
+      <c r="AQ4" s="8" t="n"/>
+      <c r="AR4" s="8" t="n"/>
+      <c r="AS4" s="8" t="n"/>
+      <c r="AT4" s="8" t="n"/>
+      <c r="AU4" s="8" t="n"/>
+      <c r="AV4" s="8" t="n"/>
+      <c r="AW4" s="8" t="n"/>
+      <c r="AX4" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Excavated soil — earthwork/excavated soil; negligible embodied material carbon</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>2.1.1.1</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Providing and laying in position ready mixed / batch mixed plain cement concrete, with cement content as per approved design mix and manufactured in fully automatic batching plant and transported to site of work in transit mixer for all leads, having continuous agitated mixer, manufactured as per mix design of specified grade for plain cement concrete work, including pumping of Concrete from transit mixer to site of laying and curing, excluding the cost of centering, shuttering and finishing, including cost of curing, admixtures in recommended proportions as per IS : 9103 to accelerate/ retard setting of concrete, improve workability without impairing strength and durability as per direction of the Engineer-in-charge.” All works upto plinth level : M-15 grade plain cement concrete (cement content considered @ 240 kg/cum)</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Sub - Head - II , Concrete Work</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Structural</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Cement concrete 1:4:8</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Concrete</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="n">
-        <v>1330.68774625</v>
-      </c>
-      <c r="O5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0002</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Filling available excavated earth (excluding rock) in trenches, plinth, sides of foundations etc. in layers not exceeding 20 cm in depth consolidating each deposited layer by ramming &amp; watering, lead upto 50 m and lift upto 1.5 m.</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Sub-Head - I, Earth Work</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Civil &amp; Sitework</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Excavated earth</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Earth</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>Earthwork</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="n"/>
+      <c r="M5" s="8" t="n"/>
+      <c r="N5" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="O5" s="8" t="inlineStr">
         <is>
           <t>cum</t>
         </is>
       </c>
-      <c r="P5" s="7" t="n">
-        <v>1330.688</v>
-      </c>
-      <c r="Y5" s="7" t="n">
-        <v>248623</v>
-      </c>
-      <c r="AB5" s="7" t="inlineStr">
-        <is>
-          <t>4.20.1.1</t>
-        </is>
-      </c>
-      <c r="AD5" s="7" t="inlineStr">
-        <is>
-          <t>Nominal-mix concrete &gt; Cement concrete (nominal mix) &gt; 1:4:8</t>
-        </is>
-      </c>
-      <c r="AX5" s="7" t="inlineStr">
-        <is>
-          <t>[OK] nominal mix</t>
+      <c r="P5" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="8" t="n"/>
+      <c r="R5" s="8" t="n"/>
+      <c r="S5" s="8" t="n"/>
+      <c r="T5" s="8" t="n"/>
+      <c r="U5" s="8" t="n"/>
+      <c r="V5" s="8" t="n"/>
+      <c r="W5" s="8" t="n"/>
+      <c r="X5" s="8" t="n"/>
+      <c r="Y5" s="8" t="n"/>
+      <c r="Z5" s="8" t="n"/>
+      <c r="AA5" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
+      <c r="AB5" s="8" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="AC5" s="8" t="n"/>
+      <c r="AD5" s="8" t="inlineStr">
+        <is>
+          <t>Earthwork &gt; Excavated earth</t>
+        </is>
+      </c>
+      <c r="AE5" s="8" t="n"/>
+      <c r="AF5" s="8" t="n"/>
+      <c r="AG5" s="8" t="n"/>
+      <c r="AH5" s="8" t="n"/>
+      <c r="AI5" s="8" t="n"/>
+      <c r="AJ5" s="8" t="n"/>
+      <c r="AK5" s="8" t="n"/>
+      <c r="AL5" s="8" t="n"/>
+      <c r="AM5" s="8" t="n"/>
+      <c r="AN5" s="8" t="n"/>
+      <c r="AO5" s="8" t="n"/>
+      <c r="AP5" s="8" t="n"/>
+      <c r="AQ5" s="8" t="n"/>
+      <c r="AR5" s="17" t="n">
+        <v>200</v>
+      </c>
+      <c r="AS5" s="8" t="n"/>
+      <c r="AT5" s="8" t="n"/>
+      <c r="AU5" s="8" t="n"/>
+      <c r="AV5" s="8" t="n"/>
+      <c r="AW5" s="8" t="n"/>
+      <c r="AX5" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Excavated earth — earthwork/excavated soil; negligible embodied material carbon</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>3.3.1</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Steel reinforcement for R.C.C. work including straightening, cutting, bending, placing in position and binding all complete upto plinth level. Thermo - Mechanically Treated bars</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Sub - Head - III ,  RCC Work</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>Structural</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>TMT reinforcement steel</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>Reinf</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="n">
-        <v>120322.27665</v>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="n">
-        <v>120322.277</v>
-      </c>
-      <c r="Y6" s="7" t="n">
-        <v>284321.5</v>
-      </c>
-      <c r="Z6" s="7" t="n">
-        <v>2.363</v>
-      </c>
-      <c r="AB6" s="7" t="inlineStr">
-        <is>
-          <t>5.22.6</t>
-        </is>
-      </c>
-      <c r="AD6" s="7" t="inlineStr">
-        <is>
-          <t>Reinforcement steel (TMT/rebar) &gt; Mild steel round bar &gt; Twisted steel/deformed TMT bars Fe-500D</t>
-        </is>
-      </c>
-      <c r="AX6" s="7" t="inlineStr">
-        <is>
-          <t>[OK] deformed bar 2.363/kg</t>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>GMAP-0003</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Filling the plinth with fine sand under floors including watering, ramming consolidating and dressing complete.</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Sub-Head - I, Earth Work</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Civil &amp; Sitework</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Fine sand</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Fine sand</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Earthwork</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="8" t="n"/>
+      <c r="N6" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P6" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q6" s="8" t="n"/>
+      <c r="R6" s="8" t="n"/>
+      <c r="S6" s="8" t="n"/>
+      <c r="T6" s="8" t="n"/>
+      <c r="U6" s="8" t="n"/>
+      <c r="V6" s="8" t="n"/>
+      <c r="W6" s="8" t="n"/>
+      <c r="X6" s="8" t="n"/>
+      <c r="Y6" s="8" t="n"/>
+      <c r="Z6" s="8" t="n"/>
+      <c r="AA6" s="8" t="inlineStr">
+        <is>
+          <t>DSR 1989</t>
+        </is>
+      </c>
+      <c r="AB6" s="8" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="AC6" s="8" t="n"/>
+      <c r="AD6" s="8" t="inlineStr">
+        <is>
+          <t>Earthwork &gt; Fine sand</t>
+        </is>
+      </c>
+      <c r="AE6" s="8" t="n"/>
+      <c r="AF6" s="8" t="n"/>
+      <c r="AG6" s="8" t="n"/>
+      <c r="AH6" s="8" t="n"/>
+      <c r="AI6" s="8" t="n"/>
+      <c r="AJ6" s="8" t="n"/>
+      <c r="AK6" s="8" t="n"/>
+      <c r="AL6" s="8" t="n"/>
+      <c r="AM6" s="8" t="n"/>
+      <c r="AN6" s="8" t="n"/>
+      <c r="AO6" s="8" t="n"/>
+      <c r="AP6" s="8" t="n"/>
+      <c r="AQ6" s="8" t="n"/>
+      <c r="AR6" s="8" t="n"/>
+      <c r="AS6" s="8" t="n"/>
+      <c r="AT6" s="8" t="n"/>
+      <c r="AU6" s="8" t="n"/>
+      <c r="AV6" s="8" t="n"/>
+      <c r="AW6" s="8" t="n"/>
+      <c r="AX6" s="8" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Fine sand — earthwork/excavated soil; negligible embodied material carbon</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0001</t>
+          <t>GMAP-0004</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C7" s="8" t="n"/>
       <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Earth work in excavation in foundation trenches or drains not exceeding 1.5 m in width or 10 Sq.m on plan including dressing of sides and ramming of bottoms, lift upto 1.5 m including getting out the excavated soil and disposal of surplus excavated soil as directed within a lead of 50 m in all types of soil except rocks.</t>
+          <t>Surface dressing of the ground including removing vegetation, and inequalities not exceeding 15 cm deep and disposal of rubbish, lead upto 50 m and lift upto 1.5 m in soft/loose soil.</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -1126,7 +1280,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Earth/Soil</t>
+          <t>Soil</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
@@ -1147,17 +1301,17 @@
       <c r="L7" s="8" t="n"/>
       <c r="M7" s="8" t="n"/>
       <c r="N7" s="17" t="n">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="O7" s="8" t="inlineStr">
         <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="P7" s="17" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q7" s="8" t="n"/>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="17" t="n">
+        <v>140</v>
+      </c>
       <c r="R7" s="8" t="n"/>
       <c r="S7" s="8" t="n"/>
       <c r="T7" s="8" t="n"/>
@@ -1174,13 +1328,13 @@
       </c>
       <c r="AB7" s="8" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.29.1</t>
         </is>
       </c>
       <c r="AC7" s="8" t="n"/>
       <c r="AD7" s="8" t="inlineStr">
         <is>
-          <t>Earthwork &gt; Earth/Soil</t>
+          <t>Earthwork &gt; Soil</t>
         </is>
       </c>
       <c r="AE7" s="8" t="n"/>
@@ -1197,33 +1351,35 @@
       <c r="AP7" s="8" t="n"/>
       <c r="AQ7" s="8" t="n"/>
       <c r="AR7" s="8" t="n"/>
-      <c r="AS7" s="8" t="n"/>
+      <c r="AS7" s="17" t="n">
+        <v>150</v>
+      </c>
       <c r="AT7" s="8" t="n"/>
       <c r="AU7" s="8" t="n"/>
       <c r="AV7" s="8" t="n"/>
       <c r="AW7" s="8" t="n"/>
       <c r="AX7" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Earth/Soil — earthwork/excavated soil; negligible embodied material carbon</t>
+          <t>[EXCLUDED] material: Soil — earthwork/excavated soil; negligible embodied material carbon</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0002</t>
+          <t>GMAP-0005</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C8" s="8" t="n"/>
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Filling available excavated earth (excluding rock) in trenches, plinth, sides of foundations etc. in layers not exceeding 20 cm in depth consolidating each deposited layer by ramming &amp; watering, lead upto 50 m and lift upto 1.5 m.</t>
+          <t>Providing and injecting chemical emulsion for PRECONSTRUCTIONAL anti termite treatment and creating a chemical barrier under and alround the column pits, wall trenches, basement excavation, top surface of plinth filling junction of wall and floor, along the external perimetre of building, expansion joints, surroundings of pipes &amp; conduits etc. complete (plinth area of the building at ground floor only shall be measured) with Aldrin Emulsifiable Concentrate (0.5%)</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -1238,17 +1394,17 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Earth/Soil</t>
+          <t>Aldrin Emulsifiable Concentrate</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Aldrin chemical emulsion</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>Earthwork</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
@@ -1259,17 +1415,17 @@
       <c r="L8" s="8" t="n"/>
       <c r="M8" s="8" t="n"/>
       <c r="N8" s="17" t="n">
-        <v>12</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O8" s="8" t="inlineStr">
         <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="P8" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q8" s="8" t="n"/>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="17" t="n">
+        <v>90.59999999999999</v>
+      </c>
       <c r="R8" s="8" t="n"/>
       <c r="S8" s="8" t="n"/>
       <c r="T8" s="8" t="n"/>
@@ -1286,13 +1442,13 @@
       </c>
       <c r="AB8" s="8" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.35.2</t>
         </is>
       </c>
       <c r="AC8" s="8" t="n"/>
       <c r="AD8" s="8" t="inlineStr">
         <is>
-          <t>Earthwork &gt; Earth/Soil</t>
+          <t>Other &gt; Aldrin Emulsifiable Concentrate</t>
         </is>
       </c>
       <c r="AE8" s="8" t="n"/>
@@ -1316,62 +1472,70 @@
       <c r="AW8" s="8" t="n"/>
       <c r="AX8" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Earth/Soil — earthwork/excavated soil; negligible embodied material carbon</t>
+          <t>[EXCLUDED] material: Aldrin Emulsifiable Concentrate — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0003</t>
+          <t>GMAP-0006</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C9" s="8" t="n"/>
       <c r="D9" s="8" t="n"/>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Filling the plinth with fine sand under floors including watering, ramming consolidating and dressing complete.</t>
+          <t>Providing and laying cement concrete in footings and bases for columns, excluding the cost of centring and shuttering with 1:5:10 (1 cement : 5 coarse sand : 10 graded stone aggregate 40 mm nominal size).</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - I, Earth Work</t>
+          <t>Sub-Head - II, Cement Concrete Work</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Sand</t>
+          <t>Cement concrete</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Sand</t>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>Earthwork</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L9" s="8" t="n"/>
-      <c r="M9" s="8" t="n"/>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>1:5:10</t>
+        </is>
+      </c>
       <c r="N9" s="17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O9" s="8" t="inlineStr">
         <is>
@@ -1379,7 +1543,7 @@
         </is>
       </c>
       <c r="P9" s="17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q9" s="8" t="n"/>
       <c r="R9" s="8" t="n"/>
@@ -1388,9 +1552,15 @@
       <c r="U9" s="8" t="n"/>
       <c r="V9" s="8" t="n"/>
       <c r="W9" s="8" t="n"/>
-      <c r="X9" s="8" t="n"/>
-      <c r="Y9" s="8" t="n"/>
-      <c r="Z9" s="8" t="n"/>
+      <c r="X9" s="17" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Y9" s="17" t="n">
+        <v>2860.8</v>
+      </c>
+      <c r="Z9" s="17" t="n">
+        <v>0.149</v>
+      </c>
       <c r="AA9" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -1398,13 +1568,13 @@
       </c>
       <c r="AB9" s="8" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>4.5.10</t>
         </is>
       </c>
       <c r="AC9" s="8" t="n"/>
       <c r="AD9" s="8" t="inlineStr">
         <is>
-          <t>Earthwork &gt; Sand</t>
+          <t>Concrete &gt; Cement concrete &gt; M5</t>
         </is>
       </c>
       <c r="AE9" s="8" t="n"/>
@@ -1428,81 +1598,95 @@
       <c r="AW9" s="8" t="n"/>
       <c r="AX9" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Sand — earthwork/excavated soil; negligible embodied material carbon</t>
+          <t>[OK] material: Cement concrete — mass 19200.0 kg [direct volume] × 0.149 kgCO2e/kg = 2860.8 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M5 inferred from nominal mix 1:5:10 (IS 456)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0004</t>
+          <t>GMAP-0007</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C10" s="8" t="n"/>
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Surface dressing of the ground including removing vegetation, and inequalities not exceeding 15 cm deep and disposal of rubbish, lead upto 50 m and lift upto 1.5 m in soft/loose soil.</t>
+          <t>Providing and laying cement concrete in retaining walls, return walls, walls (any thickness) including attached pilasters, buttresses, plinth, string courses, fillets etc. upto floor two level, excluding the cost of centring and shuttering with 1:5:10 (1 cement : 5 fine sand : 10 graded stone aggregate 40 mm nominal size)</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - I, Earth Work</t>
+          <t>Sub-Head - II, Cement Concrete Work</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Soil</t>
+          <t>Cement concrete</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Soil</t>
+          <t>Cement, Fine sand, Graded stone aggregate</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>Earthwork</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L10" s="8" t="n"/>
-      <c r="M10" s="8" t="n"/>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>1:5:10</t>
+        </is>
+      </c>
       <c r="N10" s="17" t="n">
-        <v>140</v>
+        <v>7.3</v>
       </c>
       <c r="O10" s="8" t="inlineStr">
         <is>
-          <t>sqm</t>
-        </is>
-      </c>
-      <c r="P10" s="8" t="n"/>
-      <c r="Q10" s="17" t="n">
-        <v>140</v>
-      </c>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P10" s="17" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Q10" s="8" t="n"/>
       <c r="R10" s="8" t="n"/>
       <c r="S10" s="8" t="n"/>
       <c r="T10" s="8" t="n"/>
       <c r="U10" s="8" t="n"/>
       <c r="V10" s="8" t="n"/>
       <c r="W10" s="8" t="n"/>
-      <c r="X10" s="8" t="n"/>
-      <c r="Y10" s="8" t="n"/>
-      <c r="Z10" s="8" t="n"/>
+      <c r="X10" s="17" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Y10" s="17" t="n">
+        <v>2610.48</v>
+      </c>
+      <c r="Z10" s="17" t="n">
+        <v>0.149</v>
+      </c>
       <c r="AA10" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -1510,13 +1694,13 @@
       </c>
       <c r="AB10" s="8" t="inlineStr">
         <is>
-          <t>2.29.1</t>
+          <t>4.6.11</t>
         </is>
       </c>
       <c r="AC10" s="8" t="n"/>
       <c r="AD10" s="8" t="inlineStr">
         <is>
-          <t>Earthwork &gt; Soil</t>
+          <t>Concrete &gt; Cement concrete &gt; M5</t>
         </is>
       </c>
       <c r="AE10" s="8" t="n"/>
@@ -1540,81 +1724,95 @@
       <c r="AW10" s="8" t="n"/>
       <c r="AX10" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Soil — earthwork/excavated soil; negligible embodied material carbon</t>
+          <t>[OK] material: Cement concrete — mass 17520.0 kg [direct volume] × 0.149 kgCO2e/kg = 2610.48 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M5 inferred from nominal mix 1:5:10 (IS 456)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0005</t>
+          <t>GMAP-0008</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C11" s="8" t="n"/>
       <c r="D11" s="8" t="n"/>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Providing and injecting chemical emulsion for PRECONSTRUCTIONAL anti termite treatment and creating a chemical barrier under and alround the column pits, wall trenches, basement excavation, top surface of plinth filling junction of wall and floor, along the external perimetre of building, expansion joints, surroundings of pipes &amp; conduits etc. complete (plinth area of the building at ground floor only shall be measured) with Aldrin Emulsifiable Concentrate (0.5%)</t>
+          <t>Providing and laying upto floor two level cement concrete in string or lacing courses, parapets, copings, bed blocks anchor blocks, plain window sills and the like excluding centring and shuttering, etc. with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - I, Earth Work</t>
+          <t>Sub-Head - II, Cement Concrete Work</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Aldrin Emulsifiable Concentrate</t>
+          <t>Cement concrete</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>Aldrin Emulsifiable Concentrate, Chemical emulsion</t>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="n"/>
-      <c r="M11" s="8" t="n"/>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>1:2:4</t>
+        </is>
+      </c>
       <c r="N11" s="17" t="n">
-        <v>90.59999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="O11" s="8" t="inlineStr">
         <is>
-          <t>sqm</t>
-        </is>
-      </c>
-      <c r="P11" s="8" t="n"/>
-      <c r="Q11" s="17" t="n">
-        <v>90.59999999999999</v>
-      </c>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P11" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q11" s="8" t="n"/>
       <c r="R11" s="8" t="n"/>
       <c r="S11" s="8" t="n"/>
       <c r="T11" s="8" t="n"/>
       <c r="U11" s="8" t="n"/>
       <c r="V11" s="8" t="n"/>
       <c r="W11" s="8" t="n"/>
-      <c r="X11" s="8" t="n"/>
-      <c r="Y11" s="8" t="n"/>
-      <c r="Z11" s="8" t="n"/>
+      <c r="X11" s="17" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Y11" s="17" t="n">
+        <v>35.76</v>
+      </c>
+      <c r="Z11" s="17" t="n">
+        <v>0.149</v>
+      </c>
       <c r="AA11" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -1622,13 +1820,13 @@
       </c>
       <c r="AB11" s="8" t="inlineStr">
         <is>
-          <t>2.35.2</t>
+          <t>4.11.1</t>
         </is>
       </c>
       <c r="AC11" s="8" t="n"/>
       <c r="AD11" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aldrin Emulsifiable Concentrate</t>
+          <t>Concrete &gt; Cement concrete &gt; M15</t>
         </is>
       </c>
       <c r="AE11" s="8" t="n"/>
@@ -1652,26 +1850,26 @@
       <c r="AW11" s="8" t="n"/>
       <c r="AX11" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aldrin Emulsifiable Concentrate — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[OK] material: Cement concrete — mass 240.0 kg [direct volume] × 0.149 kgCO2e/kg = 35.76 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0006</t>
+          <t>GMAP-0009</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C12" s="8" t="n"/>
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Providing and laying cement concrete in footings and bases for columns, excluding the cost of centring and shuttering with 1:5:10 (1 cement : 5 coarse sand : 10 graded stone aggregate 40 mm nominal size).</t>
+          <t>Providing and laying damp-proof course 40 mm thick with cement concrete 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 12.5 mm nominal size)</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -1681,7 +1879,7 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Civil &amp; Sitework</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
@@ -1706,37 +1904,47 @@
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M15</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>1:5:10</t>
+          <t>1:2:4</t>
         </is>
       </c>
       <c r="N12" s="17" t="n">
-        <v>8</v>
+        <v>14.4</v>
       </c>
       <c r="O12" s="8" t="inlineStr">
         <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="P12" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q12" s="8" t="n"/>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="n"/>
+      <c r="Q12" s="17" t="n">
+        <v>14.4</v>
+      </c>
       <c r="R12" s="8" t="n"/>
       <c r="S12" s="8" t="n"/>
       <c r="T12" s="8" t="n"/>
-      <c r="U12" s="8" t="n"/>
-      <c r="V12" s="8" t="n"/>
-      <c r="W12" s="8" t="n"/>
+      <c r="U12" s="17" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (40.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X12" s="17" t="n">
         <v>2400</v>
       </c>
       <c r="Y12" s="17" t="n">
-        <v>2860.8</v>
+        <v>205.98</v>
       </c>
       <c r="Z12" s="17" t="n">
         <v>0.149</v>
@@ -1748,13 +1956,13 @@
       </c>
       <c r="AB12" s="8" t="inlineStr">
         <is>
-          <t>4.5.10</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AC12" s="8" t="n"/>
       <c r="AD12" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Cement concrete &gt; M5</t>
+          <t>Concrete &gt; Cement concrete &gt; M15</t>
         </is>
       </c>
       <c r="AE12" s="8" t="n"/>
@@ -1770,7 +1978,9 @@
       <c r="AO12" s="8" t="n"/>
       <c r="AP12" s="8" t="n"/>
       <c r="AQ12" s="8" t="n"/>
-      <c r="AR12" s="8" t="n"/>
+      <c r="AR12" s="17" t="n">
+        <v>40</v>
+      </c>
       <c r="AS12" s="8" t="n"/>
       <c r="AT12" s="8" t="n"/>
       <c r="AU12" s="8" t="n"/>
@@ -1778,26 +1988,26 @@
       <c r="AW12" s="8" t="n"/>
       <c r="AX12" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Cement concrete — mass 19200.0 kg [direct volume] × 0.149 kgCO2e/kg = 2860.8 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M5 inferred from nominal mix 1:5:10 (IS 456)</t>
+          <t>[OK] material: Cement concrete — mass 1382.4 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 205.98 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0007</t>
+          <t>GMAP-0010</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C13" s="8" t="n"/>
       <c r="D13" s="8" t="n"/>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Providing and laying cement concrete in retaining walls, return walls, walls (any thickness) including attached pilasters, buttresses, plinth, string courses, fillets etc. upto floor two level, excluding the cost of centring and shuttering with 1:5:10 (1 cement : 5 fine sand : 10 graded stone aggregate 40 mm nominal size)</t>
+          <t>Applying a coat of residual petroleum bitumen of penetration 80/100 of approved quality using 1.7 Kg. per square metre on damp proof course after cleaning the surface with brushes and finally with a piece of cloth lightly soaked in kerosene oil.</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -1807,66 +2017,52 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Civil &amp; Sitework</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>Cement concrete</t>
+          <t>Residual petroleum bitumen</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>Cement, Fine sand, Graded stone aggregate</t>
+          <t>Petroleum bitumen, Kerosene oil</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="M13" s="8" t="inlineStr">
-        <is>
-          <t>1:5:10</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
       <c r="N13" s="17" t="n">
-        <v>7.3</v>
+        <v>14.4</v>
       </c>
       <c r="O13" s="8" t="inlineStr">
         <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="P13" s="17" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="Q13" s="8" t="n"/>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="17" t="n">
+        <v>14.4</v>
+      </c>
       <c r="R13" s="8" t="n"/>
       <c r="S13" s="8" t="n"/>
       <c r="T13" s="8" t="n"/>
       <c r="U13" s="8" t="n"/>
       <c r="V13" s="8" t="n"/>
       <c r="W13" s="8" t="n"/>
-      <c r="X13" s="17" t="n">
-        <v>2400</v>
-      </c>
-      <c r="Y13" s="17" t="n">
-        <v>2610.48</v>
-      </c>
-      <c r="Z13" s="17" t="n">
-        <v>0.149</v>
-      </c>
+      <c r="X13" s="8" t="n"/>
+      <c r="Y13" s="8" t="n"/>
+      <c r="Z13" s="8" t="n"/>
       <c r="AA13" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -1874,13 +2070,13 @@
       </c>
       <c r="AB13" s="8" t="inlineStr">
         <is>
-          <t>4.6.11</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AC13" s="8" t="n"/>
       <c r="AD13" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Cement concrete &gt; M5</t>
+          <t>Other &gt; Residual petroleum bitumen</t>
         </is>
       </c>
       <c r="AE13" s="8" t="n"/>
@@ -1904,31 +2100,31 @@
       <c r="AW13" s="8" t="n"/>
       <c r="AX13" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Cement concrete — mass 17520.0 kg [direct volume] × 0.149 kgCO2e/kg = 2610.48 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M5 inferred from nominal mix 1:5:10 (IS 456)</t>
+          <t>[EXCLUDED] material: Residual petroleum bitumen — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0008</t>
+          <t>GMAP-0011</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C14" s="8" t="n"/>
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Providing and laying upto floor two level cement concrete in string or lacing courses, parapets, copings, bed blocks anchor blocks, plain window sills and the like excluding centring and shuttering, etc. with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
+          <t>Reinforced cement concrete work in suspended floors, roofs, landings and balconies upto floor two level excluding cost of centring, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size)</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - II, Cement Concrete Work</t>
+          <t>Sub-Head - III, R.C.C. Work</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
@@ -1938,7 +2134,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>Cement concrete</t>
+          <t>Reinforced cement concrete</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
@@ -1967,7 +2163,7 @@
         </is>
       </c>
       <c r="N14" s="17" t="n">
-        <v>0.1</v>
+        <v>11.3</v>
       </c>
       <c r="O14" s="8" t="inlineStr">
         <is>
@@ -1975,7 +2171,7 @@
         </is>
       </c>
       <c r="P14" s="17" t="n">
-        <v>0.1</v>
+        <v>11.3</v>
       </c>
       <c r="Q14" s="8" t="n"/>
       <c r="R14" s="8" t="n"/>
@@ -1988,7 +2184,7 @@
         <v>2400</v>
       </c>
       <c r="Y14" s="17" t="n">
-        <v>35.76</v>
+        <v>4040.88</v>
       </c>
       <c r="Z14" s="17" t="n">
         <v>0.149</v>
@@ -2000,13 +2196,13 @@
       </c>
       <c r="AB14" s="8" t="inlineStr">
         <is>
-          <t>4.11.1</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AC14" s="8" t="n"/>
       <c r="AD14" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Cement concrete &gt; M15</t>
+          <t>Concrete &gt; Reinforced cement concrete &gt; M15</t>
         </is>
       </c>
       <c r="AE14" s="8" t="n"/>
@@ -2030,41 +2226,41 @@
       <c r="AW14" s="8" t="n"/>
       <c r="AX14" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Cement concrete — mass 240.0 kg [direct volume] × 0.149 kgCO2e/kg = 35.76 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[OK] material: Reinforced cement concrete — mass 27120.0 kg [direct volume] × 0.149 kgCO2e/kg = 4040.88 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0009</t>
+          <t>GMAP-0012</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C15" s="8" t="n"/>
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Providing and laying damp-proof course 40 mm thick with cement concrete 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 12.5 mm nominal size)</t>
+          <t>Reinforced cement concrete work in shelves upto floor two level excluding the cost of centering and shuttering and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - II, Cement Concrete Work</t>
+          <t>Sub-Head - III, R.C.C. Work</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>Cement concrete</t>
+          <t>Reinforced cement concrete</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
@@ -2093,38 +2289,28 @@
         </is>
       </c>
       <c r="N15" s="17" t="n">
-        <v>14.4</v>
+        <v>1</v>
       </c>
       <c r="O15" s="8" t="inlineStr">
         <is>
-          <t>sqm</t>
-        </is>
-      </c>
-      <c r="P15" s="8" t="n"/>
-      <c r="Q15" s="17" t="n">
-        <v>14.4</v>
-      </c>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P15" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="8" t="n"/>
       <c r="R15" s="8" t="n"/>
       <c r="S15" s="8" t="n"/>
       <c r="T15" s="8" t="n"/>
-      <c r="U15" s="17" t="n">
-        <v>0.576</v>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t>Area x thickness (40.0 mm, from description)</t>
-        </is>
-      </c>
+      <c r="U15" s="8" t="n"/>
+      <c r="V15" s="8" t="n"/>
+      <c r="W15" s="8" t="n"/>
       <c r="X15" s="17" t="n">
         <v>2400</v>
       </c>
       <c r="Y15" s="17" t="n">
-        <v>205.98</v>
+        <v>357.6</v>
       </c>
       <c r="Z15" s="17" t="n">
         <v>0.149</v>
@@ -2136,13 +2322,13 @@
       </c>
       <c r="AB15" s="8" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AC15" s="8" t="n"/>
       <c r="AD15" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Cement concrete &gt; M15</t>
+          <t>Concrete &gt; Reinforced cement concrete &gt; M15</t>
         </is>
       </c>
       <c r="AE15" s="8" t="n"/>
@@ -2158,9 +2344,7 @@
       <c r="AO15" s="8" t="n"/>
       <c r="AP15" s="8" t="n"/>
       <c r="AQ15" s="8" t="n"/>
-      <c r="AR15" s="17" t="n">
-        <v>40</v>
-      </c>
+      <c r="AR15" s="8" t="n"/>
       <c r="AS15" s="8" t="n"/>
       <c r="AT15" s="8" t="n"/>
       <c r="AU15" s="8" t="n"/>
@@ -2168,72 +2352,80 @@
       <c r="AW15" s="8" t="n"/>
       <c r="AX15" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Cement concrete — mass 1382.4 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 205.98 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[OK] material: Reinforced cement concrete — mass 2400.0 kg [direct volume] × 0.149 kgCO2e/kg = 357.6 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0010</t>
+          <t>GMAP-0013</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C16" s="8" t="n"/>
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Applying a coat of residual petroleum bitumen of penetration 80/100 of approved quality using 1.7 Kg. per square metre on damp proof course after cleaning the surface with brushes and finally with a piece of cloth lightly soaked in kerosene oil.</t>
+          <t>Reinforced cement concrete work in chajjas facias and gutters upto floor two level including throating of plastered drip and moulding excluding cost of centring, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - II, Cement Concrete Work</t>
+          <t>Sub-Head - III, R.C.C. Work</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>Bitumen</t>
+          <t>Reinforced cement concrete</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>Residual petroleum bitumen, Kerosene oil</t>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L16" s="8" t="n"/>
-      <c r="M16" s="8" t="n"/>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>1:2:4</t>
+        </is>
+      </c>
       <c r="N16" s="17" t="n">
-        <v>14.4</v>
+        <v>0.6</v>
       </c>
       <c r="O16" s="8" t="inlineStr">
         <is>
-          <t>sqm</t>
-        </is>
-      </c>
-      <c r="P16" s="8" t="n"/>
-      <c r="Q16" s="17" t="n">
-        <v>14.4</v>
-      </c>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P16" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q16" s="8" t="n"/>
       <c r="R16" s="8" t="n"/>
       <c r="S16" s="8" t="n"/>
       <c r="T16" s="8" t="n"/>
@@ -2241,11 +2433,13 @@
       <c r="V16" s="8" t="n"/>
       <c r="W16" s="8" t="n"/>
       <c r="X16" s="17" t="n">
-        <v>1300</v>
-      </c>
-      <c r="Y16" s="8" t="n"/>
+        <v>2400</v>
+      </c>
+      <c r="Y16" s="17" t="n">
+        <v>214.56</v>
+      </c>
       <c r="Z16" s="17" t="n">
-        <v>0.95</v>
+        <v>0.149</v>
       </c>
       <c r="AA16" s="8" t="inlineStr">
         <is>
@@ -2254,13 +2448,13 @@
       </c>
       <c r="AB16" s="8" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AC16" s="8" t="n"/>
       <c r="AD16" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish &gt; Bitumen</t>
+          <t>Concrete &gt; Reinforced cement concrete &gt; M15</t>
         </is>
       </c>
       <c r="AE16" s="8" t="n"/>
@@ -2284,26 +2478,26 @@
       <c r="AW16" s="8" t="n"/>
       <c r="AX16" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Bitumen — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[OK] material: Reinforced cement concrete — mass 1440.0 kg [direct volume] × 0.149 kgCO2e/kg = 214.56 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0011</t>
+          <t>GMAP-0014</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C17" s="8" t="n"/>
       <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Reinforced cement concrete work in suspended floors, roofs, landings and balconies upto floor two level excluding cost of centring, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size)</t>
+          <t>Reinforced cement concrete work in lintels, beams, plinth beams and bressummers upto floor two level excluding the cost of centring, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -2347,7 +2541,7 @@
         </is>
       </c>
       <c r="N17" s="17" t="n">
-        <v>11.3</v>
+        <v>1.7</v>
       </c>
       <c r="O17" s="8" t="inlineStr">
         <is>
@@ -2355,7 +2549,7 @@
         </is>
       </c>
       <c r="P17" s="17" t="n">
-        <v>11.3</v>
+        <v>1.7</v>
       </c>
       <c r="Q17" s="8" t="n"/>
       <c r="R17" s="8" t="n"/>
@@ -2368,7 +2562,7 @@
         <v>2400</v>
       </c>
       <c r="Y17" s="17" t="n">
-        <v>4040.88</v>
+        <v>607.92</v>
       </c>
       <c r="Z17" s="17" t="n">
         <v>0.149</v>
@@ -2380,7 +2574,7 @@
       </c>
       <c r="AB17" s="8" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.6.3</t>
         </is>
       </c>
       <c r="AC17" s="8" t="n"/>
@@ -2410,26 +2604,26 @@
       <c r="AW17" s="8" t="n"/>
       <c r="AX17" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Reinforced cement concrete — mass 27120.0 kg [direct volume] × 0.149 kgCO2e/kg = 4040.88 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[OK] material: Reinforced cement concrete — mass 4080.0 kg [direct volume] × 0.149 kgCO2e/kg = 607.92 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0012</t>
+          <t>GMAP-0015</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C18" s="8" t="n"/>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Reinforced cement concrete work in shelves upto floor two level excluding the cost of centering and shuttering and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
+          <t>Reinforced cement concrete work in columns, pillars, piers, abutments, posts and struts upto floor two level excluding the cost of centring, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -2473,7 +2667,7 @@
         </is>
       </c>
       <c r="N18" s="17" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="O18" s="8" t="inlineStr">
         <is>
@@ -2481,7 +2675,7 @@
         </is>
       </c>
       <c r="P18" s="17" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="Q18" s="8" t="n"/>
       <c r="R18" s="8" t="n"/>
@@ -2494,7 +2688,7 @@
         <v>2400</v>
       </c>
       <c r="Y18" s="17" t="n">
-        <v>357.6</v>
+        <v>35.76</v>
       </c>
       <c r="Z18" s="17" t="n">
         <v>0.149</v>
@@ -2506,7 +2700,7 @@
       </c>
       <c r="AB18" s="8" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.7.3</t>
         </is>
       </c>
       <c r="AC18" s="8" t="n"/>
@@ -2536,26 +2730,26 @@
       <c r="AW18" s="8" t="n"/>
       <c r="AX18" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Reinforced cement concrete — mass 2400.0 kg [direct volume] × 0.149 kgCO2e/kg = 357.6 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[OK] material: Reinforced cement concrete — mass 240.0 kg [direct volume] × 0.149 kgCO2e/kg = 35.76 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0013</t>
+          <t>GMAP-0016</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16a</t>
         </is>
       </c>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Reinforced cement concrete work in chajjas facias and gutters upto floor two level including throating of plastered drip and moulding excluding cost of centring, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Suspended floors,roofs,landings balconies and chajjas.</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -2570,61 +2764,47 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>Reinforced cement concrete</t>
+          <t>Formwork</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Formwork, Timber/Steel</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L19" s="8" t="inlineStr">
-        <is>
-          <t>M15</t>
-        </is>
-      </c>
-      <c r="M19" s="8" t="inlineStr">
-        <is>
-          <t>1:2:4</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
       <c r="N19" s="17" t="n">
-        <v>0.6</v>
+        <v>108</v>
       </c>
       <c r="O19" s="8" t="inlineStr">
         <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="P19" s="17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q19" s="8" t="n"/>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="P19" s="8" t="n"/>
+      <c r="Q19" s="17" t="n">
+        <v>108</v>
+      </c>
       <c r="R19" s="8" t="n"/>
       <c r="S19" s="8" t="n"/>
       <c r="T19" s="8" t="n"/>
       <c r="U19" s="8" t="n"/>
       <c r="V19" s="8" t="n"/>
       <c r="W19" s="8" t="n"/>
-      <c r="X19" s="17" t="n">
-        <v>2400</v>
-      </c>
-      <c r="Y19" s="17" t="n">
-        <v>214.56</v>
-      </c>
-      <c r="Z19" s="17" t="n">
-        <v>0.149</v>
-      </c>
+      <c r="X19" s="8" t="n"/>
+      <c r="Y19" s="8" t="n"/>
+      <c r="Z19" s="8" t="n"/>
       <c r="AA19" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -2632,13 +2812,13 @@
       </c>
       <c r="AB19" s="8" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AC19" s="8" t="n"/>
       <c r="AD19" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Reinforced cement concrete &gt; M15</t>
+          <t>Other &gt; Formwork</t>
         </is>
       </c>
       <c r="AE19" s="8" t="n"/>
@@ -2662,26 +2842,26 @@
       <c r="AW19" s="8" t="n"/>
       <c r="AX19" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Reinforced cement concrete — mass 1440.0 kg [direct volume] × 0.149 kgCO2e/kg = 214.56 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[EXCLUDED] material: Formwork — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0014</t>
+          <t>GMAP-0017</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16b</t>
         </is>
       </c>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Reinforced cement concrete work in lintels, beams, plinth beams and bresummers upto floor two level excluding the cost of centring, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Shelves</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -2696,61 +2876,47 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Reinforced cement concrete</t>
+          <t>Formwork</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Formwork, Timber/Steel</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L20" s="8" t="inlineStr">
-        <is>
-          <t>M15</t>
-        </is>
-      </c>
-      <c r="M20" s="8" t="inlineStr">
-        <is>
-          <t>1:2:4</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
       <c r="N20" s="17" t="n">
-        <v>1.7</v>
+        <v>17</v>
       </c>
       <c r="O20" s="8" t="inlineStr">
         <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="P20" s="17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q20" s="8" t="n"/>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="P20" s="8" t="n"/>
+      <c r="Q20" s="17" t="n">
+        <v>17</v>
+      </c>
       <c r="R20" s="8" t="n"/>
       <c r="S20" s="8" t="n"/>
       <c r="T20" s="8" t="n"/>
       <c r="U20" s="8" t="n"/>
       <c r="V20" s="8" t="n"/>
       <c r="W20" s="8" t="n"/>
-      <c r="X20" s="17" t="n">
-        <v>2400</v>
-      </c>
-      <c r="Y20" s="17" t="n">
-        <v>607.92</v>
-      </c>
-      <c r="Z20" s="17" t="n">
-        <v>0.149</v>
-      </c>
+      <c r="X20" s="8" t="n"/>
+      <c r="Y20" s="8" t="n"/>
+      <c r="Z20" s="8" t="n"/>
       <c r="AA20" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -2758,13 +2924,13 @@
       </c>
       <c r="AB20" s="8" t="inlineStr">
         <is>
-          <t>5.6.3</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AC20" s="8" t="n"/>
       <c r="AD20" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Reinforced cement concrete &gt; M15</t>
+          <t>Other &gt; Formwork</t>
         </is>
       </c>
       <c r="AE20" s="8" t="n"/>
@@ -2788,26 +2954,26 @@
       <c r="AW20" s="8" t="n"/>
       <c r="AX20" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Reinforced cement concrete — mass 4080.0 kg [direct volume] × 0.149 kgCO2e/kg = 607.92 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[EXCLUDED] material: Formwork — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0015</t>
+          <t>GMAP-0018</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16c</t>
         </is>
       </c>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Reinforced cement concrete work in columns, pillars, piers, abutments, posts and struts upto floor two level excluding the cost of centring, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Lintels, beams, plinth beams, girders bressumers and cantilever.</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -2822,61 +2988,47 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Reinforced cement concrete</t>
+          <t>Formwork</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Formwork, Timber/Steel</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t>M15</t>
-        </is>
-      </c>
-      <c r="M21" s="8" t="inlineStr">
-        <is>
-          <t>1:2:4</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="n"/>
+      <c r="M21" s="8" t="n"/>
       <c r="N21" s="17" t="n">
-        <v>0.1</v>
+        <v>19</v>
       </c>
       <c r="O21" s="8" t="inlineStr">
         <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="P21" s="17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q21" s="8" t="n"/>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="P21" s="8" t="n"/>
+      <c r="Q21" s="17" t="n">
+        <v>19</v>
+      </c>
       <c r="R21" s="8" t="n"/>
       <c r="S21" s="8" t="n"/>
       <c r="T21" s="8" t="n"/>
       <c r="U21" s="8" t="n"/>
       <c r="V21" s="8" t="n"/>
       <c r="W21" s="8" t="n"/>
-      <c r="X21" s="17" t="n">
-        <v>2400</v>
-      </c>
-      <c r="Y21" s="17" t="n">
-        <v>35.76</v>
-      </c>
-      <c r="Z21" s="17" t="n">
-        <v>0.149</v>
-      </c>
+      <c r="X21" s="8" t="n"/>
+      <c r="Y21" s="8" t="n"/>
+      <c r="Z21" s="8" t="n"/>
       <c r="AA21" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -2884,13 +3036,13 @@
       </c>
       <c r="AB21" s="8" t="inlineStr">
         <is>
-          <t>5.7.3</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AC21" s="8" t="n"/>
       <c r="AD21" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Reinforced cement concrete &gt; M15</t>
+          <t>Other &gt; Formwork</t>
         </is>
       </c>
       <c r="AE21" s="8" t="n"/>
@@ -2914,26 +3066,26 @@
       <c r="AW21" s="8" t="n"/>
       <c r="AX21" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Reinforced cement concrete — mass 240.0 kg [direct volume] × 0.149 kgCO2e/kg = 35.76 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[EXCLUDED] material: Formwork — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0016</t>
+          <t>GMAP-0019</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>16a</t>
+          <t>16d</t>
         </is>
       </c>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : i) Suspended floors, roofs, landings balconies and chajjas.</t>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Columns, pillars, posts and struts.</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -2953,7 +3105,7 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>Timber, Steel</t>
+          <t>Formwork, Timber/Steel</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -2969,7 +3121,7 @@
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
       <c r="N22" s="17" t="n">
-        <v>108</v>
+        <v>2</v>
       </c>
       <c r="O22" s="8" t="inlineStr">
         <is>
@@ -2978,7 +3130,7 @@
       </c>
       <c r="P22" s="8" t="n"/>
       <c r="Q22" s="17" t="n">
-        <v>108</v>
+        <v>2</v>
       </c>
       <c r="R22" s="8" t="n"/>
       <c r="S22" s="8" t="n"/>
@@ -3033,19 +3185,19 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0017</t>
+          <t>GMAP-0020</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>16b</t>
+          <t>16e</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : ii) Shelves</t>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Vertical and horizontal fins individually or forming box louvers hand and facias.</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -3065,7 +3217,7 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>Timber, Steel</t>
+          <t>Formwork, Timber/Steel</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
@@ -3081,7 +3233,7 @@
       <c r="L23" s="8" t="n"/>
       <c r="M23" s="8" t="n"/>
       <c r="N23" s="17" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="O23" s="8" t="inlineStr">
         <is>
@@ -3090,7 +3242,7 @@
       </c>
       <c r="P23" s="8" t="n"/>
       <c r="Q23" s="17" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="R23" s="8" t="n"/>
       <c r="S23" s="8" t="n"/>
@@ -3145,19 +3297,19 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0018</t>
+          <t>GMAP-0021</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>16c</t>
+          <t>17a</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : iii) Lintels, beams, plinth beams, girders bressumers and cantilever.</t>
+          <t>Reinforcement for RCC work including bending binding and placing in position complete. Mild steel and medium tensile steel bars.</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -3172,47 +3324,53 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Formwork</t>
+          <t>Mild steel bars</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>Timber, Steel</t>
+          <t>Mild steel, Medium tensile steel</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
       <c r="N24" s="17" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="O24" s="8" t="inlineStr">
         <is>
-          <t>sqm</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="P24" s="8" t="n"/>
-      <c r="Q24" s="17" t="n">
-        <v>19</v>
-      </c>
+      <c r="Q24" s="8" t="n"/>
       <c r="R24" s="8" t="n"/>
-      <c r="S24" s="8" t="n"/>
+      <c r="S24" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="T24" s="8" t="n"/>
       <c r="U24" s="8" t="n"/>
       <c r="V24" s="8" t="n"/>
       <c r="W24" s="8" t="n"/>
-      <c r="X24" s="8" t="n"/>
-      <c r="Y24" s="8" t="n"/>
-      <c r="Z24" s="8" t="n"/>
+      <c r="X24" s="17" t="n">
+        <v>7850</v>
+      </c>
+      <c r="Y24" s="17" t="n">
+        <v>155</v>
+      </c>
+      <c r="Z24" s="17" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA24" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -3220,13 +3378,13 @@
       </c>
       <c r="AB24" s="8" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AC24" s="8" t="n"/>
       <c r="AD24" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Formwork</t>
+          <t>Steel &gt; Mild steel bars</t>
         </is>
       </c>
       <c r="AE24" s="8" t="n"/>
@@ -3250,26 +3408,26 @@
       <c r="AW24" s="8" t="n"/>
       <c r="AX24" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Formwork — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[OK] material: Mild steel bars — mass 100.0 kg [direct weight] × 1.55 kgCO2e/kg = 155.0 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0019</t>
+          <t>GMAP-0022</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>16d</t>
+          <t>17b</t>
         </is>
       </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : iv) Columns, pillars, posts and struts.</t>
+          <t>Reinforcement for RCC work including bending binding and placing in position complete. Cold twisted bars</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -3284,47 +3442,53 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>Formwork</t>
+          <t>Cold twisted bars</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>Timber, Steel</t>
+          <t>Cold twisted steel bars</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L25" s="8" t="n"/>
       <c r="M25" s="8" t="n"/>
       <c r="N25" s="17" t="n">
-        <v>2</v>
+        <v>1375</v>
       </c>
       <c r="O25" s="8" t="inlineStr">
         <is>
-          <t>sqm</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="P25" s="8" t="n"/>
-      <c r="Q25" s="17" t="n">
-        <v>2</v>
-      </c>
+      <c r="Q25" s="8" t="n"/>
       <c r="R25" s="8" t="n"/>
-      <c r="S25" s="8" t="n"/>
+      <c r="S25" s="17" t="n">
+        <v>1375</v>
+      </c>
       <c r="T25" s="8" t="n"/>
       <c r="U25" s="8" t="n"/>
       <c r="V25" s="8" t="n"/>
       <c r="W25" s="8" t="n"/>
-      <c r="X25" s="8" t="n"/>
-      <c r="Y25" s="8" t="n"/>
-      <c r="Z25" s="8" t="n"/>
+      <c r="X25" s="17" t="n">
+        <v>7850</v>
+      </c>
+      <c r="Y25" s="17" t="n">
+        <v>2131.25</v>
+      </c>
+      <c r="Z25" s="17" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA25" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -3332,13 +3496,13 @@
       </c>
       <c r="AB25" s="8" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AC25" s="8" t="n"/>
       <c r="AD25" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Formwork</t>
+          <t>Steel &gt; Cold twisted bars</t>
         </is>
       </c>
       <c r="AE25" s="8" t="n"/>
@@ -3362,26 +3526,26 @@
       <c r="AW25" s="8" t="n"/>
       <c r="AX25" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Formwork — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[OK] material: Cold twisted bars — mass 1375.0 kg [direct weight] × 1.55 kgCO2e/kg = 2131.25 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0020</t>
+          <t>GMAP-0023</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>16e</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : v) Vertical and horizontal fins individually or forming box louvers hand and facias.</t>
+          <t>Providing and laying upto floor two level RCC in string courses, bands, copings, bed plates, anchor blocks, plain window sills and the like excluding the cost of centering, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2, coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -3396,47 +3560,61 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Formwork</t>
+          <t>Reinforced cement concrete</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>Timber, Steel</t>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="n"/>
-      <c r="M26" s="8" t="n"/>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>1:2:4</t>
+        </is>
+      </c>
       <c r="N26" s="17" t="n">
-        <v>9</v>
+        <v>0.8</v>
       </c>
       <c r="O26" s="8" t="inlineStr">
         <is>
-          <t>sqm</t>
-        </is>
-      </c>
-      <c r="P26" s="8" t="n"/>
-      <c r="Q26" s="17" t="n">
-        <v>9</v>
-      </c>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P26" s="17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q26" s="8" t="n"/>
       <c r="R26" s="8" t="n"/>
       <c r="S26" s="8" t="n"/>
       <c r="T26" s="8" t="n"/>
       <c r="U26" s="8" t="n"/>
       <c r="V26" s="8" t="n"/>
       <c r="W26" s="8" t="n"/>
-      <c r="X26" s="8" t="n"/>
-      <c r="Y26" s="8" t="n"/>
-      <c r="Z26" s="8" t="n"/>
+      <c r="X26" s="17" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Y26" s="17" t="n">
+        <v>286.08</v>
+      </c>
+      <c r="Z26" s="17" t="n">
+        <v>0.149</v>
+      </c>
       <c r="AA26" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -3444,13 +3622,13 @@
       </c>
       <c r="AB26" s="8" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="AC26" s="8" t="n"/>
       <c r="AD26" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Formwork</t>
+          <t>Concrete &gt; Reinforced cement concrete &gt; M15</t>
         </is>
       </c>
       <c r="AE26" s="8" t="n"/>
@@ -3474,51 +3652,51 @@
       <c r="AW26" s="8" t="n"/>
       <c r="AX26" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Formwork — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[OK] material: Reinforced cement concrete — mass 1920.0 kg [direct volume] × 0.149 kgCO2e/kg = 286.08 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0021</t>
+          <t>GMAP-0024</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>17a</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Reinforcement for RCC work including bending binding and placing in position complete. i) Mild steel and medium tensile steel bars.</t>
+          <t>Brick work with bricks of class designation _____ in foundation and plinth in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - III, R.C.C. Work</t>
+          <t>Sub-Head - IV, Brick Work</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Civil &amp; Sitework</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>Steel reinforcement</t>
+          <t>Bricks</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>Mild steel, Medium tensile steel</t>
+          <t>Bricks, Cement, Coarse sand</t>
         </is>
       </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Masonry</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
@@ -3527,33 +3705,37 @@
         </is>
       </c>
       <c r="L27" s="8" t="n"/>
-      <c r="M27" s="8" t="n"/>
+      <c r="M27" s="8" t="inlineStr">
+        <is>
+          <t>1:6</t>
+        </is>
+      </c>
       <c r="N27" s="17" t="n">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="O27" s="8" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="P27" s="8" t="n"/>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P27" s="17" t="n">
+        <v>17</v>
+      </c>
       <c r="Q27" s="8" t="n"/>
       <c r="R27" s="8" t="n"/>
-      <c r="S27" s="17" t="n">
-        <v>100</v>
-      </c>
+      <c r="S27" s="8" t="n"/>
       <c r="T27" s="8" t="n"/>
       <c r="U27" s="8" t="n"/>
       <c r="V27" s="8" t="n"/>
       <c r="W27" s="8" t="n"/>
       <c r="X27" s="17" t="n">
-        <v>7850</v>
+        <v>1800</v>
       </c>
       <c r="Y27" s="17" t="n">
-        <v>155</v>
+        <v>6517.8</v>
       </c>
       <c r="Z27" s="17" t="n">
-        <v>1.55</v>
+        <v>0.213</v>
       </c>
       <c r="AA27" s="8" t="inlineStr">
         <is>
@@ -3562,13 +3744,13 @@
       </c>
       <c r="AB27" s="8" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>6.1.14/6.5.1</t>
         </is>
       </c>
       <c r="AC27" s="8" t="n"/>
       <c r="AD27" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Steel reinforcement</t>
+          <t>Masonry &gt; Bricks &gt; 1:6</t>
         </is>
       </c>
       <c r="AE27" s="8" t="n"/>
@@ -3592,51 +3774,51 @@
       <c r="AW27" s="8" t="n"/>
       <c r="AX27" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Steel reinforcement — mass 100.0 kg [direct weight] × 1.55 kgCO2e/kg = 155.0 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[OK] material: Bricks — mass 30600.0 kg [direct volume] × 0.213 kgCO2e/kg = 6517.8 kgCO2e — ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0022</t>
+          <t>GMAP-0025</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>17b</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Reinforcement for RCC work including bending binding and placing in position complete. ii) Cold twisted bars</t>
+          <t>Brick work with bricks of class designation _____ in super structure above plinth upto floor two level in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - III, R.C.C. Work</t>
+          <t>Sub-Head - IV, Brick Work</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Civil &amp; Sitework</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>Cold twisted steel bars</t>
+          <t>Bricks</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>Cold twisted steel</t>
+          <t>Bricks, Cement, Coarse sand</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Masonry</t>
         </is>
       </c>
       <c r="K28" s="8" t="inlineStr">
@@ -3645,33 +3827,37 @@
         </is>
       </c>
       <c r="L28" s="8" t="n"/>
-      <c r="M28" s="8" t="n"/>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>1:6</t>
+        </is>
+      </c>
       <c r="N28" s="17" t="n">
-        <v>1375</v>
+        <v>40.3</v>
       </c>
       <c r="O28" s="8" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="P28" s="8" t="n"/>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P28" s="17" t="n">
+        <v>40.3</v>
+      </c>
       <c r="Q28" s="8" t="n"/>
       <c r="R28" s="8" t="n"/>
-      <c r="S28" s="17" t="n">
-        <v>1375</v>
-      </c>
+      <c r="S28" s="8" t="n"/>
       <c r="T28" s="8" t="n"/>
       <c r="U28" s="8" t="n"/>
       <c r="V28" s="8" t="n"/>
       <c r="W28" s="8" t="n"/>
       <c r="X28" s="17" t="n">
-        <v>7850</v>
+        <v>1800</v>
       </c>
       <c r="Y28" s="17" t="n">
-        <v>2131.25</v>
+        <v>15451.02</v>
       </c>
       <c r="Z28" s="17" t="n">
-        <v>1.55</v>
+        <v>0.213</v>
       </c>
       <c r="AA28" s="8" t="inlineStr">
         <is>
@@ -3680,13 +3866,13 @@
       </c>
       <c r="AB28" s="8" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>6.1.14/6.3</t>
         </is>
       </c>
       <c r="AC28" s="8" t="n"/>
       <c r="AD28" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Cold twisted steel bars</t>
+          <t>Masonry &gt; Bricks &gt; 1:6</t>
         </is>
       </c>
       <c r="AE28" s="8" t="n"/>
@@ -3710,51 +3896,51 @@
       <c r="AW28" s="8" t="n"/>
       <c r="AX28" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Cold twisted steel bars — mass 1375.0 kg [direct weight] × 1.55 kgCO2e/kg = 2131.25 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[OK] material: Bricks — mass 72540.0 kg [direct volume] × 0.213 kgCO2e/kg = 15451.02 kgCO2e — ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0023</t>
+          <t>GMAP-0026</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C29" s="8" t="n"/>
       <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Providing and laying upto floor two level RCC in string courses, bands, copings, bed plates, anchor blocks, plain window sills and the like excluding the cost of centering, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
+          <t>Brick work 7 cm thick with bricks of class designation ______ in super structure upto floor two level in cement mortar 1:3 (1 cement : 3 coarse sand).</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - III, R.C.C. Work</t>
+          <t>Sub-Head - IV, Brick Work</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Civil &amp; Sitework</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>Reinforced cement concrete</t>
+          <t>Bricks</t>
         </is>
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Bricks, Cement, Coarse sand</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>Masonry</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
@@ -3762,42 +3948,48 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="L29" s="8" t="inlineStr">
-        <is>
-          <t>M15</t>
-        </is>
-      </c>
+      <c r="L29" s="8" t="n"/>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t>1:2:4</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="N29" s="17" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O29" s="8" t="inlineStr">
         <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="P29" s="17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q29" s="8" t="n"/>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="P29" s="8" t="n"/>
+      <c r="Q29" s="17" t="n">
+        <v>0.9</v>
+      </c>
       <c r="R29" s="8" t="n"/>
       <c r="S29" s="8" t="n"/>
       <c r="T29" s="8" t="n"/>
-      <c r="U29" s="8" t="n"/>
-      <c r="V29" s="8" t="n"/>
-      <c r="W29" s="8" t="n"/>
+      <c r="U29" s="17" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W29" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (70.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X29" s="17" t="n">
-        <v>2400</v>
+        <v>1800</v>
       </c>
       <c r="Y29" s="17" t="n">
-        <v>286.08</v>
+        <v>24.15</v>
       </c>
       <c r="Z29" s="17" t="n">
-        <v>0.149</v>
+        <v>0.213</v>
       </c>
       <c r="AA29" s="8" t="inlineStr">
         <is>
@@ -3806,13 +3998,13 @@
       </c>
       <c r="AB29" s="8" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>6.13/6.21</t>
         </is>
       </c>
       <c r="AC29" s="8" t="n"/>
       <c r="AD29" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Reinforced cement concrete &gt; M15</t>
+          <t>Masonry &gt; Bricks &gt; 1:3</t>
         </is>
       </c>
       <c r="AE29" s="8" t="n"/>
@@ -3828,7 +4020,9 @@
       <c r="AO29" s="8" t="n"/>
       <c r="AP29" s="8" t="n"/>
       <c r="AQ29" s="8" t="n"/>
-      <c r="AR29" s="8" t="n"/>
+      <c r="AR29" s="17" t="n">
+        <v>70</v>
+      </c>
       <c r="AS29" s="8" t="n"/>
       <c r="AT29" s="8" t="n"/>
       <c r="AU29" s="8" t="n"/>
@@ -3836,26 +4030,26 @@
       <c r="AW29" s="8" t="n"/>
       <c r="AX29" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Reinforced cement concrete — mass 1920.0 kg [direct volume] × 0.149 kgCO2e/kg = 286.08 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[OK] material: Bricks — mass 113.4 kg [area × thickness (derived)] × 0.213 kgCO2e/kg = 24.15 kgCO2e — ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0024</t>
+          <t>GMAP-0027</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C30" s="8" t="n"/>
       <c r="D30" s="8" t="n"/>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Brick work with bricks of class designation _____ in foundation and plinth in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
+          <t>Half brick masonry with bricks of class designation _____ in foundation &amp; plinth in cement mortar 1:4 (1 cement : 4 coarse sand)</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -3870,7 +4064,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Bricks</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
@@ -3885,27 +4079,27 @@
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L30" s="8" t="n"/>
       <c r="M30" s="8" t="inlineStr">
         <is>
-          <t>1:6</t>
+          <t>1:4</t>
         </is>
       </c>
       <c r="N30" s="17" t="n">
-        <v>17</v>
+        <v>4.8</v>
       </c>
       <c r="O30" s="8" t="inlineStr">
         <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="P30" s="17" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q30" s="8" t="n"/>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="P30" s="8" t="n"/>
+      <c r="Q30" s="17" t="n">
+        <v>4.8</v>
+      </c>
       <c r="R30" s="8" t="n"/>
       <c r="S30" s="8" t="n"/>
       <c r="T30" s="8" t="n"/>
@@ -3915,9 +4109,7 @@
       <c r="X30" s="17" t="n">
         <v>1800</v>
       </c>
-      <c r="Y30" s="17" t="n">
-        <v>6517.8</v>
-      </c>
+      <c r="Y30" s="8" t="n"/>
       <c r="Z30" s="17" t="n">
         <v>0.213</v>
       </c>
@@ -3928,13 +4120,13 @@
       </c>
       <c r="AB30" s="8" t="inlineStr">
         <is>
-          <t>6.1.14/6.5.1/6.5.2</t>
+          <t>6.18.4/6.21</t>
         </is>
       </c>
       <c r="AC30" s="8" t="n"/>
       <c r="AD30" s="8" t="inlineStr">
         <is>
-          <t>Masonry &gt; Brick &gt; 1:6</t>
+          <t>Masonry &gt; Bricks &gt; 1:4</t>
         </is>
       </c>
       <c r="AE30" s="8" t="n"/>
@@ -3958,26 +4150,26 @@
       <c r="AW30" s="8" t="n"/>
       <c r="AX30" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Brick — mass 30600.0 kg [direct volume] × 0.213 kgCO2e/kg = 6517.8 kgCO2e — ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
+          <t>[EXCLUDED] material: Bricks — category 'Masonry' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0025</t>
+          <t>GMAP-0028</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>
       <c r="D31" s="8" t="n"/>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Brick work with bricks of class designation _____ in super structure above plinth upto floor two level in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
+          <t>Half brick masonry with bricks of class designation _____ in super structure upto floor two level in cement mortar 1:4 (1 cement : 4 coarse sand).</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -3992,7 +4184,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Bricks</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
@@ -4007,27 +4199,27 @@
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L31" s="8" t="n"/>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>1:6</t>
+          <t>1:4</t>
         </is>
       </c>
       <c r="N31" s="17" t="n">
-        <v>40.3</v>
+        <v>18</v>
       </c>
       <c r="O31" s="8" t="inlineStr">
         <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="P31" s="17" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="Q31" s="8" t="n"/>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="P31" s="8" t="n"/>
+      <c r="Q31" s="17" t="n">
+        <v>18</v>
+      </c>
       <c r="R31" s="8" t="n"/>
       <c r="S31" s="8" t="n"/>
       <c r="T31" s="8" t="n"/>
@@ -4037,9 +4229,7 @@
       <c r="X31" s="17" t="n">
         <v>1800</v>
       </c>
-      <c r="Y31" s="17" t="n">
-        <v>15451.02</v>
-      </c>
+      <c r="Y31" s="8" t="n"/>
       <c r="Z31" s="17" t="n">
         <v>0.213</v>
       </c>
@@ -4050,13 +4240,13 @@
       </c>
       <c r="AB31" s="8" t="inlineStr">
         <is>
-          <t>6.1.14/6.3/6.5.1/6.5.2</t>
+          <t>6.18.4/6.19.1</t>
         </is>
       </c>
       <c r="AC31" s="8" t="n"/>
       <c r="AD31" s="8" t="inlineStr">
         <is>
-          <t>Masonry &gt; Brick &gt; 1:6</t>
+          <t>Masonry &gt; Bricks &gt; 1:4</t>
         </is>
       </c>
       <c r="AE31" s="8" t="n"/>
@@ -4080,115 +4270,97 @@
       <c r="AW31" s="8" t="n"/>
       <c r="AX31" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Brick — mass 72540.0 kg [direct volume] × 0.213 kgCO2e/kg = 15451.02 kgCO2e — ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
+          <t>[EXCLUDED] material: Bricks — category 'Masonry' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0026</t>
+          <t>GMAP-0029</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Brick work 7 cm thick with bricks of class designation _____ in super structure upto floor two level in cement mortar 1:3 (1 cement : 3 coarse sand).</t>
+          <t>Providing wood work in frames of doors, windows, clerestory windows and other frames, wrought framed and fixed in position.</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - IV, Brick Work</t>
+          <t>Sub-Head - V, Wood Work</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Finishes</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>Bricks, Cement, Coarse sand</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>Masonry</t>
+          <t>Timber</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L32" s="8" t="n"/>
-      <c r="M32" s="8" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
+      <c r="M32" s="8" t="n"/>
       <c r="N32" s="17" t="n">
-        <v>0.9</v>
+        <v>0.035</v>
       </c>
       <c r="O32" s="8" t="inlineStr">
         <is>
-          <t>sqm</t>
-        </is>
-      </c>
-      <c r="P32" s="8" t="n"/>
-      <c r="Q32" s="17" t="n">
-        <v>0.9</v>
-      </c>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="P32" s="17" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Q32" s="8" t="n"/>
       <c r="R32" s="8" t="n"/>
       <c r="S32" s="8" t="n"/>
       <c r="T32" s="8" t="n"/>
-      <c r="U32" s="17" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="W32" s="8" t="inlineStr">
-        <is>
-          <t>Area x thickness (70.0 mm, from description)</t>
-        </is>
-      </c>
+      <c r="U32" s="8" t="n"/>
+      <c r="V32" s="8" t="n"/>
+      <c r="W32" s="8" t="n"/>
       <c r="X32" s="17" t="n">
-        <v>1800</v>
+        <v>750</v>
       </c>
       <c r="Y32" s="17" t="n">
-        <v>24.15</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Z32" s="17" t="n">
-        <v>0.213</v>
+        <v>0.306</v>
       </c>
       <c r="AA32" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
         </is>
       </c>
-      <c r="AB32" s="8" t="inlineStr">
-        <is>
-          <t>6.13/6.21/6.5.1/6.5.2</t>
-        </is>
-      </c>
+      <c r="AB32" s="8" t="n"/>
       <c r="AC32" s="8" t="n"/>
       <c r="AD32" s="8" t="inlineStr">
         <is>
-          <t>Masonry &gt; Brick &gt; 1:3</t>
+          <t>Timber &gt; Wood</t>
         </is>
       </c>
       <c r="AE32" s="8" t="n"/>
@@ -4204,9 +4376,7 @@
       <c r="AO32" s="8" t="n"/>
       <c r="AP32" s="8" t="n"/>
       <c r="AQ32" s="8" t="n"/>
-      <c r="AR32" s="17" t="n">
-        <v>70</v>
-      </c>
+      <c r="AR32" s="8" t="n"/>
       <c r="AS32" s="8" t="n"/>
       <c r="AT32" s="8" t="n"/>
       <c r="AU32" s="8" t="n"/>
@@ -4214,66 +4384,62 @@
       <c r="AW32" s="8" t="n"/>
       <c r="AX32" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Brick — mass 113.4 kg [area × thickness (derived)] × 0.213 kgCO2e/kg = 24.15 kgCO2e — ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
+          <t>[OK] material: Wood — mass 26.25 kg [direct volume] × 0.306 kgCO2e/kg = 8.03 kgCO2e — ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0027</t>
+          <t>GMAP-0030</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C33" s="8" t="n"/>
       <c r="D33" s="8" t="n"/>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Half brick masonry with bricks of class designation _____ in foundation &amp; plinth in cement mortar 1:4 (1 cement : 4 coarse sand)</t>
+          <t>Providing and fixing 35 mm thick battended and framed door shutters of wood including bright finished or/and black enamelled MS butt hinges with necessary screws.</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - IV, Brick Work</t>
+          <t>Sub-Head - V, Wood Work</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Finishes</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Wood shutter</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>Bricks, Cement, Coarse sand</t>
+          <t>Wood, MS butt hinges</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>Masonry</t>
+          <t>Timber</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L33" s="8" t="n"/>
-      <c r="M33" s="8" t="inlineStr">
-        <is>
-          <t>1:4</t>
-        </is>
-      </c>
+      <c r="M33" s="8" t="n"/>
       <c r="N33" s="17" t="n">
-        <v>4.8</v>
+        <v>18</v>
       </c>
       <c r="O33" s="8" t="inlineStr">
         <is>
@@ -4282,20 +4448,32 @@
       </c>
       <c r="P33" s="8" t="n"/>
       <c r="Q33" s="17" t="n">
-        <v>4.8</v>
+        <v>18</v>
       </c>
       <c r="R33" s="8" t="n"/>
       <c r="S33" s="8" t="n"/>
       <c r="T33" s="8" t="n"/>
-      <c r="U33" s="8" t="n"/>
-      <c r="V33" s="8" t="n"/>
-      <c r="W33" s="8" t="n"/>
+      <c r="U33" s="17" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W33" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (35.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X33" s="17" t="n">
-        <v>1800</v>
-      </c>
-      <c r="Y33" s="8" t="n"/>
+        <v>750</v>
+      </c>
+      <c r="Y33" s="17" t="n">
+        <v>144.59</v>
+      </c>
       <c r="Z33" s="17" t="n">
-        <v>0.213</v>
+        <v>0.306</v>
       </c>
       <c r="AA33" s="8" t="inlineStr">
         <is>
@@ -4304,13 +4482,13 @@
       </c>
       <c r="AB33" s="8" t="inlineStr">
         <is>
-          <t>6.18.4/6.21/6.5.1/6.5.2</t>
+          <t>9.26.4</t>
         </is>
       </c>
       <c r="AC33" s="8" t="n"/>
       <c r="AD33" s="8" t="inlineStr">
         <is>
-          <t>Masonry &gt; Brick &gt; 1:4</t>
+          <t>Timber &gt; Wood shutter</t>
         </is>
       </c>
       <c r="AE33" s="8" t="n"/>
@@ -4326,7 +4504,9 @@
       <c r="AO33" s="8" t="n"/>
       <c r="AP33" s="8" t="n"/>
       <c r="AQ33" s="8" t="n"/>
-      <c r="AR33" s="8" t="n"/>
+      <c r="AR33" s="17" t="n">
+        <v>35</v>
+      </c>
       <c r="AS33" s="8" t="n"/>
       <c r="AT33" s="8" t="n"/>
       <c r="AU33" s="8" t="n"/>
@@ -4334,66 +4514,62 @@
       <c r="AW33" s="8" t="n"/>
       <c r="AX33" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Brick — category 'Masonry' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[OK] material: Wood shutter — mass 472.5 kg [area × thickness (derived)] × 0.306 kgCO2e/kg = 144.59 kgCO2e — ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0028</t>
+          <t>GMAP-0031</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="n"/>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Half brick masonry with bricks of class designation _____ in super structure upto floor two level in cement mortar 1:4 (1 cement : 4 coarse sand).</t>
+          <t>Providing and fixing 25 mm thick flush door (for cupboard) shutters core of block board construction with frame of Ist class hard wood and well matched Ist class teak ply veneering with vertical grains or cross bands and face veneer on one face and commercial ply veneering with vertical grains or cross bands and face veneer on other face of shutters, including nickel plated bright finished MS piano hinges with necessary screws.</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - IV, Brick Work</t>
+          <t>Sub-Head - V, Wood Work</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Finishes</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Flush door shutter</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>Bricks, Cement, Coarse sand</t>
+          <t>Block board, Hard wood, Teak ply veneer, Commercial ply, MS piano hinges</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>Masonry</t>
+          <t>Timber</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L34" s="8" t="n"/>
-      <c r="M34" s="8" t="inlineStr">
-        <is>
-          <t>1:4</t>
-        </is>
-      </c>
+      <c r="M34" s="8" t="n"/>
       <c r="N34" s="17" t="n">
-        <v>18</v>
+        <v>4.7</v>
       </c>
       <c r="O34" s="8" t="inlineStr">
         <is>
@@ -4402,35 +4578,43 @@
       </c>
       <c r="P34" s="8" t="n"/>
       <c r="Q34" s="17" t="n">
-        <v>18</v>
+        <v>4.7</v>
       </c>
       <c r="R34" s="8" t="n"/>
       <c r="S34" s="8" t="n"/>
       <c r="T34" s="8" t="n"/>
-      <c r="U34" s="8" t="n"/>
-      <c r="V34" s="8" t="n"/>
-      <c r="W34" s="8" t="n"/>
+      <c r="U34" s="17" t="n">
+        <v>0.1175</v>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W34" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (25.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X34" s="17" t="n">
-        <v>1800</v>
-      </c>
-      <c r="Y34" s="8" t="n"/>
+        <v>750</v>
+      </c>
+      <c r="Y34" s="17" t="n">
+        <v>26.97</v>
+      </c>
       <c r="Z34" s="17" t="n">
-        <v>0.213</v>
+        <v>0.306</v>
       </c>
       <c r="AA34" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
         </is>
       </c>
-      <c r="AB34" s="8" t="inlineStr">
-        <is>
-          <t>6.18.4/6.19.1/6.20/6.21.1/6.21.2</t>
-        </is>
-      </c>
+      <c r="AB34" s="8" t="n"/>
       <c r="AC34" s="8" t="n"/>
       <c r="AD34" s="8" t="inlineStr">
         <is>
-          <t>Masonry &gt; Brick &gt; 1:4</t>
+          <t>Timber &gt; Flush door shutter</t>
         </is>
       </c>
       <c r="AE34" s="8" t="n"/>
@@ -4446,7 +4630,9 @@
       <c r="AO34" s="8" t="n"/>
       <c r="AP34" s="8" t="n"/>
       <c r="AQ34" s="8" t="n"/>
-      <c r="AR34" s="8" t="n"/>
+      <c r="AR34" s="17" t="n">
+        <v>25</v>
+      </c>
       <c r="AS34" s="8" t="n"/>
       <c r="AT34" s="8" t="n"/>
       <c r="AU34" s="8" t="n"/>
@@ -4454,26 +4640,26 @@
       <c r="AW34" s="8" t="n"/>
       <c r="AX34" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Brick — category 'Masonry' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[OK] material: Flush door shutter — mass 88.12 kg [area × thickness (derived)] × 0.306 kgCO2e/kg = 26.97 kgCO2e — ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0029</t>
+          <t>GMAP-0032</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Providing wood work in frames of doors, windows, clerestory windows and other frames, wrought framed and fixed in position.</t>
+          <t>Providing 50x50x50 mm 2nd class Teak wood plugs including cutting brick work and fixing in cement mortar 1:3 (1 cement :3 fine sand) and making good the walls etc.</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -4483,17 +4669,17 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>Finishes</t>
+          <t>Civil &amp; Sitework</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Teak wood plugs</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Teak wood, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J35" s="8" t="inlineStr">
@@ -4503,35 +4689,37 @@
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L35" s="8" t="n"/>
-      <c r="M35" s="8" t="n"/>
+      <c r="M35" s="8" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
       <c r="N35" s="17" t="n">
-        <v>0.035</v>
+        <v>20</v>
       </c>
       <c r="O35" s="8" t="inlineStr">
         <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="P35" s="17" t="n">
-        <v>0.035</v>
-      </c>
+          <t>nos</t>
+        </is>
+      </c>
+      <c r="P35" s="8" t="n"/>
       <c r="Q35" s="8" t="n"/>
       <c r="R35" s="8" t="n"/>
       <c r="S35" s="8" t="n"/>
-      <c r="T35" s="8" t="n"/>
+      <c r="T35" s="17" t="n">
+        <v>20</v>
+      </c>
       <c r="U35" s="8" t="n"/>
       <c r="V35" s="8" t="n"/>
       <c r="W35" s="8" t="n"/>
       <c r="X35" s="17" t="n">
         <v>750</v>
       </c>
-      <c r="Y35" s="17" t="n">
-        <v>8.029999999999999</v>
-      </c>
+      <c r="Y35" s="8" t="n"/>
       <c r="Z35" s="17" t="n">
         <v>0.306</v>
       </c>
@@ -4540,11 +4728,15 @@
           <t>DSR 1989</t>
         </is>
       </c>
-      <c r="AB35" s="8" t="n"/>
+      <c r="AB35" s="8" t="inlineStr">
+        <is>
+          <t>9.51</t>
+        </is>
+      </c>
       <c r="AC35" s="8" t="n"/>
       <c r="AD35" s="8" t="inlineStr">
         <is>
-          <t>Timber &gt; Wood</t>
+          <t>Timber &gt; Teak wood plugs &gt; 1:3</t>
         </is>
       </c>
       <c r="AE35" s="8" t="n"/>
@@ -4557,9 +4749,15 @@
       <c r="AL35" s="8" t="n"/>
       <c r="AM35" s="8" t="n"/>
       <c r="AN35" s="8" t="n"/>
-      <c r="AO35" s="8" t="n"/>
-      <c r="AP35" s="8" t="n"/>
-      <c r="AQ35" s="8" t="n"/>
+      <c r="AO35" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP35" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AQ35" s="17" t="n">
+        <v>50</v>
+      </c>
       <c r="AR35" s="8" t="n"/>
       <c r="AS35" s="8" t="n"/>
       <c r="AT35" s="8" t="n"/>
@@ -4568,31 +4766,31 @@
       <c r="AW35" s="8" t="n"/>
       <c r="AX35" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Wood — mass 26.25 kg [direct volume] × 0.306 kgCO2e/kg = 8.03 kgCO2e — ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
+          <t>[EXCLUDED] material: Teak wood plugs — category 'Timber' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0030</t>
+          <t>GMAP-0033</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing 35 mm thick battended and framed door shutters of wood including bright finished or/and black enamelled MS butt hinges with necessary screws.</t>
+          <t>Providing and fixing M.S.oxidised fan light vantilator catch with necessary screws etc. complete.</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - V, Wood Work</t>
+          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
@@ -4602,77 +4800,61 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>M.S. oxidised fan light ventilator catch</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>Wood, MS butt hinges</t>
+          <t>Mild steel</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>Timber</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L36" s="8" t="n"/>
       <c r="M36" s="8" t="n"/>
       <c r="N36" s="17" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="O36" s="8" t="inlineStr">
         <is>
-          <t>sqm</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P36" s="8" t="n"/>
-      <c r="Q36" s="17" t="n">
-        <v>18</v>
-      </c>
+      <c r="Q36" s="8" t="n"/>
       <c r="R36" s="8" t="n"/>
       <c r="S36" s="8" t="n"/>
-      <c r="T36" s="8" t="n"/>
-      <c r="U36" s="17" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="W36" s="8" t="inlineStr">
-        <is>
-          <t>Area x thickness (35.0 mm, from description)</t>
-        </is>
-      </c>
+      <c r="T36" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="U36" s="8" t="n"/>
+      <c r="V36" s="8" t="n"/>
+      <c r="W36" s="8" t="n"/>
       <c r="X36" s="17" t="n">
-        <v>750</v>
-      </c>
-      <c r="Y36" s="17" t="n">
-        <v>144.59</v>
-      </c>
+        <v>7850</v>
+      </c>
+      <c r="Y36" s="8" t="n"/>
       <c r="Z36" s="17" t="n">
-        <v>0.306</v>
+        <v>1.55</v>
       </c>
       <c r="AA36" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
         </is>
       </c>
-      <c r="AB36" s="8" t="inlineStr">
-        <is>
-          <t>9.26.4</t>
-        </is>
-      </c>
+      <c r="AB36" s="8" t="n"/>
       <c r="AC36" s="8" t="n"/>
       <c r="AD36" s="8" t="inlineStr">
         <is>
-          <t>Timber &gt; Wood</t>
+          <t>Steel &gt; M.S. oxidised fan light ventilator catch</t>
         </is>
       </c>
       <c r="AE36" s="8" t="n"/>
@@ -4688,9 +4870,7 @@
       <c r="AO36" s="8" t="n"/>
       <c r="AP36" s="8" t="n"/>
       <c r="AQ36" s="8" t="n"/>
-      <c r="AR36" s="17" t="n">
-        <v>35</v>
-      </c>
+      <c r="AR36" s="8" t="n"/>
       <c r="AS36" s="8" t="n"/>
       <c r="AT36" s="8" t="n"/>
       <c r="AU36" s="8" t="n"/>
@@ -4698,31 +4878,31 @@
       <c r="AW36" s="8" t="n"/>
       <c r="AX36" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Wood — mass 472.5 kg [area × thickness (derived)] × 0.306 kgCO2e/kg = 144.59 kgCO2e — ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
+          <t>[EXCLUDED] material: M.S. oxidised fan light ventilator catch — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0031</t>
+          <t>GMAP-0034</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C37" s="8" t="n"/>
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing 25 mm thick flush door (for cupboard) shutters core of block board construction with frame of 1st class hard wood and well matched 1st class teak ply veneering with vertical grains or cross bands and face veneer on one face and commercial ply veneering with vertical grains or cross bands and face veneer on other face of shutters, including nickel plated bright finished MS piano hinges with necessary screws.</t>
+          <t>Providing and fixing 90 mm oxidised M.S. hasp and staple (safety type) with necessaary screws etc. complete.</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - V, Wood Work</t>
+          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
@@ -4732,62 +4912,50 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>Flush door shutter</t>
+          <t>Oxidised M.S. hasp and staple</t>
         </is>
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>Block board, Hard wood, Teak ply veneer, Commercial ply veneer, MS piano hinges</t>
+          <t>Mild steel</t>
         </is>
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>Timber</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L37" s="8" t="n"/>
       <c r="M37" s="8" t="n"/>
       <c r="N37" s="17" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="O37" s="8" t="inlineStr">
         <is>
-          <t>sqm</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P37" s="8" t="n"/>
-      <c r="Q37" s="17" t="n">
-        <v>4.7</v>
-      </c>
+      <c r="Q37" s="8" t="n"/>
       <c r="R37" s="8" t="n"/>
       <c r="S37" s="8" t="n"/>
-      <c r="T37" s="8" t="n"/>
-      <c r="U37" s="17" t="n">
-        <v>0.1175</v>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="W37" s="8" t="inlineStr">
-        <is>
-          <t>Area x thickness (25.0 mm, from description)</t>
-        </is>
-      </c>
+      <c r="T37" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" s="8" t="n"/>
+      <c r="V37" s="8" t="n"/>
+      <c r="W37" s="8" t="n"/>
       <c r="X37" s="17" t="n">
-        <v>750</v>
-      </c>
-      <c r="Y37" s="17" t="n">
-        <v>26.97</v>
-      </c>
+        <v>7850</v>
+      </c>
+      <c r="Y37" s="8" t="n"/>
       <c r="Z37" s="17" t="n">
-        <v>0.306</v>
+        <v>1.55</v>
       </c>
       <c r="AA37" s="8" t="inlineStr">
         <is>
@@ -4796,13 +4964,13 @@
       </c>
       <c r="AB37" s="8" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>9.127.3</t>
         </is>
       </c>
       <c r="AC37" s="8" t="n"/>
       <c r="AD37" s="8" t="inlineStr">
         <is>
-          <t>Timber &gt; Flush door shutter</t>
+          <t>Steel &gt; Oxidised M.S. hasp and staple</t>
         </is>
       </c>
       <c r="AE37" s="8" t="n"/>
@@ -4815,12 +4983,12 @@
       <c r="AL37" s="8" t="n"/>
       <c r="AM37" s="8" t="n"/>
       <c r="AN37" s="8" t="n"/>
-      <c r="AO37" s="8" t="n"/>
+      <c r="AO37" s="17" t="n">
+        <v>90</v>
+      </c>
       <c r="AP37" s="8" t="n"/>
       <c r="AQ37" s="8" t="n"/>
-      <c r="AR37" s="17" t="n">
-        <v>25</v>
-      </c>
+      <c r="AR37" s="8" t="n"/>
       <c r="AS37" s="8" t="n"/>
       <c r="AT37" s="8" t="n"/>
       <c r="AU37" s="8" t="n"/>
@@ -4828,51 +4996,51 @@
       <c r="AW37" s="8" t="n"/>
       <c r="AX37" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Flush door shutter — mass 88.12 kg [area × thickness (derived)] × 0.306 kgCO2e/kg = 26.97 kgCO2e — ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
+          <t>[EXCLUDED] material: Oxidised M.S. hasp and staple — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0032</t>
+          <t>GMAP-0035</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C38" s="8" t="n"/>
       <c r="D38" s="8" t="n"/>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Providing 50x50x50 mm 2nd class Teak wood plugs including cutting brick work and fixing in cement mortar 1:3 (1 cement : 3 fine sand) and making good the walls etc.</t>
+          <t>Providing and fixing aluminium sliding door bolts 300 x 16 mm anodised transparent or dyed to required colour or shade with nuts and screws etc. complete.</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - V, Wood Work</t>
+          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Finishes</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>Teak wood plug</t>
+          <t>Aluminium sliding door bolt</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>Teak wood, Cement, Fine sand</t>
+          <t>Aluminium</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>Timber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K38" s="8" t="inlineStr">
@@ -4881,13 +5049,9 @@
         </is>
       </c>
       <c r="L38" s="8" t="n"/>
-      <c r="M38" s="8" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
+      <c r="M38" s="8" t="n"/>
       <c r="N38" s="17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O38" s="8" t="inlineStr">
         <is>
@@ -4899,28 +5063,28 @@
       <c r="R38" s="8" t="n"/>
       <c r="S38" s="8" t="n"/>
       <c r="T38" s="17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="U38" s="8" t="n"/>
       <c r="V38" s="8" t="n"/>
       <c r="W38" s="8" t="n"/>
-      <c r="X38" s="17" t="n">
-        <v>750</v>
-      </c>
+      <c r="X38" s="8" t="n"/>
       <c r="Y38" s="8" t="n"/>
-      <c r="Z38" s="17" t="n">
-        <v>0.306</v>
-      </c>
+      <c r="Z38" s="8" t="n"/>
       <c r="AA38" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
         </is>
       </c>
-      <c r="AB38" s="8" t="n"/>
+      <c r="AB38" s="8" t="inlineStr">
+        <is>
+          <t>9.218.1</t>
+        </is>
+      </c>
       <c r="AC38" s="8" t="n"/>
       <c r="AD38" s="8" t="inlineStr">
         <is>
-          <t>Timber &gt; Teak wood plug &gt; 1:3</t>
+          <t>Other &gt; Aluminium sliding door bolt</t>
         </is>
       </c>
       <c r="AE38" s="8" t="n"/>
@@ -4934,42 +5098,40 @@
       <c r="AM38" s="8" t="n"/>
       <c r="AN38" s="8" t="n"/>
       <c r="AO38" s="17" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP38" s="17" t="n">
-        <v>50</v>
-      </c>
-      <c r="AQ38" s="17" t="n">
-        <v>50</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="AP38" s="8" t="n"/>
+      <c r="AQ38" s="8" t="n"/>
       <c r="AR38" s="8" t="n"/>
       <c r="AS38" s="8" t="n"/>
-      <c r="AT38" s="8" t="n"/>
+      <c r="AT38" s="17" t="n">
+        <v>16</v>
+      </c>
       <c r="AU38" s="8" t="n"/>
       <c r="AV38" s="8" t="n"/>
       <c r="AW38" s="8" t="n"/>
       <c r="AX38" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Teak wood plug — category 'Timber' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Aluminium sliding door bolt — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0033</t>
+          <t>GMAP-0036</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31a</t>
         </is>
       </c>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing M.S. oxidised fan light ventilator catch with necessary screws etc. complete.</t>
+          <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 200 x 10 mm</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
@@ -4984,17 +5146,17 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>M.S. oxidised ventilator catch</t>
+          <t>Aluminium tower bolt</t>
         </is>
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>M.S. oxidised steel</t>
+          <t>Aluminium</t>
         </is>
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
@@ -5005,7 +5167,7 @@
       <c r="L39" s="8" t="n"/>
       <c r="M39" s="8" t="n"/>
       <c r="N39" s="17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O39" s="8" t="inlineStr">
         <is>
@@ -5017,18 +5179,14 @@
       <c r="R39" s="8" t="n"/>
       <c r="S39" s="8" t="n"/>
       <c r="T39" s="17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U39" s="8" t="n"/>
       <c r="V39" s="8" t="n"/>
       <c r="W39" s="8" t="n"/>
-      <c r="X39" s="17" t="n">
-        <v>7850</v>
-      </c>
+      <c r="X39" s="8" t="n"/>
       <c r="Y39" s="8" t="n"/>
-      <c r="Z39" s="17" t="n">
-        <v>1.55</v>
-      </c>
+      <c r="Z39" s="8" t="n"/>
       <c r="AA39" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -5036,13 +5194,13 @@
       </c>
       <c r="AB39" s="8" t="inlineStr">
         <is>
-          <t>9.127.3</t>
+          <t>9.219.3</t>
         </is>
       </c>
       <c r="AC39" s="8" t="n"/>
       <c r="AD39" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; M.S. oxidised ventilator catch</t>
+          <t>Other &gt; Aluminium tower bolt</t>
         </is>
       </c>
       <c r="AE39" s="8" t="n"/>
@@ -5055,37 +5213,41 @@
       <c r="AL39" s="8" t="n"/>
       <c r="AM39" s="8" t="n"/>
       <c r="AN39" s="8" t="n"/>
-      <c r="AO39" s="8" t="n"/>
+      <c r="AO39" s="17" t="n">
+        <v>200</v>
+      </c>
       <c r="AP39" s="8" t="n"/>
       <c r="AQ39" s="8" t="n"/>
       <c r="AR39" s="8" t="n"/>
       <c r="AS39" s="8" t="n"/>
-      <c r="AT39" s="8" t="n"/>
+      <c r="AT39" s="17" t="n">
+        <v>10</v>
+      </c>
       <c r="AU39" s="8" t="n"/>
       <c r="AV39" s="8" t="n"/>
       <c r="AW39" s="8" t="n"/>
       <c r="AX39" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: M.S. oxidised ventilator catch — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Aluminium tower bolt — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0034</t>
+          <t>GMAP-0037</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31b</t>
         </is>
       </c>
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing 90 mm oxidised M.S. hasp and staple (safety type) with necessary screws etc. complete.</t>
+          <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 100 x 10 mm</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -5100,17 +5262,17 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>Oxidised M.S. hasp and staple</t>
+          <t>Aluminium tower bolt</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>M.S. oxidised steel</t>
+          <t>Aluminium</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K40" s="8" t="inlineStr">
@@ -5121,7 +5283,7 @@
       <c r="L40" s="8" t="n"/>
       <c r="M40" s="8" t="n"/>
       <c r="N40" s="17" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O40" s="8" t="inlineStr">
         <is>
@@ -5133,18 +5295,14 @@
       <c r="R40" s="8" t="n"/>
       <c r="S40" s="8" t="n"/>
       <c r="T40" s="17" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U40" s="8" t="n"/>
       <c r="V40" s="8" t="n"/>
       <c r="W40" s="8" t="n"/>
-      <c r="X40" s="17" t="n">
-        <v>7850</v>
-      </c>
+      <c r="X40" s="8" t="n"/>
       <c r="Y40" s="8" t="n"/>
-      <c r="Z40" s="17" t="n">
-        <v>1.55</v>
-      </c>
+      <c r="Z40" s="8" t="n"/>
       <c r="AA40" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -5152,13 +5310,13 @@
       </c>
       <c r="AB40" s="8" t="inlineStr">
         <is>
-          <t>9.218.1</t>
+          <t>9.219.5</t>
         </is>
       </c>
       <c r="AC40" s="8" t="n"/>
       <c r="AD40" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Oxidised M.S. hasp and staple</t>
+          <t>Other &gt; Aluminium tower bolt</t>
         </is>
       </c>
       <c r="AE40" s="8" t="n"/>
@@ -5172,38 +5330,40 @@
       <c r="AM40" s="8" t="n"/>
       <c r="AN40" s="8" t="n"/>
       <c r="AO40" s="17" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP40" s="8" t="n"/>
       <c r="AQ40" s="8" t="n"/>
       <c r="AR40" s="8" t="n"/>
       <c r="AS40" s="8" t="n"/>
-      <c r="AT40" s="8" t="n"/>
+      <c r="AT40" s="17" t="n">
+        <v>10</v>
+      </c>
       <c r="AU40" s="8" t="n"/>
       <c r="AV40" s="8" t="n"/>
       <c r="AW40" s="8" t="n"/>
       <c r="AX40" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Oxidised M.S. hasp and staple — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Aluminium tower bolt — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0035</t>
+          <t>GMAP-0038</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32a</t>
         </is>
       </c>
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium sliding door bolts 300 x 16 mm anodised transparent or dyed to required colour or shade with nuts and screws etc. complete.</t>
+          <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 100 mm</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -5218,7 +5378,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>Aluminium sliding door bolt</t>
+          <t>Aluminium handle</t>
         </is>
       </c>
       <c r="I41" s="8" t="inlineStr">
@@ -5239,7 +5399,7 @@
       <c r="L41" s="8" t="n"/>
       <c r="M41" s="8" t="n"/>
       <c r="N41" s="17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O41" s="8" t="inlineStr">
         <is>
@@ -5251,7 +5411,7 @@
       <c r="R41" s="8" t="n"/>
       <c r="S41" s="8" t="n"/>
       <c r="T41" s="17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="U41" s="8" t="n"/>
       <c r="V41" s="8" t="n"/>
@@ -5264,11 +5424,15 @@
           <t>DSR 1989</t>
         </is>
       </c>
-      <c r="AB41" s="8" t="n"/>
+      <c r="AB41" s="8" t="inlineStr">
+        <is>
+          <t>9.222.2</t>
+        </is>
+      </c>
       <c r="AC41" s="8" t="n"/>
       <c r="AD41" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium sliding door bolt</t>
+          <t>Other &gt; Aluminium handle</t>
         </is>
       </c>
       <c r="AE41" s="8" t="n"/>
@@ -5282,40 +5446,38 @@
       <c r="AM41" s="8" t="n"/>
       <c r="AN41" s="8" t="n"/>
       <c r="AO41" s="17" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AP41" s="8" t="n"/>
       <c r="AQ41" s="8" t="n"/>
       <c r="AR41" s="8" t="n"/>
       <c r="AS41" s="8" t="n"/>
-      <c r="AT41" s="17" t="n">
-        <v>16</v>
-      </c>
+      <c r="AT41" s="8" t="n"/>
       <c r="AU41" s="8" t="n"/>
       <c r="AV41" s="8" t="n"/>
       <c r="AW41" s="8" t="n"/>
       <c r="AX41" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aluminium sliding door bolt — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Aluminium handle — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0036</t>
+          <t>GMAP-0039</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>31a</t>
+          <t>32b</t>
         </is>
       </c>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. i) 200 x 10 mm</t>
+          <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 75 mm</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -5330,7 +5492,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>Aluminium tower bolt</t>
+          <t>Aluminium handle</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
@@ -5351,7 +5513,7 @@
       <c r="L42" s="8" t="n"/>
       <c r="M42" s="8" t="n"/>
       <c r="N42" s="17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O42" s="8" t="inlineStr">
         <is>
@@ -5363,7 +5525,7 @@
       <c r="R42" s="8" t="n"/>
       <c r="S42" s="8" t="n"/>
       <c r="T42" s="17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U42" s="8" t="n"/>
       <c r="V42" s="8" t="n"/>
@@ -5378,13 +5540,13 @@
       </c>
       <c r="AB42" s="8" t="inlineStr">
         <is>
-          <t>9.219.3</t>
+          <t>9.222.3</t>
         </is>
       </c>
       <c r="AC42" s="8" t="n"/>
       <c r="AD42" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium tower bolt</t>
+          <t>Other &gt; Aluminium handle</t>
         </is>
       </c>
       <c r="AE42" s="8" t="n"/>
@@ -5398,40 +5560,38 @@
       <c r="AM42" s="8" t="n"/>
       <c r="AN42" s="8" t="n"/>
       <c r="AO42" s="17" t="n">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="AP42" s="8" t="n"/>
       <c r="AQ42" s="8" t="n"/>
       <c r="AR42" s="8" t="n"/>
       <c r="AS42" s="8" t="n"/>
-      <c r="AT42" s="17" t="n">
-        <v>10</v>
-      </c>
+      <c r="AT42" s="8" t="n"/>
       <c r="AU42" s="8" t="n"/>
       <c r="AV42" s="8" t="n"/>
       <c r="AW42" s="8" t="n"/>
       <c r="AX42" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aluminium tower bolt — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Aluminium handle — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0037</t>
+          <t>GMAP-0040</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>31b</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. ii) 100 x 10 mm</t>
+          <t>Providing and fixing aluminium hanging floor door stopper anodised transparent or dyed to required colour &amp; shade with necessary screws etc. complete.</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
@@ -5446,7 +5606,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>Aluminium tower bolt</t>
+          <t>Aluminium floor door stopper</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
@@ -5467,7 +5627,7 @@
       <c r="L43" s="8" t="n"/>
       <c r="M43" s="8" t="n"/>
       <c r="N43" s="17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O43" s="8" t="inlineStr">
         <is>
@@ -5479,7 +5639,7 @@
       <c r="R43" s="8" t="n"/>
       <c r="S43" s="8" t="n"/>
       <c r="T43" s="17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U43" s="8" t="n"/>
       <c r="V43" s="8" t="n"/>
@@ -5494,13 +5654,13 @@
       </c>
       <c r="AB43" s="8" t="inlineStr">
         <is>
-          <t>9.219.5</t>
+          <t>9.223</t>
         </is>
       </c>
       <c r="AC43" s="8" t="n"/>
       <c r="AD43" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium tower bolt</t>
+          <t>Other &gt; Aluminium floor door stopper</t>
         </is>
       </c>
       <c r="AE43" s="8" t="n"/>
@@ -5513,41 +5673,37 @@
       <c r="AL43" s="8" t="n"/>
       <c r="AM43" s="8" t="n"/>
       <c r="AN43" s="8" t="n"/>
-      <c r="AO43" s="17" t="n">
-        <v>100</v>
-      </c>
+      <c r="AO43" s="8" t="n"/>
       <c r="AP43" s="8" t="n"/>
       <c r="AQ43" s="8" t="n"/>
       <c r="AR43" s="8" t="n"/>
       <c r="AS43" s="8" t="n"/>
-      <c r="AT43" s="17" t="n">
-        <v>10</v>
-      </c>
+      <c r="AT43" s="8" t="n"/>
       <c r="AU43" s="8" t="n"/>
       <c r="AV43" s="8" t="n"/>
       <c r="AW43" s="8" t="n"/>
       <c r="AX43" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aluminium tower bolt — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Aluminium floor door stopper — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0038</t>
+          <t>GMAP-0041</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>32a</t>
+          <t>34a</t>
         </is>
       </c>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. i) 100 mm</t>
+          <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. Windows - side hung</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -5562,47 +5718,67 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>Aluminium handle</t>
+          <t>Steel glazed windows</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Steel, Glass, Cement, Coarse sand, Graded stone aggregate, Sash putty, Steel primer</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L44" s="8" t="n"/>
-      <c r="M44" s="8" t="n"/>
+      <c r="M44" s="8" t="inlineStr">
+        <is>
+          <t>1:3:6</t>
+        </is>
+      </c>
       <c r="N44" s="17" t="n">
-        <v>20</v>
+        <v>11.3</v>
       </c>
       <c r="O44" s="8" t="inlineStr">
         <is>
-          <t>nos</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P44" s="8" t="n"/>
-      <c r="Q44" s="8" t="n"/>
+      <c r="Q44" s="17" t="n">
+        <v>11.3</v>
+      </c>
       <c r="R44" s="8" t="n"/>
       <c r="S44" s="8" t="n"/>
-      <c r="T44" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="U44" s="8" t="n"/>
-      <c r="V44" s="8" t="n"/>
-      <c r="W44" s="8" t="n"/>
-      <c r="X44" s="8" t="n"/>
-      <c r="Y44" s="8" t="n"/>
-      <c r="Z44" s="8" t="n"/>
+      <c r="T44" s="8" t="n"/>
+      <c r="U44" s="17" t="n">
+        <v>0.0339</v>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W44" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (3.0 mm, from description)</t>
+        </is>
+      </c>
+      <c r="X44" s="17" t="n">
+        <v>7850</v>
+      </c>
+      <c r="Y44" s="17" t="n">
+        <v>412.48</v>
+      </c>
+      <c r="Z44" s="17" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA44" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -5610,13 +5786,13 @@
       </c>
       <c r="AB44" s="8" t="inlineStr">
         <is>
-          <t>9.222.2</t>
+          <t>N.S.I.</t>
         </is>
       </c>
       <c r="AC44" s="8" t="n"/>
       <c r="AD44" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium handle</t>
+          <t>Steel &gt; Steel glazed windows &gt; 1:3:6</t>
         </is>
       </c>
       <c r="AE44" s="8" t="n"/>
@@ -5632,9 +5808,13 @@
       <c r="AO44" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="AP44" s="8" t="n"/>
+      <c r="AP44" s="17" t="n">
+        <v>15</v>
+      </c>
       <c r="AQ44" s="8" t="n"/>
-      <c r="AR44" s="8" t="n"/>
+      <c r="AR44" s="17" t="n">
+        <v>3</v>
+      </c>
       <c r="AS44" s="8" t="n"/>
       <c r="AT44" s="8" t="n"/>
       <c r="AU44" s="8" t="n"/>
@@ -5642,26 +5822,26 @@
       <c r="AW44" s="8" t="n"/>
       <c r="AX44" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aluminium handle — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[OK] material: Steel glazed windows — mass 266.12 kg [area × thickness (derived)] × 1.55 kgCO2e/kg = 412.48 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0039</t>
+          <t>GMAP-0042</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>32b</t>
+          <t>34b</t>
         </is>
       </c>
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. ii) 75 mm</t>
+          <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. Ventilators - centre hung</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -5676,47 +5856,67 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>Aluminium handle</t>
+          <t>Steel glazed ventilators</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Steel, Glass, Cement, Coarse sand, Graded stone aggregate, Sash putty, Steel primer</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L45" s="8" t="n"/>
-      <c r="M45" s="8" t="n"/>
+      <c r="M45" s="8" t="inlineStr">
+        <is>
+          <t>1:3:6</t>
+        </is>
+      </c>
       <c r="N45" s="17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O45" s="8" t="inlineStr">
         <is>
-          <t>nos</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P45" s="8" t="n"/>
-      <c r="Q45" s="8" t="n"/>
+      <c r="Q45" s="17" t="n">
+        <v>1</v>
+      </c>
       <c r="R45" s="8" t="n"/>
       <c r="S45" s="8" t="n"/>
-      <c r="T45" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="U45" s="8" t="n"/>
-      <c r="V45" s="8" t="n"/>
-      <c r="W45" s="8" t="n"/>
-      <c r="X45" s="8" t="n"/>
-      <c r="Y45" s="8" t="n"/>
-      <c r="Z45" s="8" t="n"/>
+      <c r="T45" s="8" t="n"/>
+      <c r="U45" s="17" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W45" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (3.0 mm, from description)</t>
+        </is>
+      </c>
+      <c r="X45" s="17" t="n">
+        <v>7850</v>
+      </c>
+      <c r="Y45" s="17" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="Z45" s="17" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA45" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -5724,13 +5924,13 @@
       </c>
       <c r="AB45" s="8" t="inlineStr">
         <is>
-          <t>9.222.3</t>
+          <t>N.S.I.</t>
         </is>
       </c>
       <c r="AC45" s="8" t="n"/>
       <c r="AD45" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium handle</t>
+          <t>Steel &gt; Steel glazed ventilators &gt; 1:3:6</t>
         </is>
       </c>
       <c r="AE45" s="8" t="n"/>
@@ -5744,11 +5944,15 @@
       <c r="AM45" s="8" t="n"/>
       <c r="AN45" s="8" t="n"/>
       <c r="AO45" s="17" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP45" s="8" t="n"/>
+        <v>100</v>
+      </c>
+      <c r="AP45" s="17" t="n">
+        <v>15</v>
+      </c>
       <c r="AQ45" s="8" t="n"/>
-      <c r="AR45" s="8" t="n"/>
+      <c r="AR45" s="17" t="n">
+        <v>3</v>
+      </c>
       <c r="AS45" s="8" t="n"/>
       <c r="AT45" s="8" t="n"/>
       <c r="AU45" s="8" t="n"/>
@@ -5756,26 +5960,26 @@
       <c r="AW45" s="8" t="n"/>
       <c r="AX45" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aluminium handle — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[OK] material: Steel glazed ventilators — mass 23.55 kg [area × thickness (derived)] × 1.55 kgCO2e/kg = 36.5 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0040</t>
+          <t>GMAP-0043</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C46" s="8" t="n"/>
       <c r="D46" s="8" t="n"/>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium hanging floor door stopper anodised transparent or dyed to required colour &amp; shade with necessary screws etc. complete.</t>
+          <t>Providing and fixing oxidised mild steel casement window fastners of minimum weight 200 grams to side hung steel windows with necessary welding and machine screws etc. complete.</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
@@ -5790,17 +5994,17 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>Aluminium hanging floor door stopper</t>
+          <t>Oxidised mild steel casement window fasteners</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Mild steel</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr">
@@ -5811,7 +6015,7 @@
       <c r="L46" s="8" t="n"/>
       <c r="M46" s="8" t="n"/>
       <c r="N46" s="17" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="O46" s="8" t="inlineStr">
         <is>
@@ -5823,14 +6027,18 @@
       <c r="R46" s="8" t="n"/>
       <c r="S46" s="8" t="n"/>
       <c r="T46" s="17" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="U46" s="8" t="n"/>
       <c r="V46" s="8" t="n"/>
       <c r="W46" s="8" t="n"/>
-      <c r="X46" s="8" t="n"/>
+      <c r="X46" s="17" t="n">
+        <v>7850</v>
+      </c>
       <c r="Y46" s="8" t="n"/>
-      <c r="Z46" s="8" t="n"/>
+      <c r="Z46" s="17" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA46" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -5838,13 +6046,13 @@
       </c>
       <c r="AB46" s="8" t="inlineStr">
         <is>
-          <t>9.223</t>
+          <t>N.S.I.</t>
         </is>
       </c>
       <c r="AC46" s="8" t="n"/>
       <c r="AD46" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium hanging floor door stopper</t>
+          <t>Steel &gt; Oxidised mild steel casement window fasteners</t>
         </is>
       </c>
       <c r="AE46" s="8" t="n"/>
@@ -5868,26 +6076,26 @@
       <c r="AW46" s="8" t="n"/>
       <c r="AX46" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aluminium hanging floor door stopper — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Oxidised mild steel casement window fasteners — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0041</t>
+          <t>GMAP-0044</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>34a</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C47" s="8" t="n"/>
       <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. i) Windows - side hung</t>
+          <t>Providing and fixing aluminium casement stays anodised transparent or dyed to required colour and shade with with necessary welding and machine screws etc. complete.</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
@@ -5902,67 +6110,47 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>Steel glazed window</t>
+          <t>Aluminium casement stays</t>
         </is>
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>Steel, Cement, Coarse sand, Graded stone aggregate, Glass, Putty, Primer</t>
+          <t>Aluminium</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L47" s="8" t="n"/>
-      <c r="M47" s="8" t="inlineStr">
-        <is>
-          <t>1:3:6</t>
-        </is>
-      </c>
+      <c r="M47" s="8" t="n"/>
       <c r="N47" s="17" t="n">
-        <v>11.3</v>
+        <v>21</v>
       </c>
       <c r="O47" s="8" t="inlineStr">
         <is>
-          <t>sqm</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P47" s="8" t="n"/>
-      <c r="Q47" s="17" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="Q47" s="8" t="n"/>
       <c r="R47" s="8" t="n"/>
       <c r="S47" s="8" t="n"/>
-      <c r="T47" s="8" t="n"/>
-      <c r="U47" s="17" t="n">
-        <v>0.0339</v>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="W47" s="8" t="inlineStr">
-        <is>
-          <t>Area x thickness (3.0 mm, from description)</t>
-        </is>
-      </c>
-      <c r="X47" s="17" t="n">
-        <v>7850</v>
-      </c>
-      <c r="Y47" s="17" t="n">
-        <v>412.48</v>
-      </c>
-      <c r="Z47" s="17" t="n">
-        <v>1.55</v>
-      </c>
+      <c r="T47" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="U47" s="8" t="n"/>
+      <c r="V47" s="8" t="n"/>
+      <c r="W47" s="8" t="n"/>
+      <c r="X47" s="8" t="n"/>
+      <c r="Y47" s="8" t="n"/>
+      <c r="Z47" s="8" t="n"/>
       <c r="AA47" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -5970,13 +6158,13 @@
       </c>
       <c r="AB47" s="8" t="inlineStr">
         <is>
-          <t>N.S.I.</t>
+          <t>9.224</t>
         </is>
       </c>
       <c r="AC47" s="8" t="n"/>
       <c r="AD47" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Steel glazed window &gt; 1:3:6</t>
+          <t>Other &gt; Aluminium casement stays</t>
         </is>
       </c>
       <c r="AE47" s="8" t="n"/>
@@ -5992,9 +6180,7 @@
       <c r="AO47" s="8" t="n"/>
       <c r="AP47" s="8" t="n"/>
       <c r="AQ47" s="8" t="n"/>
-      <c r="AR47" s="17" t="n">
-        <v>3</v>
-      </c>
+      <c r="AR47" s="8" t="n"/>
       <c r="AS47" s="8" t="n"/>
       <c r="AT47" s="8" t="n"/>
       <c r="AU47" s="8" t="n"/>
@@ -6002,26 +6188,26 @@
       <c r="AW47" s="8" t="n"/>
       <c r="AX47" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Steel glazed window — mass 266.12 kg [area × thickness (derived)] × 1.55 kgCO2e/kg = 412.48 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[EXCLUDED] material: Aluminium casement stays — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0042</t>
+          <t>GMAP-0045</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>34b</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C48" s="8" t="n"/>
       <c r="D48" s="8" t="n"/>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. ii) Ventilators - centre hung</t>
+          <t>Providing and welding 20x4 mm M S Guard Flats 10cm c/c in steel windows of standard rolled steel section including a coat of steel peimer as per drawing and spetification complete in all respect.</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
@@ -6036,12 +6222,12 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>Steel glazed ventilator</t>
+          <t>MS Guard Flats</t>
         </is>
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>Steel, Cement, Coarse sand, Graded stone aggregate, Glass, Putty, Primer</t>
+          <t>Mild steel, Steel primer</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
@@ -6051,48 +6237,34 @@
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L48" s="8" t="n"/>
-      <c r="M48" s="8" t="inlineStr">
-        <is>
-          <t>1:3:6</t>
-        </is>
-      </c>
+      <c r="M48" s="8" t="n"/>
       <c r="N48" s="17" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="O48" s="8" t="inlineStr">
         <is>
-          <t>sqm</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="P48" s="8" t="n"/>
-      <c r="Q48" s="17" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q48" s="8" t="n"/>
       <c r="R48" s="8" t="n"/>
-      <c r="S48" s="8" t="n"/>
+      <c r="S48" s="17" t="n">
+        <v>66</v>
+      </c>
       <c r="T48" s="8" t="n"/>
-      <c r="U48" s="17" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="W48" s="8" t="inlineStr">
-        <is>
-          <t>Area x thickness (3.0 mm, from description)</t>
-        </is>
-      </c>
+      <c r="U48" s="8" t="n"/>
+      <c r="V48" s="8" t="n"/>
+      <c r="W48" s="8" t="n"/>
       <c r="X48" s="17" t="n">
         <v>7850</v>
       </c>
       <c r="Y48" s="17" t="n">
-        <v>36.5</v>
+        <v>102.3</v>
       </c>
       <c r="Z48" s="17" t="n">
         <v>1.55</v>
@@ -6110,7 +6282,7 @@
       <c r="AC48" s="8" t="n"/>
       <c r="AD48" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Steel glazed ventilator &gt; 1:3:6</t>
+          <t>Steel &gt; MS Guard Flats</t>
         </is>
       </c>
       <c r="AE48" s="8" t="n"/>
@@ -6124,10 +6296,12 @@
       <c r="AM48" s="8" t="n"/>
       <c r="AN48" s="8" t="n"/>
       <c r="AO48" s="8" t="n"/>
-      <c r="AP48" s="8" t="n"/>
+      <c r="AP48" s="17" t="n">
+        <v>20</v>
+      </c>
       <c r="AQ48" s="8" t="n"/>
       <c r="AR48" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS48" s="8" t="n"/>
       <c r="AT48" s="8" t="n"/>
@@ -6136,26 +6310,26 @@
       <c r="AW48" s="8" t="n"/>
       <c r="AX48" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Steel glazed ventilator — mass 23.55 kg [area × thickness (derived)] × 1.55 kgCO2e/kg = 36.5 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[OK] material: MS Guard Flats — mass 66.0 kg [direct weight] × 1.55 kgCO2e/kg = 102.3 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0043</t>
+          <t>GMAP-0046</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing oxidised mild steel casement window fastners of minimum weight 200 grams to side hung steel windows with necessary welding and machine screws etc. complete.</t>
+          <t>Providing and fixing T - Iron frames for doors, windows and ventilators of mild steel Tee - sections, joints mitred and welded with 15x3 mm lugs 10 cm long embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including fixing of necessary butt hinges and screws and applying a priming coat of approved steel primer.</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
@@ -6170,12 +6344,12 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>Oxidised mild steel casement window fastener</t>
+          <t>T-Iron frames</t>
         </is>
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>Mild steel Tee sections, Cement, Coarse sand, Graded stone aggregate, Steel primer</t>
         </is>
       </c>
       <c r="J49" s="8" t="inlineStr">
@@ -6185,33 +6359,39 @@
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L49" s="8" t="n"/>
-      <c r="M49" s="8" t="n"/>
+      <c r="M49" s="8" t="inlineStr">
+        <is>
+          <t>1:3:6</t>
+        </is>
+      </c>
       <c r="N49" s="17" t="n">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="O49" s="8" t="inlineStr">
         <is>
-          <t>nos</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="P49" s="8" t="n"/>
       <c r="Q49" s="8" t="n"/>
       <c r="R49" s="8" t="n"/>
-      <c r="S49" s="8" t="n"/>
-      <c r="T49" s="17" t="n">
-        <v>21</v>
-      </c>
+      <c r="S49" s="17" t="n">
+        <v>187</v>
+      </c>
+      <c r="T49" s="8" t="n"/>
       <c r="U49" s="8" t="n"/>
       <c r="V49" s="8" t="n"/>
       <c r="W49" s="8" t="n"/>
       <c r="X49" s="17" t="n">
         <v>7850</v>
       </c>
-      <c r="Y49" s="8" t="n"/>
+      <c r="Y49" s="17" t="n">
+        <v>289.85</v>
+      </c>
       <c r="Z49" s="17" t="n">
         <v>1.55</v>
       </c>
@@ -6222,13 +6402,13 @@
       </c>
       <c r="AB49" s="8" t="inlineStr">
         <is>
-          <t>N.S.I.</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="AC49" s="8" t="n"/>
       <c r="AD49" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Oxidised mild steel casement window fastener</t>
+          <t>Steel &gt; T-Iron frames &gt; 1:3:6</t>
         </is>
       </c>
       <c r="AE49" s="8" t="n"/>
@@ -6241,10 +6421,16 @@
       <c r="AL49" s="8" t="n"/>
       <c r="AM49" s="8" t="n"/>
       <c r="AN49" s="8" t="n"/>
-      <c r="AO49" s="8" t="n"/>
-      <c r="AP49" s="8" t="n"/>
+      <c r="AO49" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP49" s="17" t="n">
+        <v>15</v>
+      </c>
       <c r="AQ49" s="8" t="n"/>
-      <c r="AR49" s="8" t="n"/>
+      <c r="AR49" s="17" t="n">
+        <v>3</v>
+      </c>
       <c r="AS49" s="8" t="n"/>
       <c r="AT49" s="8" t="n"/>
       <c r="AU49" s="8" t="n"/>
@@ -6252,26 +6438,26 @@
       <c r="AW49" s="8" t="n"/>
       <c r="AX49" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Oxidised mild steel casement window fastener — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[OK] material: T-Iron frames — mass 187.0 kg [direct weight] × 1.55 kgCO2e/kg = 289.85 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0044</t>
+          <t>GMAP-0047</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium casement stays anodised transparent or dyed to required colour and shade with with necessary welding and machine screws etc. complete.</t>
+          <t>Providing and fixing MS fan clamp type I of 16 mm dia MS bar bent to shape with hooked ends in RCC slabs during laying including painting the exposed portion of loop, all as per standard design complete.</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
@@ -6281,22 +6467,22 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>Finishes</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>Aluminium casement stay</t>
+          <t>MS fan clamp</t>
         </is>
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Mild steel bar, Paint</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="K50" s="8" t="inlineStr">
@@ -6307,7 +6493,7 @@
       <c r="L50" s="8" t="n"/>
       <c r="M50" s="8" t="n"/>
       <c r="N50" s="17" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="O50" s="8" t="inlineStr">
         <is>
@@ -6319,14 +6505,18 @@
       <c r="R50" s="8" t="n"/>
       <c r="S50" s="8" t="n"/>
       <c r="T50" s="17" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="U50" s="8" t="n"/>
       <c r="V50" s="8" t="n"/>
       <c r="W50" s="8" t="n"/>
-      <c r="X50" s="8" t="n"/>
+      <c r="X50" s="17" t="n">
+        <v>7850</v>
+      </c>
       <c r="Y50" s="8" t="n"/>
-      <c r="Z50" s="8" t="n"/>
+      <c r="Z50" s="17" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA50" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -6334,13 +6524,13 @@
       </c>
       <c r="AB50" s="8" t="inlineStr">
         <is>
-          <t>9.224</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AC50" s="8" t="n"/>
       <c r="AD50" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium casement stay</t>
+          <t>Steel &gt; MS fan clamp</t>
         </is>
       </c>
       <c r="AE50" s="8" t="n"/>
@@ -6358,92 +6548,112 @@
       <c r="AQ50" s="8" t="n"/>
       <c r="AR50" s="8" t="n"/>
       <c r="AS50" s="8" t="n"/>
-      <c r="AT50" s="8" t="n"/>
+      <c r="AT50" s="17" t="n">
+        <v>16</v>
+      </c>
       <c r="AU50" s="8" t="n"/>
       <c r="AV50" s="8" t="n"/>
       <c r="AW50" s="8" t="n"/>
       <c r="AX50" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aluminium casement stay — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: MS fan clamp — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0045</t>
+          <t>GMAP-0048</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C51" s="8" t="n"/>
       <c r="D51" s="8" t="n"/>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>Providing and welding 20x4 mm MS Guard Flats 10cm c/c in steel windows of standard rolled steel section including a coat of steel primer as per drawing and specification complete in all respect.</t>
+          <t>40 mm thick cement concrete flooring 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20.0 mm nominal size) finished with a floating coat of neat cement including cement slurry, rounding off edges and strips etc. but excluding the cost of nosing of steps etc. complete.</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
+          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Finishes</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>MS Guard Flats</t>
+          <t>Cement concrete flooring</t>
         </is>
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>Mild steel, Primer</t>
+          <t>Cement, Coarse sand, Graded stone aggregate</t>
         </is>
       </c>
       <c r="J51" s="8" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L51" s="8" t="n"/>
-      <c r="M51" s="8" t="n"/>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L51" s="8" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="M51" s="8" t="inlineStr">
+        <is>
+          <t>1:2:4</t>
+        </is>
+      </c>
       <c r="N51" s="17" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O51" s="8" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P51" s="8" t="n"/>
-      <c r="Q51" s="8" t="n"/>
+      <c r="Q51" s="17" t="n">
+        <v>68</v>
+      </c>
       <c r="R51" s="8" t="n"/>
-      <c r="S51" s="17" t="n">
-        <v>66</v>
-      </c>
+      <c r="S51" s="8" t="n"/>
       <c r="T51" s="8" t="n"/>
-      <c r="U51" s="8" t="n"/>
-      <c r="V51" s="8" t="n"/>
-      <c r="W51" s="8" t="n"/>
+      <c r="U51" s="17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W51" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (40.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X51" s="17" t="n">
-        <v>7850</v>
+        <v>2400</v>
       </c>
       <c r="Y51" s="17" t="n">
-        <v>102.3</v>
+        <v>972.67</v>
       </c>
       <c r="Z51" s="17" t="n">
-        <v>1.55</v>
+        <v>0.149</v>
       </c>
       <c r="AA51" s="8" t="inlineStr">
         <is>
@@ -6452,13 +6662,13 @@
       </c>
       <c r="AB51" s="8" t="inlineStr">
         <is>
-          <t>N.S.I.</t>
+          <t>11.4.2</t>
         </is>
       </c>
       <c r="AC51" s="8" t="n"/>
       <c r="AD51" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; MS Guard Flats</t>
+          <t>Concrete &gt; Cement concrete flooring &gt; M15</t>
         </is>
       </c>
       <c r="AE51" s="8" t="n"/>
@@ -6472,12 +6682,10 @@
       <c r="AM51" s="8" t="n"/>
       <c r="AN51" s="8" t="n"/>
       <c r="AO51" s="8" t="n"/>
-      <c r="AP51" s="17" t="n">
-        <v>20</v>
-      </c>
+      <c r="AP51" s="8" t="n"/>
       <c r="AQ51" s="8" t="n"/>
       <c r="AR51" s="17" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="AS51" s="8" t="n"/>
       <c r="AT51" s="8" t="n"/>
@@ -6486,90 +6694,100 @@
       <c r="AW51" s="8" t="n"/>
       <c r="AX51" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: MS Guard Flats — mass 66.0 kg [direct weight] × 1.55 kgCO2e/kg = 102.3 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[OK] material: Cement concrete flooring — mass 6528.0 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 972.67 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0046</t>
+          <t>GMAP-0049</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C52" s="8" t="n"/>
       <c r="D52" s="8" t="n"/>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing T - Iron frames for doors, windows and ventilators of mild steel Tee - sections, joints mitred and welded with 15x3 mm lugs 10 cm long embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including fixing of necessary butt hinges and screws and applying a priming coat of approved steel primer.</t>
+          <t>18 mm thick cement plaster skirting (upto 30 cm height) with cement mortar 1:3 (1 cement : 3 coarse sand) finished with a floating coat of neat cement including rounding of junctions with floors.</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
+          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Finishes</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>T-Iron frame</t>
+          <t>Cement plaster skirting</t>
         </is>
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>Mild steel, Cement, Coarse sand, Graded stone aggregate, Steel primer</t>
+          <t>Cement, Coarse sand</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Plaster</t>
         </is>
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L52" s="8" t="n"/>
       <c r="M52" s="8" t="inlineStr">
         <is>
-          <t>1:3:6</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="N52" s="17" t="n">
-        <v>187</v>
+        <v>11</v>
       </c>
       <c r="O52" s="8" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P52" s="8" t="n"/>
-      <c r="Q52" s="8" t="n"/>
+      <c r="Q52" s="17" t="n">
+        <v>11</v>
+      </c>
       <c r="R52" s="8" t="n"/>
-      <c r="S52" s="17" t="n">
-        <v>187</v>
-      </c>
+      <c r="S52" s="8" t="n"/>
       <c r="T52" s="8" t="n"/>
-      <c r="U52" s="8" t="n"/>
-      <c r="V52" s="8" t="n"/>
-      <c r="W52" s="8" t="n"/>
+      <c r="U52" s="17" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="V52" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W52" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (18.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X52" s="17" t="n">
-        <v>7850</v>
+        <v>1900</v>
       </c>
       <c r="Y52" s="17" t="n">
-        <v>289.85</v>
+        <v>61.32</v>
       </c>
       <c r="Z52" s="17" t="n">
-        <v>1.55</v>
+        <v>0.163</v>
       </c>
       <c r="AA52" s="8" t="inlineStr">
         <is>
@@ -6578,13 +6796,13 @@
       </c>
       <c r="AB52" s="8" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>11.10.1</t>
         </is>
       </c>
       <c r="AC52" s="8" t="n"/>
       <c r="AD52" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; T-Iron frame &gt; 1:3:6</t>
+          <t>Plaster &gt; Cement plaster skirting &gt; 1:3</t>
         </is>
       </c>
       <c r="AE52" s="8" t="n"/>
@@ -6599,8 +6817,12 @@
       <c r="AN52" s="8" t="n"/>
       <c r="AO52" s="8" t="n"/>
       <c r="AP52" s="8" t="n"/>
-      <c r="AQ52" s="8" t="n"/>
-      <c r="AR52" s="8" t="n"/>
+      <c r="AQ52" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="AR52" s="17" t="n">
+        <v>18</v>
+      </c>
       <c r="AS52" s="8" t="n"/>
       <c r="AT52" s="8" t="n"/>
       <c r="AU52" s="8" t="n"/>
@@ -6608,84 +6830,104 @@
       <c r="AW52" s="8" t="n"/>
       <c r="AX52" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: T-Iron frame — mass 187.0 kg [direct weight] × 1.55 kgCO2e/kg = 289.85 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[OK] material: Cement plaster skirting — mass 376.2 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 61.32 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0047</t>
+          <t>GMAP-0050</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C53" s="8" t="n"/>
       <c r="D53" s="8" t="n"/>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing MS fan clamp type I of 16 mm dia MS bar bent to shape with hooked ends in RCC slabs during laying including painting the exposed portion of loop, all as per standard design complete.</t>
+          <t>40 mm thick marble chips flooring, rubbed and polished to granolithic finish, under layer 31 mm thick cement concrete 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 12.5 mm nominal size) and top layer 9 mm thick with white black, chocolate, grey yellow or Baroda green marble chips of sizes from 4 mm to 7 mm nominal size laid in cement marble powder mix 3:1 (3 cement : 1 marble powder) by weight in proportion of 4:7 (4 cement marble powder mix : 7 marble chips) by volume including cement slurry etc., complete using dark shade pigment with ordinary cement.</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
+          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>Finishes</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>MS fan clamp</t>
+          <t>Marble chips flooring</t>
         </is>
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>MS bar, Paint</t>
+          <t>Marble chips, Cement, Marble powder, Coarse sand, Graded stone aggregate, Pigment</t>
         </is>
       </c>
       <c r="J53" s="8" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L53" s="8" t="n"/>
-      <c r="M53" s="8" t="n"/>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L53" s="8" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="M53" s="8" t="inlineStr">
+        <is>
+          <t>1:2:4</t>
+        </is>
+      </c>
       <c r="N53" s="17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O53" s="8" t="inlineStr">
         <is>
-          <t>nos</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P53" s="8" t="n"/>
-      <c r="Q53" s="8" t="n"/>
+      <c r="Q53" s="17" t="n">
+        <v>9</v>
+      </c>
       <c r="R53" s="8" t="n"/>
       <c r="S53" s="8" t="n"/>
-      <c r="T53" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="U53" s="8" t="n"/>
-      <c r="V53" s="8" t="n"/>
-      <c r="W53" s="8" t="n"/>
+      <c r="T53" s="8" t="n"/>
+      <c r="U53" s="17" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W53" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (40.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X53" s="17" t="n">
-        <v>7850</v>
-      </c>
-      <c r="Y53" s="8" t="n"/>
+        <v>2400</v>
+      </c>
+      <c r="Y53" s="17" t="n">
+        <v>128.74</v>
+      </c>
       <c r="Z53" s="17" t="n">
-        <v>1.55</v>
+        <v>0.149</v>
       </c>
       <c r="AA53" s="8" t="inlineStr">
         <is>
@@ -6694,13 +6936,13 @@
       </c>
       <c r="AB53" s="8" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>11.16.1</t>
         </is>
       </c>
       <c r="AC53" s="8" t="n"/>
       <c r="AD53" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; MS fan clamp</t>
+          <t>Concrete &gt; Marble chips flooring &gt; M15</t>
         </is>
       </c>
       <c r="AE53" s="8" t="n"/>
@@ -6716,36 +6958,36 @@
       <c r="AO53" s="8" t="n"/>
       <c r="AP53" s="8" t="n"/>
       <c r="AQ53" s="8" t="n"/>
-      <c r="AR53" s="8" t="n"/>
+      <c r="AR53" s="17" t="n">
+        <v>40</v>
+      </c>
       <c r="AS53" s="8" t="n"/>
-      <c r="AT53" s="17" t="n">
-        <v>16</v>
-      </c>
+      <c r="AT53" s="8" t="n"/>
       <c r="AU53" s="8" t="n"/>
       <c r="AV53" s="8" t="n"/>
       <c r="AW53" s="8" t="n"/>
       <c r="AX53" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: MS fan clamp — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[OK] material: Marble chips flooring — mass 864.0 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 128.74 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0048</t>
+          <t>GMAP-0051</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="8" t="n"/>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>40 mm thick cement concrete flooring 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20.0 mm nominal size) finished with a floating coat of neat cement including cement slurry, rounding off edges and strips etc. but excluding the cost of nosing of steps etc. complete.</t>
+          <t>Add or deduct for providing and fixing glass strips in joints of terrazzo/cement concrete floors- 40 mm wide and 6 mm thick.</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -6760,71 +7002,47 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>Cement concrete flooring</t>
+          <t>Glass strips</t>
         </is>
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Glass</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K54" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L54" s="8" t="inlineStr">
-        <is>
-          <t>M15</t>
-        </is>
-      </c>
-      <c r="M54" s="8" t="inlineStr">
-        <is>
-          <t>1:2:4</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L54" s="8" t="n"/>
+      <c r="M54" s="8" t="n"/>
       <c r="N54" s="17" t="n">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="O54" s="8" t="inlineStr">
         <is>
-          <t>sqm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="P54" s="8" t="n"/>
-      <c r="Q54" s="17" t="n">
-        <v>68</v>
-      </c>
-      <c r="R54" s="8" t="n"/>
+      <c r="Q54" s="8" t="n"/>
+      <c r="R54" s="17" t="n">
+        <v>18</v>
+      </c>
       <c r="S54" s="8" t="n"/>
       <c r="T54" s="8" t="n"/>
-      <c r="U54" s="17" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="W54" s="8" t="inlineStr">
-        <is>
-          <t>Area x thickness (40.0 mm, from description)</t>
-        </is>
-      </c>
-      <c r="X54" s="17" t="n">
-        <v>2400</v>
-      </c>
-      <c r="Y54" s="17" t="n">
-        <v>972.67</v>
-      </c>
-      <c r="Z54" s="17" t="n">
-        <v>0.149</v>
-      </c>
+      <c r="U54" s="8" t="n"/>
+      <c r="V54" s="8" t="n"/>
+      <c r="W54" s="8" t="n"/>
+      <c r="X54" s="8" t="n"/>
+      <c r="Y54" s="8" t="n"/>
+      <c r="Z54" s="8" t="n"/>
       <c r="AA54" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -6832,13 +7050,13 @@
       </c>
       <c r="AB54" s="8" t="inlineStr">
         <is>
-          <t>11.4.2</t>
+          <t>11.20.2</t>
         </is>
       </c>
       <c r="AC54" s="8" t="n"/>
       <c r="AD54" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Cement concrete flooring &gt; M15</t>
+          <t>Other &gt; Glass strips</t>
         </is>
       </c>
       <c r="AE54" s="8" t="n"/>
@@ -6852,10 +7070,12 @@
       <c r="AM54" s="8" t="n"/>
       <c r="AN54" s="8" t="n"/>
       <c r="AO54" s="8" t="n"/>
-      <c r="AP54" s="8" t="n"/>
+      <c r="AP54" s="17" t="n">
+        <v>40</v>
+      </c>
       <c r="AQ54" s="8" t="n"/>
       <c r="AR54" s="17" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="AS54" s="8" t="n"/>
       <c r="AT54" s="8" t="n"/>
@@ -6864,26 +7084,26 @@
       <c r="AW54" s="8" t="n"/>
       <c r="AX54" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Cement concrete flooring — mass 6528.0 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 972.67 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[EXCLUDED] material: Glass strips — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0049</t>
+          <t>GMAP-0052</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C55" s="8" t="n"/>
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>18 mm thick cement plaster skirting (upto 30 cm height) with cement mortar 1:3 (1 cement : 3 coarse sand) finished with a floating coat of neat cement including rounding of junctions with floors.</t>
+          <t>Painting top of roofs with bitumen of approved quality at 17 Kg. per 10 square metre impregnated with a coat of coarse sand at 3/2 60 dm per 10 m including cleaning the slab surface with brushes and finally with a piece of cloth lightly soaked in kerosene oil complete with residual type petroleum bitumen of penetration 80/100.</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -6893,37 +7113,33 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>Finishes</t>
+          <t>Civil &amp; Sitework</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>Cement plaster skirting</t>
+          <t>Petroleum bitumen</t>
         </is>
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand</t>
+          <t>Bitumen, Coarse sand, Kerosene oil</t>
         </is>
       </c>
       <c r="J55" s="8" t="inlineStr">
         <is>
-          <t>Plaster</t>
+          <t>Paint/Finish</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L55" s="8" t="n"/>
-      <c r="M55" s="8" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
+      <c r="M55" s="8" t="n"/>
       <c r="N55" s="17" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="O55" s="8" t="inlineStr">
         <is>
@@ -6932,32 +7148,20 @@
       </c>
       <c r="P55" s="8" t="n"/>
       <c r="Q55" s="17" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="R55" s="8" t="n"/>
       <c r="S55" s="8" t="n"/>
       <c r="T55" s="8" t="n"/>
-      <c r="U55" s="17" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="W55" s="8" t="inlineStr">
-        <is>
-          <t>Area x thickness (18.0 mm, from description)</t>
-        </is>
-      </c>
+      <c r="U55" s="8" t="n"/>
+      <c r="V55" s="8" t="n"/>
+      <c r="W55" s="8" t="n"/>
       <c r="X55" s="17" t="n">
-        <v>1900</v>
-      </c>
-      <c r="Y55" s="17" t="n">
-        <v>61.32</v>
-      </c>
+        <v>1300</v>
+      </c>
+      <c r="Y55" s="8" t="n"/>
       <c r="Z55" s="17" t="n">
-        <v>0.163</v>
+        <v>0.95</v>
       </c>
       <c r="AA55" s="8" t="inlineStr">
         <is>
@@ -6966,13 +7170,13 @@
       </c>
       <c r="AB55" s="8" t="inlineStr">
         <is>
-          <t>11.10.1</t>
+          <t>12.29.1</t>
         </is>
       </c>
       <c r="AC55" s="8" t="n"/>
       <c r="AD55" s="8" t="inlineStr">
         <is>
-          <t>Plaster &gt; Cement plaster skirting &gt; 1:3</t>
+          <t>Paint/Finish &gt; Petroleum bitumen</t>
         </is>
       </c>
       <c r="AE55" s="8" t="n"/>
@@ -6987,12 +7191,8 @@
       <c r="AN55" s="8" t="n"/>
       <c r="AO55" s="8" t="n"/>
       <c r="AP55" s="8" t="n"/>
-      <c r="AQ55" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="AR55" s="17" t="n">
-        <v>18</v>
-      </c>
+      <c r="AQ55" s="8" t="n"/>
+      <c r="AR55" s="8" t="n"/>
       <c r="AS55" s="8" t="n"/>
       <c r="AT55" s="8" t="n"/>
       <c r="AU55" s="8" t="n"/>
@@ -7000,26 +7200,26 @@
       <c r="AW55" s="8" t="n"/>
       <c r="AX55" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Cement plaster skirting — mass 376.2 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 61.32 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
+          <t>[EXCLUDED] material: Petroleum bitumen — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0050</t>
+          <t>GMAP-0053</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C56" s="8" t="n"/>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>40 mm thick marble chips flooring, rubbed and polished to granolithic finish, under layer 31 mm thick cement concrete 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 12.5 mm nominal size) and top layer 9 mm thick with white black, chocolate, grey yellow or Baroda green marble chips of sizes from 4 mm to 7 mm nominal size laid in cement marble powder mix 3:1 (3 cement : 1 marble powder) by weight in proportion of 4:7 (4 cement marble powder mix : 7 marble chips) by volume including cement slurry etc., complete using dark shade pigment with ordinary cement.</t>
+          <t>Lime concrete terracing on roofs, average thickness 10 cm laid to fall with 25 mm nominal size brick aggregate and 50% lime mortar 1:2 (1 lime putty : 2 surkhi) rammed and finished with gur and belgiri treatment complete and covered with flat FPS brick tiles of class designation 100 grouted with cement mortar 1:3 (1 cement : 3 fine sand) mixed with 5% crude oil by wt. of cement, over 12 mm layer of cement mortar 1:3 (1 cement : 3 fine sand) and finished neat.</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -7029,17 +7229,17 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>Finishes</t>
+          <t>Civil &amp; Sitework</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>Marble chips flooring</t>
+          <t>Lime concrete</t>
         </is>
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>Marble chips, Cement, Coarse sand, Graded stone aggregate, Marble powder, Pigment</t>
+          <t>Lime putty, Surkhi, Brick aggregate, Brick tiles, Cement, Fine sand, Crude oil, Gur, Belgiri</t>
         </is>
       </c>
       <c r="J56" s="8" t="inlineStr">
@@ -7052,18 +7252,14 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="L56" s="8" t="inlineStr">
-        <is>
-          <t>M15</t>
-        </is>
-      </c>
+      <c r="L56" s="8" t="n"/>
       <c r="M56" s="8" t="inlineStr">
         <is>
-          <t>1:2:4</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="N56" s="17" t="n">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="O56" s="8" t="inlineStr">
         <is>
@@ -7072,13 +7268,13 @@
       </c>
       <c r="P56" s="8" t="n"/>
       <c r="Q56" s="17" t="n">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="R56" s="8" t="n"/>
       <c r="S56" s="8" t="n"/>
       <c r="T56" s="8" t="n"/>
       <c r="U56" s="17" t="n">
-        <v>0.36</v>
+        <v>6.5</v>
       </c>
       <c r="V56" s="8" t="inlineStr">
         <is>
@@ -7087,14 +7283,14 @@
       </c>
       <c r="W56" s="8" t="inlineStr">
         <is>
-          <t>Area x thickness (40.0 mm, from description)</t>
+          <t>Area x thickness (100.0 mm, from description)</t>
         </is>
       </c>
       <c r="X56" s="17" t="n">
         <v>2400</v>
       </c>
       <c r="Y56" s="17" t="n">
-        <v>128.74</v>
+        <v>2324.4</v>
       </c>
       <c r="Z56" s="17" t="n">
         <v>0.149</v>
@@ -7106,13 +7302,13 @@
       </c>
       <c r="AB56" s="8" t="inlineStr">
         <is>
-          <t>11.16.1</t>
+          <t>12.35.2</t>
         </is>
       </c>
       <c r="AC56" s="8" t="n"/>
       <c r="AD56" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Marble chips flooring &gt; M15</t>
+          <t>Concrete &gt; Lime concrete &gt; 1:2</t>
         </is>
       </c>
       <c r="AE56" s="8" t="n"/>
@@ -7129,7 +7325,7 @@
       <c r="AP56" s="8" t="n"/>
       <c r="AQ56" s="8" t="n"/>
       <c r="AR56" s="17" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="AS56" s="8" t="n"/>
       <c r="AT56" s="8" t="n"/>
@@ -7138,26 +7334,26 @@
       <c r="AW56" s="8" t="n"/>
       <c r="AX56" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Marble chips flooring — mass 864.0 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 128.74 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[OK] material: Lime concrete — mass 15600.0 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 2324.4 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0051</t>
+          <t>GMAP-0054</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>Add or deduct for providing and fixing glass strips in joints of terrazzo/cement concrete floors- 40 mm wide and 6 mm thick.</t>
+          <t>Providing and laying 25 mm thick burnt clay tiles 250x250x25 mm of approved quality over roofs with 1 cm side joints grouted with CM 1:3 (1 cement : 3 fine sand) over 15 mm thick bed of cement mortar 1:3 (1 cement : 3 fine sand) and finished neat.</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
@@ -7172,47 +7368,67 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>Glass strips</t>
+          <t>Burnt clay tiles</t>
         </is>
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>Glass</t>
+          <t>Burnt clay tiles, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J57" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Masonry</t>
         </is>
       </c>
       <c r="K57" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L57" s="8" t="n"/>
-      <c r="M57" s="8" t="n"/>
+      <c r="M57" s="8" t="inlineStr">
+        <is>
+          <t>1:3</t>
+        </is>
+      </c>
       <c r="N57" s="17" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="O57" s="8" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P57" s="8" t="n"/>
-      <c r="Q57" s="8" t="n"/>
-      <c r="R57" s="17" t="n">
-        <v>18</v>
-      </c>
+      <c r="Q57" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="R57" s="8" t="n"/>
       <c r="S57" s="8" t="n"/>
       <c r="T57" s="8" t="n"/>
-      <c r="U57" s="8" t="n"/>
-      <c r="V57" s="8" t="n"/>
-      <c r="W57" s="8" t="n"/>
-      <c r="X57" s="8" t="n"/>
-      <c r="Y57" s="8" t="n"/>
-      <c r="Z57" s="8" t="n"/>
+      <c r="U57" s="17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W57" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (25.0 mm, from description)</t>
+        </is>
+      </c>
+      <c r="X57" s="17" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Y57" s="17" t="n">
+        <v>306.72</v>
+      </c>
+      <c r="Z57" s="17" t="n">
+        <v>0.213</v>
+      </c>
       <c r="AA57" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -7220,13 +7436,13 @@
       </c>
       <c r="AB57" s="8" t="inlineStr">
         <is>
-          <t>11.20.2</t>
+          <t>N.S.I.</t>
         </is>
       </c>
       <c r="AC57" s="8" t="n"/>
       <c r="AD57" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Glass strips</t>
+          <t>Masonry &gt; Burnt clay tiles &gt; 1:3</t>
         </is>
       </c>
       <c r="AE57" s="8" t="n"/>
@@ -7239,13 +7455,15 @@
       <c r="AL57" s="8" t="n"/>
       <c r="AM57" s="8" t="n"/>
       <c r="AN57" s="8" t="n"/>
-      <c r="AO57" s="8" t="n"/>
+      <c r="AO57" s="17" t="n">
+        <v>250</v>
+      </c>
       <c r="AP57" s="17" t="n">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="AQ57" s="8" t="n"/>
       <c r="AR57" s="17" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="AS57" s="8" t="n"/>
       <c r="AT57" s="8" t="n"/>
@@ -7254,26 +7472,26 @@
       <c r="AW57" s="8" t="n"/>
       <c r="AX57" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Glass strips — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[OK] material: Burnt clay tiles — mass 1440.0 kg [area × thickness (derived)] × 0.213 kgCO2e/kg = 306.72 kgCO2e — ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0052</t>
+          <t>GMAP-0055</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C58" s="8" t="n"/>
       <c r="D58" s="8" t="n"/>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>Painting top of roofs with bitumen of approved quality at 17 Kg. per 10 square metre impregnated with a coat of coarse sand at 60 dm3 per 10 m2 including cleaning the slab surface with brushes and finally with a piece of cloth lightly soaked in kerosene oil complete with residual type petroleum bitumen of penetration 80/100.</t>
+          <t>Providing gola 15x15 cm in size in cement concrete mix 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) covered with brick tiles in CM 1:3 (1 cement : 3 coarse sand) as per drawing and specifications complete in all respects.</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -7288,17 +7506,17 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>Bitumen</t>
+          <t>Cement concrete gola</t>
         </is>
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>Petroleum bitumen, Coarse sand, Kerosene oil</t>
+          <t>Cement, Coarse sand, Graded stone aggregate, Brick tiles</t>
         </is>
       </c>
       <c r="J58" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="K58" s="8" t="inlineStr">
@@ -7306,32 +7524,40 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L58" s="8" t="n"/>
-      <c r="M58" s="8" t="n"/>
+      <c r="L58" s="8" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="M58" s="8" t="inlineStr">
+        <is>
+          <t>1:3:6</t>
+        </is>
+      </c>
       <c r="N58" s="17" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="O58" s="8" t="inlineStr">
         <is>
-          <t>sqm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="P58" s="8" t="n"/>
-      <c r="Q58" s="17" t="n">
-        <v>65</v>
-      </c>
-      <c r="R58" s="8" t="n"/>
+      <c r="Q58" s="8" t="n"/>
+      <c r="R58" s="17" t="n">
+        <v>46</v>
+      </c>
       <c r="S58" s="8" t="n"/>
       <c r="T58" s="8" t="n"/>
       <c r="U58" s="8" t="n"/>
       <c r="V58" s="8" t="n"/>
       <c r="W58" s="8" t="n"/>
       <c r="X58" s="17" t="n">
-        <v>1300</v>
+        <v>2400</v>
       </c>
       <c r="Y58" s="8" t="n"/>
       <c r="Z58" s="17" t="n">
-        <v>0.95</v>
+        <v>0.149</v>
       </c>
       <c r="AA58" s="8" t="inlineStr">
         <is>
@@ -7340,13 +7566,13 @@
       </c>
       <c r="AB58" s="8" t="inlineStr">
         <is>
-          <t>12.29.1</t>
+          <t>N.S.I.</t>
         </is>
       </c>
       <c r="AC58" s="8" t="n"/>
       <c r="AD58" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish &gt; Bitumen</t>
+          <t>Concrete &gt; Cement concrete gola &gt; M10</t>
         </is>
       </c>
       <c r="AE58" s="8" t="n"/>
@@ -7360,8 +7586,12 @@
       <c r="AM58" s="8" t="n"/>
       <c r="AN58" s="8" t="n"/>
       <c r="AO58" s="8" t="n"/>
-      <c r="AP58" s="8" t="n"/>
-      <c r="AQ58" s="8" t="n"/>
+      <c r="AP58" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="AQ58" s="17" t="n">
+        <v>150</v>
+      </c>
       <c r="AR58" s="8" t="n"/>
       <c r="AS58" s="8" t="n"/>
       <c r="AT58" s="8" t="n"/>
@@ -7370,26 +7600,26 @@
       <c r="AW58" s="8" t="n"/>
       <c r="AX58" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Bitumen — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Cement concrete gola — category 'Concrete' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0053</t>
+          <t>GMAP-0056</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C59" s="8" t="n"/>
       <c r="D59" s="8" t="n"/>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>Lime concrete terracing on roofs, average thickness 10 cm laid to fall with 25 mm nominal size brick aggregate and 50% lime mortar 1:2 (1 lime putty : 2 surkhi) rammed and finished with gur and belgiri treatment complete and covered with flat FPS brick tiles of class designation 100 grouted with cement mortar 1:3 (1 cement : 3 fine sand) mixed with 5% crude oil by wt. of cement, over 12 mm layer of cement mortar 1:3 (1 cement : 3 fine sand) and finished neat.</t>
+          <t>Making khurras 45 x 45 cm with average minimum thickness of 5 cm cement concrete 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size) over PVC sheet 1m x 1m x 400 micron, finished with 12 cement plaster 1:3 (1 cement : 3 coarse sand) and a coat of neat cement rounding the edges and making and finishing the outlet complete.</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -7404,12 +7634,12 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>Lime concrete</t>
+          <t>Cement concrete khurras</t>
         </is>
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>Brick aggregate, Lime putty, Surkhi, FPS brick tiles, Cement, Fine sand, Crude oil</t>
+          <t>Cement, Coarse sand, Graded stone aggregate, PVC sheet</t>
         </is>
       </c>
       <c r="J59" s="8" t="inlineStr">
@@ -7419,49 +7649,41 @@
       </c>
       <c r="K59" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L59" s="8" t="n"/>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L59" s="8" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
       <c r="M59" s="8" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>1:2:4</t>
         </is>
       </c>
       <c r="N59" s="17" t="n">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="O59" s="8" t="inlineStr">
         <is>
-          <t>sqm</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P59" s="8" t="n"/>
-      <c r="Q59" s="17" t="n">
-        <v>65</v>
-      </c>
+      <c r="Q59" s="8" t="n"/>
       <c r="R59" s="8" t="n"/>
       <c r="S59" s="8" t="n"/>
-      <c r="T59" s="8" t="n"/>
-      <c r="U59" s="17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="W59" s="8" t="inlineStr">
-        <is>
-          <t>Area x thickness (100.0 mm, from description)</t>
-        </is>
-      </c>
+      <c r="T59" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" s="8" t="n"/>
+      <c r="V59" s="8" t="n"/>
+      <c r="W59" s="8" t="n"/>
       <c r="X59" s="17" t="n">
         <v>2400</v>
       </c>
-      <c r="Y59" s="17" t="n">
-        <v>2324.4</v>
-      </c>
+      <c r="Y59" s="8" t="n"/>
       <c r="Z59" s="17" t="n">
         <v>0.149</v>
       </c>
@@ -7472,13 +7694,13 @@
       </c>
       <c r="AB59" s="8" t="inlineStr">
         <is>
-          <t>12.35.2</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="AC59" s="8" t="n"/>
       <c r="AD59" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Lime concrete &gt; 1:2</t>
+          <t>Concrete &gt; Cement concrete khurras &gt; M15</t>
         </is>
       </c>
       <c r="AE59" s="8" t="n"/>
@@ -7491,11 +7713,15 @@
       <c r="AL59" s="8" t="n"/>
       <c r="AM59" s="8" t="n"/>
       <c r="AN59" s="8" t="n"/>
-      <c r="AO59" s="8" t="n"/>
-      <c r="AP59" s="8" t="n"/>
+      <c r="AO59" s="17" t="n">
+        <v>450</v>
+      </c>
+      <c r="AP59" s="17" t="n">
+        <v>450</v>
+      </c>
       <c r="AQ59" s="8" t="n"/>
       <c r="AR59" s="17" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AS59" s="8" t="n"/>
       <c r="AT59" s="8" t="n"/>
@@ -7504,101 +7730,85 @@
       <c r="AW59" s="8" t="n"/>
       <c r="AX59" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Lime concrete — mass 15600.0 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 2324.4 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+          <t>[EXCLUDED] material: Cement concrete khurras — category 'Concrete' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0054</t>
+          <t>GMAP-0057</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C60" s="8" t="n"/>
       <c r="D60" s="8" t="n"/>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>Providing and laying 25 mm thick burnt clay tiles 250x250x25 mm of approved quality over roofs with 1 cm side joints grouted with CM 1:3 (1 cement : 3 fine sand) over 15 mm thick bed of cement mortar 1:3 (1 cement : 3 fine sand) and finished neat.</t>
+          <t>Providing and fixing on wallface 100 mm diameter CI rain water pipe including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand)</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
+          <t>Sub-Head - VIII, Sanitary Installation (Rain Water Pipes)</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>Finishes</t>
+          <t>Plumbing &amp; Sanitary</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>Burnt clay tiles</t>
+          <t>CI rain water pipe</t>
         </is>
       </c>
       <c r="I60" s="8" t="inlineStr">
         <is>
-          <t>Burnt clay tiles, Cement, Fine sand</t>
+          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J60" s="8" t="inlineStr">
         <is>
-          <t>Masonry</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K60" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L60" s="8" t="n"/>
       <c r="M60" s="8" t="inlineStr">
         <is>
-          <t>1:3</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="N60" s="17" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="O60" s="8" t="inlineStr">
         <is>
-          <t>sqm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="P60" s="8" t="n"/>
-      <c r="Q60" s="17" t="n">
-        <v>32</v>
-      </c>
-      <c r="R60" s="8" t="n"/>
+      <c r="Q60" s="8" t="n"/>
+      <c r="R60" s="17" t="n">
+        <v>10</v>
+      </c>
       <c r="S60" s="8" t="n"/>
       <c r="T60" s="8" t="n"/>
-      <c r="U60" s="17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="V60" s="8" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="W60" s="8" t="inlineStr">
-        <is>
-          <t>Area x thickness (25.0 mm, from description)</t>
-        </is>
-      </c>
-      <c r="X60" s="17" t="n">
-        <v>1800</v>
-      </c>
-      <c r="Y60" s="17" t="n">
-        <v>306.72</v>
-      </c>
-      <c r="Z60" s="17" t="n">
-        <v>0.213</v>
-      </c>
+      <c r="U60" s="8" t="n"/>
+      <c r="V60" s="8" t="n"/>
+      <c r="W60" s="8" t="n"/>
+      <c r="X60" s="8" t="n"/>
+      <c r="Y60" s="8" t="n"/>
+      <c r="Z60" s="8" t="n"/>
       <c r="AA60" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -7606,13 +7816,13 @@
       </c>
       <c r="AB60" s="8" t="inlineStr">
         <is>
-          <t>N.S.I.</t>
+          <t>12.69.2</t>
         </is>
       </c>
       <c r="AC60" s="8" t="n"/>
       <c r="AD60" s="8" t="inlineStr">
         <is>
-          <t>Masonry &gt; Burnt clay tiles &gt; 1:3</t>
+          <t>Other &gt; CI rain water pipe &gt; 1:2</t>
         </is>
       </c>
       <c r="AE60" s="8" t="n"/>
@@ -7625,68 +7835,64 @@
       <c r="AL60" s="8" t="n"/>
       <c r="AM60" s="8" t="n"/>
       <c r="AN60" s="8" t="n"/>
-      <c r="AO60" s="17" t="n">
-        <v>250</v>
-      </c>
-      <c r="AP60" s="17" t="n">
-        <v>250</v>
-      </c>
+      <c r="AO60" s="8" t="n"/>
+      <c r="AP60" s="8" t="n"/>
       <c r="AQ60" s="8" t="n"/>
-      <c r="AR60" s="17" t="n">
-        <v>25</v>
-      </c>
+      <c r="AR60" s="8" t="n"/>
       <c r="AS60" s="8" t="n"/>
-      <c r="AT60" s="8" t="n"/>
+      <c r="AT60" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="AU60" s="8" t="n"/>
       <c r="AV60" s="8" t="n"/>
       <c r="AW60" s="8" t="n"/>
       <c r="AX60" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Burnt clay tiles — mass 1440.0 kg [area × thickness (derived)] × 0.213 kgCO2e/kg = 306.72 kgCO2e — ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
+          <t>[EXCLUDED] material: CI rain water pipe — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0055</t>
+          <t>GMAP-0058</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C61" s="8" t="n"/>
       <c r="D61" s="8" t="n"/>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>Providing gola 15x15 cm in size in cement concrete mix 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) covered with brick tiles in CM 1:3 (1 cement : 3 coarse sand) as per drawing and specifications complete in all respects.</t>
+          <t>Providing and fixing 100 mm dia MS holderbat clamps of approved design to CI or SCI rain water pipes embedded in and including cement concrete blocks 10 x 10 x 10 cm of 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size) and cost of cutting holes and making good the walls etc.</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
+          <t>Sub-Head - VIII, Sanitary Installation (Rain Water Pipes)</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Plumbing &amp; Sanitary</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>Cement concrete gola</t>
+          <t>MS holderbat clamps</t>
         </is>
       </c>
       <c r="I61" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate, Brick tiles</t>
+          <t>Mild steel, Cement, Coarse sand, Graded stone aggregate</t>
         </is>
       </c>
       <c r="J61" s="8" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="K61" s="8" t="inlineStr">
@@ -7694,40 +7900,36 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L61" s="8" t="inlineStr">
-        <is>
-          <t>M10</t>
-        </is>
-      </c>
+      <c r="L61" s="8" t="n"/>
       <c r="M61" s="8" t="inlineStr">
         <is>
-          <t>1:3:6</t>
+          <t>1:2:4</t>
         </is>
       </c>
       <c r="N61" s="17" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="O61" s="8" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P61" s="8" t="n"/>
       <c r="Q61" s="8" t="n"/>
-      <c r="R61" s="17" t="n">
-        <v>46</v>
-      </c>
+      <c r="R61" s="8" t="n"/>
       <c r="S61" s="8" t="n"/>
-      <c r="T61" s="8" t="n"/>
+      <c r="T61" s="17" t="n">
+        <v>9</v>
+      </c>
       <c r="U61" s="8" t="n"/>
       <c r="V61" s="8" t="n"/>
       <c r="W61" s="8" t="n"/>
       <c r="X61" s="17" t="n">
-        <v>2400</v>
+        <v>7850</v>
       </c>
       <c r="Y61" s="8" t="n"/>
       <c r="Z61" s="17" t="n">
-        <v>0.149</v>
+        <v>1.55</v>
       </c>
       <c r="AA61" s="8" t="inlineStr">
         <is>
@@ -7736,13 +7938,13 @@
       </c>
       <c r="AB61" s="8" t="inlineStr">
         <is>
-          <t>N.S.I.</t>
+          <t>12.71.2</t>
         </is>
       </c>
       <c r="AC61" s="8" t="n"/>
       <c r="AD61" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Cement concrete gola &gt; M10</t>
+          <t>Steel &gt; MS holderbat clamps &gt; 1:2:4</t>
         </is>
       </c>
       <c r="AE61" s="8" t="n"/>
@@ -7755,66 +7957,70 @@
       <c r="AL61" s="8" t="n"/>
       <c r="AM61" s="8" t="n"/>
       <c r="AN61" s="8" t="n"/>
-      <c r="AO61" s="8" t="n"/>
+      <c r="AO61" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="AP61" s="17" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AQ61" s="17" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AR61" s="8" t="n"/>
       <c r="AS61" s="8" t="n"/>
-      <c r="AT61" s="8" t="n"/>
+      <c r="AT61" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="AU61" s="8" t="n"/>
       <c r="AV61" s="8" t="n"/>
       <c r="AW61" s="8" t="n"/>
       <c r="AX61" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Cement concrete gola — category 'Concrete' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: MS holderbat clamps — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0056</t>
+          <t>GMAP-0059</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>51a</t>
         </is>
       </c>
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Making khurras 45 x 45 cm with average minimum thickness of 5 cm cement concrete 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size) over PVC sheet 1m x 1m x 400 micron, finished with 12 cement plaster 1:3 (1 cement : 3 coarse sand) and a coat of neat cement rounding the edges and making and finishing the outlet complete.</t>
+          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) CI plain head 100 mm dia</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
+          <t>Sub-Head - VIII, Sanitary Installation (Rain Water Pipes)</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Plumbing &amp; Sanitary</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>Cement concrete khurras</t>
+          <t>CI plain head</t>
         </is>
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate, PVC sheet</t>
+          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J62" s="8" t="inlineStr">
         <is>
-          <t>Concrete</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K62" s="8" t="inlineStr">
@@ -7822,14 +8028,10 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L62" s="8" t="inlineStr">
-        <is>
-          <t>M15</t>
-        </is>
-      </c>
+      <c r="L62" s="8" t="n"/>
       <c r="M62" s="8" t="inlineStr">
         <is>
-          <t>1:2:4</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="N62" s="17" t="n">
@@ -7850,13 +8052,9 @@
       <c r="U62" s="8" t="n"/>
       <c r="V62" s="8" t="n"/>
       <c r="W62" s="8" t="n"/>
-      <c r="X62" s="17" t="n">
-        <v>2400</v>
-      </c>
+      <c r="X62" s="8" t="n"/>
       <c r="Y62" s="8" t="n"/>
-      <c r="Z62" s="17" t="n">
-        <v>0.149</v>
-      </c>
+      <c r="Z62" s="8" t="n"/>
       <c r="AA62" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -7864,13 +8062,13 @@
       </c>
       <c r="AB62" s="8" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>12.72.2.2</t>
         </is>
       </c>
       <c r="AC62" s="8" t="n"/>
       <c r="AD62" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Cement concrete khurras &gt; M15</t>
+          <t>Other &gt; CI plain head &gt; 1:2</t>
         </is>
       </c>
       <c r="AE62" s="8" t="n"/>
@@ -7883,43 +8081,39 @@
       <c r="AL62" s="8" t="n"/>
       <c r="AM62" s="8" t="n"/>
       <c r="AN62" s="8" t="n"/>
-      <c r="AO62" s="17" t="n">
-        <v>450</v>
-      </c>
-      <c r="AP62" s="17" t="n">
-        <v>450</v>
-      </c>
+      <c r="AO62" s="8" t="n"/>
+      <c r="AP62" s="8" t="n"/>
       <c r="AQ62" s="8" t="n"/>
-      <c r="AR62" s="17" t="n">
-        <v>50</v>
-      </c>
+      <c r="AR62" s="8" t="n"/>
       <c r="AS62" s="8" t="n"/>
-      <c r="AT62" s="8" t="n"/>
+      <c r="AT62" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="AU62" s="8" t="n"/>
       <c r="AV62" s="8" t="n"/>
       <c r="AW62" s="8" t="n"/>
       <c r="AX62" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Cement concrete khurras — category 'Concrete' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: CI plain head — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0057</t>
+          <t>GMAP-0060</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51b</t>
         </is>
       </c>
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing on wallface 100 mm diameter CI rain water pipe including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand)</t>
+          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) CI plain shoe - 100 mm dia</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
@@ -7934,7 +8128,7 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>Cast Iron rain water pipe</t>
+          <t>CI plain shoe</t>
         </is>
       </c>
       <c r="I63" s="8" t="inlineStr">
@@ -7944,7 +8138,7 @@
       </c>
       <c r="J63" s="8" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K63" s="8" t="inlineStr">
@@ -7959,30 +8153,26 @@
         </is>
       </c>
       <c r="N63" s="17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O63" s="8" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>nos</t>
         </is>
       </c>
       <c r="P63" s="8" t="n"/>
       <c r="Q63" s="8" t="n"/>
-      <c r="R63" s="17" t="n">
-        <v>10</v>
-      </c>
+      <c r="R63" s="8" t="n"/>
       <c r="S63" s="8" t="n"/>
-      <c r="T63" s="8" t="n"/>
+      <c r="T63" s="17" t="n">
+        <v>3</v>
+      </c>
       <c r="U63" s="8" t="n"/>
       <c r="V63" s="8" t="n"/>
       <c r="W63" s="8" t="n"/>
-      <c r="X63" s="17" t="n">
-        <v>7850</v>
-      </c>
+      <c r="X63" s="8" t="n"/>
       <c r="Y63" s="8" t="n"/>
-      <c r="Z63" s="17" t="n">
-        <v>1.55</v>
-      </c>
+      <c r="Z63" s="8" t="n"/>
       <c r="AA63" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -7990,13 +8180,13 @@
       </c>
       <c r="AB63" s="8" t="inlineStr">
         <is>
-          <t>12.69.2</t>
+          <t>12.72.3.2</t>
         </is>
       </c>
       <c r="AC63" s="8" t="n"/>
       <c r="AD63" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Cast Iron rain water pipe &gt; 1:2</t>
+          <t>Other &gt; CI plain shoe &gt; 1:2</t>
         </is>
       </c>
       <c r="AE63" s="8" t="n"/>
@@ -8022,26 +8212,26 @@
       <c r="AW63" s="8" t="n"/>
       <c r="AX63" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Cast Iron rain water pipe — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: CI plain shoe — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0058</t>
+          <t>GMAP-0061</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51c</t>
         </is>
       </c>
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing 100 mm dia MS holderbat clamps of approved design to CI or SCI rain water pipes embedded in and including cement concrete blocks 10 x 10 x 10 cm of 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size) and cost of cutting holes and making good the walls etc.</t>
+          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) CI plain bend - 100 mm dia</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
@@ -8056,17 +8246,17 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>MS holderbat clamps</t>
+          <t>CI plain bend</t>
         </is>
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>Mild steel, Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J64" s="8" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K64" s="8" t="inlineStr">
@@ -8077,11 +8267,11 @@
       <c r="L64" s="8" t="n"/>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>1:2:4</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="N64" s="17" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O64" s="8" t="inlineStr">
         <is>
@@ -8093,18 +8283,14 @@
       <c r="R64" s="8" t="n"/>
       <c r="S64" s="8" t="n"/>
       <c r="T64" s="17" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U64" s="8" t="n"/>
       <c r="V64" s="8" t="n"/>
       <c r="W64" s="8" t="n"/>
-      <c r="X64" s="17" t="n">
-        <v>7850</v>
-      </c>
+      <c r="X64" s="8" t="n"/>
       <c r="Y64" s="8" t="n"/>
-      <c r="Z64" s="17" t="n">
-        <v>1.55</v>
-      </c>
+      <c r="Z64" s="8" t="n"/>
       <c r="AA64" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -8112,13 +8298,13 @@
       </c>
       <c r="AB64" s="8" t="inlineStr">
         <is>
-          <t>12.71.2</t>
+          <t>12.72.1.2</t>
         </is>
       </c>
       <c r="AC64" s="8" t="n"/>
       <c r="AD64" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; MS holderbat clamps &gt; 1:2:4</t>
+          <t>Other &gt; CI plain bend &gt; 1:2</t>
         </is>
       </c>
       <c r="AE64" s="8" t="n"/>
@@ -8144,51 +8330,51 @@
       <c r="AW64" s="8" t="n"/>
       <c r="AX64" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: MS holderbat clamps — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: CI plain bend — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0059</t>
+          <t>GMAP-0062</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>51a</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C65" s="8" t="n"/>
       <c r="D65" s="8" t="n"/>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) i) CI plain head 100 mm dia</t>
+          <t>12 mm cement plaster of mix 1:6 (1 cement : 6 fine sand)</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - VIII, Sanitary Installation (Rain Water Pipes)</t>
+          <t>Sub-Head - IX, Plastering</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>Plumbing &amp; Sanitary</t>
+          <t>Finishes</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>CI plain head</t>
+          <t>Cement plaster</t>
         </is>
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
+          <t>Cement, Fine sand</t>
         </is>
       </c>
       <c r="J65" s="8" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Plaster</t>
         </is>
       </c>
       <c r="K65" s="8" t="inlineStr">
@@ -8199,33 +8385,31 @@
       <c r="L65" s="8" t="n"/>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>1:6</t>
         </is>
       </c>
       <c r="N65" s="17" t="n">
-        <v>3</v>
+        <v>220</v>
       </c>
       <c r="O65" s="8" t="inlineStr">
         <is>
-          <t>nos</t>
+          <t>Sq.m .</t>
         </is>
       </c>
       <c r="P65" s="8" t="n"/>
       <c r="Q65" s="8" t="n"/>
       <c r="R65" s="8" t="n"/>
       <c r="S65" s="8" t="n"/>
-      <c r="T65" s="17" t="n">
-        <v>3</v>
-      </c>
+      <c r="T65" s="8" t="n"/>
       <c r="U65" s="8" t="n"/>
       <c r="V65" s="8" t="n"/>
       <c r="W65" s="8" t="n"/>
       <c r="X65" s="17" t="n">
-        <v>7850</v>
+        <v>1900</v>
       </c>
       <c r="Y65" s="8" t="n"/>
       <c r="Z65" s="17" t="n">
-        <v>1.55</v>
+        <v>0.163</v>
       </c>
       <c r="AA65" s="8" t="inlineStr">
         <is>
@@ -8234,13 +8418,13 @@
       </c>
       <c r="AB65" s="8" t="inlineStr">
         <is>
-          <t>12.72.2.2</t>
+          <t>13.8.4</t>
         </is>
       </c>
       <c r="AC65" s="8" t="n"/>
       <c r="AD65" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; CI plain head &gt; 1:2</t>
+          <t>Plaster &gt; Cement plaster &gt; 1:6</t>
         </is>
       </c>
       <c r="AE65" s="8" t="n"/>
@@ -8256,98 +8440,110 @@
       <c r="AO65" s="8" t="n"/>
       <c r="AP65" s="8" t="n"/>
       <c r="AQ65" s="8" t="n"/>
-      <c r="AR65" s="8" t="n"/>
+      <c r="AR65" s="17" t="n">
+        <v>12</v>
+      </c>
       <c r="AS65" s="8" t="n"/>
-      <c r="AT65" s="17" t="n">
-        <v>100</v>
-      </c>
+      <c r="AT65" s="8" t="n"/>
       <c r="AU65" s="8" t="n"/>
       <c r="AV65" s="8" t="n"/>
       <c r="AW65" s="8" t="n"/>
       <c r="AX65" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: CI plain head — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Cement plaster — category 'Plaster' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0060</t>
+          <t>GMAP-0063</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>51b</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C66" s="8" t="n"/>
       <c r="D66" s="8" t="n"/>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) ii) CI plain shoe - 100 mm dia</t>
+          <t>15 mm cement plaster on the rough side of single or half brick wall of mix 1:6 (1 cement : 6 fine sand)</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - VIII, Sanitary Installation (Rain Water Pipes)</t>
+          <t>Sub-Head - IX, Plastering</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>Plumbing &amp; Sanitary</t>
+          <t>Finishes</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>CI plain shoe</t>
+          <t>Cement plaster</t>
         </is>
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
+          <t>Cement, Fine sand</t>
         </is>
       </c>
       <c r="J66" s="8" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Plaster</t>
         </is>
       </c>
       <c r="K66" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L66" s="8" t="n"/>
       <c r="M66" s="8" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>1:6</t>
         </is>
       </c>
       <c r="N66" s="17" t="n">
-        <v>3</v>
+        <v>220</v>
       </c>
       <c r="O66" s="8" t="inlineStr">
         <is>
-          <t>nos</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P66" s="8" t="n"/>
-      <c r="Q66" s="8" t="n"/>
+      <c r="Q66" s="17" t="n">
+        <v>220</v>
+      </c>
       <c r="R66" s="8" t="n"/>
       <c r="S66" s="8" t="n"/>
-      <c r="T66" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U66" s="8" t="n"/>
-      <c r="V66" s="8" t="n"/>
-      <c r="W66" s="8" t="n"/>
+      <c r="T66" s="8" t="n"/>
+      <c r="U66" s="17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V66" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W66" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (15.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X66" s="17" t="n">
-        <v>7850</v>
-      </c>
-      <c r="Y66" s="8" t="n"/>
+        <v>1900</v>
+      </c>
+      <c r="Y66" s="17" t="n">
+        <v>1022.01</v>
+      </c>
       <c r="Z66" s="17" t="n">
-        <v>1.55</v>
+        <v>0.163</v>
       </c>
       <c r="AA66" s="8" t="inlineStr">
         <is>
@@ -8356,13 +8552,13 @@
       </c>
       <c r="AB66" s="8" t="inlineStr">
         <is>
-          <t>12.72.3.2</t>
+          <t>13.9.4</t>
         </is>
       </c>
       <c r="AC66" s="8" t="n"/>
       <c r="AD66" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; CI plain shoe &gt; 1:2</t>
+          <t>Plaster &gt; Cement plaster &gt; 1:6</t>
         </is>
       </c>
       <c r="AE66" s="8" t="n"/>
@@ -8378,98 +8574,110 @@
       <c r="AO66" s="8" t="n"/>
       <c r="AP66" s="8" t="n"/>
       <c r="AQ66" s="8" t="n"/>
-      <c r="AR66" s="8" t="n"/>
+      <c r="AR66" s="17" t="n">
+        <v>15</v>
+      </c>
       <c r="AS66" s="8" t="n"/>
-      <c r="AT66" s="17" t="n">
-        <v>100</v>
-      </c>
+      <c r="AT66" s="8" t="n"/>
       <c r="AU66" s="8" t="n"/>
       <c r="AV66" s="8" t="n"/>
       <c r="AW66" s="8" t="n"/>
       <c r="AX66" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: CI plain shoe — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[OK] material: Cement plaster — mass 6270.0 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 1022.01 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0061</t>
+          <t>GMAP-0064</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>51c</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C67" s="8" t="n"/>
       <c r="D67" s="8" t="n"/>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) iii) CI plain bend - 100 mm dia</t>
+          <t>6 mm cement plaster of mix 1:3 (1 cement : 3 fine sand) finished with a floating coat of neat cement and thick coat of lime wash on top of walls when dry for bearing of RCC slabs and beams.</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - VIII, Sanitary Installation (Rain Water Pipes)</t>
+          <t>Sub-Head - IX, Plastering</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>Plumbing &amp; Sanitary</t>
+          <t>Finishes</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>CI plain bend</t>
+          <t>Cement plaster</t>
         </is>
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
+          <t>Cement, Fine sand, Lime wash</t>
         </is>
       </c>
       <c r="J67" s="8" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Plaster</t>
         </is>
       </c>
       <c r="K67" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L67" s="8" t="n"/>
       <c r="M67" s="8" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="N67" s="17" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="O67" s="8" t="inlineStr">
         <is>
-          <t>nos</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P67" s="8" t="n"/>
-      <c r="Q67" s="8" t="n"/>
+      <c r="Q67" s="17" t="n">
+        <v>19</v>
+      </c>
       <c r="R67" s="8" t="n"/>
       <c r="S67" s="8" t="n"/>
-      <c r="T67" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U67" s="8" t="n"/>
-      <c r="V67" s="8" t="n"/>
-      <c r="W67" s="8" t="n"/>
+      <c r="T67" s="8" t="n"/>
+      <c r="U67" s="17" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="V67" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W67" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (6.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X67" s="17" t="n">
-        <v>7850</v>
-      </c>
-      <c r="Y67" s="8" t="n"/>
+        <v>1900</v>
+      </c>
+      <c r="Y67" s="17" t="n">
+        <v>35.31</v>
+      </c>
       <c r="Z67" s="17" t="n">
-        <v>1.55</v>
+        <v>0.163</v>
       </c>
       <c r="AA67" s="8" t="inlineStr">
         <is>
@@ -8478,13 +8686,13 @@
       </c>
       <c r="AB67" s="8" t="inlineStr">
         <is>
-          <t>12.72.1.2</t>
+          <t>13.25</t>
         </is>
       </c>
       <c r="AC67" s="8" t="n"/>
       <c r="AD67" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; CI plain bend &gt; 1:2</t>
+          <t>Plaster &gt; Cement plaster &gt; 1:3</t>
         </is>
       </c>
       <c r="AE67" s="8" t="n"/>
@@ -8500,36 +8708,36 @@
       <c r="AO67" s="8" t="n"/>
       <c r="AP67" s="8" t="n"/>
       <c r="AQ67" s="8" t="n"/>
-      <c r="AR67" s="8" t="n"/>
+      <c r="AR67" s="17" t="n">
+        <v>6</v>
+      </c>
       <c r="AS67" s="8" t="n"/>
-      <c r="AT67" s="17" t="n">
-        <v>100</v>
-      </c>
+      <c r="AT67" s="8" t="n"/>
       <c r="AU67" s="8" t="n"/>
       <c r="AV67" s="8" t="n"/>
       <c r="AW67" s="8" t="n"/>
       <c r="AX67" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: CI plain bend — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[OK] material: Cement plaster — mass 216.6 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 35.31 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0062</t>
+          <t>GMAP-0065</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C68" s="8" t="n"/>
       <c r="D68" s="8" t="n"/>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>12 mm cement plaster of mix 1:6 (1 cement : 6 fine sand)</t>
+          <t>18 mm plastering with terrazzo finish for dado rubbed and polished complete, under layer 12 mm thick cement plaster 1:3 (1 cement : 3 coarse sand) and top layer 6 mm thick white, black, chocolate, grey, yellow or Baroda green marble chips of 3 mm and down size laid in cement marble powder mix 3:1 (3 cement : 1 marble powder) by weight in proportion of 4:7 (4 cement marble powder mix : 7 marble chips) by volume.</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
@@ -8544,12 +8752,12 @@
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>Cement plaster</t>
+          <t>Terrazzo plaster</t>
         </is>
       </c>
       <c r="I68" s="8" t="inlineStr">
         <is>
-          <t>Cement, Fine sand</t>
+          <t>Cement, Coarse sand, Marble chips, Marble powder</t>
         </is>
       </c>
       <c r="J68" s="8" t="inlineStr">
@@ -8565,11 +8773,11 @@
       <c r="L68" s="8" t="n"/>
       <c r="M68" s="8" t="inlineStr">
         <is>
-          <t>1:6</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="N68" s="17" t="n">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="O68" s="8" t="inlineStr">
         <is>
@@ -8578,13 +8786,13 @@
       </c>
       <c r="P68" s="8" t="n"/>
       <c r="Q68" s="17" t="n">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="R68" s="8" t="n"/>
       <c r="S68" s="8" t="n"/>
       <c r="T68" s="8" t="n"/>
       <c r="U68" s="17" t="n">
-        <v>2.64</v>
+        <v>0.36</v>
       </c>
       <c r="V68" s="8" t="inlineStr">
         <is>
@@ -8593,14 +8801,14 @@
       </c>
       <c r="W68" s="8" t="inlineStr">
         <is>
-          <t>Area x thickness (12.0 mm, from description)</t>
+          <t>Area x thickness (18.0 mm, from description)</t>
         </is>
       </c>
       <c r="X68" s="17" t="n">
         <v>1900</v>
       </c>
       <c r="Y68" s="17" t="n">
-        <v>817.61</v>
+        <v>111.49</v>
       </c>
       <c r="Z68" s="17" t="n">
         <v>0.163</v>
@@ -8612,13 +8820,13 @@
       </c>
       <c r="AB68" s="8" t="inlineStr">
         <is>
-          <t>13.8.4</t>
+          <t>5.31/13.24.1</t>
         </is>
       </c>
       <c r="AC68" s="8" t="n"/>
       <c r="AD68" s="8" t="inlineStr">
         <is>
-          <t>Plaster &gt; Cement plaster &gt; 1:6</t>
+          <t>Plaster &gt; Terrazzo plaster &gt; 1:3</t>
         </is>
       </c>
       <c r="AE68" s="8" t="n"/>
@@ -8635,7 +8843,7 @@
       <c r="AP68" s="8" t="n"/>
       <c r="AQ68" s="8" t="n"/>
       <c r="AR68" s="17" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AS68" s="8" t="n"/>
       <c r="AT68" s="8" t="n"/>
@@ -8644,26 +8852,26 @@
       <c r="AW68" s="8" t="n"/>
       <c r="AX68" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Cement plaster — mass 5016.0 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 817.61 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
+          <t>[OK] material: Terrazzo plaster — mass 684.0 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 111.49 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0063</t>
+          <t>GMAP-0066</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C69" s="8" t="n"/>
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>15 mm cement plaster on the rough side of single or half brick wall of mix 1:6 (1 cement : 6 fine sand)</t>
+          <t>Finishing and plastering the exposed surface of RCC with cement mortar 1:3</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
@@ -8678,12 +8886,12 @@
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>Cement plaster</t>
+          <t>Cement mortar plaster</t>
         </is>
       </c>
       <c r="I69" s="8" t="inlineStr">
         <is>
-          <t>Cement, Fine sand</t>
+          <t>Cement, Sand</t>
         </is>
       </c>
       <c r="J69" s="8" t="inlineStr">
@@ -8693,17 +8901,17 @@
       </c>
       <c r="K69" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L69" s="8" t="n"/>
       <c r="M69" s="8" t="inlineStr">
         <is>
-          <t>1:6</t>
+          <t>1:3</t>
         </is>
       </c>
       <c r="N69" s="17" t="n">
-        <v>220</v>
+        <v>155</v>
       </c>
       <c r="O69" s="8" t="inlineStr">
         <is>
@@ -8712,30 +8920,18 @@
       </c>
       <c r="P69" s="8" t="n"/>
       <c r="Q69" s="17" t="n">
-        <v>220</v>
+        <v>155</v>
       </c>
       <c r="R69" s="8" t="n"/>
       <c r="S69" s="8" t="n"/>
       <c r="T69" s="8" t="n"/>
-      <c r="U69" s="17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V69" s="8" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="W69" s="8" t="inlineStr">
-        <is>
-          <t>Area x thickness (15.0 mm, from description)</t>
-        </is>
-      </c>
+      <c r="U69" s="8" t="n"/>
+      <c r="V69" s="8" t="n"/>
+      <c r="W69" s="8" t="n"/>
       <c r="X69" s="17" t="n">
         <v>1900</v>
       </c>
-      <c r="Y69" s="17" t="n">
-        <v>1022.01</v>
-      </c>
+      <c r="Y69" s="8" t="n"/>
       <c r="Z69" s="17" t="n">
         <v>0.163</v>
       </c>
@@ -8746,13 +8942,13 @@
       </c>
       <c r="AB69" s="8" t="inlineStr">
         <is>
-          <t>13.9.4</t>
+          <t>13.70.1</t>
         </is>
       </c>
       <c r="AC69" s="8" t="n"/>
       <c r="AD69" s="8" t="inlineStr">
         <is>
-          <t>Plaster &gt; Cement plaster &gt; 1:6</t>
+          <t>Plaster &gt; Cement mortar plaster &gt; 1:3</t>
         </is>
       </c>
       <c r="AE69" s="8" t="n"/>
@@ -8768,9 +8964,7 @@
       <c r="AO69" s="8" t="n"/>
       <c r="AP69" s="8" t="n"/>
       <c r="AQ69" s="8" t="n"/>
-      <c r="AR69" s="17" t="n">
-        <v>15</v>
-      </c>
+      <c r="AR69" s="8" t="n"/>
       <c r="AS69" s="8" t="n"/>
       <c r="AT69" s="8" t="n"/>
       <c r="AU69" s="8" t="n"/>
@@ -8778,31 +8972,31 @@
       <c r="AW69" s="8" t="n"/>
       <c r="AX69" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Cement plaster — mass 6270.0 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 1022.01 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
+          <t>[EXCLUDED] material: Cement mortar plaster — category 'Plaster' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0064</t>
+          <t>GMAP-0067</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>57</t>
         </is>
       </c>
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>6 mm cement plaster of mix 1:3 (1 cement : 3 fine sand) finished with a floating coat of neat cement and thick coat of lime wash on top of walls when dry for bearing of RCC slabs and beams.</t>
+          <t>White washing with lime to give an even shade on new work (three or more coats).</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - IX, Plastering</t>
+          <t>Sub-Head - X, White/Colour Washing &amp; Painting</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
@@ -8812,32 +9006,28 @@
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>Cement plaster</t>
+          <t>Lime white wash</t>
         </is>
       </c>
       <c r="I70" s="8" t="inlineStr">
         <is>
-          <t>Cement, Fine sand, Lime wash</t>
+          <t>Lime</t>
         </is>
       </c>
       <c r="J70" s="8" t="inlineStr">
         <is>
-          <t>Plaster</t>
+          <t>Paint/Finish</t>
         </is>
       </c>
       <c r="K70" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L70" s="8" t="n"/>
-      <c r="M70" s="8" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
+      <c r="M70" s="8" t="n"/>
       <c r="N70" s="17" t="n">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="O70" s="8" t="inlineStr">
         <is>
@@ -8846,32 +9036,20 @@
       </c>
       <c r="P70" s="8" t="n"/>
       <c r="Q70" s="17" t="n">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="R70" s="8" t="n"/>
       <c r="S70" s="8" t="n"/>
       <c r="T70" s="8" t="n"/>
-      <c r="U70" s="17" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="V70" s="8" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="W70" s="8" t="inlineStr">
-        <is>
-          <t>Area x thickness (6.0 mm, from description)</t>
-        </is>
-      </c>
+      <c r="U70" s="8" t="n"/>
+      <c r="V70" s="8" t="n"/>
+      <c r="W70" s="8" t="n"/>
       <c r="X70" s="17" t="n">
-        <v>1900</v>
-      </c>
-      <c r="Y70" s="17" t="n">
-        <v>35.31</v>
-      </c>
+        <v>1300</v>
+      </c>
+      <c r="Y70" s="8" t="n"/>
       <c r="Z70" s="17" t="n">
-        <v>0.163</v>
+        <v>0.95</v>
       </c>
       <c r="AA70" s="8" t="inlineStr">
         <is>
@@ -8880,13 +9058,13 @@
       </c>
       <c r="AB70" s="8" t="inlineStr">
         <is>
-          <t>13.25</t>
+          <t>13.73.1</t>
         </is>
       </c>
       <c r="AC70" s="8" t="n"/>
       <c r="AD70" s="8" t="inlineStr">
         <is>
-          <t>Plaster &gt; Cement plaster &gt; 1:3</t>
+          <t>Paint/Finish &gt; Lime white wash</t>
         </is>
       </c>
       <c r="AE70" s="8" t="n"/>
@@ -8902,9 +9080,7 @@
       <c r="AO70" s="8" t="n"/>
       <c r="AP70" s="8" t="n"/>
       <c r="AQ70" s="8" t="n"/>
-      <c r="AR70" s="17" t="n">
-        <v>6</v>
-      </c>
+      <c r="AR70" s="8" t="n"/>
       <c r="AS70" s="8" t="n"/>
       <c r="AT70" s="8" t="n"/>
       <c r="AU70" s="8" t="n"/>
@@ -8912,31 +9088,31 @@
       <c r="AW70" s="8" t="n"/>
       <c r="AX70" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Cement plaster — mass 216.6 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 35.31 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
+          <t>[EXCLUDED] material: Lime white wash — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>GMAP-0065</t>
+          <t>GMAP-0068</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>18 mm plastering with terrazzo finish for dado rubbed and polished complete, under layer 12 mm thick cement plaster 1:3 (1 cement : 3 coarse sand) and top layer 6 mm thick white, black, chocolate, grey, yellow or Baroda green marble chips of 3 mm and down size laid in cement marble powder mix 3:1 (3 cement : 1 marble powder) by weight in proportion of 4:7 (4 cement marble powder mix : 7 marble chips) by volume.</t>
+          <t>Colour washing such as green, blue or buff to give an even shade on new work (two or more coats) with a base coat of white washing with lime.</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - IX, Plastering</t>
+          <t>Sub-Head - X, White/Colour Washing &amp; Painting</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
@@ -8946,32 +9122,28 @@
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>Terrazzo plaster</t>
+          <t>Colour wash</t>
         </is>
       </c>
       <c r="I71" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Marble chips, Marble powder</t>
+          <t>Lime, Colour wash</t>
         </is>
       </c>
       <c r="J71" s="8" t="inlineStr">
         <is>
-          <t>Plaster</t>
+          <t>Paint/Finish</t>
         </is>
       </c>
       <c r="K71" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L71" s="8" t="n"/>
-      <c r="M71" s="8" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
+      <c r="M71" s="8" t="n"/>
       <c r="N71" s="17" t="n">
-        <v>20</v>
+        <v>285</v>
       </c>
       <c r="O71" s="8" t="inlineStr">
         <is>
@@ -8980,32 +9152,20 @@
       </c>
       <c r="P71" s="8" t="n"/>
       <c r="Q71" s="17" t="n">
-        <v>20</v>
+        <v>285</v>
       </c>
       <c r="R71" s="8" t="n"/>
       <c r="S71" s="8" t="n"/>
       <c r="T71" s="8" t="n"/>
-      <c r="U71" s="17" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="V71" s="8" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="W71" s="8" t="inlineStr">
-        <is>
-          <t>Area x thickness (18.0 mm, from description)</t>
-        </is>
-      </c>
+      <c r="U71" s="8" t="n"/>
+      <c r="V71" s="8" t="n"/>
+      <c r="W71" s="8" t="n"/>
       <c r="X71" s="17" t="n">
-        <v>1900</v>
-      </c>
-      <c r="Y71" s="17" t="n">
-        <v>111.49</v>
-      </c>
+        <v>1300</v>
+      </c>
+      <c r="Y71" s="8" t="n"/>
       <c r="Z71" s="17" t="n">
-        <v>0.163</v>
+        <v>0.95</v>
       </c>
       <c r="AA71" s="8" t="inlineStr">
         <is>
@@ -9014,13 +9174,13 @@
       </c>
       <c r="AB71" s="8" t="inlineStr">
         <is>
-          <t>5.31/13.24.1</t>
+          <t>13.81.1</t>
         </is>
       </c>
       <c r="AC71" s="8" t="n"/>
       <c r="AD71" s="8" t="inlineStr">
         <is>
-          <t>Plaster &gt; Terrazzo plaster &gt; 1:3</t>
+          <t>Paint/Finish &gt; Colour wash</t>
         </is>
       </c>
       <c r="AE71" s="8" t="n"/>
@@ -9036,9 +9196,7 @@
       <c r="AO71" s="8" t="n"/>
       <c r="AP71" s="8" t="n"/>
       <c r="AQ71" s="8" t="n"/>
-      <c r="AR71" s="17" t="n">
-        <v>18</v>
-      </c>
+      <c r="AR71" s="8" t="n"/>
       <c r="AS71" s="8" t="n"/>
       <c r="AT71" s="8" t="n"/>
       <c r="AU71" s="8" t="n"/>
@@ -9046,376 +9204,279 @@
       <c r="AW71" s="8" t="n"/>
       <c r="AX71" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Terrazzo plaster — mass 684.0 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 111.49 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
+          <t>[EXCLUDED] material: Colour wash — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>GMAP-0066</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="n"/>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>Finishing and plastering the exposed surface of RCC with cement mortar 1:3</t>
-        </is>
-      </c>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>Sub-Head - IX, Plastering</t>
-        </is>
-      </c>
-      <c r="G72" s="8" t="inlineStr">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>GMAP-0069</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Applying priming coat with ready mixed pink or gray primer of approved brand and manufacture - on wood work (hard and soft wood)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Sub-Head - X, White/Colour Washing &amp; Painting</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H72" s="8" t="inlineStr">
-        <is>
-          <t>Cement plaster</t>
-        </is>
-      </c>
-      <c r="I72" s="8" t="inlineStr">
-        <is>
-          <t>Cement, Sand</t>
-        </is>
-      </c>
-      <c r="J72" s="8" t="inlineStr">
-        <is>
-          <t>Plaster</t>
-        </is>
-      </c>
-      <c r="K72" s="8" t="inlineStr">
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Primer</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Pink or gray primer</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Paint/Finish</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="L72" s="8" t="n"/>
-      <c r="M72" s="8" t="inlineStr">
-        <is>
-          <t>1:3</t>
-        </is>
-      </c>
-      <c r="N72" s="17" t="n">
-        <v>155</v>
-      </c>
-      <c r="O72" s="8" t="inlineStr">
+      <c r="N72" s="18" t="n">
+        <v>47</v>
+      </c>
+      <c r="O72" t="inlineStr">
         <is>
           <t>sqm</t>
         </is>
       </c>
-      <c r="P72" s="8" t="n"/>
-      <c r="Q72" s="17" t="n">
-        <v>155</v>
-      </c>
-      <c r="R72" s="8" t="n"/>
-      <c r="S72" s="8" t="n"/>
-      <c r="T72" s="8" t="n"/>
-      <c r="U72" s="8" t="n"/>
-      <c r="V72" s="8" t="n"/>
-      <c r="W72" s="8" t="n"/>
-      <c r="X72" s="17" t="n">
-        <v>1900</v>
-      </c>
-      <c r="Y72" s="8" t="n"/>
-      <c r="Z72" s="17" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="AA72" s="8" t="inlineStr">
+      <c r="Q72" s="18" t="n">
+        <v>47</v>
+      </c>
+      <c r="X72" s="18" t="n">
+        <v>1300</v>
+      </c>
+      <c r="Z72" s="18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AA72" t="inlineStr">
         <is>
           <t>DSR 1989</t>
         </is>
       </c>
-      <c r="AB72" s="8" t="inlineStr">
-        <is>
-          <t>13.70.1</t>
-        </is>
-      </c>
-      <c r="AC72" s="8" t="n"/>
-      <c r="AD72" s="8" t="inlineStr">
-        <is>
-          <t>Plaster &gt; Cement plaster &gt; 1:3</t>
-        </is>
-      </c>
-      <c r="AE72" s="8" t="n"/>
-      <c r="AF72" s="8" t="n"/>
-      <c r="AG72" s="8" t="n"/>
-      <c r="AH72" s="8" t="n"/>
-      <c r="AI72" s="8" t="n"/>
-      <c r="AJ72" s="8" t="n"/>
-      <c r="AK72" s="8" t="n"/>
-      <c r="AL72" s="8" t="n"/>
-      <c r="AM72" s="8" t="n"/>
-      <c r="AN72" s="8" t="n"/>
-      <c r="AO72" s="8" t="n"/>
-      <c r="AP72" s="8" t="n"/>
-      <c r="AQ72" s="8" t="n"/>
-      <c r="AR72" s="8" t="n"/>
-      <c r="AS72" s="8" t="n"/>
-      <c r="AT72" s="8" t="n"/>
-      <c r="AU72" s="8" t="n"/>
-      <c r="AV72" s="8" t="n"/>
-      <c r="AW72" s="8" t="n"/>
-      <c r="AX72" s="8" t="inlineStr">
-        <is>
-          <t>[EXCLUDED] material: Cement plaster — category 'Plaster' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13.81.4</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>Paint/Finish &gt; Primer</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Primer — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>GMAP-0067</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="n"/>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>White washing with lime to give an even shade on new work (three or more coats).</t>
-        </is>
-      </c>
-      <c r="F73" s="8" t="inlineStr">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>GMAP-0070</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Applying priming coat with readymixed zinc chromate yellow primer of approved brand and manufacture on steelwork (second coat)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>Sub-Head - X, White/Colour Washing &amp; Painting</t>
         </is>
       </c>
-      <c r="G73" s="8" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>Lime white wash</t>
-        </is>
-      </c>
-      <c r="I73" s="8" t="inlineStr">
-        <is>
-          <t>Lime</t>
-        </is>
-      </c>
-      <c r="J73" s="8" t="inlineStr">
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Zinc chromate yellow primer</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Zinc chromate yellow primer</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
         <is>
           <t>Paint/Finish</t>
         </is>
       </c>
-      <c r="K73" s="8" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="L73" s="8" t="n"/>
-      <c r="M73" s="8" t="n"/>
-      <c r="N73" s="17" t="n">
-        <v>285</v>
-      </c>
-      <c r="O73" s="8" t="inlineStr">
+      <c r="N73" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="O73" t="inlineStr">
         <is>
           <t>sqm</t>
         </is>
       </c>
-      <c r="P73" s="8" t="n"/>
-      <c r="Q73" s="17" t="n">
-        <v>285</v>
-      </c>
-      <c r="R73" s="8" t="n"/>
-      <c r="S73" s="8" t="n"/>
-      <c r="T73" s="8" t="n"/>
-      <c r="U73" s="8" t="n"/>
-      <c r="V73" s="8" t="n"/>
-      <c r="W73" s="8" t="n"/>
-      <c r="X73" s="17" t="n">
+      <c r="Q73" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="X73" s="18" t="n">
         <v>1300</v>
       </c>
-      <c r="Y73" s="8" t="n"/>
-      <c r="Z73" s="17" t="n">
+      <c r="Z73" s="18" t="n">
         <v>0.95</v>
       </c>
-      <c r="AA73" s="8" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>DSR 1989</t>
         </is>
       </c>
-      <c r="AB73" s="8" t="inlineStr">
-        <is>
-          <t>13.73.1</t>
-        </is>
-      </c>
-      <c r="AC73" s="8" t="n"/>
-      <c r="AD73" s="8" t="inlineStr">
-        <is>
-          <t>Paint/Finish &gt; Lime white wash</t>
-        </is>
-      </c>
-      <c r="AE73" s="8" t="n"/>
-      <c r="AF73" s="8" t="n"/>
-      <c r="AG73" s="8" t="n"/>
-      <c r="AH73" s="8" t="n"/>
-      <c r="AI73" s="8" t="n"/>
-      <c r="AJ73" s="8" t="n"/>
-      <c r="AK73" s="8" t="n"/>
-      <c r="AL73" s="8" t="n"/>
-      <c r="AM73" s="8" t="n"/>
-      <c r="AN73" s="8" t="n"/>
-      <c r="AO73" s="8" t="n"/>
-      <c r="AP73" s="8" t="n"/>
-      <c r="AQ73" s="8" t="n"/>
-      <c r="AR73" s="8" t="n"/>
-      <c r="AS73" s="8" t="n"/>
-      <c r="AT73" s="8" t="n"/>
-      <c r="AU73" s="8" t="n"/>
-      <c r="AV73" s="8" t="n"/>
-      <c r="AW73" s="8" t="n"/>
-      <c r="AX73" s="8" t="inlineStr">
-        <is>
-          <t>[EXCLUDED] material: Lime white wash — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>13.84.3</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>Paint/Finish &gt; Zinc chromate yellow primer</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Zinc chromate yellow primer — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>GMAP-0068</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="n"/>
-      <c r="D74" s="8" t="n"/>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>Colour washing such as green, blue or buff to give an even shade on new work (two or more coats) with a base coat of white washing with lime.</t>
-        </is>
-      </c>
-      <c r="F74" s="8" t="inlineStr">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>GMAP-0071</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Painting (two or more coats) on rain water, soil, waste and vent pipes and fittings with black anticorrosive bitumastic paint of approved brand and manufacture over and including a priming coat of ready mixed zinc chromate yellow primer on new work on 100 mm diameter pipes.</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>Sub-Head - X, White/Colour Washing &amp; Painting</t>
         </is>
       </c>
-      <c r="G74" s="8" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-      <c r="H74" s="8" t="inlineStr">
-        <is>
-          <t>Colour wash</t>
-        </is>
-      </c>
-      <c r="I74" s="8" t="inlineStr">
-        <is>
-          <t>Lime, Pigment</t>
-        </is>
-      </c>
-      <c r="J74" s="8" t="inlineStr">
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Bitumastic paint</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Bitumastic paint, Zinc chromate yellow primer</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
         <is>
           <t>Paint/Finish</t>
         </is>
       </c>
-      <c r="K74" s="8" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="L74" s="8" t="n"/>
-      <c r="M74" s="8" t="n"/>
-      <c r="N74" s="17" t="n">
-        <v>285</v>
-      </c>
-      <c r="O74" s="8" t="inlineStr">
-        <is>
-          <t>sqm</t>
-        </is>
-      </c>
-      <c r="P74" s="8" t="n"/>
-      <c r="Q74" s="17" t="n">
-        <v>285</v>
-      </c>
-      <c r="R74" s="8" t="n"/>
-      <c r="S74" s="8" t="n"/>
-      <c r="T74" s="8" t="n"/>
-      <c r="U74" s="8" t="n"/>
-      <c r="V74" s="8" t="n"/>
-      <c r="W74" s="8" t="n"/>
-      <c r="X74" s="17" t="n">
+      <c r="N74" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="R74" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="X74" s="18" t="n">
         <v>1300</v>
       </c>
-      <c r="Y74" s="8" t="n"/>
-      <c r="Z74" s="17" t="n">
+      <c r="Z74" s="18" t="n">
         <v>0.95</v>
       </c>
-      <c r="AA74" s="8" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>DSR 1989</t>
         </is>
       </c>
-      <c r="AB74" s="8" t="inlineStr">
-        <is>
-          <t>13.81.1</t>
-        </is>
-      </c>
-      <c r="AC74" s="8" t="n"/>
-      <c r="AD74" s="8" t="inlineStr">
-        <is>
-          <t>Paint/Finish &gt; Colour wash</t>
-        </is>
-      </c>
-      <c r="AE74" s="8" t="n"/>
-      <c r="AF74" s="8" t="n"/>
-      <c r="AG74" s="8" t="n"/>
-      <c r="AH74" s="8" t="n"/>
-      <c r="AI74" s="8" t="n"/>
-      <c r="AJ74" s="8" t="n"/>
-      <c r="AK74" s="8" t="n"/>
-      <c r="AL74" s="8" t="n"/>
-      <c r="AM74" s="8" t="n"/>
-      <c r="AN74" s="8" t="n"/>
-      <c r="AO74" s="8" t="n"/>
-      <c r="AP74" s="8" t="n"/>
-      <c r="AQ74" s="8" t="n"/>
-      <c r="AR74" s="8" t="n"/>
-      <c r="AS74" s="8" t="n"/>
-      <c r="AT74" s="8" t="n"/>
-      <c r="AU74" s="8" t="n"/>
-      <c r="AV74" s="8" t="n"/>
-      <c r="AW74" s="8" t="n"/>
-      <c r="AX74" s="8" t="inlineStr">
-        <is>
-          <t>[EXCLUDED] material: Colour wash — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13.94.1</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>Paint/Finish &gt; Bitumastic paint</t>
+        </is>
+      </c>
+      <c r="AT74" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>[EXCLUDED] material: Bitumastic paint — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GMAP-0069</t>
+          <t>GMAP-0072</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Applying priming coat with ready mixed pink or gray primer of approved brand and manufacture - on wood work (hard and soft wood)</t>
+          <t>Painting with synthetic enamel paint of approved brand and manufacture to give an even shade in two or more coats on new work in black or chocolate shade over an under coat of suitable shade with ordinary paint of approved brand and manufacture.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -9430,12 +9491,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Wood primer</t>
+          <t>Synthetic enamel paint</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Pink primer, Gray primer</t>
+          <t>Synthetic enamel paint</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9449,7 +9510,7 @@
         </is>
       </c>
       <c r="N75" s="18" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -9457,7 +9518,7 @@
         </is>
       </c>
       <c r="Q75" s="18" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="X75" s="18" t="n">
         <v>1300</v>
@@ -9470,36 +9531,31 @@
           <t>DSR 1989</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>13.81.4</t>
-        </is>
-      </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>Paint/Finish &gt; Wood primer</t>
+          <t>Paint/Finish &gt; Synthetic enamel paint</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Wood primer — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Synthetic enamel paint — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GMAP-0070</t>
+          <t>GMAP-0073</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Applying priming coat with readymixed zinc chromate yellow primer of approved brand and manufacture on steelwork (second coat)</t>
+          <t>French spirit polishing two or more coats on new works including a coat of wood filler.</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -9514,12 +9570,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Zinc chromate yellow primer</t>
+          <t>French spirit polish</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Zinc chromate yellow primer</t>
+          <t>French spirit polish, Wood filler</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9533,7 +9589,7 @@
         </is>
       </c>
       <c r="N76" s="18" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -9541,7 +9597,7 @@
         </is>
       </c>
       <c r="Q76" s="18" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="X76" s="18" t="n">
         <v>1300</v>
@@ -9556,82 +9612,108 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13.84.3</t>
+          <t>13.101.1</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>Paint/Finish &gt; Zinc chromate yellow primer</t>
+          <t>Paint/Finish &gt; French spirit polish</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Zinc chromate yellow primer — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: French spirit polish — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GMAP-0071</t>
+          <t>GMAP-0074</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Painting (two or more coats) on rain water, soil, waste and vent pipes and fittings with black anticorrosive bitumastic paint of approved brand and manufacture over and including a priming coat of ready mixed zinc chromate yellow primer on new work on 100 mm diameter pipes.</t>
+          <t>Making plinth protection 50 mm thick of cement concrete 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) over 75 mm bed of dry brick ballast 40 mm nominal size well rammed and consolidated and grouted with fine sand, including finishing the top smooth.</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sub-Head - X, White/Colour Washing &amp; Painting</t>
+          <t>Sub-Head - XI, Sundry Items / Site Development</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Finishes</t>
+          <t>Civil &amp; Sitework</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Bitumastic paint</t>
+          <t>Cement concrete</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Bitumastic paint, Zinc chromate yellow primer</t>
+          <t>Cement, Coarse sand, Graded stone aggregate, Brick ballast, Fine sand</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Paint/Finish</t>
+          <t>Concrete</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>1:3:6</t>
         </is>
       </c>
       <c r="N77" s="18" t="n">
-        <v>10</v>
+        <v>34.6</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="R77" s="18" t="n">
-        <v>10</v>
+          <t>sqm</t>
+        </is>
+      </c>
+      <c r="Q77" s="18" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="U77" s="18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Area x thickness (50.0 mm, from description)</t>
+        </is>
       </c>
       <c r="X77" s="18" t="n">
-        <v>1300</v>
+        <v>2400</v>
+      </c>
+      <c r="Y77" s="18" t="n">
+        <v>618.65</v>
       </c>
       <c r="Z77" s="18" t="n">
-        <v>0.95</v>
+        <v>0.149</v>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
@@ -9640,296 +9722,20 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13.94.1</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>Paint/Finish &gt; Bitumastic paint</t>
-        </is>
-      </c>
-      <c r="AT77" s="18" t="n">
-        <v>100</v>
+          <t>Concrete &gt; Cement concrete &gt; M10</t>
+        </is>
+      </c>
+      <c r="AR77" s="18" t="n">
+        <v>50</v>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Bitumastic paint — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>GMAP-0072</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Painting with synthetic enamel paint of approved brand and manufacture to give an even shade in two or more coats on new work in black or chocolate shade over an under coat of suitable shade with ordinary paint of approved brand and manufacture.</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Sub-Head - X, White/Colour Washing &amp; Painting</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Finishes</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Synthetic enamel paint</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Synthetic enamel paint</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Paint/Finish</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N78" s="18" t="n">
-        <v>77</v>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>sqm</t>
-        </is>
-      </c>
-      <c r="Q78" s="18" t="n">
-        <v>77</v>
-      </c>
-      <c r="X78" s="18" t="n">
-        <v>1300</v>
-      </c>
-      <c r="Z78" s="18" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>DSR 1989</t>
-        </is>
-      </c>
-      <c r="AD78" t="inlineStr">
-        <is>
-          <t>Paint/Finish &gt; Synthetic enamel paint</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>[EXCLUDED] material: Synthetic enamel paint — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>GMAP-0073</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>French spirit polishing two or more coats on new works including a coat of wood filler.</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Sub-Head - X, White/Colour Washing &amp; Painting</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Finishes</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>French spirit polish</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>French spirit, Wood filler</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Paint/Finish</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N79" s="18" t="n">
-        <v>13</v>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>sqm</t>
-        </is>
-      </c>
-      <c r="Q79" s="18" t="n">
-        <v>13</v>
-      </c>
-      <c r="X79" s="18" t="n">
-        <v>1300</v>
-      </c>
-      <c r="Z79" s="18" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>DSR 1989</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13.101.1</t>
-        </is>
-      </c>
-      <c r="AD79" t="inlineStr">
-        <is>
-          <t>Paint/Finish &gt; French spirit polish</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>[EXCLUDED] material: French spirit polish — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>GMAP-0074</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Making plinth protection 50 mm thick of cement concrete 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) over 75 mm bed of dry brick ballast 40 mm nominal size well rammed and consolidated and grouted with fine sand, including finishing the top smooth.</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Sub-Head - XI, Sundry Items / Site Development</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Civil &amp; Sitework</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Cement concrete plinth protection</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Cement, Coarse sand, Graded stone aggregate, Brick ballast, Fine sand</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Concrete</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>1:3:6</t>
-        </is>
-      </c>
-      <c r="N80" s="18" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>sqm</t>
-        </is>
-      </c>
-      <c r="Q80" s="18" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="U80" s="18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Area x thickness (50.0 mm, from description)</t>
-        </is>
-      </c>
-      <c r="X80" s="18" t="n">
-        <v>2400</v>
-      </c>
-      <c r="Y80" s="18" t="n">
-        <v>618.65</v>
-      </c>
-      <c r="Z80" s="18" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>DSR 1989</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
-      </c>
-      <c r="AD80" t="inlineStr">
-        <is>
-          <t>Concrete &gt; Cement concrete plinth protection &gt; M10</t>
-        </is>
-      </c>
-      <c r="AR80" s="18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>[OK] material: Cement concrete plinth protection — mass 4152.0 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 618.65 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M10 inferred from nominal mix 1:3:6 (IS 456)</t>
+          <t>[OK] material: Cement concrete — mass 4152.0 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 618.65 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M10 inferred from nominal mix 1:3:6 (IS 456)</t>
         </is>
       </c>
     </row>

--- a/output/passport_filled.xlsx
+++ b/output/passport_filled.xlsx
@@ -940,7 +940,7 @@
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>Excavated soil</t>
+          <t>Soil</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
@@ -994,7 +994,7 @@
       <c r="AC4" s="8" t="n"/>
       <c r="AD4" s="8" t="inlineStr">
         <is>
-          <t>Earthwork &gt; Excavated soil</t>
+          <t>Earthwork &gt; Soil</t>
         </is>
       </c>
       <c r="AE4" s="8" t="n"/>
@@ -1008,9 +1008,7 @@
       <c r="AM4" s="8" t="n"/>
       <c r="AN4" s="8" t="n"/>
       <c r="AO4" s="8" t="n"/>
-      <c r="AP4" s="17" t="n">
-        <v>1500</v>
-      </c>
+      <c r="AP4" s="8" t="n"/>
       <c r="AQ4" s="8" t="n"/>
       <c r="AR4" s="8" t="n"/>
       <c r="AS4" s="8" t="n"/>
@@ -1020,7 +1018,7 @@
       <c r="AW4" s="8" t="n"/>
       <c r="AX4" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Excavated soil — earthwork/excavated soil; negligible embodied material carbon</t>
+          <t>[EXCLUDED] material: Soil — earthwork/excavated soil; negligible embodied material carbon</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1052,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Excavated earth</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
@@ -1108,7 +1106,7 @@
       <c r="AC5" s="8" t="n"/>
       <c r="AD5" s="8" t="inlineStr">
         <is>
-          <t>Earthwork &gt; Excavated earth</t>
+          <t>Earthwork &gt; Earth</t>
         </is>
       </c>
       <c r="AE5" s="8" t="n"/>
@@ -1124,17 +1122,17 @@
       <c r="AO5" s="8" t="n"/>
       <c r="AP5" s="8" t="n"/>
       <c r="AQ5" s="8" t="n"/>
-      <c r="AR5" s="17" t="n">
+      <c r="AR5" s="8" t="n"/>
+      <c r="AS5" s="17" t="n">
         <v>200</v>
       </c>
-      <c r="AS5" s="8" t="n"/>
       <c r="AT5" s="8" t="n"/>
       <c r="AU5" s="8" t="n"/>
       <c r="AV5" s="8" t="n"/>
       <c r="AW5" s="8" t="n"/>
       <c r="AX5" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Excavated earth — earthwork/excavated soil; negligible embodied material carbon</t>
+          <t>[EXCLUDED] material: Earth — earthwork/excavated soil; negligible embodied material carbon</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1171,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Fine sand</t>
+          <t>Sand</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -1399,7 +1397,7 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Aldrin chemical emulsion</t>
+          <t>Chemical emulsion, Aldrin Emulsifiable Concentrate</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -1511,7 +1509,7 @@
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -1637,7 +1635,7 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Cement, Fine sand, Graded stone aggregate</t>
+          <t>Cement, Fine sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -1763,7 +1761,7 @@
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
@@ -1889,7 +1887,7 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -2139,7 +2137,7 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -2265,7 +2263,7 @@
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J15" s="8" t="inlineStr">
@@ -2391,7 +2389,7 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -2517,7 +2515,7 @@
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -2643,7 +2641,7 @@
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -2742,14 +2740,14 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>16a</t>
+          <t>16i</t>
         </is>
       </c>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Suspended floors,roofs,landings balconies and chajjas.</t>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : i) Suspended floors, roofs, landings balconies and chajjas.</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -2769,12 +2767,12 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>Formwork, Timber/Steel</t>
+          <t>Formwork</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Timber</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
@@ -2802,9 +2800,13 @@
       <c r="U19" s="8" t="n"/>
       <c r="V19" s="8" t="n"/>
       <c r="W19" s="8" t="n"/>
-      <c r="X19" s="8" t="n"/>
+      <c r="X19" s="17" t="n">
+        <v>750</v>
+      </c>
       <c r="Y19" s="8" t="n"/>
-      <c r="Z19" s="8" t="n"/>
+      <c r="Z19" s="17" t="n">
+        <v>0.306</v>
+      </c>
       <c r="AA19" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -2818,7 +2820,7 @@
       <c r="AC19" s="8" t="n"/>
       <c r="AD19" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Formwork</t>
+          <t>Timber &gt; Formwork</t>
         </is>
       </c>
       <c r="AE19" s="8" t="n"/>
@@ -2842,7 +2844,7 @@
       <c r="AW19" s="8" t="n"/>
       <c r="AX19" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Formwork — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Formwork — category 'Timber' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -2854,14 +2856,14 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>16b</t>
+          <t>16ii</t>
         </is>
       </c>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Shelves</t>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : ii) Shelves</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -2881,12 +2883,12 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>Formwork, Timber/Steel</t>
+          <t>Formwork</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Timber</t>
         </is>
       </c>
       <c r="K20" s="8" t="inlineStr">
@@ -2914,9 +2916,13 @@
       <c r="U20" s="8" t="n"/>
       <c r="V20" s="8" t="n"/>
       <c r="W20" s="8" t="n"/>
-      <c r="X20" s="8" t="n"/>
+      <c r="X20" s="17" t="n">
+        <v>750</v>
+      </c>
       <c r="Y20" s="8" t="n"/>
-      <c r="Z20" s="8" t="n"/>
+      <c r="Z20" s="17" t="n">
+        <v>0.306</v>
+      </c>
       <c r="AA20" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -2930,7 +2936,7 @@
       <c r="AC20" s="8" t="n"/>
       <c r="AD20" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Formwork</t>
+          <t>Timber &gt; Formwork</t>
         </is>
       </c>
       <c r="AE20" s="8" t="n"/>
@@ -2954,7 +2960,7 @@
       <c r="AW20" s="8" t="n"/>
       <c r="AX20" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Formwork — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Formwork — category 'Timber' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -2966,14 +2972,14 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>16c</t>
+          <t>16iii</t>
         </is>
       </c>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Lintels, beams, plinth beams, girders bressumers and cantilever.</t>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : iii) Lintels, beams, plinth beams, girders bressumers and cantilever.</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -2993,12 +2999,12 @@
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>Formwork, Timber/Steel</t>
+          <t>Formwork</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Timber</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
@@ -3026,9 +3032,13 @@
       <c r="U21" s="8" t="n"/>
       <c r="V21" s="8" t="n"/>
       <c r="W21" s="8" t="n"/>
-      <c r="X21" s="8" t="n"/>
+      <c r="X21" s="17" t="n">
+        <v>750</v>
+      </c>
       <c r="Y21" s="8" t="n"/>
-      <c r="Z21" s="8" t="n"/>
+      <c r="Z21" s="17" t="n">
+        <v>0.306</v>
+      </c>
       <c r="AA21" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -3042,7 +3052,7 @@
       <c r="AC21" s="8" t="n"/>
       <c r="AD21" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Formwork</t>
+          <t>Timber &gt; Formwork</t>
         </is>
       </c>
       <c r="AE21" s="8" t="n"/>
@@ -3066,7 +3076,7 @@
       <c r="AW21" s="8" t="n"/>
       <c r="AX21" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Formwork — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Formwork — category 'Timber' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -3078,14 +3088,14 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>16d</t>
+          <t>16iv</t>
         </is>
       </c>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Columns, pillars, posts and struts.</t>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : iv) Columns, pillars, posts and struts.</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -3105,12 +3115,12 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>Formwork, Timber/Steel</t>
+          <t>Formwork</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Timber</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
@@ -3138,9 +3148,13 @@
       <c r="U22" s="8" t="n"/>
       <c r="V22" s="8" t="n"/>
       <c r="W22" s="8" t="n"/>
-      <c r="X22" s="8" t="n"/>
+      <c r="X22" s="17" t="n">
+        <v>750</v>
+      </c>
       <c r="Y22" s="8" t="n"/>
-      <c r="Z22" s="8" t="n"/>
+      <c r="Z22" s="17" t="n">
+        <v>0.306</v>
+      </c>
       <c r="AA22" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -3154,7 +3168,7 @@
       <c r="AC22" s="8" t="n"/>
       <c r="AD22" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Formwork</t>
+          <t>Timber &gt; Formwork</t>
         </is>
       </c>
       <c r="AE22" s="8" t="n"/>
@@ -3178,7 +3192,7 @@
       <c r="AW22" s="8" t="n"/>
       <c r="AX22" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Formwork — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Formwork — category 'Timber' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -3190,14 +3204,14 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>16e</t>
+          <t>16v</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Vertical and horizontal fins individually or forming box louvers hand and facias.</t>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : v) Vertical and horizontal fins individually or forming box louvers hand and facias.</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -3217,12 +3231,12 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>Formwork, Timber/Steel</t>
+          <t>Formwork</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Timber</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
@@ -3250,9 +3264,13 @@
       <c r="U23" s="8" t="n"/>
       <c r="V23" s="8" t="n"/>
       <c r="W23" s="8" t="n"/>
-      <c r="X23" s="8" t="n"/>
+      <c r="X23" s="17" t="n">
+        <v>750</v>
+      </c>
       <c r="Y23" s="8" t="n"/>
-      <c r="Z23" s="8" t="n"/>
+      <c r="Z23" s="17" t="n">
+        <v>0.306</v>
+      </c>
       <c r="AA23" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -3266,7 +3284,7 @@
       <c r="AC23" s="8" t="n"/>
       <c r="AD23" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Formwork</t>
+          <t>Timber &gt; Formwork</t>
         </is>
       </c>
       <c r="AE23" s="8" t="n"/>
@@ -3290,7 +3308,7 @@
       <c r="AW23" s="8" t="n"/>
       <c r="AX23" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Formwork — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Formwork — category 'Timber' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -3302,14 +3320,14 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>17a</t>
+          <t>17i</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Reinforcement for RCC work including bending binding and placing in position complete. Mild steel and medium tensile steel bars.</t>
+          <t>Reinforcement for RCC work including bending binding and placing in position complete. i) Mild steel and medium tensile steel bars.</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -3329,7 +3347,7 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>Mild steel, Medium tensile steel</t>
+          <t>Mild steel</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
@@ -3420,14 +3438,14 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>17b</t>
+          <t>17ii</t>
         </is>
       </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Reinforcement for RCC work including bending binding and placing in position complete. Cold twisted bars</t>
+          <t>Reinforcement for RCC work including bending binding and placing in position complete. ii) Cold twisted bars</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -3447,7 +3465,7 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>Cold twisted steel bars</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
@@ -3545,7 +3563,7 @@
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Providing and laying upto floor two level RCC in string courses, bands, copings, bed plates, anchor blocks, plain window sills and the like excluding the cost of centering, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2, coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
+          <t>Providing and laying upto floor two level RCC in string courses, bands, copings, bed plates, anchor blocks, plain window sills and the like excluding the cost of centering, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -3565,7 +3583,7 @@
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -3671,7 +3689,7 @@
       <c r="D27" s="8" t="n"/>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Brick work with bricks of class designation _____ in foundation and plinth in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
+          <t>Brick work with bricks of class designation___ in foundation and plinth in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -3793,7 +3811,7 @@
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Brick work with bricks of class designation _____ in super structure above plinth upto floor two level in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
+          <t>Brick work with bricks of class designation___ in super structure above plinth upto floor two level in cement mortar 1:6 (1 cement : 6 coarse sand).</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -3998,7 +4016,7 @@
       </c>
       <c r="AB29" s="8" t="inlineStr">
         <is>
-          <t>6.13/6.21</t>
+          <t>6.13/6.21/</t>
         </is>
       </c>
       <c r="AC29" s="8" t="n"/>
@@ -4049,7 +4067,7 @@
       <c r="D30" s="8" t="n"/>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Half brick masonry with bricks of class designation _____ in foundation &amp; plinth in cement mortar 1:4 (1 cement : 4 coarse sand)</t>
+          <t>Half brick masonry with bricks of class designation ______ in foundation &amp; plinth in cement mortar 1:4 (1 cement : 4 coarse sand)</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -4169,7 +4187,7 @@
       <c r="D31" s="8" t="n"/>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Half brick masonry with bricks of class designation _____ in super structure upto floor two level in cement mortar 1:4 (1 cement : 4 coarse sand).</t>
+          <t>Half brick masonry with bricks of class designation ____ in super structure upto floor two level in cement mortar 1:4 (1 cement : 4 coarse sand).</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -4418,12 +4436,12 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>Wood shutter</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>Wood, MS butt hinges</t>
+          <t>Wood, MS</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
@@ -4488,7 +4506,7 @@
       <c r="AC33" s="8" t="n"/>
       <c r="AD33" s="8" t="inlineStr">
         <is>
-          <t>Timber &gt; Wood shutter</t>
+          <t>Timber &gt; Wood</t>
         </is>
       </c>
       <c r="AE33" s="8" t="n"/>
@@ -4514,7 +4532,7 @@
       <c r="AW33" s="8" t="n"/>
       <c r="AX33" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Wood shutter — mass 472.5 kg [area × thickness (derived)] × 0.306 kgCO2e/kg = 144.59 kgCO2e — ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
+          <t>[OK] material: Wood — mass 472.5 kg [area × thickness (derived)] × 0.306 kgCO2e/kg = 144.59 kgCO2e — ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -4548,12 +4566,12 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>Flush door shutter</t>
+          <t>Teak ply veneer</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>Block board, Hard wood, Teak ply veneer, Commercial ply, MS piano hinges</t>
+          <t>Hard wood, Teak ply, Commercial ply, MS</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -4614,7 +4632,7 @@
       <c r="AC34" s="8" t="n"/>
       <c r="AD34" s="8" t="inlineStr">
         <is>
-          <t>Timber &gt; Flush door shutter</t>
+          <t>Timber &gt; Teak ply veneer</t>
         </is>
       </c>
       <c r="AE34" s="8" t="n"/>
@@ -4640,7 +4658,7 @@
       <c r="AW34" s="8" t="n"/>
       <c r="AX34" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Flush door shutter — mass 88.12 kg [area × thickness (derived)] × 0.306 kgCO2e/kg = 26.97 kgCO2e — ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
+          <t>[OK] material: Teak ply veneer — mass 88.12 kg [area × thickness (derived)] × 0.306 kgCO2e/kg = 26.97 kgCO2e — ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4677,7 @@
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Providing 50x50x50 mm 2nd class Teak wood plugs including cutting brick work and fixing in cement mortar 1:3 (1 cement :3 fine sand) and making good the walls etc.</t>
+          <t>Providing 50x50x50 mm 2nd class Teak wood plugs including cutting brick work and fixing in cement mortar 1:3 (1 cement : 3 fine sand) and making good the walls etc.</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
@@ -4669,12 +4687,12 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Finishes</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>Teak wood plugs</t>
+          <t>Teak wood</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
@@ -4736,7 +4754,7 @@
       <c r="AC35" s="8" t="n"/>
       <c r="AD35" s="8" t="inlineStr">
         <is>
-          <t>Timber &gt; Teak wood plugs &gt; 1:3</t>
+          <t>Timber &gt; Teak wood &gt; 1:3</t>
         </is>
       </c>
       <c r="AE35" s="8" t="n"/>
@@ -4766,7 +4784,7 @@
       <c r="AW35" s="8" t="n"/>
       <c r="AX35" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Teak wood plugs — category 'Timber' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Teak wood — category 'Timber' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4818,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>M.S. oxidised fan light ventilator catch</t>
+          <t>Mild steel</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
@@ -4854,7 +4872,7 @@
       <c r="AC36" s="8" t="n"/>
       <c r="AD36" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; M.S. oxidised fan light ventilator catch</t>
+          <t>Steel &gt; Mild steel</t>
         </is>
       </c>
       <c r="AE36" s="8" t="n"/>
@@ -4878,7 +4896,7 @@
       <c r="AW36" s="8" t="n"/>
       <c r="AX36" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: M.S. oxidised fan light ventilator catch — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Mild steel — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4915,7 @@
       <c r="D37" s="8" t="n"/>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing 90 mm oxidised M.S. hasp and staple (safety type) with necessaary screws etc. complete.</t>
+          <t>Providing and fixing 90 mm oxidised M.S. hasp and staple (safety type) with necessary screws etc. complete.</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
@@ -4912,7 +4930,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>Oxidised M.S. hasp and staple</t>
+          <t>Mild steel</t>
         </is>
       </c>
       <c r="I37" s="8" t="inlineStr">
@@ -4970,7 +4988,7 @@
       <c r="AC37" s="8" t="n"/>
       <c r="AD37" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Oxidised M.S. hasp and staple</t>
+          <t>Steel &gt; Mild steel</t>
         </is>
       </c>
       <c r="AE37" s="8" t="n"/>
@@ -4996,7 +5014,7 @@
       <c r="AW37" s="8" t="n"/>
       <c r="AX37" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Oxidised M.S. hasp and staple — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Mild steel — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5048,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>Aluminium sliding door bolt</t>
+          <t>Aluminium</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
@@ -5084,7 +5102,7 @@
       <c r="AC38" s="8" t="n"/>
       <c r="AD38" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium sliding door bolt</t>
+          <t>Other &gt; Aluminium</t>
         </is>
       </c>
       <c r="AE38" s="8" t="n"/>
@@ -5112,7 +5130,7 @@
       <c r="AW38" s="8" t="n"/>
       <c r="AX38" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aluminium sliding door bolt — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Aluminium — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -5124,14 +5142,14 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>31a</t>
+          <t>31i</t>
         </is>
       </c>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 200 x 10 mm</t>
+          <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. i) 200 x 10 mm</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
@@ -5146,7 +5164,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>Aluminium tower bolt</t>
+          <t>Aluminium</t>
         </is>
       </c>
       <c r="I39" s="8" t="inlineStr">
@@ -5200,7 +5218,7 @@
       <c r="AC39" s="8" t="n"/>
       <c r="AD39" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium tower bolt</t>
+          <t>Other &gt; Aluminium</t>
         </is>
       </c>
       <c r="AE39" s="8" t="n"/>
@@ -5228,7 +5246,7 @@
       <c r="AW39" s="8" t="n"/>
       <c r="AX39" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aluminium tower bolt — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Aluminium — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -5240,14 +5258,14 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>31b</t>
+          <t>31ii</t>
         </is>
       </c>
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 100 x 10 mm</t>
+          <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. ii) 100 x 10 mm</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -5262,7 +5280,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>Aluminium tower bolt</t>
+          <t>Aluminium</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
@@ -5316,7 +5334,7 @@
       <c r="AC40" s="8" t="n"/>
       <c r="AD40" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium tower bolt</t>
+          <t>Other &gt; Aluminium</t>
         </is>
       </c>
       <c r="AE40" s="8" t="n"/>
@@ -5344,7 +5362,7 @@
       <c r="AW40" s="8" t="n"/>
       <c r="AX40" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aluminium tower bolt — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Aluminium — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -5356,14 +5374,14 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>32a</t>
+          <t>32i</t>
         </is>
       </c>
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 100 mm</t>
+          <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. i) 100 mm</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -5378,7 +5396,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>Aluminium handle</t>
+          <t>Aluminium</t>
         </is>
       </c>
       <c r="I41" s="8" t="inlineStr">
@@ -5432,7 +5450,7 @@
       <c r="AC41" s="8" t="n"/>
       <c r="AD41" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium handle</t>
+          <t>Other &gt; Aluminium</t>
         </is>
       </c>
       <c r="AE41" s="8" t="n"/>
@@ -5458,7 +5476,7 @@
       <c r="AW41" s="8" t="n"/>
       <c r="AX41" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aluminium handle — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Aluminium — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -5470,14 +5488,14 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>32b</t>
+          <t>32ii</t>
         </is>
       </c>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 75 mm</t>
+          <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. ii) 75 mm</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -5492,7 +5510,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>Aluminium handle</t>
+          <t>Aluminium</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
@@ -5546,7 +5564,7 @@
       <c r="AC42" s="8" t="n"/>
       <c r="AD42" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium handle</t>
+          <t>Other &gt; Aluminium</t>
         </is>
       </c>
       <c r="AE42" s="8" t="n"/>
@@ -5572,7 +5590,7 @@
       <c r="AW42" s="8" t="n"/>
       <c r="AX42" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aluminium handle — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Aluminium — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5624,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>Aluminium floor door stopper</t>
+          <t>Aluminium</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
@@ -5660,7 +5678,7 @@
       <c r="AC43" s="8" t="n"/>
       <c r="AD43" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium floor door stopper</t>
+          <t>Other &gt; Aluminium</t>
         </is>
       </c>
       <c r="AE43" s="8" t="n"/>
@@ -5684,7 +5702,7 @@
       <c r="AW43" s="8" t="n"/>
       <c r="AX43" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aluminium floor door stopper — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Aluminium — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -5696,14 +5714,14 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>34a</t>
+          <t>34i</t>
         </is>
       </c>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. Windows - side hung</t>
+          <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. i) Windows - side hung</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -5718,12 +5736,12 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>Steel glazed windows</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>Steel, Glass, Cement, Coarse sand, Graded stone aggregate, Sash putty, Steel primer</t>
+          <t>Steel, Glass, Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
@@ -5792,7 +5810,7 @@
       <c r="AC44" s="8" t="n"/>
       <c r="AD44" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Steel glazed windows &gt; 1:3:6</t>
+          <t>Steel &gt; Steel &gt; 1:3:6</t>
         </is>
       </c>
       <c r="AE44" s="8" t="n"/>
@@ -5805,12 +5823,8 @@
       <c r="AL44" s="8" t="n"/>
       <c r="AM44" s="8" t="n"/>
       <c r="AN44" s="8" t="n"/>
-      <c r="AO44" s="17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP44" s="17" t="n">
-        <v>15</v>
-      </c>
+      <c r="AO44" s="8" t="n"/>
+      <c r="AP44" s="8" t="n"/>
       <c r="AQ44" s="8" t="n"/>
       <c r="AR44" s="17" t="n">
         <v>3</v>
@@ -5822,7 +5836,7 @@
       <c r="AW44" s="8" t="n"/>
       <c r="AX44" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Steel glazed windows — mass 266.12 kg [area × thickness (derived)] × 1.55 kgCO2e/kg = 412.48 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[OK] material: Steel — mass 266.12 kg [area × thickness (derived)] × 1.55 kgCO2e/kg = 412.48 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -5834,14 +5848,14 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>34b</t>
+          <t>34ii</t>
         </is>
       </c>
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. Ventilators - centre hung</t>
+          <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. ii) Ventilators - centre hung</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -5856,12 +5870,12 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>Steel glazed ventilators</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>Steel, Glass, Cement, Coarse sand, Graded stone aggregate, Sash putty, Steel primer</t>
+          <t>Steel, Glass, Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr">
@@ -5930,7 +5944,7 @@
       <c r="AC45" s="8" t="n"/>
       <c r="AD45" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Steel glazed ventilators &gt; 1:3:6</t>
+          <t>Steel &gt; Steel &gt; 1:3:6</t>
         </is>
       </c>
       <c r="AE45" s="8" t="n"/>
@@ -5943,12 +5957,8 @@
       <c r="AL45" s="8" t="n"/>
       <c r="AM45" s="8" t="n"/>
       <c r="AN45" s="8" t="n"/>
-      <c r="AO45" s="17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP45" s="17" t="n">
-        <v>15</v>
-      </c>
+      <c r="AO45" s="8" t="n"/>
+      <c r="AP45" s="8" t="n"/>
       <c r="AQ45" s="8" t="n"/>
       <c r="AR45" s="17" t="n">
         <v>3</v>
@@ -5960,7 +5970,7 @@
       <c r="AW45" s="8" t="n"/>
       <c r="AX45" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Steel glazed ventilators — mass 23.55 kg [area × thickness (derived)] × 1.55 kgCO2e/kg = 36.5 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[OK] material: Steel — mass 23.55 kg [area × thickness (derived)] × 1.55 kgCO2e/kg = 36.5 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -5994,7 +6004,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>Oxidised mild steel casement window fasteners</t>
+          <t>Mild steel</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
@@ -6052,7 +6062,7 @@
       <c r="AC46" s="8" t="n"/>
       <c r="AD46" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Oxidised mild steel casement window fasteners</t>
+          <t>Steel &gt; Mild steel</t>
         </is>
       </c>
       <c r="AE46" s="8" t="n"/>
@@ -6076,7 +6086,7 @@
       <c r="AW46" s="8" t="n"/>
       <c r="AX46" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Oxidised mild steel casement window fasteners — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Mild steel — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6105,7 @@
       <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium casement stays anodised transparent or dyed to required colour and shade with with necessary welding and machine screws etc. complete.</t>
+          <t>Providing and fixing aluminium casement stays anodised transparent or dyed to requird colour and shade with with necessary welding and machine screws etc. complete.</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
@@ -6110,7 +6120,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>Aluminium casement stays</t>
+          <t>Aluminium</t>
         </is>
       </c>
       <c r="I47" s="8" t="inlineStr">
@@ -6164,7 +6174,7 @@
       <c r="AC47" s="8" t="n"/>
       <c r="AD47" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium casement stays</t>
+          <t>Other &gt; Aluminium</t>
         </is>
       </c>
       <c r="AE47" s="8" t="n"/>
@@ -6188,7 +6198,7 @@
       <c r="AW47" s="8" t="n"/>
       <c r="AX47" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aluminium casement stays — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Aluminium — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -6222,12 +6232,12 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>MS Guard Flats</t>
+          <t>Mild steel</t>
         </is>
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>Mild steel, Steel primer</t>
+          <t>Mild steel</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
@@ -6282,7 +6292,7 @@
       <c r="AC48" s="8" t="n"/>
       <c r="AD48" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; MS Guard Flats</t>
+          <t>Steel &gt; Mild steel</t>
         </is>
       </c>
       <c r="AE48" s="8" t="n"/>
@@ -6310,7 +6320,7 @@
       <c r="AW48" s="8" t="n"/>
       <c r="AX48" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: MS Guard Flats — mass 66.0 kg [direct weight] × 1.55 kgCO2e/kg = 102.3 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[OK] material: Mild steel — mass 66.0 kg [direct weight] × 1.55 kgCO2e/kg = 102.3 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -6344,12 +6354,12 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>T-Iron frames</t>
+          <t>Mild steel</t>
         </is>
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>Mild steel Tee sections, Cement, Coarse sand, Graded stone aggregate, Steel primer</t>
+          <t>Mild steel, Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J49" s="8" t="inlineStr">
@@ -6408,7 +6418,7 @@
       <c r="AC49" s="8" t="n"/>
       <c r="AD49" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; T-Iron frames &gt; 1:3:6</t>
+          <t>Steel &gt; Mild steel &gt; 1:3:6</t>
         </is>
       </c>
       <c r="AE49" s="8" t="n"/>
@@ -6421,16 +6431,10 @@
       <c r="AL49" s="8" t="n"/>
       <c r="AM49" s="8" t="n"/>
       <c r="AN49" s="8" t="n"/>
-      <c r="AO49" s="17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP49" s="17" t="n">
-        <v>15</v>
-      </c>
+      <c r="AO49" s="8" t="n"/>
+      <c r="AP49" s="8" t="n"/>
       <c r="AQ49" s="8" t="n"/>
-      <c r="AR49" s="17" t="n">
-        <v>3</v>
-      </c>
+      <c r="AR49" s="8" t="n"/>
       <c r="AS49" s="8" t="n"/>
       <c r="AT49" s="8" t="n"/>
       <c r="AU49" s="8" t="n"/>
@@ -6438,7 +6442,7 @@
       <c r="AW49" s="8" t="n"/>
       <c r="AX49" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: T-Iron frames — mass 187.0 kg [direct weight] × 1.55 kgCO2e/kg = 289.85 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[OK] material: Mild steel — mass 187.0 kg [direct weight] × 1.55 kgCO2e/kg = 289.85 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -6472,12 +6476,12 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>MS fan clamp</t>
+          <t>Mild steel bar</t>
         </is>
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>Mild steel bar, Paint</t>
+          <t>Mild steel</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
@@ -6530,7 +6534,7 @@
       <c r="AC50" s="8" t="n"/>
       <c r="AD50" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; MS fan clamp</t>
+          <t>Steel &gt; Mild steel bar</t>
         </is>
       </c>
       <c r="AE50" s="8" t="n"/>
@@ -6556,7 +6560,7 @@
       <c r="AW50" s="8" t="n"/>
       <c r="AX50" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: MS fan clamp — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Mild steel bar — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -6590,12 +6594,12 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>Cement concrete flooring</t>
+          <t>Cement concrete</t>
         </is>
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J51" s="8" t="inlineStr">
@@ -6668,7 +6672,7 @@
       <c r="AC51" s="8" t="n"/>
       <c r="AD51" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Cement concrete flooring &gt; M15</t>
+          <t>Concrete &gt; Cement concrete &gt; M15</t>
         </is>
       </c>
       <c r="AE51" s="8" t="n"/>
@@ -6694,7 +6698,7 @@
       <c r="AW51" s="8" t="n"/>
       <c r="AX51" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Cement concrete flooring — mass 6528.0 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 972.67 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[OK] material: Cement concrete — mass 6528.0 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 972.67 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -6713,7 +6717,7 @@
       <c r="D52" s="8" t="n"/>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>18 mm thick cement plaster skirting (upto 30 cm height) with cement mortar 1:3 (1 cement : 3 coarse sand) finished with a floating coat of neat cement including rounding of junctions with floors.</t>
+          <t>18 mm thick cement plastesr skirting (upto 30 cm height) with cement mortar 1:3 (1 cement : 3 coarse sand) finished with a floating coat of neat cement including rounding of junctions with floors.</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
@@ -6728,7 +6732,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>Cement plaster skirting</t>
+          <t>Cement plaster</t>
         </is>
       </c>
       <c r="I52" s="8" t="inlineStr">
@@ -6802,7 +6806,7 @@
       <c r="AC52" s="8" t="n"/>
       <c r="AD52" s="8" t="inlineStr">
         <is>
-          <t>Plaster &gt; Cement plaster skirting &gt; 1:3</t>
+          <t>Plaster &gt; Cement plaster &gt; 1:3</t>
         </is>
       </c>
       <c r="AE52" s="8" t="n"/>
@@ -6830,7 +6834,7 @@
       <c r="AW52" s="8" t="n"/>
       <c r="AX52" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Cement plaster skirting — mass 376.2 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 61.32 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
+          <t>[OK] material: Cement plaster — mass 376.2 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 61.32 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -6869,7 +6873,7 @@
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>Marble chips, Cement, Marble powder, Coarse sand, Graded stone aggregate, Pigment</t>
+          <t>Cement, Coarse sand, Stone aggregate, Marble chips, Marble powder</t>
         </is>
       </c>
       <c r="J53" s="8" t="inlineStr">
@@ -7118,7 +7122,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>Petroleum bitumen</t>
+          <t>Bitumen</t>
         </is>
       </c>
       <c r="I55" s="8" t="inlineStr">
@@ -7176,7 +7180,7 @@
       <c r="AC55" s="8" t="n"/>
       <c r="AD55" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish &gt; Petroleum bitumen</t>
+          <t>Paint/Finish &gt; Bitumen</t>
         </is>
       </c>
       <c r="AE55" s="8" t="n"/>
@@ -7200,7 +7204,7 @@
       <c r="AW55" s="8" t="n"/>
       <c r="AX55" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Petroleum bitumen — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Bitumen — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7243,7 @@
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>Lime putty, Surkhi, Brick aggregate, Brick tiles, Cement, Fine sand, Crude oil, Gur, Belgiri</t>
+          <t>Lime putty, Surkhi, Brick aggregate, Brick tiles, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J56" s="8" t="inlineStr">
@@ -7506,12 +7510,12 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>Cement concrete gola</t>
+          <t>Cement concrete</t>
         </is>
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate, Brick tiles</t>
+          <t>Cement, Coarse sand, Stone aggregate, Brick tiles</t>
         </is>
       </c>
       <c r="J58" s="8" t="inlineStr">
@@ -7572,7 +7576,7 @@
       <c r="AC58" s="8" t="n"/>
       <c r="AD58" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Cement concrete gola &gt; M10</t>
+          <t>Concrete &gt; Cement concrete &gt; M10</t>
         </is>
       </c>
       <c r="AE58" s="8" t="n"/>
@@ -7600,7 +7604,7 @@
       <c r="AW58" s="8" t="n"/>
       <c r="AX58" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Cement concrete gola — category 'Concrete' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Cement concrete — category 'Concrete' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -7634,12 +7638,12 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>Cement concrete khurras</t>
+          <t>Cement concrete</t>
         </is>
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate, PVC sheet</t>
+          <t>Cement, Coarse sand, Stone aggregate, PVC sheet</t>
         </is>
       </c>
       <c r="J59" s="8" t="inlineStr">
@@ -7700,7 +7704,7 @@
       <c r="AC59" s="8" t="n"/>
       <c r="AD59" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Cement concrete khurras &gt; M15</t>
+          <t>Concrete &gt; Cement concrete &gt; M15</t>
         </is>
       </c>
       <c r="AE59" s="8" t="n"/>
@@ -7730,7 +7734,7 @@
       <c r="AW59" s="8" t="n"/>
       <c r="AX59" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Cement concrete khurras — category 'Concrete' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Cement concrete — category 'Concrete' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -7764,12 +7768,12 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>CI rain water pipe</t>
+          <t>Cast iron pipe</t>
         </is>
       </c>
       <c r="I60" s="8" t="inlineStr">
         <is>
-          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
+          <t>Cast iron, Cement, Fine sand, Spun yarn</t>
         </is>
       </c>
       <c r="J60" s="8" t="inlineStr">
@@ -7822,7 +7826,7 @@
       <c r="AC60" s="8" t="n"/>
       <c r="AD60" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; CI rain water pipe &gt; 1:2</t>
+          <t>Other &gt; Cast iron pipe &gt; 1:2</t>
         </is>
       </c>
       <c r="AE60" s="8" t="n"/>
@@ -7848,7 +7852,7 @@
       <c r="AW60" s="8" t="n"/>
       <c r="AX60" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: CI rain water pipe — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Cast iron pipe — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -7882,12 +7886,12 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>MS holderbat clamps</t>
+          <t>Mild steel holderbat clamp</t>
         </is>
       </c>
       <c r="I61" s="8" t="inlineStr">
         <is>
-          <t>Mild steel, Cement, Coarse sand, Graded stone aggregate</t>
+          <t>Mild steel, Cement, Coarse sand, Stone aggregate</t>
         </is>
       </c>
       <c r="J61" s="8" t="inlineStr">
@@ -7944,7 +7948,7 @@
       <c r="AC61" s="8" t="n"/>
       <c r="AD61" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; MS holderbat clamps &gt; 1:2:4</t>
+          <t>Steel &gt; Mild steel holderbat clamp &gt; 1:2:4</t>
         </is>
       </c>
       <c r="AE61" s="8" t="n"/>
@@ -7957,15 +7961,9 @@
       <c r="AL61" s="8" t="n"/>
       <c r="AM61" s="8" t="n"/>
       <c r="AN61" s="8" t="n"/>
-      <c r="AO61" s="17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP61" s="17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AQ61" s="17" t="n">
-        <v>100</v>
-      </c>
+      <c r="AO61" s="8" t="n"/>
+      <c r="AP61" s="8" t="n"/>
+      <c r="AQ61" s="8" t="n"/>
       <c r="AR61" s="8" t="n"/>
       <c r="AS61" s="8" t="n"/>
       <c r="AT61" s="17" t="n">
@@ -7976,7 +7974,7 @@
       <c r="AW61" s="8" t="n"/>
       <c r="AX61" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: MS holderbat clamps — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Mild steel holderbat clamp — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -7988,14 +7986,14 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>51a</t>
+          <t>51i</t>
         </is>
       </c>
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) CI plain head 100 mm dia</t>
+          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) i) CI plain head 100 mm dia</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
@@ -8010,12 +8008,12 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>CI plain head</t>
+          <t>Cast iron</t>
         </is>
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
+          <t>Cast iron, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J62" s="8" t="inlineStr">
@@ -8068,7 +8066,7 @@
       <c r="AC62" s="8" t="n"/>
       <c r="AD62" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; CI plain head &gt; 1:2</t>
+          <t>Other &gt; Cast iron &gt; 1:2</t>
         </is>
       </c>
       <c r="AE62" s="8" t="n"/>
@@ -8094,7 +8092,7 @@
       <c r="AW62" s="8" t="n"/>
       <c r="AX62" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: CI plain head — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Cast iron — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -8106,14 +8104,14 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>51b</t>
+          <t>51ii</t>
         </is>
       </c>
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) CI plain shoe - 100 mm dia</t>
+          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) ii) CI plain shoe - 100 mm dia</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
@@ -8128,12 +8126,12 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>CI plain shoe</t>
+          <t>Cast iron</t>
         </is>
       </c>
       <c r="I63" s="8" t="inlineStr">
         <is>
-          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
+          <t>Cast iron, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J63" s="8" t="inlineStr">
@@ -8186,7 +8184,7 @@
       <c r="AC63" s="8" t="n"/>
       <c r="AD63" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; CI plain shoe &gt; 1:2</t>
+          <t>Other &gt; Cast iron &gt; 1:2</t>
         </is>
       </c>
       <c r="AE63" s="8" t="n"/>
@@ -8212,7 +8210,7 @@
       <c r="AW63" s="8" t="n"/>
       <c r="AX63" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: CI plain shoe — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Cast iron — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -8224,14 +8222,14 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>51c</t>
+          <t>51iii</t>
         </is>
       </c>
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) CI plain bend - 100 mm dia</t>
+          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) iii) CI plain bend - 100 mm dia</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
@@ -8246,12 +8244,12 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>CI plain bend</t>
+          <t>Cast iron</t>
         </is>
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
+          <t>Cast iron, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J64" s="8" t="inlineStr">
@@ -8304,7 +8302,7 @@
       <c r="AC64" s="8" t="n"/>
       <c r="AD64" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; CI plain bend &gt; 1:2</t>
+          <t>Other &gt; Cast iron &gt; 1:2</t>
         </is>
       </c>
       <c r="AE64" s="8" t="n"/>
@@ -8330,7 +8328,7 @@
       <c r="AW64" s="8" t="n"/>
       <c r="AX64" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: CI plain bend — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Cast iron — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -8379,7 +8377,7 @@
       </c>
       <c r="K65" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L65" s="8" t="n"/>
@@ -8393,21 +8391,35 @@
       </c>
       <c r="O65" s="8" t="inlineStr">
         <is>
-          <t>Sq.m .</t>
+          <t>sqm</t>
         </is>
       </c>
       <c r="P65" s="8" t="n"/>
-      <c r="Q65" s="8" t="n"/>
+      <c r="Q65" s="17" t="n">
+        <v>220</v>
+      </c>
       <c r="R65" s="8" t="n"/>
       <c r="S65" s="8" t="n"/>
       <c r="T65" s="8" t="n"/>
-      <c r="U65" s="8" t="n"/>
-      <c r="V65" s="8" t="n"/>
-      <c r="W65" s="8" t="n"/>
+      <c r="U65" s="17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V65" s="8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="W65" s="8" t="inlineStr">
+        <is>
+          <t>Area x thickness (12.0 mm, from description)</t>
+        </is>
+      </c>
       <c r="X65" s="17" t="n">
         <v>1900</v>
       </c>
-      <c r="Y65" s="8" t="n"/>
+      <c r="Y65" s="17" t="n">
+        <v>817.61</v>
+      </c>
       <c r="Z65" s="17" t="n">
         <v>0.163</v>
       </c>
@@ -8450,7 +8462,7 @@
       <c r="AW65" s="8" t="n"/>
       <c r="AX65" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Cement plaster — category 'Plaster' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[OK] material: Cement plaster — mass 5016.0 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 817.61 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8635,7 @@
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>Cement, Fine sand, Lime wash</t>
+          <t>Cement, Fine sand, Lime</t>
         </is>
       </c>
       <c r="J67" s="8" t="inlineStr">
@@ -8820,7 +8832,7 @@
       </c>
       <c r="AB68" s="8" t="inlineStr">
         <is>
-          <t>5.31/13.24.1</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AC68" s="8" t="n"/>
@@ -8942,7 +8954,7 @@
       </c>
       <c r="AB69" s="8" t="inlineStr">
         <is>
-          <t>13.70.1</t>
+          <t>5.31/13.24.1</t>
         </is>
       </c>
       <c r="AC69" s="8" t="n"/>
@@ -9006,7 +9018,7 @@
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>Lime white wash</t>
+          <t>Lime wash</t>
         </is>
       </c>
       <c r="I70" s="8" t="inlineStr">
@@ -9058,13 +9070,13 @@
       </c>
       <c r="AB70" s="8" t="inlineStr">
         <is>
-          <t>13.73.1</t>
+          <t>13.70.1</t>
         </is>
       </c>
       <c r="AC70" s="8" t="n"/>
       <c r="AD70" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish &gt; Lime white wash</t>
+          <t>Paint/Finish &gt; Lime wash</t>
         </is>
       </c>
       <c r="AE70" s="8" t="n"/>
@@ -9088,7 +9100,7 @@
       <c r="AW70" s="8" t="n"/>
       <c r="AX70" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Lime white wash — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Lime wash — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9139,7 @@
       </c>
       <c r="I71" s="8" t="inlineStr">
         <is>
-          <t>Lime, Colour wash</t>
+          <t>Lime</t>
         </is>
       </c>
       <c r="J71" s="8" t="inlineStr">
@@ -9174,7 +9186,7 @@
       </c>
       <c r="AB71" s="8" t="inlineStr">
         <is>
-          <t>13.81.1</t>
+          <t>13.73.1</t>
         </is>
       </c>
       <c r="AC71" s="8" t="n"/>
@@ -9241,7 +9253,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Pink or gray primer</t>
+          <t>Primer</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9278,7 +9290,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13.81.4</t>
+          <t>13.81.1</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr">
@@ -9320,12 +9332,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Zinc chromate yellow primer</t>
+          <t>Zinc chromate primer</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Zinc chromate yellow primer</t>
+          <t>Zinc chromate primer</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9362,17 +9374,17 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13.84.3</t>
+          <t>13.81.4</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>Paint/Finish &gt; Zinc chromate yellow primer</t>
+          <t>Paint/Finish &gt; Zinc chromate primer</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Zinc chromate yellow primer — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Zinc chromate primer — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -9409,7 +9421,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Bitumastic paint, Zinc chromate yellow primer</t>
+          <t>Bitumastic paint, Zinc chromate primer</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9446,7 +9458,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13.94.1</t>
+          <t>13.84.3</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr">
@@ -9531,6 +9543,11 @@
           <t>DSR 1989</t>
         </is>
       </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>13.94.1</t>
+        </is>
+      </c>
       <c r="AD75" t="inlineStr">
         <is>
           <t>Paint/Finish &gt; Synthetic enamel paint</t>
@@ -9659,7 +9676,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Graded stone aggregate, Brick ballast, Fine sand</t>
+          <t>Cement, Coarse sand, Stone aggregate, Brick ballast, Fine sand</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">

--- a/output/passport_filled.xlsx
+++ b/output/passport_filled.xlsx
@@ -940,7 +940,7 @@
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>Soil</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
@@ -994,7 +994,7 @@
       <c r="AC4" s="8" t="n"/>
       <c r="AD4" s="8" t="inlineStr">
         <is>
-          <t>Earthwork &gt; Soil</t>
+          <t>Earthwork &gt; Earth</t>
         </is>
       </c>
       <c r="AE4" s="8" t="n"/>
@@ -1015,10 +1015,14 @@
       <c r="AT4" s="8" t="n"/>
       <c r="AU4" s="8" t="n"/>
       <c r="AV4" s="8" t="n"/>
-      <c r="AW4" s="8" t="n"/>
+      <c r="AW4" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX4" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Soil — earthwork/excavated soil; negligible embodied material carbon</t>
+          <t>[EXCLUDED] material: Earth — earthwork/excavated soil; negligible embodied material carbon</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1056,12 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Excavated earth</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Earth, Water</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
@@ -1106,7 +1110,7 @@
       <c r="AC5" s="8" t="n"/>
       <c r="AD5" s="8" t="inlineStr">
         <is>
-          <t>Earthwork &gt; Earth</t>
+          <t>Earthwork &gt; Excavated earth</t>
         </is>
       </c>
       <c r="AE5" s="8" t="n"/>
@@ -1129,10 +1133,14 @@
       <c r="AT5" s="8" t="n"/>
       <c r="AU5" s="8" t="n"/>
       <c r="AV5" s="8" t="n"/>
-      <c r="AW5" s="8" t="n"/>
+      <c r="AW5" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX5" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Earth — earthwork/excavated soil; negligible embodied material carbon</t>
+          <t>[EXCLUDED] material: Excavated earth — earthwork/excavated soil; negligible embodied material carbon</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1179,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Sand</t>
+          <t>Sand, Water</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -1241,7 +1249,11 @@
       <c r="AT6" s="8" t="n"/>
       <c r="AU6" s="8" t="n"/>
       <c r="AV6" s="8" t="n"/>
-      <c r="AW6" s="8" t="n"/>
+      <c r="AW6" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX6" s="8" t="inlineStr">
         <is>
           <t>[EXCLUDED] material: Fine sand — earthwork/excavated soil; negligible embodied material carbon</t>
@@ -1299,7 +1311,7 @@
       <c r="L7" s="8" t="n"/>
       <c r="M7" s="8" t="n"/>
       <c r="N7" s="17" t="n">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="O7" s="8" t="inlineStr">
         <is>
@@ -1308,7 +1320,7 @@
       </c>
       <c r="P7" s="8" t="n"/>
       <c r="Q7" s="17" t="n">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="R7" s="8" t="n"/>
       <c r="S7" s="8" t="n"/>
@@ -1355,7 +1367,11 @@
       <c r="AT7" s="8" t="n"/>
       <c r="AU7" s="8" t="n"/>
       <c r="AV7" s="8" t="n"/>
-      <c r="AW7" s="8" t="n"/>
+      <c r="AW7" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX7" s="8" t="inlineStr">
         <is>
           <t>[EXCLUDED] material: Soil — earthwork/excavated soil; negligible embodied material carbon</t>
@@ -1397,7 +1413,7 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Chemical emulsion, Aldrin Emulsifiable Concentrate</t>
+          <t>Aldrin chemical emulsion</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -1467,7 +1483,11 @@
       <c r="AT8" s="8" t="n"/>
       <c r="AU8" s="8" t="n"/>
       <c r="AV8" s="8" t="n"/>
-      <c r="AW8" s="8" t="n"/>
+      <c r="AW8" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX8" s="8" t="inlineStr">
         <is>
           <t>[EXCLUDED] material: Aldrin Emulsifiable Concentrate — category 'Other' not in current EPD database; carbon not estimated</t>
@@ -1593,7 +1613,11 @@
       <c r="AT9" s="8" t="n"/>
       <c r="AU9" s="8" t="n"/>
       <c r="AV9" s="8" t="n"/>
-      <c r="AW9" s="8" t="n"/>
+      <c r="AW9" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX9" s="8" t="inlineStr">
         <is>
           <t>[OK] material: Cement concrete — mass 19200.0 kg [direct volume] × 0.149 kgCO2e/kg = 2860.8 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M5 inferred from nominal mix 1:5:10 (IS 456)</t>
@@ -1719,7 +1743,11 @@
       <c r="AT10" s="8" t="n"/>
       <c r="AU10" s="8" t="n"/>
       <c r="AV10" s="8" t="n"/>
-      <c r="AW10" s="8" t="n"/>
+      <c r="AW10" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX10" s="8" t="inlineStr">
         <is>
           <t>[OK] material: Cement concrete — mass 17520.0 kg [direct volume] × 0.149 kgCO2e/kg = 2610.48 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M5 inferred from nominal mix 1:5:10 (IS 456)</t>
@@ -1845,7 +1873,11 @@
       <c r="AT11" s="8" t="n"/>
       <c r="AU11" s="8" t="n"/>
       <c r="AV11" s="8" t="n"/>
-      <c r="AW11" s="8" t="n"/>
+      <c r="AW11" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX11" s="8" t="inlineStr">
         <is>
           <t>[OK] material: Cement concrete — mass 240.0 kg [direct volume] × 0.149 kgCO2e/kg = 35.76 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
@@ -1983,7 +2015,11 @@
       <c r="AT12" s="8" t="n"/>
       <c r="AU12" s="8" t="n"/>
       <c r="AV12" s="8" t="n"/>
-      <c r="AW12" s="8" t="n"/>
+      <c r="AW12" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX12" s="8" t="inlineStr">
         <is>
           <t>[OK] material: Cement concrete — mass 1382.4 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 205.98 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
@@ -2030,7 +2066,7 @@
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Paint/Finish</t>
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr">
@@ -2058,9 +2094,13 @@
       <c r="U13" s="8" t="n"/>
       <c r="V13" s="8" t="n"/>
       <c r="W13" s="8" t="n"/>
-      <c r="X13" s="8" t="n"/>
+      <c r="X13" s="17" t="n">
+        <v>1300</v>
+      </c>
       <c r="Y13" s="8" t="n"/>
-      <c r="Z13" s="8" t="n"/>
+      <c r="Z13" s="17" t="n">
+        <v>0.95</v>
+      </c>
       <c r="AA13" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -2074,7 +2114,7 @@
       <c r="AC13" s="8" t="n"/>
       <c r="AD13" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Residual petroleum bitumen</t>
+          <t>Paint/Finish &gt; Residual petroleum bitumen</t>
         </is>
       </c>
       <c r="AE13" s="8" t="n"/>
@@ -2095,10 +2135,14 @@
       <c r="AT13" s="8" t="n"/>
       <c r="AU13" s="8" t="n"/>
       <c r="AV13" s="8" t="n"/>
-      <c r="AW13" s="8" t="n"/>
+      <c r="AW13" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX13" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Residual petroleum bitumen — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Residual petroleum bitumen — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2265,11 @@
       <c r="AT14" s="8" t="n"/>
       <c r="AU14" s="8" t="n"/>
       <c r="AV14" s="8" t="n"/>
-      <c r="AW14" s="8" t="n"/>
+      <c r="AW14" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX14" s="8" t="inlineStr">
         <is>
           <t>[OK] material: Reinforced cement concrete — mass 27120.0 kg [direct volume] × 0.149 kgCO2e/kg = 4040.88 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
@@ -2347,7 +2395,11 @@
       <c r="AT15" s="8" t="n"/>
       <c r="AU15" s="8" t="n"/>
       <c r="AV15" s="8" t="n"/>
-      <c r="AW15" s="8" t="n"/>
+      <c r="AW15" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX15" s="8" t="inlineStr">
         <is>
           <t>[OK] material: Reinforced cement concrete — mass 2400.0 kg [direct volume] × 0.149 kgCO2e/kg = 357.6 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
@@ -2473,7 +2525,11 @@
       <c r="AT16" s="8" t="n"/>
       <c r="AU16" s="8" t="n"/>
       <c r="AV16" s="8" t="n"/>
-      <c r="AW16" s="8" t="n"/>
+      <c r="AW16" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX16" s="8" t="inlineStr">
         <is>
           <t>[OK] material: Reinforced cement concrete — mass 1440.0 kg [direct volume] × 0.149 kgCO2e/kg = 214.56 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
@@ -2495,7 +2551,7 @@
       <c r="D17" s="8" t="n"/>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Reinforced cement concrete work in lintels, beams, plinth beams and bressummers upto floor two level excluding the cost of centring, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
+          <t>Reinforced cement concrete work in lintels, beams, plinth beams and bresummers upto floor two level excluding the cost of centring, shuttering, finishing and reinforcement with 1:2:4 (1 cement : 2 coarse sand : 4 graded stone aggregate 20 mm nominal size).</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -2599,7 +2655,11 @@
       <c r="AT17" s="8" t="n"/>
       <c r="AU17" s="8" t="n"/>
       <c r="AV17" s="8" t="n"/>
-      <c r="AW17" s="8" t="n"/>
+      <c r="AW17" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX17" s="8" t="inlineStr">
         <is>
           <t>[OK] material: Reinforced cement concrete — mass 4080.0 kg [direct volume] × 0.149 kgCO2e/kg = 607.92 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
@@ -2725,7 +2785,11 @@
       <c r="AT18" s="8" t="n"/>
       <c r="AU18" s="8" t="n"/>
       <c r="AV18" s="8" t="n"/>
-      <c r="AW18" s="8" t="n"/>
+      <c r="AW18" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX18" s="8" t="inlineStr">
         <is>
           <t>[OK] material: Reinforced cement concrete — mass 240.0 kg [direct volume] × 0.149 kgCO2e/kg = 35.76 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
@@ -2740,14 +2804,14 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>16i</t>
+          <t>16 i</t>
         </is>
       </c>
       <c r="C19" s="8" t="n"/>
       <c r="D19" s="8" t="n"/>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : i) Suspended floors, roofs, landings balconies and chajjas.</t>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Suspended floors, roofs, landings balconies and chajjas.</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -2762,17 +2826,17 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>Formwork</t>
+          <t>Formwork shuttering</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>Formwork</t>
+          <t>Timber/Steel formwork</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>Timber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
@@ -2800,13 +2864,9 @@
       <c r="U19" s="8" t="n"/>
       <c r="V19" s="8" t="n"/>
       <c r="W19" s="8" t="n"/>
-      <c r="X19" s="17" t="n">
-        <v>750</v>
-      </c>
+      <c r="X19" s="8" t="n"/>
       <c r="Y19" s="8" t="n"/>
-      <c r="Z19" s="17" t="n">
-        <v>0.306</v>
-      </c>
+      <c r="Z19" s="8" t="n"/>
       <c r="AA19" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -2820,7 +2880,7 @@
       <c r="AC19" s="8" t="n"/>
       <c r="AD19" s="8" t="inlineStr">
         <is>
-          <t>Timber &gt; Formwork</t>
+          <t>Other &gt; Formwork shuttering</t>
         </is>
       </c>
       <c r="AE19" s="8" t="n"/>
@@ -2841,10 +2901,14 @@
       <c r="AT19" s="8" t="n"/>
       <c r="AU19" s="8" t="n"/>
       <c r="AV19" s="8" t="n"/>
-      <c r="AW19" s="8" t="n"/>
+      <c r="AW19" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX19" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Formwork — category 'Timber' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Formwork shuttering — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -2856,14 +2920,14 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>16ii</t>
+          <t>16 ii</t>
         </is>
       </c>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : ii) Shelves</t>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Shelves</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -2878,17 +2942,17 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Formwork</t>
+          <t>Formwork shuttering</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>Formwork</t>
+          <t>Timber/Steel formwork</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>Timber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K20" s="8" t="inlineStr">
@@ -2916,13 +2980,9 @@
       <c r="U20" s="8" t="n"/>
       <c r="V20" s="8" t="n"/>
       <c r="W20" s="8" t="n"/>
-      <c r="X20" s="17" t="n">
-        <v>750</v>
-      </c>
+      <c r="X20" s="8" t="n"/>
       <c r="Y20" s="8" t="n"/>
-      <c r="Z20" s="17" t="n">
-        <v>0.306</v>
-      </c>
+      <c r="Z20" s="8" t="n"/>
       <c r="AA20" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -2936,7 +2996,7 @@
       <c r="AC20" s="8" t="n"/>
       <c r="AD20" s="8" t="inlineStr">
         <is>
-          <t>Timber &gt; Formwork</t>
+          <t>Other &gt; Formwork shuttering</t>
         </is>
       </c>
       <c r="AE20" s="8" t="n"/>
@@ -2957,10 +3017,14 @@
       <c r="AT20" s="8" t="n"/>
       <c r="AU20" s="8" t="n"/>
       <c r="AV20" s="8" t="n"/>
-      <c r="AW20" s="8" t="n"/>
+      <c r="AW20" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX20" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Formwork — category 'Timber' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Formwork shuttering — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -2972,14 +3036,14 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>16iii</t>
+          <t>16 iii</t>
         </is>
       </c>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : iii) Lintels, beams, plinth beams, girders bressumers and cantilever.</t>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Lintels, beams, plinth beams, girders bressumers and cantilever.</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -2994,17 +3058,17 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Formwork</t>
+          <t>Formwork shuttering</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>Formwork</t>
+          <t>Timber/Steel formwork</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>Timber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
@@ -3032,13 +3096,9 @@
       <c r="U21" s="8" t="n"/>
       <c r="V21" s="8" t="n"/>
       <c r="W21" s="8" t="n"/>
-      <c r="X21" s="17" t="n">
-        <v>750</v>
-      </c>
+      <c r="X21" s="8" t="n"/>
       <c r="Y21" s="8" t="n"/>
-      <c r="Z21" s="17" t="n">
-        <v>0.306</v>
-      </c>
+      <c r="Z21" s="8" t="n"/>
       <c r="AA21" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -3052,7 +3112,7 @@
       <c r="AC21" s="8" t="n"/>
       <c r="AD21" s="8" t="inlineStr">
         <is>
-          <t>Timber &gt; Formwork</t>
+          <t>Other &gt; Formwork shuttering</t>
         </is>
       </c>
       <c r="AE21" s="8" t="n"/>
@@ -3073,10 +3133,14 @@
       <c r="AT21" s="8" t="n"/>
       <c r="AU21" s="8" t="n"/>
       <c r="AV21" s="8" t="n"/>
-      <c r="AW21" s="8" t="n"/>
+      <c r="AW21" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX21" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Formwork — category 'Timber' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Formwork shuttering — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -3088,14 +3152,14 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>16iv</t>
+          <t>16 iv</t>
         </is>
       </c>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : iv) Columns, pillars, posts and struts.</t>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Columns, pillars, posts and struts.</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -3110,17 +3174,17 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Formwork</t>
+          <t>Formwork shuttering</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>Formwork</t>
+          <t>Timber/Steel formwork</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>Timber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
@@ -3148,13 +3212,9 @@
       <c r="U22" s="8" t="n"/>
       <c r="V22" s="8" t="n"/>
       <c r="W22" s="8" t="n"/>
-      <c r="X22" s="17" t="n">
-        <v>750</v>
-      </c>
+      <c r="X22" s="8" t="n"/>
       <c r="Y22" s="8" t="n"/>
-      <c r="Z22" s="17" t="n">
-        <v>0.306</v>
-      </c>
+      <c r="Z22" s="8" t="n"/>
       <c r="AA22" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -3168,7 +3228,7 @@
       <c r="AC22" s="8" t="n"/>
       <c r="AD22" s="8" t="inlineStr">
         <is>
-          <t>Timber &gt; Formwork</t>
+          <t>Other &gt; Formwork shuttering</t>
         </is>
       </c>
       <c r="AE22" s="8" t="n"/>
@@ -3189,10 +3249,14 @@
       <c r="AT22" s="8" t="n"/>
       <c r="AU22" s="8" t="n"/>
       <c r="AV22" s="8" t="n"/>
-      <c r="AW22" s="8" t="n"/>
+      <c r="AW22" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX22" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Formwork — category 'Timber' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Formwork shuttering — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -3204,14 +3268,14 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>16v</t>
+          <t>16 v</t>
         </is>
       </c>
       <c r="C23" s="8" t="n"/>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : v) Vertical and horizontal fins individually or forming box louvers hand and facias.</t>
+          <t>Centring and shuttering including strutting, proping etc. and removal of form work for : Vertical and horizontal fins individually or forming box louvers hand and facias.</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -3226,17 +3290,17 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>Formwork</t>
+          <t>Formwork shuttering</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>Formwork</t>
+          <t>Timber/Steel formwork</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>Timber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
@@ -3264,13 +3328,9 @@
       <c r="U23" s="8" t="n"/>
       <c r="V23" s="8" t="n"/>
       <c r="W23" s="8" t="n"/>
-      <c r="X23" s="17" t="n">
-        <v>750</v>
-      </c>
+      <c r="X23" s="8" t="n"/>
       <c r="Y23" s="8" t="n"/>
-      <c r="Z23" s="17" t="n">
-        <v>0.306</v>
-      </c>
+      <c r="Z23" s="8" t="n"/>
       <c r="AA23" s="8" t="inlineStr">
         <is>
           <t>DSR 1989</t>
@@ -3284,7 +3344,7 @@
       <c r="AC23" s="8" t="n"/>
       <c r="AD23" s="8" t="inlineStr">
         <is>
-          <t>Timber &gt; Formwork</t>
+          <t>Other &gt; Formwork shuttering</t>
         </is>
       </c>
       <c r="AE23" s="8" t="n"/>
@@ -3305,10 +3365,14 @@
       <c r="AT23" s="8" t="n"/>
       <c r="AU23" s="8" t="n"/>
       <c r="AV23" s="8" t="n"/>
-      <c r="AW23" s="8" t="n"/>
+      <c r="AW23" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX23" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Formwork — category 'Timber' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Formwork shuttering — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -3320,14 +3384,14 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>17i</t>
+          <t>17 i</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Reinforcement for RCC work including bending binding and placing in position complete. i) Mild steel and medium tensile steel bars.</t>
+          <t>Reinforcement for RCC work including bending binding and placing in position complete. Mild steel and medium tensile steel bars.</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -3423,7 +3487,11 @@
       <c r="AT24" s="8" t="n"/>
       <c r="AU24" s="8" t="n"/>
       <c r="AV24" s="8" t="n"/>
-      <c r="AW24" s="8" t="n"/>
+      <c r="AW24" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX24" s="8" t="inlineStr">
         <is>
           <t>[OK] material: Mild steel bars — mass 100.0 kg [direct weight] × 1.55 kgCO2e/kg = 155.0 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
@@ -3438,14 +3506,14 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>17ii</t>
+          <t>17 ii</t>
         </is>
       </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="8" t="n"/>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Reinforcement for RCC work including bending binding and placing in position complete. ii) Cold twisted bars</t>
+          <t>Reinforcement for RCC work including bending binding and placing in position complete. Cold twisted bars</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -3460,12 +3528,12 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>Cold twisted bars</t>
+          <t>Cold twisted steel bars</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Cold twisted steel</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
@@ -3520,7 +3588,7 @@
       <c r="AC25" s="8" t="n"/>
       <c r="AD25" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Cold twisted bars</t>
+          <t>Steel &gt; Cold twisted steel bars</t>
         </is>
       </c>
       <c r="AE25" s="8" t="n"/>
@@ -3541,10 +3609,14 @@
       <c r="AT25" s="8" t="n"/>
       <c r="AU25" s="8" t="n"/>
       <c r="AV25" s="8" t="n"/>
-      <c r="AW25" s="8" t="n"/>
+      <c r="AW25" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX25" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Cold twisted bars — mass 1375.0 kg [direct weight] × 1.55 kgCO2e/kg = 2131.25 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[OK] material: Cold twisted steel bars — mass 1375.0 kg [direct weight] × 1.55 kgCO2e/kg = 2131.25 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3739,11 @@
       <c r="AT26" s="8" t="n"/>
       <c r="AU26" s="8" t="n"/>
       <c r="AV26" s="8" t="n"/>
-      <c r="AW26" s="8" t="n"/>
+      <c r="AW26" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX26" s="8" t="inlineStr">
         <is>
           <t>[OK] material: Reinforced cement concrete — mass 1920.0 kg [direct volume] × 0.149 kgCO2e/kg = 286.08 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
@@ -3699,12 +3775,12 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>Bricks</t>
+          <t>Brick masonry</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
@@ -3768,7 +3844,7 @@
       <c r="AC27" s="8" t="n"/>
       <c r="AD27" s="8" t="inlineStr">
         <is>
-          <t>Masonry &gt; Bricks &gt; 1:6</t>
+          <t>Masonry &gt; Brick masonry &gt; 1:6</t>
         </is>
       </c>
       <c r="AE27" s="8" t="n"/>
@@ -3789,10 +3865,14 @@
       <c r="AT27" s="8" t="n"/>
       <c r="AU27" s="8" t="n"/>
       <c r="AV27" s="8" t="n"/>
-      <c r="AW27" s="8" t="n"/>
+      <c r="AW27" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX27" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Bricks — mass 30600.0 kg [direct volume] × 0.213 kgCO2e/kg = 6517.8 kgCO2e — ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
+          <t>[OK] material: Brick masonry — mass 30600.0 kg [direct volume] × 0.213 kgCO2e/kg = 6517.8 kgCO2e — ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3901,12 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>Bricks</t>
+          <t>Brick masonry</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
@@ -3890,7 +3970,7 @@
       <c r="AC28" s="8" t="n"/>
       <c r="AD28" s="8" t="inlineStr">
         <is>
-          <t>Masonry &gt; Bricks &gt; 1:6</t>
+          <t>Masonry &gt; Brick masonry &gt; 1:6</t>
         </is>
       </c>
       <c r="AE28" s="8" t="n"/>
@@ -3911,10 +3991,14 @@
       <c r="AT28" s="8" t="n"/>
       <c r="AU28" s="8" t="n"/>
       <c r="AV28" s="8" t="n"/>
-      <c r="AW28" s="8" t="n"/>
+      <c r="AW28" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX28" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Bricks — mass 72540.0 kg [direct volume] × 0.213 kgCO2e/kg = 15451.02 kgCO2e — ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
+          <t>[OK] material: Brick masonry — mass 72540.0 kg [direct volume] × 0.213 kgCO2e/kg = 15451.02 kgCO2e — ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -3933,7 +4017,7 @@
       <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Brick work 7 cm thick with bricks of class designation ______ in super structure upto floor two level in cement mortar 1:3 (1 cement : 3 coarse sand).</t>
+          <t>Brick work 7 cm thick with bricks of class designation ------ in super structure upto floor two level in cement mortar 1:3 (1 cement : 3 coarse sand).</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
@@ -3943,12 +4027,12 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>Bricks</t>
+          <t>Brick masonry</t>
         </is>
       </c>
       <c r="I29" s="8" t="inlineStr">
@@ -4022,7 +4106,7 @@
       <c r="AC29" s="8" t="n"/>
       <c r="AD29" s="8" t="inlineStr">
         <is>
-          <t>Masonry &gt; Bricks &gt; 1:3</t>
+          <t>Masonry &gt; Brick masonry &gt; 1:3</t>
         </is>
       </c>
       <c r="AE29" s="8" t="n"/>
@@ -4045,10 +4129,14 @@
       <c r="AT29" s="8" t="n"/>
       <c r="AU29" s="8" t="n"/>
       <c r="AV29" s="8" t="n"/>
-      <c r="AW29" s="8" t="n"/>
+      <c r="AW29" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX29" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Bricks — mass 113.4 kg [area × thickness (derived)] × 0.213 kgCO2e/kg = 24.15 kgCO2e — ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
+          <t>[OK] material: Brick masonry — mass 113.4 kg [area × thickness (derived)] × 0.213 kgCO2e/kg = 24.15 kgCO2e — ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4155,7 @@
       <c r="D30" s="8" t="n"/>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Half brick masonry with bricks of class designation ______ in foundation &amp; plinth in cement mortar 1:4 (1 cement : 4 coarse sand)</t>
+          <t>Half brick masonry with bricks of class designation _____ in foundation &amp; plinth in cement mortar 1:4 (1 cement : 4 coarse sand)</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -4077,12 +4165,12 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>Bricks</t>
+          <t>Half brick masonry</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
@@ -4144,7 +4232,7 @@
       <c r="AC30" s="8" t="n"/>
       <c r="AD30" s="8" t="inlineStr">
         <is>
-          <t>Masonry &gt; Bricks &gt; 1:4</t>
+          <t>Masonry &gt; Half brick masonry &gt; 1:4</t>
         </is>
       </c>
       <c r="AE30" s="8" t="n"/>
@@ -4165,10 +4253,14 @@
       <c r="AT30" s="8" t="n"/>
       <c r="AU30" s="8" t="n"/>
       <c r="AV30" s="8" t="n"/>
-      <c r="AW30" s="8" t="n"/>
+      <c r="AW30" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX30" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Bricks — category 'Masonry' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Half brick masonry — category 'Masonry' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4279,7 @@
       <c r="D31" s="8" t="n"/>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Half brick masonry with bricks of class designation ____ in super structure upto floor two level in cement mortar 1:4 (1 cement : 4 coarse sand).</t>
+          <t>Half brick masonry with bricks of class designation ______ in super structure upto floor two level in cement mortar 1:4 (1 cement : 4 coarse sand).</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -4197,12 +4289,12 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>Civil &amp; Sitework</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>Bricks</t>
+          <t>Half brick masonry</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
@@ -4264,7 +4356,7 @@
       <c r="AC31" s="8" t="n"/>
       <c r="AD31" s="8" t="inlineStr">
         <is>
-          <t>Masonry &gt; Bricks &gt; 1:4</t>
+          <t>Masonry &gt; Half brick masonry &gt; 1:4</t>
         </is>
       </c>
       <c r="AE31" s="8" t="n"/>
@@ -4285,10 +4377,14 @@
       <c r="AT31" s="8" t="n"/>
       <c r="AU31" s="8" t="n"/>
       <c r="AV31" s="8" t="n"/>
-      <c r="AW31" s="8" t="n"/>
+      <c r="AW31" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX31" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Bricks — category 'Masonry' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Half brick masonry — category 'Masonry' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4418,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Wood work frame</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
@@ -4378,7 +4474,7 @@
       <c r="AC32" s="8" t="n"/>
       <c r="AD32" s="8" t="inlineStr">
         <is>
-          <t>Timber &gt; Wood</t>
+          <t>Timber &gt; Wood work frame</t>
         </is>
       </c>
       <c r="AE32" s="8" t="n"/>
@@ -4399,10 +4495,14 @@
       <c r="AT32" s="8" t="n"/>
       <c r="AU32" s="8" t="n"/>
       <c r="AV32" s="8" t="n"/>
-      <c r="AW32" s="8" t="n"/>
+      <c r="AW32" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX32" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Wood — mass 26.25 kg [direct volume] × 0.306 kgCO2e/kg = 8.03 kgCO2e — ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
+          <t>[OK] material: Wood work frame — mass 26.25 kg [direct volume] × 0.306 kgCO2e/kg = 8.03 kgCO2e — ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -4436,12 +4536,12 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Wood door shutters</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>Wood, MS</t>
+          <t>Wood, MS butt hinges, Screws</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
@@ -4506,7 +4606,7 @@
       <c r="AC33" s="8" t="n"/>
       <c r="AD33" s="8" t="inlineStr">
         <is>
-          <t>Timber &gt; Wood</t>
+          <t>Timber &gt; Wood door shutters</t>
         </is>
       </c>
       <c r="AE33" s="8" t="n"/>
@@ -4529,10 +4629,14 @@
       <c r="AT33" s="8" t="n"/>
       <c r="AU33" s="8" t="n"/>
       <c r="AV33" s="8" t="n"/>
-      <c r="AW33" s="8" t="n"/>
+      <c r="AW33" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX33" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Wood — mass 472.5 kg [area × thickness (derived)] × 0.306 kgCO2e/kg = 144.59 kgCO2e — ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
+          <t>[OK] material: Wood door shutters — mass 472.5 kg [area × thickness (derived)] × 0.306 kgCO2e/kg = 144.59 kgCO2e — ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -4566,12 +4670,12 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>Teak ply veneer</t>
+          <t>Flush door shutters</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>Hard wood, Teak ply, Commercial ply, MS</t>
+          <t>Block board, Hardwood, Teak ply, Commercial ply, Nickel plated MS piano hinges</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -4628,11 +4732,15 @@
           <t>DSR 1989</t>
         </is>
       </c>
-      <c r="AB34" s="8" t="n"/>
+      <c r="AB34" s="8" t="inlineStr">
+        <is>
+          <t>9.51</t>
+        </is>
+      </c>
       <c r="AC34" s="8" t="n"/>
       <c r="AD34" s="8" t="inlineStr">
         <is>
-          <t>Timber &gt; Teak ply veneer</t>
+          <t>Timber &gt; Flush door shutters</t>
         </is>
       </c>
       <c r="AE34" s="8" t="n"/>
@@ -4655,10 +4763,14 @@
       <c r="AT34" s="8" t="n"/>
       <c r="AU34" s="8" t="n"/>
       <c r="AV34" s="8" t="n"/>
-      <c r="AW34" s="8" t="n"/>
+      <c r="AW34" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX34" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Teak ply veneer — mass 88.12 kg [area × thickness (derived)] × 0.306 kgCO2e/kg = 26.97 kgCO2e — ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
+          <t>[OK] material: Flush door shutters — mass 88.12 kg [area × thickness (derived)] × 0.306 kgCO2e/kg = 26.97 kgCO2e — ICE Database V4.0 (Timber Hardwood) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4804,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>Teak wood</t>
+          <t>Teak wood plugs</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
@@ -4746,15 +4858,11 @@
           <t>DSR 1989</t>
         </is>
       </c>
-      <c r="AB35" s="8" t="inlineStr">
-        <is>
-          <t>9.51</t>
-        </is>
-      </c>
+      <c r="AB35" s="8" t="n"/>
       <c r="AC35" s="8" t="n"/>
       <c r="AD35" s="8" t="inlineStr">
         <is>
-          <t>Timber &gt; Teak wood &gt; 1:3</t>
+          <t>Timber &gt; Teak wood plugs &gt; 1:3</t>
         </is>
       </c>
       <c r="AE35" s="8" t="n"/>
@@ -4776,15 +4884,21 @@
       <c r="AQ35" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="AR35" s="8" t="n"/>
+      <c r="AR35" s="17" t="n">
+        <v>50</v>
+      </c>
       <c r="AS35" s="8" t="n"/>
       <c r="AT35" s="8" t="n"/>
       <c r="AU35" s="8" t="n"/>
       <c r="AV35" s="8" t="n"/>
-      <c r="AW35" s="8" t="n"/>
+      <c r="AW35" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX35" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Teak wood — category 'Timber' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Teak wood plugs — category 'Timber' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4917,7 @@
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing M.S.oxidised fan light vantilator catch with necessary screws etc. complete.</t>
+          <t>Providing and fixing M.S.oxidised fan light ventilator catch with necessary screws etc. complete.</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -4818,12 +4932,12 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>M.S. oxidised ventilator catch</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>M.S., Screws</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
@@ -4868,11 +4982,15 @@
           <t>DSR 1989</t>
         </is>
       </c>
-      <c r="AB36" s="8" t="n"/>
+      <c r="AB36" s="8" t="inlineStr">
+        <is>
+          <t>9.127.3</t>
+        </is>
+      </c>
       <c r="AC36" s="8" t="n"/>
       <c r="AD36" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Mild steel</t>
+          <t>Steel &gt; M.S. oxidised ventilator catch</t>
         </is>
       </c>
       <c r="AE36" s="8" t="n"/>
@@ -4893,10 +5011,14 @@
       <c r="AT36" s="8" t="n"/>
       <c r="AU36" s="8" t="n"/>
       <c r="AV36" s="8" t="n"/>
-      <c r="AW36" s="8" t="n"/>
+      <c r="AW36" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX36" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Mild steel — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: M.S. oxidised ventilator catch — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -4930,12 +5052,12 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>M.S. hasp and staple</t>
         </is>
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>Oxidised M.S., Screws</t>
         </is>
       </c>
       <c r="J37" s="8" t="inlineStr">
@@ -4982,13 +5104,13 @@
       </c>
       <c r="AB37" s="8" t="inlineStr">
         <is>
-          <t>9.127.3</t>
+          <t>9.218.1</t>
         </is>
       </c>
       <c r="AC37" s="8" t="n"/>
       <c r="AD37" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Mild steel</t>
+          <t>Steel &gt; M.S. hasp and staple</t>
         </is>
       </c>
       <c r="AE37" s="8" t="n"/>
@@ -5011,10 +5133,14 @@
       <c r="AT37" s="8" t="n"/>
       <c r="AU37" s="8" t="n"/>
       <c r="AV37" s="8" t="n"/>
-      <c r="AW37" s="8" t="n"/>
+      <c r="AW37" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX37" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Mild steel — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: M.S. hasp and staple — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5174,12 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Aluminium sliding door bolts</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Aluminium, Nuts, Screws</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
@@ -5094,15 +5220,11 @@
           <t>DSR 1989</t>
         </is>
       </c>
-      <c r="AB38" s="8" t="inlineStr">
-        <is>
-          <t>9.218.1</t>
-        </is>
-      </c>
+      <c r="AB38" s="8" t="n"/>
       <c r="AC38" s="8" t="n"/>
       <c r="AD38" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium</t>
+          <t>Other &gt; Aluminium sliding door bolts</t>
         </is>
       </c>
       <c r="AE38" s="8" t="n"/>
@@ -5127,10 +5249,14 @@
       </c>
       <c r="AU38" s="8" t="n"/>
       <c r="AV38" s="8" t="n"/>
-      <c r="AW38" s="8" t="n"/>
+      <c r="AW38" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX38" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aluminium — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Aluminium sliding door bolts — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -5142,14 +5268,14 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>31i</t>
+          <t>31 i</t>
         </is>
       </c>
       <c r="C39" s="8" t="n"/>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. i) 200 x 10 mm</t>
+          <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 200 x 10 mm</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
@@ -5164,12 +5290,12 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Aluminium tower bolts</t>
         </is>
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Aluminium, Screws</t>
         </is>
       </c>
       <c r="J39" s="8" t="inlineStr">
@@ -5218,7 +5344,7 @@
       <c r="AC39" s="8" t="n"/>
       <c r="AD39" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium</t>
+          <t>Other &gt; Aluminium tower bolts</t>
         </is>
       </c>
       <c r="AE39" s="8" t="n"/>
@@ -5243,10 +5369,14 @@
       </c>
       <c r="AU39" s="8" t="n"/>
       <c r="AV39" s="8" t="n"/>
-      <c r="AW39" s="8" t="n"/>
+      <c r="AW39" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX39" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aluminium — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Aluminium tower bolts — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -5258,14 +5388,14 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>31ii</t>
+          <t>31 ii</t>
         </is>
       </c>
       <c r="C40" s="8" t="n"/>
       <c r="D40" s="8" t="n"/>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. ii) 100 x 10 mm</t>
+          <t>Providing and fixing aluminium tower bolts anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 100 x 10 mm</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -5280,12 +5410,12 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Aluminium tower bolts</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Aluminium, Screws</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
@@ -5334,7 +5464,7 @@
       <c r="AC40" s="8" t="n"/>
       <c r="AD40" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium</t>
+          <t>Other &gt; Aluminium tower bolts</t>
         </is>
       </c>
       <c r="AE40" s="8" t="n"/>
@@ -5359,10 +5489,14 @@
       </c>
       <c r="AU40" s="8" t="n"/>
       <c r="AV40" s="8" t="n"/>
-      <c r="AW40" s="8" t="n"/>
+      <c r="AW40" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX40" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aluminium — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Aluminium tower bolts — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -5374,14 +5508,14 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>32i</t>
+          <t>32 i</t>
         </is>
       </c>
       <c r="C41" s="8" t="n"/>
       <c r="D41" s="8" t="n"/>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. i) 100 mm</t>
+          <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 100 mm</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -5396,12 +5530,12 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Aluminium handles</t>
         </is>
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Aluminium, Screws</t>
         </is>
       </c>
       <c r="J41" s="8" t="inlineStr">
@@ -5450,7 +5584,7 @@
       <c r="AC41" s="8" t="n"/>
       <c r="AD41" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium</t>
+          <t>Other &gt; Aluminium handles</t>
         </is>
       </c>
       <c r="AE41" s="8" t="n"/>
@@ -5473,10 +5607,14 @@
       <c r="AT41" s="8" t="n"/>
       <c r="AU41" s="8" t="n"/>
       <c r="AV41" s="8" t="n"/>
-      <c r="AW41" s="8" t="n"/>
+      <c r="AW41" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX41" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aluminium — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Aluminium handles — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -5488,14 +5626,14 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>32ii</t>
+          <t>32 ii</t>
         </is>
       </c>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. ii) 75 mm</t>
+          <t>Providing and fixing aluminium handles anodised transparent or dyed to required colour or shade with necessary screws etc. complete. 75 mm</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -5510,12 +5648,12 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Aluminium handles</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Aluminium, Screws</t>
         </is>
       </c>
       <c r="J42" s="8" t="inlineStr">
@@ -5564,7 +5702,7 @@
       <c r="AC42" s="8" t="n"/>
       <c r="AD42" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium</t>
+          <t>Other &gt; Aluminium handles</t>
         </is>
       </c>
       <c r="AE42" s="8" t="n"/>
@@ -5587,10 +5725,14 @@
       <c r="AT42" s="8" t="n"/>
       <c r="AU42" s="8" t="n"/>
       <c r="AV42" s="8" t="n"/>
-      <c r="AW42" s="8" t="n"/>
+      <c r="AW42" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX42" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aluminium — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Aluminium handles — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5766,12 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Aluminium hanging floor door stopper</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Aluminium, Screws</t>
         </is>
       </c>
       <c r="J43" s="8" t="inlineStr">
@@ -5678,7 +5820,7 @@
       <c r="AC43" s="8" t="n"/>
       <c r="AD43" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium</t>
+          <t>Other &gt; Aluminium hanging floor door stopper</t>
         </is>
       </c>
       <c r="AE43" s="8" t="n"/>
@@ -5699,10 +5841,14 @@
       <c r="AT43" s="8" t="n"/>
       <c r="AU43" s="8" t="n"/>
       <c r="AV43" s="8" t="n"/>
-      <c r="AW43" s="8" t="n"/>
+      <c r="AW43" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX43" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aluminium — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Aluminium hanging floor door stopper — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -5714,14 +5860,14 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>34i</t>
+          <t>34 i</t>
         </is>
       </c>
       <c r="C44" s="8" t="n"/>
       <c r="D44" s="8" t="n"/>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. i) Windows - side hung</t>
+          <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. Windows - side hung</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -5736,12 +5882,12 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Steel glazed windows</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>Steel, Glass, Cement, Coarse sand, Stone aggregate</t>
+          <t>Steel sections, Glass, Cement concrete, Putty, Steel primer</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
@@ -5810,7 +5956,7 @@
       <c r="AC44" s="8" t="n"/>
       <c r="AD44" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Steel &gt; 1:3:6</t>
+          <t>Steel &gt; Steel glazed windows &gt; 1:3:6</t>
         </is>
       </c>
       <c r="AE44" s="8" t="n"/>
@@ -5833,10 +5979,14 @@
       <c r="AT44" s="8" t="n"/>
       <c r="AU44" s="8" t="n"/>
       <c r="AV44" s="8" t="n"/>
-      <c r="AW44" s="8" t="n"/>
+      <c r="AW44" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX44" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Steel — mass 266.12 kg [area × thickness (derived)] × 1.55 kgCO2e/kg = 412.48 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[OK] material: Steel glazed windows — mass 266.12 kg [area × thickness (derived)] × 1.55 kgCO2e/kg = 412.48 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -5848,14 +5998,14 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>34ii</t>
+          <t>34 ii</t>
         </is>
       </c>
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. ii) Ventilators - centre hung</t>
+          <t>Providing and fixing steel glazed doors, windows and ventilators of standard rolled steel sections, joints mitred and welded with 15x3 mm lugs, 10 cm long, with steel lugs, embedded in cement concrete blocks 15x10x10 cm of 1:3:6 (1 cement : 3 coarse sand : 6 graded stone aggregate 20 mm nominal size) or with wooden plugs and screws or rawl plugs and screws or with fixing clips or with bolts and nuts as required, including providing and fixing of (Pin Head) 3mm thick glass panes with glazing clips and special metal sash putty of approved make complete including applying a priming coat of approved steel primer; excluding the cost of metal beading and other fitting except necessary hinges or pivots as required. Ventilators - centre hung</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -5870,12 +6020,12 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Steel glazed ventilators</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>Steel, Glass, Cement, Coarse sand, Stone aggregate</t>
+          <t>Steel sections, Glass, Cement concrete, Putty, Steel primer</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr">
@@ -5944,7 +6094,7 @@
       <c r="AC45" s="8" t="n"/>
       <c r="AD45" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Steel &gt; 1:3:6</t>
+          <t>Steel &gt; Steel glazed ventilators &gt; 1:3:6</t>
         </is>
       </c>
       <c r="AE45" s="8" t="n"/>
@@ -5967,10 +6117,14 @@
       <c r="AT45" s="8" t="n"/>
       <c r="AU45" s="8" t="n"/>
       <c r="AV45" s="8" t="n"/>
-      <c r="AW45" s="8" t="n"/>
+      <c r="AW45" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX45" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Steel — mass 23.55 kg [area × thickness (derived)] × 1.55 kgCO2e/kg = 36.5 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[OK] material: Steel glazed ventilators — mass 23.55 kg [area × thickness (derived)] × 1.55 kgCO2e/kg = 36.5 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -6004,12 +6158,12 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>Mild steel casement window fasteners</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>Oxidised mild steel, Machine screws</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
@@ -6062,7 +6216,7 @@
       <c r="AC46" s="8" t="n"/>
       <c r="AD46" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Mild steel</t>
+          <t>Steel &gt; Mild steel casement window fasteners</t>
         </is>
       </c>
       <c r="AE46" s="8" t="n"/>
@@ -6083,10 +6237,14 @@
       <c r="AT46" s="8" t="n"/>
       <c r="AU46" s="8" t="n"/>
       <c r="AV46" s="8" t="n"/>
-      <c r="AW46" s="8" t="n"/>
+      <c r="AW46" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX46" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Mild steel — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Mild steel casement window fasteners — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -6105,7 +6263,7 @@
       <c r="D47" s="8" t="n"/>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing aluminium casement stays anodised transparent or dyed to requird colour and shade with with necessary welding and machine screws etc. complete.</t>
+          <t>Providing and fixing aluminium casement stays anodised transparent or dyed to required colour and shade with with necessary welding and machine screws etc. complete.</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
@@ -6120,12 +6278,12 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Aluminium casement stays</t>
         </is>
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Aluminium, Screws</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
@@ -6174,7 +6332,7 @@
       <c r="AC47" s="8" t="n"/>
       <c r="AD47" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Aluminium</t>
+          <t>Other &gt; Aluminium casement stays</t>
         </is>
       </c>
       <c r="AE47" s="8" t="n"/>
@@ -6195,10 +6353,14 @@
       <c r="AT47" s="8" t="n"/>
       <c r="AU47" s="8" t="n"/>
       <c r="AV47" s="8" t="n"/>
-      <c r="AW47" s="8" t="n"/>
+      <c r="AW47" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX47" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Aluminium — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: Aluminium casement stays — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -6232,12 +6394,12 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>MS Guard Flats</t>
         </is>
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>Mild steel, Steel primer</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
@@ -6292,7 +6454,7 @@
       <c r="AC48" s="8" t="n"/>
       <c r="AD48" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Mild steel</t>
+          <t>Steel &gt; MS Guard Flats</t>
         </is>
       </c>
       <c r="AE48" s="8" t="n"/>
@@ -6317,10 +6479,14 @@
       <c r="AT48" s="8" t="n"/>
       <c r="AU48" s="8" t="n"/>
       <c r="AV48" s="8" t="n"/>
-      <c r="AW48" s="8" t="n"/>
+      <c r="AW48" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX48" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Mild steel — mass 66.0 kg [direct weight] × 1.55 kgCO2e/kg = 102.3 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[OK] material: MS Guard Flats — mass 66.0 kg [direct weight] × 1.55 kgCO2e/kg = 102.3 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -6354,12 +6520,12 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>T-Iron frames</t>
         </is>
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>Mild steel, Cement, Coarse sand, Stone aggregate</t>
+          <t>Mild steel Tee sections, Cement concrete, Steel primer</t>
         </is>
       </c>
       <c r="J49" s="8" t="inlineStr">
@@ -6418,7 +6584,7 @@
       <c r="AC49" s="8" t="n"/>
       <c r="AD49" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Mild steel &gt; 1:3:6</t>
+          <t>Steel &gt; T-Iron frames &gt; 1:3:6</t>
         </is>
       </c>
       <c r="AE49" s="8" t="n"/>
@@ -6439,10 +6605,14 @@
       <c r="AT49" s="8" t="n"/>
       <c r="AU49" s="8" t="n"/>
       <c r="AV49" s="8" t="n"/>
-      <c r="AW49" s="8" t="n"/>
+      <c r="AW49" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX49" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Mild steel — mass 187.0 kg [direct weight] × 1.55 kgCO2e/kg = 289.85 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
+          <t>[OK] material: T-Iron frames — mass 187.0 kg [direct weight] × 1.55 kgCO2e/kg = 289.85 kgCO2e — ICE Database V4.0 (Steel Open Sections) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -6471,17 +6641,17 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Structural</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>Mild steel bar</t>
+          <t>MS fan clamp</t>
         </is>
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>Mild steel</t>
+          <t>Mild steel bar, Paint</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
@@ -6534,7 +6704,7 @@
       <c r="AC50" s="8" t="n"/>
       <c r="AD50" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Mild steel bar</t>
+          <t>Steel &gt; MS fan clamp</t>
         </is>
       </c>
       <c r="AE50" s="8" t="n"/>
@@ -6557,10 +6727,14 @@
       </c>
       <c r="AU50" s="8" t="n"/>
       <c r="AV50" s="8" t="n"/>
-      <c r="AW50" s="8" t="n"/>
+      <c r="AW50" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX50" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Mild steel bar — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: MS fan clamp — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6768,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>Cement concrete</t>
+          <t>Cement concrete flooring</t>
         </is>
       </c>
       <c r="I51" s="8" t="inlineStr">
@@ -6672,7 +6846,7 @@
       <c r="AC51" s="8" t="n"/>
       <c r="AD51" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Cement concrete &gt; M15</t>
+          <t>Concrete &gt; Cement concrete flooring &gt; M15</t>
         </is>
       </c>
       <c r="AE51" s="8" t="n"/>
@@ -6695,10 +6869,14 @@
       <c r="AT51" s="8" t="n"/>
       <c r="AU51" s="8" t="n"/>
       <c r="AV51" s="8" t="n"/>
-      <c r="AW51" s="8" t="n"/>
+      <c r="AW51" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX51" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Cement concrete — mass 6528.0 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 972.67 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
+          <t>[OK] material: Cement concrete flooring — mass 6528.0 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 972.67 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6895,7 @@
       <c r="D52" s="8" t="n"/>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>18 mm thick cement plastesr skirting (upto 30 cm height) with cement mortar 1:3 (1 cement : 3 coarse sand) finished with a floating coat of neat cement including rounding of junctions with floors.</t>
+          <t>18 mm thick cement plaster skirting (upto 30 cm height) with cement mortar 1:3 (1 cement : 3 coarse sand) finished with a floating coat of neat cement including rounding of junctions with floors.</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
@@ -6732,7 +6910,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>Cement plaster</t>
+          <t>Cement plaster skirting</t>
         </is>
       </c>
       <c r="I52" s="8" t="inlineStr">
@@ -6806,7 +6984,7 @@
       <c r="AC52" s="8" t="n"/>
       <c r="AD52" s="8" t="inlineStr">
         <is>
-          <t>Plaster &gt; Cement plaster &gt; 1:3</t>
+          <t>Plaster &gt; Cement plaster skirting &gt; 1:3</t>
         </is>
       </c>
       <c r="AE52" s="8" t="n"/>
@@ -6831,10 +7009,14 @@
       <c r="AT52" s="8" t="n"/>
       <c r="AU52" s="8" t="n"/>
       <c r="AV52" s="8" t="n"/>
-      <c r="AW52" s="8" t="n"/>
+      <c r="AW52" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX52" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Cement plaster — mass 376.2 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 61.32 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
+          <t>[OK] material: Cement plaster skirting — mass 376.2 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 61.32 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -6873,7 +7055,7 @@
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>Cement, Coarse sand, Stone aggregate, Marble chips, Marble powder</t>
+          <t>Marble chips, Cement, Coarse sand, Stone aggregate, Marble powder, Pigment</t>
         </is>
       </c>
       <c r="J53" s="8" t="inlineStr">
@@ -6969,7 +7151,11 @@
       <c r="AT53" s="8" t="n"/>
       <c r="AU53" s="8" t="n"/>
       <c r="AV53" s="8" t="n"/>
-      <c r="AW53" s="8" t="n"/>
+      <c r="AW53" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX53" s="8" t="inlineStr">
         <is>
           <t>[OK] material: Marble chips flooring — mass 864.0 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 128.74 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M15 inferred from nominal mix 1:2:4 (IS 456)</t>
@@ -7085,7 +7271,11 @@
       <c r="AT54" s="8" t="n"/>
       <c r="AU54" s="8" t="n"/>
       <c r="AV54" s="8" t="n"/>
-      <c r="AW54" s="8" t="n"/>
+      <c r="AW54" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX54" s="8" t="inlineStr">
         <is>
           <t>[EXCLUDED] material: Glass strips — category 'Other' not in current EPD database; carbon not estimated</t>
@@ -7107,7 +7297,7 @@
       <c r="D55" s="8" t="n"/>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>Painting top of roofs with bitumen of approved quality at 17 Kg. per 10 square metre impregnated with a coat of coarse sand at 3/2 60 dm per 10 m including cleaning the slab surface with brushes and finally with a piece of cloth lightly soaked in kerosene oil complete with residual type petroleum bitumen of penetration 80/100.</t>
+          <t>Painting top of roofs with bitumen of approved quality at 17 Kg. per 10 square metre impregnated with a coat of coarse sand at 3/60 dm^2 per 10 m^2 including cleaning the slab surface with brushes and finally with a piece of cloth lightly soaked in kerosene oil complete with residual type petroleum bitumen of penetration 80/100.</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -7122,7 +7312,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>Bitumen</t>
+          <t>Bitumen painting</t>
         </is>
       </c>
       <c r="I55" s="8" t="inlineStr">
@@ -7180,7 +7370,7 @@
       <c r="AC55" s="8" t="n"/>
       <c r="AD55" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish &gt; Bitumen</t>
+          <t>Paint/Finish &gt; Bitumen painting</t>
         </is>
       </c>
       <c r="AE55" s="8" t="n"/>
@@ -7201,10 +7391,14 @@
       <c r="AT55" s="8" t="n"/>
       <c r="AU55" s="8" t="n"/>
       <c r="AV55" s="8" t="n"/>
-      <c r="AW55" s="8" t="n"/>
+      <c r="AW55" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX55" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Bitumen — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Bitumen painting — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7432,12 @@
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>Lime concrete</t>
+          <t>Lime concrete terracing</t>
         </is>
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>Lime putty, Surkhi, Brick aggregate, Brick tiles, Cement, Fine sand</t>
+          <t>Brick aggregate, Lime putty, Surkhi, Gur, Belgiri, Brick tiles, Cement, Fine sand, Crude oil</t>
         </is>
       </c>
       <c r="J56" s="8" t="inlineStr">
@@ -7312,7 +7506,7 @@
       <c r="AC56" s="8" t="n"/>
       <c r="AD56" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Lime concrete &gt; 1:2</t>
+          <t>Concrete &gt; Lime concrete terracing &gt; 1:2</t>
         </is>
       </c>
       <c r="AE56" s="8" t="n"/>
@@ -7335,10 +7529,14 @@
       <c r="AT56" s="8" t="n"/>
       <c r="AU56" s="8" t="n"/>
       <c r="AV56" s="8" t="n"/>
-      <c r="AW56" s="8" t="n"/>
+      <c r="AW56" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX56" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Lime concrete — mass 15600.0 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 2324.4 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
+          <t>[OK] material: Lime concrete terracing — mass 15600.0 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 2324.4 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -7367,7 +7565,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>Finishes</t>
+          <t>Civil &amp; Sitework</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -7473,7 +7671,11 @@
       <c r="AT57" s="8" t="n"/>
       <c r="AU57" s="8" t="n"/>
       <c r="AV57" s="8" t="n"/>
-      <c r="AW57" s="8" t="n"/>
+      <c r="AW57" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX57" s="8" t="inlineStr">
         <is>
           <t>[OK] material: Burnt clay tiles — mass 1440.0 kg [area × thickness (derived)] × 0.213 kgCO2e/kg = 306.72 kgCO2e — ICE Database V4.0 (Brick Clay) via NZBG Guide V1.0</t>
@@ -7510,7 +7712,7 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>Cement concrete</t>
+          <t>Cement concrete gola</t>
         </is>
       </c>
       <c r="I58" s="8" t="inlineStr">
@@ -7576,7 +7778,7 @@
       <c r="AC58" s="8" t="n"/>
       <c r="AD58" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Cement concrete &gt; M10</t>
+          <t>Concrete &gt; Cement concrete gola &gt; M10</t>
         </is>
       </c>
       <c r="AE58" s="8" t="n"/>
@@ -7601,10 +7803,14 @@
       <c r="AT58" s="8" t="n"/>
       <c r="AU58" s="8" t="n"/>
       <c r="AV58" s="8" t="n"/>
-      <c r="AW58" s="8" t="n"/>
+      <c r="AW58" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX58" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Cement concrete — category 'Concrete' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Cement concrete gola — category 'Concrete' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7844,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>Cement concrete</t>
+          <t>Cement concrete khurras</t>
         </is>
       </c>
       <c r="I59" s="8" t="inlineStr">
@@ -7704,7 +7910,7 @@
       <c r="AC59" s="8" t="n"/>
       <c r="AD59" s="8" t="inlineStr">
         <is>
-          <t>Concrete &gt; Cement concrete &gt; M15</t>
+          <t>Concrete &gt; Cement concrete khurras &gt; M15</t>
         </is>
       </c>
       <c r="AE59" s="8" t="n"/>
@@ -7731,10 +7937,14 @@
       <c r="AT59" s="8" t="n"/>
       <c r="AU59" s="8" t="n"/>
       <c r="AV59" s="8" t="n"/>
-      <c r="AW59" s="8" t="n"/>
+      <c r="AW59" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX59" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Cement concrete — category 'Concrete' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Cement concrete khurras — category 'Concrete' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -7768,12 +7978,12 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>Cast iron pipe</t>
+          <t>CI rain water pipe</t>
         </is>
       </c>
       <c r="I60" s="8" t="inlineStr">
         <is>
-          <t>Cast iron, Cement, Fine sand, Spun yarn</t>
+          <t>Cast Iron, Spun yarn, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J60" s="8" t="inlineStr">
@@ -7826,7 +8036,7 @@
       <c r="AC60" s="8" t="n"/>
       <c r="AD60" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Cast iron pipe &gt; 1:2</t>
+          <t>Other &gt; CI rain water pipe &gt; 1:2</t>
         </is>
       </c>
       <c r="AE60" s="8" t="n"/>
@@ -7849,10 +8059,14 @@
       </c>
       <c r="AU60" s="8" t="n"/>
       <c r="AV60" s="8" t="n"/>
-      <c r="AW60" s="8" t="n"/>
+      <c r="AW60" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX60" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Cast iron pipe — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: CI rain water pipe — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -7886,7 +8100,7 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>Mild steel holderbat clamp</t>
+          <t>MS holderbat clamps</t>
         </is>
       </c>
       <c r="I61" s="8" t="inlineStr">
@@ -7948,7 +8162,7 @@
       <c r="AC61" s="8" t="n"/>
       <c r="AD61" s="8" t="inlineStr">
         <is>
-          <t>Steel &gt; Mild steel holderbat clamp &gt; 1:2:4</t>
+          <t>Steel &gt; MS holderbat clamps &gt; 1:2:4</t>
         </is>
       </c>
       <c r="AE61" s="8" t="n"/>
@@ -7961,9 +8175,15 @@
       <c r="AL61" s="8" t="n"/>
       <c r="AM61" s="8" t="n"/>
       <c r="AN61" s="8" t="n"/>
-      <c r="AO61" s="8" t="n"/>
-      <c r="AP61" s="8" t="n"/>
-      <c r="AQ61" s="8" t="n"/>
+      <c r="AO61" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP61" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AQ61" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="AR61" s="8" t="n"/>
       <c r="AS61" s="8" t="n"/>
       <c r="AT61" s="17" t="n">
@@ -7971,10 +8191,14 @@
       </c>
       <c r="AU61" s="8" t="n"/>
       <c r="AV61" s="8" t="n"/>
-      <c r="AW61" s="8" t="n"/>
+      <c r="AW61" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX61" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Mild steel holderbat clamp — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: MS holderbat clamps — category 'Steel' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -7986,14 +8210,14 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>51i</t>
+          <t>51 i</t>
         </is>
       </c>
       <c r="C62" s="8" t="n"/>
       <c r="D62" s="8" t="n"/>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) i) CI plain head 100 mm dia</t>
+          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) CI plain head 100 mm dia</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
@@ -8008,12 +8232,12 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>Cast iron</t>
+          <t>CI plain head</t>
         </is>
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>Cast iron, Cement, Fine sand</t>
+          <t>Cast iron, Spun yarn, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J62" s="8" t="inlineStr">
@@ -8066,7 +8290,7 @@
       <c r="AC62" s="8" t="n"/>
       <c r="AD62" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Cast iron &gt; 1:2</t>
+          <t>Other &gt; CI plain head &gt; 1:2</t>
         </is>
       </c>
       <c r="AE62" s="8" t="n"/>
@@ -8089,10 +8313,14 @@
       </c>
       <c r="AU62" s="8" t="n"/>
       <c r="AV62" s="8" t="n"/>
-      <c r="AW62" s="8" t="n"/>
+      <c r="AW62" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX62" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Cast iron — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: CI plain head — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -8104,14 +8332,14 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>51ii</t>
+          <t>51 ii</t>
         </is>
       </c>
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) ii) CI plain shoe - 100 mm dia</t>
+          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) CI plain shoe - 100 mm dia</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
@@ -8126,12 +8354,12 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>Cast iron</t>
+          <t>CI plain shoe</t>
         </is>
       </c>
       <c r="I63" s="8" t="inlineStr">
         <is>
-          <t>Cast iron, Cement, Fine sand</t>
+          <t>Cast iron, Spun yarn, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J63" s="8" t="inlineStr">
@@ -8184,7 +8412,7 @@
       <c r="AC63" s="8" t="n"/>
       <c r="AD63" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Cast iron &gt; 1:2</t>
+          <t>Other &gt; CI plain shoe &gt; 1:2</t>
         </is>
       </c>
       <c r="AE63" s="8" t="n"/>
@@ -8207,10 +8435,14 @@
       </c>
       <c r="AU63" s="8" t="n"/>
       <c r="AV63" s="8" t="n"/>
-      <c r="AW63" s="8" t="n"/>
+      <c r="AW63" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX63" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Cast iron — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: CI plain shoe — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -8222,14 +8454,14 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>51iii</t>
+          <t>51 iii</t>
         </is>
       </c>
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) iii) CI plain bend - 100 mm dia</t>
+          <t>Providing and fixing on wall face CI accessories for rain water pipes including filling the joints with spun yarn soaked in neat cement slurry and cement mortar 1:2 (1 cement : 2 fine sand) CI plain bend - 100 mm dia</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
@@ -8244,12 +8476,12 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>Cast iron</t>
+          <t>CI plain bend</t>
         </is>
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>Cast iron, Cement, Fine sand</t>
+          <t>Cast iron, Spun yarn, Cement, Fine sand</t>
         </is>
       </c>
       <c r="J64" s="8" t="inlineStr">
@@ -8302,7 +8534,7 @@
       <c r="AC64" s="8" t="n"/>
       <c r="AD64" s="8" t="inlineStr">
         <is>
-          <t>Other &gt; Cast iron &gt; 1:2</t>
+          <t>Other &gt; CI plain bend &gt; 1:2</t>
         </is>
       </c>
       <c r="AE64" s="8" t="n"/>
@@ -8325,10 +8557,14 @@
       </c>
       <c r="AU64" s="8" t="n"/>
       <c r="AV64" s="8" t="n"/>
-      <c r="AW64" s="8" t="n"/>
+      <c r="AW64" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX64" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Cast iron — category 'Other' not in current EPD database; carbon not estimated</t>
+          <t>[EXCLUDED] material: CI plain bend — category 'Other' not in current EPD database; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8695,11 @@
       <c r="AT65" s="8" t="n"/>
       <c r="AU65" s="8" t="n"/>
       <c r="AV65" s="8" t="n"/>
-      <c r="AW65" s="8" t="n"/>
+      <c r="AW65" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX65" s="8" t="inlineStr">
         <is>
           <t>[OK] material: Cement plaster — mass 5016.0 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 817.61 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
@@ -8593,7 +8833,11 @@
       <c r="AT66" s="8" t="n"/>
       <c r="AU66" s="8" t="n"/>
       <c r="AV66" s="8" t="n"/>
-      <c r="AW66" s="8" t="n"/>
+      <c r="AW66" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX66" s="8" t="inlineStr">
         <is>
           <t>[OK] material: Cement plaster — mass 6270.0 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 1022.01 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
@@ -8635,7 +8879,7 @@
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>Cement, Fine sand, Lime</t>
+          <t>Cement, Fine sand, Lime wash</t>
         </is>
       </c>
       <c r="J67" s="8" t="inlineStr">
@@ -8727,7 +8971,11 @@
       <c r="AT67" s="8" t="n"/>
       <c r="AU67" s="8" t="n"/>
       <c r="AV67" s="8" t="n"/>
-      <c r="AW67" s="8" t="n"/>
+      <c r="AW67" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX67" s="8" t="inlineStr">
         <is>
           <t>[OK] material: Cement plaster — mass 216.6 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 35.31 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
@@ -8764,7 +9012,7 @@
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>Terrazzo plaster</t>
+          <t>Terrazzo plaster dado</t>
         </is>
       </c>
       <c r="I68" s="8" t="inlineStr">
@@ -8838,7 +9086,7 @@
       <c r="AC68" s="8" t="n"/>
       <c r="AD68" s="8" t="inlineStr">
         <is>
-          <t>Plaster &gt; Terrazzo plaster &gt; 1:3</t>
+          <t>Plaster &gt; Terrazzo plaster dado &gt; 1:3</t>
         </is>
       </c>
       <c r="AE68" s="8" t="n"/>
@@ -8861,10 +9109,14 @@
       <c r="AT68" s="8" t="n"/>
       <c r="AU68" s="8" t="n"/>
       <c r="AV68" s="8" t="n"/>
-      <c r="AW68" s="8" t="n"/>
+      <c r="AW68" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX68" s="8" t="inlineStr">
         <is>
-          <t>[OK] material: Terrazzo plaster — mass 684.0 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 111.49 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
+          <t>[OK] material: Terrazzo plaster dado — mass 684.0 kg [area × thickness (derived)] × 0.163 kgCO2e/kg = 111.49 kgCO2e — ICE Database V4.0 (Cement Mortar 1:3, general) via NZBG Guide V1.0</t>
         </is>
       </c>
     </row>
@@ -8898,7 +9150,7 @@
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>Cement mortar plaster</t>
+          <t>Cement plaster</t>
         </is>
       </c>
       <c r="I69" s="8" t="inlineStr">
@@ -8960,7 +9212,7 @@
       <c r="AC69" s="8" t="n"/>
       <c r="AD69" s="8" t="inlineStr">
         <is>
-          <t>Plaster &gt; Cement mortar plaster &gt; 1:3</t>
+          <t>Plaster &gt; Cement plaster &gt; 1:3</t>
         </is>
       </c>
       <c r="AE69" s="8" t="n"/>
@@ -8981,10 +9233,14 @@
       <c r="AT69" s="8" t="n"/>
       <c r="AU69" s="8" t="n"/>
       <c r="AV69" s="8" t="n"/>
-      <c r="AW69" s="8" t="n"/>
+      <c r="AW69" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX69" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Cement mortar plaster — category 'Plaster' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Cement plaster — category 'Plaster' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9274,7 @@
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>Lime wash</t>
+          <t>White wash</t>
         </is>
       </c>
       <c r="I70" s="8" t="inlineStr">
@@ -9076,7 +9332,7 @@
       <c r="AC70" s="8" t="n"/>
       <c r="AD70" s="8" t="inlineStr">
         <is>
-          <t>Paint/Finish &gt; Lime wash</t>
+          <t>Paint/Finish &gt; White wash</t>
         </is>
       </c>
       <c r="AE70" s="8" t="n"/>
@@ -9097,10 +9353,14 @@
       <c r="AT70" s="8" t="n"/>
       <c r="AU70" s="8" t="n"/>
       <c r="AV70" s="8" t="n"/>
-      <c r="AW70" s="8" t="n"/>
+      <c r="AW70" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX70" s="8" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Lime wash — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: White wash — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -9139,7 +9399,7 @@
       </c>
       <c r="I71" s="8" t="inlineStr">
         <is>
-          <t>Lime</t>
+          <t>Lime, Colour wash pigment</t>
         </is>
       </c>
       <c r="J71" s="8" t="inlineStr">
@@ -9213,7 +9473,11 @@
       <c r="AT71" s="8" t="n"/>
       <c r="AU71" s="8" t="n"/>
       <c r="AV71" s="8" t="n"/>
-      <c r="AW71" s="8" t="n"/>
+      <c r="AW71" s="8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX71" s="8" t="inlineStr">
         <is>
           <t>[EXCLUDED] material: Colour wash — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
@@ -9248,12 +9512,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Primer</t>
+          <t>Wood primer</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Primer</t>
+          <t>Pink/gray primer</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9295,12 +9559,17 @@
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>Paint/Finish &gt; Primer</t>
+          <t>Paint/Finish &gt; Wood primer</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>INR</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Primer — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Wood primer — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -9332,12 +9601,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Zinc chromate primer</t>
+          <t>Zinc chromate yellow primer</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Zinc chromate primer</t>
+          <t>Zinc chromate yellow primer</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9379,12 +9648,17 @@
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>Paint/Finish &gt; Zinc chromate primer</t>
+          <t>Paint/Finish &gt; Zinc chromate yellow primer</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>INR</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>[EXCLUDED] material: Zinc chromate primer — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
+          <t>[EXCLUDED] material: Zinc chromate yellow primer — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9695,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Bitumastic paint, Zinc chromate primer</t>
+          <t>Bitumastic paint, Zinc chromate yellow primer</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9469,6 +9743,11 @@
       <c r="AT74" s="18" t="n">
         <v>100</v>
       </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX74" t="inlineStr">
         <is>
           <t>[EXCLUDED] material: Bitumastic paint — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
@@ -9553,6 +9832,11 @@
           <t>Paint/Finish &gt; Synthetic enamel paint</t>
         </is>
       </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX75" t="inlineStr">
         <is>
           <t>[EXCLUDED] material: Synthetic enamel paint — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
@@ -9592,7 +9876,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>French spirit polish, Wood filler</t>
+          <t>French spirit, Wood filler</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9637,6 +9921,11 @@
           <t>Paint/Finish &gt; French spirit polish</t>
         </is>
       </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX76" t="inlineStr">
         <is>
           <t>[EXCLUDED] material: French spirit polish — category 'Paint/Finish' has an EPD factor but no usable weight/volume figure was available to compute mass; carbon not estimated</t>
@@ -9671,7 +9960,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Cement concrete</t>
+          <t>Cement concrete plinth protection</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -9744,15 +10033,20 @@
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>Concrete &gt; Cement concrete &gt; M10</t>
+          <t>Concrete &gt; Cement concrete plinth protection &gt; M10</t>
         </is>
       </c>
       <c r="AR77" s="18" t="n">
         <v>50</v>
       </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>[OK] material: Cement concrete — mass 4152.0 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 618.65 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M10 inferred from nominal mix 1:3:6 (IS 456)</t>
+          <t>[OK] material: Cement concrete plinth protection — mass 4152.0 kg [area × thickness (derived)] × 0.149 kgCO2e/kg = 618.65 kgCO2e — ICE Database V4.1 (Concrete C35/45) via NZBG Guide V1.0; Grade M10 inferred from nominal mix 1:3:6 (IS 456)</t>
         </is>
       </c>
     </row>

--- a/output/passport_filled.xlsx
+++ b/output/passport_filled.xlsx
@@ -1164,7 +1164,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - I, Earth Work</t>
+          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - I, Earth Work</t>
+          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - II, Cement Concrete Work</t>
+          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - II, Cement Concrete Work</t>
+          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - II, Cement Concrete Work</t>
+          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - II, Cement Concrete Work</t>
+          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - III, R.C.C. Work</t>
+          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - III, R.C.C. Work</t>
+          <t>Schedule 'A'</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - III, R.C.C. Work</t>
+          <t>Schedule 'A'</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - III, R.C.C. Work</t>
+          <t>Schedule 'A'</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - III, R.C.C. Work</t>
+          <t>Schedule 'A'</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - V, Wood Work</t>
+          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
+          <t>Sub-Head - V, Wood Work</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
+          <t>Sub-Head - V, Wood Work</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
+          <t>Sub-Head - V, Wood Work</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
+          <t>Sub-Head - III, R.C.C. Work</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
+          <t>Sub-Head - X, White/Colour Washing &amp; Painting</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
+          <t>Sub-Head - IV, Brick Work</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
+          <t>Sub-Head - II, Cement Concrete Work</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
+          <t>Sub-Head - IX, Plastering</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - VIII, Sanitary Installation (Rain Water Pipes)</t>
+          <t>Sub-Head - VI, Steel &amp; Aluminium Fittings</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - IX, Plastering</t>
+          <t>Sub-Head - III, R.C.C. Work</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - IX, Plastering</t>
+          <t>Sub-Head - VII, Flooring &amp; Roof Treatment</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>Sub-Head - IX, Plastering</t>
+          <t>Sub-Head - III, R.C.C. Work</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sub-Head - X, White/Colour Washing &amp; Painting</t>
+          <t>Sub-Head - V, Wood Work</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sub-Head - XI, Sundry Items / Site Development</t>
+          <t>Sub-Head - II, Cement Concrete Work</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
